--- a/sheet/AI직업데이터.xlsx
+++ b/sheet/AI직업데이터.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>동아시아 역사 기행, 세계사, 한문, 지구과학, 한국지리 탐구</t>
+          <t>동아시아 역사 기행, 세계사, 한문, 지구과학, 한국지리 탐구, 독서와 작문, 영어 I</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -524,7 +524,9 @@
 세계사: 여러 문명의 유물을 비교해야 해서 → 세계 여러 문명의 흐름을 배워요.
 한문: 옛 기록과 비문을 읽어야 해서 → 한자와 한문 문장 읽는 법을 배워요.
 지구과학: 유적이 묻힌 지층을 해석해야 해서 → 지층·암석과 지구의 변화를 배워요.
-한국지리 탐구: 유적이 있는 지형과 입지를 살펴야 해서 → 우리 국토의 지형과 지역 특성을 배워요.</t>
+한국지리 탐구: 유적이 있는 지형과 입지를 살펴야 해서 → 우리 국토의 지형과 지역 특성을 배워요.
+독서와 작문: 발굴 결과를 보고서와 논문으로 남겨야 해서 → 자료를 읽고 논리적으로 글 쓰는 법을 배워요.
+영어 I: 해외 고고학 연구 자료를 참고해야 해서 → 기본 영어 독해 실력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -546,7 +548,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>언어생활 탐구, 독서 토론과 글쓰기, 주제 탐구 독서, 언어생활과 한자, 논리와 사고</t>
+          <t>언어생활 탐구, 독서 토론과 글쓰기, 주제 탐구 독서, 언어생활과 한자, 논리와 사고, 화법과 언어, 독서와 작문</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -560,7 +562,9 @@
 독서 토론과 글쓰기: 문장을 매끄럽게 고쳐야 해서 → 글을 분석하고 고쳐 쓰는 법을 배워요.
 주제 탐구 독서: 다양한 분야의 원고를 다루므로 → 여러 분야의 글을 깊이 읽는 법을 배워요.
 언어생활과 한자: 한자어를 바르게 써야 해서 → 한자어의 뜻과 쓰임을 배워요.
-논리와 사고: 글의 논리적 오류를 찾아야 해서 → 논증 구조와 오류 판별법을 배워요.</t>
+논리와 사고: 글의 논리적 오류를 찾아야 해서 → 논증 구조와 오류 판별법을 배워요.
+화법과 언어: 맞춤법과 문법 오류를 정확히 짚어야 해서 → 국어의 음운·문법 규칙을 체계적으로 배워요.
+독서와 작문: 글의 흐름과 논리를 다듬어야 해서 → 글의 구조를 분석하고 고쳐 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -582,7 +586,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>문학과 영상, 독서 토론과 글쓰기, 인간과 심리, 주제 탐구 독서, 영미 문학 읽기</t>
+          <t>문학과 영상, 독서 토론과 글쓰기, 인간과 심리, 주제 탐구 독서, 영미 문학 읽기, 문학, 화법과 언어, 독서와 작문</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -596,7 +600,10 @@
 독서 토론과 글쓰기: 꾸준히 대본을 써야 하는 일이라 → 생각을 글로 표현하는 법을 연습해요.
 인간과 심리: 인물의 감정과 갈등을 그려야 해서 → 인간의 마음과 행동 원리를 배워요.
 주제 탐구 독서: 작품 소재를 깊이 조사해야 해서 → 주제를 정해 깊이 읽고 탐구해요.
-영미 문학 읽기: 셰익스피어 등 고전 희곡을 참고하므로 → 영미 문학 작품을 읽고 감상해요.</t>
+영미 문학 읽기: 셰익스피어 등 고전 희곡을 참고하므로 → 영미 문학 작품을 읽고 감상해요.
+문학: 인물과 갈등이 살아 있는 이야기를 써야 해서 → 소설·희곡의 구성과 표현 방식을 배워요.
+화법과 언어: 인물마다 실감 나는 대사를 만들어야 해서 → 상황에 맞는 말하기와 언어 표현을 배워요.
+독서와 작문: 대본을 여러 번 고쳐 완성해야 해서 → 글을 계획하고 고쳐 쓰는 과정을 배워요.</t>
         </is>
       </c>
     </row>
@@ -618,7 +625,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>정보, 한문, 동아시아 역사 기행, 법과 사회</t>
+          <t>정보, 한문, 동아시아 역사 기행, 법과 사회, 독서와 작문, 확률과 통계</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -631,7 +638,9 @@
           <t>정보: 기록을 전자 시스템으로 관리하므로 → 데이터 구조와 자료 처리를 배워요.
 한문: 옛 문서와 고문서를 다루기도 해서 → 한문 문장을 읽고 해석하는 법을 배워요.
 동아시아 역사 기행: 기록의 역사적 맥락을 알아야 해서 → 한국·동아시아 역사의 흐름을 배워요.
-법과 사회: 기록물 관련 법령에 따라 일하므로 → 법의 기본 원리와 사회 속 법을 배워요.</t>
+법과 사회: 기록물 관련 법령에 따라 일하므로 → 법의 기본 원리와 사회 속 법을 배워요.
+독서와 작문: 기록의 내용을 요약해 목록을 만들어야 해서 → 핵심을 파악해 간결하게 정리하는 법을 배워요.
+확률과 통계: 많은 기록물을 분류·관리해야 해서 → 자료를 기준에 따라 정리·분석하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -653,7 +662,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>화학, 화학 실험, 물질과 에너지, 동아시아 역사 기행, 미술 감상과 비평</t>
+          <t>화학, 화학 실험, 물질과 에너지, 동아시아 역사 기행, 미술 감상과 비평, 독서와 작문, 영어 I</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -667,7 +676,9 @@
 화학 실험: 보존 처리를 실험실에서 하므로 → 실험 설계와 안전한 실험 기술을 익혀요.
 물질과 에너지: 금속·목재 등 재료 성질을 알아야 해서 → 물질의 상태와 성질을 깊이 배워요.
 동아시아 역사 기행: 유물의 시대적 배경을 알아야 해서 → 한국·동아시아의 역사와 문화를 배워요.
-미술 감상과 비평: 원래의 미적 가치를 살려야 해서 → 미술 작품을 감상하고 분석해요.</t>
+미술 감상과 비평: 원래의 미적 가치를 살려야 해서 → 미술 작품을 감상하고 분석해요.
+독서와 작문: 보존 처리 과정을 보고서로 남겨야 해서 → 과정과 결과를 정확히 기록하는 글쓰기를 배워요.
+영어 I: 해외 보존 기술 자료를 읽어야 해서 → 전문 자료를 읽는 기본 영어 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -689,7 +700,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>문학과 영상, 매체 의사소통, 미술과 매체, 동아시아 역사 기행, 사회와 문화</t>
+          <t>문학과 영상, 매체 의사소통, 미술과 매체, 동아시아 역사 기행, 사회와 문화, 문학, 화법과 언어, 확률과 통계</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -703,7 +714,10 @@
 매체 의사소통: 다양한 매체로 콘텐츠를 알려야 해서 → 매체별 표현과 소통 방법을 배워요.
 미술과 매체: 시각 콘텐츠를 함께 기획하므로 → 다양한 매체로 표현하는 법을 배워요.
 동아시아 역사 기행: 역사 소재를 많이 활용하므로 → 동아시아 역사와 문화유산을 배워요.
-사회와 문화: 대중의 취향과 문화 흐름을 읽어야 해서 → 문화 현상을 사회학적으로 분석해요.</t>
+사회와 문화: 대중의 취향과 문화 흐름을 읽어야 해서 → 문화 현상을 사회학적으로 분석해요.
+문학: 이야기를 소재로 콘텐츠를 만들어야 해서 → 작품 속 인물·사건·주제를 해석하는 법을 배워요.
+화법과 언어: 기획안을 발표하고 설득해야 해서 → 청중을 설득하는 말하기 방법을 배워요.
+확률과 통계: 관객 반응과 흥행 자료를 살펴야 해서 → 자료를 정리하고 경향을 읽는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -725,7 +739,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>동아시아 역사 기행, 한문, 여행지리, 미술 감상과 비평, 실생활 영어 회화</t>
+          <t>동아시아 역사 기행, 한문, 여행지리, 미술 감상과 비평, 실생활 영어 회화, 화법과 언어, 영어 I, 스포츠 생활1</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -739,7 +753,10 @@
 한문: 현판·비문을 풀이해 주어야 해서 → 한자와 한문 읽는 법을 배워요.
 여행지리: 지역 명소를 안내하는 일이라 → 여행지의 자연·문화 특성을 배워요.
 미술 감상과 비평: 건축·회화 유산을 설명해야 해서 → 미술 작품을 감상하고 해석해요.
-실생활 영어 회화: 외국인 방문객도 안내하므로 → 생활 속 영어 회화를 연습해요.</t>
+실생활 영어 회화: 외국인 방문객도 안내하므로 → 생활 속 영어 회화를 연습해요.
+화법과 언어: 방문객 앞에서 쉽고 재미있게 설명해야 해서 → 듣는 사람에 맞춘 말하기 방법을 배워요.
+영어 I: 외국인 관광객에게도 해설해야 해서 → 기본 영어 표현과 의사소통을 배워요.
+스포츠 생활1: 유적지를 오래 걸으며 안내해야 해서 → 꾸준한 운동으로 체력을 기르는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -761,7 +778,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>미술 감상과 비평, 동아시아 역사 기행, 한문, 세계사, 화학</t>
+          <t>미술 감상과 비평, 동아시아 역사 기행, 한문, 세계사, 화학, 독서와 작문, 영어 I</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -775,7 +792,9 @@
 동아시아 역사 기행: 고서화·도자기를 많이 다루므로 → 동아시아 역사와 문화유산을 배워요.
 한문: 고서화의 낙관과 글씨를 읽어야 해서 → 한자와 한문 해석법을 배워요.
 세계사: 작품이 만들어진 시대를 알아야 해서 → 세계 여러 시대의 역사와 문화를 배워요.
-화학: 안료·재료를 과학적으로 분석하기도 해서 → 물질의 성질과 화학 반응을 배워요.</t>
+화학: 안료·재료를 과학적으로 분석하기도 해서 → 물질의 성질과 화학 반응을 배워요.
+독서와 작문: 감정 결과를 감정서로 정확히 써야 해서 → 근거를 들어 논리적으로 글 쓰는 법을 배워요.
+영어 I: 해외 경매 자료와 작품 기록을 봐야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -797,7 +816,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>매체 의사소통, 문학과 영상, 독서 토론과 글쓰기, 주제 탐구 독서, 사회문제 탐구</t>
+          <t>매체 의사소통, 문학과 영상, 독서 토론과 글쓰기, 주제 탐구 독서, 사회문제 탐구, 화법과 언어, 독서와 작문, 문학</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -811,7 +830,10 @@
 문학과 영상: 영상에 맞는 이야기를 써야 해서 → 문학과 영상의 표현 방식을 배워요.
 독서 토론과 글쓰기: 대본과 원고를 매일 쓰므로 → 논리적으로 글을 쓰는 법을 연습해요.
 주제 탐구 독서: 프로그램 자료를 조사해야 해서 → 주제를 정해 깊이 읽고 정리해요.
-사회문제 탐구: 시사 프로그램 소재를 찾아야 해서 → 사회 문제를 조사하고 분석해요.</t>
+사회문제 탐구: 시사 프로그램 소재를 찾아야 해서 → 사회 문제를 조사하고 분석해요.
+화법과 언어: 진행자가 말하기 좋은 대본을 써야 해서 → 말하기에 맞는 문장 표현을 배워요.
+독서와 작문: 자료를 조사해 원고로 정리해야 해서 → 자료를 읽고 목적에 맞게 글 쓰는 법을 배워요.
+문학: 드라마·교양 프로그램의 이야기를 짜야 해서 → 작품의 구성과 표현 방식을 배워요.</t>
         </is>
       </c>
     </row>
@@ -833,7 +855,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>동아시아 역사 기행, 세계사, 역사로 탐구하는 현대 세계, 한문, 독서 토론과 글쓰기</t>
+          <t>동아시아 역사 기행, 세계사, 역사로 탐구하는 현대 세계, 한문, 독서 토론과 글쓰기, 독서와 작문, 문학, 영어 I</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -847,7 +869,10 @@
 세계사: 넓은 시야로 역사를 서술해야 해서 → 세계 여러 문명의 역사를 배워요.
 역사로 탐구하는 현대 세계: 과거와 오늘을 연결해야 해서 → 현대 세계의 문제를 역사로 탐구해요.
 한문: 사료 원문을 직접 읽어야 해서 → 한문 문장을 읽고 해석하는 법을 배워요.
-독서 토론과 글쓰기: 책을 쓰는 것이 주된 일이라 → 자료를 바탕으로 글 쓰는 법을 익혀요.</t>
+독서 토론과 글쓰기: 책을 쓰는 것이 주된 일이라 → 자료를 바탕으로 글 쓰는 법을 익혀요.
+독서와 작문: 사료를 읽고 책으로 엮어야 해서 → 긴 글을 읽고 체계적으로 쓰는 법을 배워요.
+문학: 독자가 빠져드는 역사 이야기를 써야 해서 → 이야기를 생생하게 표현하는 방법을 배워요.
+영어 I: 해외 역사 연구서를 참고해야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -869,7 +894,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>독서 토론과 글쓰기, 문학과 영상, 매체 의사소통, 인간과 심리, 주제 탐구 독서</t>
+          <t>독서 토론과 글쓰기, 문학과 영상, 매체 의사소통, 인간과 심리, 주제 탐구 독서, 문학, 화법과 언어, 독서와 작문</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -883,7 +908,10 @@
 문학과 영상: 웹툰·드라마로 각색되기도 해서 → 문학과 영상 서사의 특징을 배워요.
 매체 의사소통: 플랫폼에서 독자와 소통하므로 → 디지털 매체의 특성과 소통법을 배워요.
 인간과 심리: 독자가 공감할 인물을 만들어야 해서 → 인간의 감정과 행동 원리를 배워요.
-주제 탐구 독서: 작품 배경을 조사해야 해서 → 주제를 정해 깊이 읽고 탐구해요.</t>
+주제 탐구 독서: 작품 배경을 조사해야 해서 → 주제를 정해 깊이 읽고 탐구해요.
+문학: 독자를 사로잡는 인물과 사건을 만들어야 해서 → 소설의 구성과 서술 방식을 배워요.
+화법과 언어: 캐릭터마다 개성 있는 말투가 필요해서 → 다양한 언어 표현과 문체를 배워요.
+독서와 작문: 매일 연재 분량을 써내야 해서 → 글을 계획하고 고쳐 쓰는 과정을 배워요.</t>
         </is>
       </c>
     </row>
@@ -905,7 +933,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>음악 감상과 비평, 음악과 미디어, 독서 토론과 글쓰기, 언어생활 탐구, 미디어 영어</t>
+          <t>음악 감상과 비평, 음악과 미디어, 독서 토론과 글쓰기, 언어생활 탐구, 미디어 영어, 문학, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -919,7 +947,10 @@
 음악과 미디어: 음원·영상 등 미디어로 유통되므로 → 미디어 속 음악의 제작과 활용을 배워요.
 독서 토론과 글쓰기: 짧은 말로 감정을 담아내야 해서 → 생각을 글로 표현하는 법을 연습해요.
 언어생활 탐구: 말의 소리와 리듬을 살려야 해서 → 국어의 소리와 단어 쓰임을 탐구해요.
-미디어 영어: 영어 가사를 섞어 쓰는 경우가 많아서 → 미디어 속 영어 표현을 배워요.</t>
+미디어 영어: 영어 가사를 섞어 쓰는 경우가 많아서 → 미디어 속 영어 표현을 배워요.
+문학: 짧은 노랫말에 감정을 담아야 해서 → 시의 운율과 비유 표현을 배워요.
+화법과 언어: 소리 내어 부르기 좋은 말을 골라야 해서 → 말소리와 단어의 느낌을 배워요.
+영어 I: K팝 가사에 영어 표현이 자주 쓰여서 → 자연스러운 영어 표현을 배워요.</t>
         </is>
       </c>
     </row>
@@ -941,7 +972,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>주제 탐구 독서, 독서 토론과 글쓰기, 매체 의사소통, 사회와 문화, 경제</t>
+          <t>주제 탐구 독서, 독서 토론과 글쓰기, 매체 의사소통, 사회와 문화, 경제, 독서와 작문, 확률과 통계, 문학</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -955,7 +986,10 @@
 독서 토론과 글쓰기: 기획서와 소개 글을 써야 해서 → 논리적으로 글을 쓰는 법을 익혀요.
 매체 의사소통: 책을 여러 매체로 홍보하므로 → 매체별 표현과 소통 방법을 배워요.
 사회와 문화: 독자의 관심과 유행을 읽어야 해서 → 사회·문화 현상을 분석하는 법을 배워요.
-경제: 책의 판매와 수익을 따져야 해서 → 시장과 수요·공급의 원리를 배워요.</t>
+경제: 책의 판매와 수익을 따져야 해서 → 시장과 수요·공급의 원리를 배워요.
+독서와 작문: 원고의 가치를 판단하고 기획서를 써야 해서 → 글을 분석하고 설득하는 글쓰기를 배워요.
+확률과 통계: 독자 수요와 판매 자료를 분석해야 해서 → 자료를 정리하고 경향을 읽는 법을 배워요.
+문학: 좋은 작품을 알아보는 눈이 필요해서 → 문학 작품을 해석하고 감상하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -977,7 +1011,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>언어생활 탐구, 독서 토론과 글쓰기, 주제 탐구 독서, 미술과 매체, 매체 의사소통</t>
+          <t>언어생활 탐구, 독서 토론과 글쓰기, 주제 탐구 독서, 미술과 매체, 매체 의사소통, 화법과 언어, 독서와 작문, 문학</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -991,7 +1025,10 @@
 독서 토론과 글쓰기: 원고를 고치고 다듬어야 해서 → 글을 분석하고 고쳐 쓰는 법을 배워요.
 주제 탐구 독서: 여러 분야의 원고를 다루므로 → 다양한 글을 깊이 읽는 법을 배워요.
 미술과 매체: 표지·편집 디자인을 함께 정해서 → 시각 매체로 표현하는 법을 배워요.
-매체 의사소통: 전자책 등 새로운 매체도 다루므로 → 매체의 특성과 소통 방식을 배워요.</t>
+매체 의사소통: 전자책 등 새로운 매체도 다루므로 → 매체의 특성과 소통 방식을 배워요.
+화법과 언어: 원고의 문장과 표기를 바로잡아야 해서 → 국어 문법과 바른 표현을 배워요.
+독서와 작문: 원고의 구성과 흐름을 다듬어야 해서 → 글의 구조를 분석하고 고쳐 쓰는 법을 배워요.
+문학: 작가와 작품을 깊이 이해해야 해서 → 문학 작품을 해석하는 방법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1050,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>독서 토론과 글쓰기, 사회문제 탐구, 논리와 사고, 인간과 철학, 매체 의사소통</t>
+          <t>독서 토론과 글쓰기, 사회문제 탐구, 논리와 사고, 인간과 철학, 매체 의사소통, 독서와 작문, 화법과 언어, 확률과 통계</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1027,7 +1064,10 @@
 사회문제 탐구: 시사 문제를 주로 다루므로 → 사회 문제를 조사하고 분석해요.
 논리와 사고: 설득력 있는 주장을 펴야 해서 → 논증과 비판적 사고를 배워요.
 인간과 철학: 깊이 있는 관점이 필요해서 → 인간과 세계에 대한 철학적 사유를 배워요.
-매체 의사소통: 다양한 매체에 글을 실으므로 → 매체별 글쓰기와 소통 방식을 배워요.</t>
+매체 의사소통: 다양한 매체에 글을 실으므로 → 매체별 글쓰기와 소통 방식을 배워요.
+독서와 작문: 주장을 근거와 함께 글로 펼쳐야 해서 → 논리적으로 설득하는 글쓰기를 배워요.
+화법과 언어: 독자에게 와닿는 문장을 써야 해서 → 정확하고 효과적인 언어 표현을 배워요.
+확률과 통계: 통계 자료로 사회 현상을 분석해야 해서 → 자료를 해석하고 근거로 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1089,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>문학과 영상, 독서 토론과 글쓰기, 미술 감상과 비평, 음악 감상과 비평, 논리와 사고</t>
+          <t>문학과 영상, 독서 토론과 글쓰기, 미술 감상과 비평, 음악 감상과 비평, 논리와 사고, 문학, 독서와 작문</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1063,7 +1103,9 @@
 독서 토론과 글쓰기: 평론은 결국 글로 쓰므로 → 근거를 들어 글 쓰는 법을 익혀요.
 미술 감상과 비평: 미술 분야 평론도 하므로 → 미술 작품을 감상하고 비평해요.
 음악 감상과 비평: 음악 분야 평론도 하므로 → 음악을 듣고 분석·비평해요.
-논리와 사고: 평가에 타당한 근거가 필요해서 → 논증과 비판적 사고를 배워요.</t>
+논리와 사고: 평가에 타당한 근거가 필요해서 → 논증과 비판적 사고를 배워요.
+문학: 작품을 깊이 분석하고 평가해야 해서 → 작품의 주제와 표현을 해석하는 법을 배워요.
+독서와 작문: 평가를 설득력 있는 글로 써야 해서 → 근거를 들어 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1127,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>사회문제 탐구, 세계시민과 지리, 기후변화와 지속가능한 세계, 국제정치, 영어 발표와 토론</t>
+          <t>사회문제 탐구, 세계시민과 지리, 기후변화와 지속가능한 세계, 국제정치, 영어 발표와 토론, 영어 I, 화법과 언어, 확률과 통계</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1099,7 +1141,10 @@
 세계시민과 지리: 지구촌 문제를 함께 다루므로 → 세계 여러 지역의 문제와 시민 역할을 배워요.
 기후변화와 지속가능한 세계: 환경 문제 활동도 많아서 → 기후 위기와 지속가능한 발전을 배워요.
 국제정치: 국제기구·각국 정부와 협력하므로 → 국제 관계와 국제기구의 역할을 배워요.
-영어 발표와 토론: 해외 단체와 소통·협력해서 → 영어로 발표하고 토론하는 법을 배워요.</t>
+영어 발표와 토론: 해외 단체와 소통·협력해서 → 영어로 발표하고 토론하는 법을 배워요.
+영어 I: 해외 단체와 함께 일하는 경우가 많아서 → 영어로 소통하는 기본 실력을 키워요.
+화법과 언어: 캠페인에서 시민의 참여를 이끌어야 해서 → 사람들을 설득하는 말하기를 배워요.
+확률과 통계: 사업 효과를 자료로 보여 줘야 해서 → 자료를 정리하고 분석하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1166,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>법과 사회, 운동과 건강, 인간과 심리, 사회문제 탐구</t>
+          <t>법과 사회, 운동과 건강, 인간과 심리, 사회문제 탐구, 스포츠 생활1, 스포츠 생활2, 화법과 언어</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1134,7 +1179,10 @@
           <t>법과 사회: 법에 따라 수사하고 단속하므로 → 생활 속 법과 형사 절차를 배워요.
 운동과 건강: 체력 시험이 있고 현장 업무가 많아서 → 체력 관리와 건강한 운동법을 배워요.
 인간과 심리: 피의자·피해자를 대해야 해서 → 사람의 마음과 행동 원리를 배워요.
-사회문제 탐구: 범죄의 사회적 원인을 알아야 해서 → 사회 문제를 조사하고 분석해요.</t>
+사회문제 탐구: 범죄의 사회적 원인을 알아야 해서 → 사회 문제를 조사하고 분석해요.
+스포츠 생활1: 범인을 쫓고 제압할 강한 체력이 필요해서 → 꾸준한 운동으로 기초 체력을 길러요.
+스포츠 생활2: 체력 시험과 현장 활동에 대비해야 해서 → 운동을 습관으로 만들어 체력을 키워요.
+화법과 언어: 시민과 대화하고 조서를 써야 해서 → 정확하고 차분한 말하기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1204,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>매체 의사소통, 인간과 심리, 실용 통계, 경제, 미술과 매체</t>
+          <t>매체 의사소통, 인간과 심리, 실용 통계, 경제, 미술과 매체, 화법과 언어, 확률과 통계, 영어 I</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1170,7 +1218,10 @@
 인간과 심리: 소비자의 마음을 움직여야 해서 → 사람의 심리와 행동 원리를 배워요.
 실용 통계: 시장·소비자 조사를 분석해야 해서 → 자료를 수집하고 통계로 해석해요.
 경제: 시장과 소비 흐름을 읽어야 해서 → 시장과 소비자 선택의 원리를 배워요.
-미술과 매체: 광고 시안을 함께 검토하므로 → 시각 매체로 표현하는 법을 배워요.</t>
+미술과 매체: 광고 시안을 함께 검토하므로 → 시각 매체로 표현하는 법을 배워요.
+화법과 언어: 광고주에게 전략을 발표해야 해서 → 설득력 있게 말하고 발표하는 법을 배워요.
+확률과 통계: 소비자 조사 결과를 분석해야 해서 → 자료를 정리하고 해석하는 법을 배워요.
+영어 I: 해외 광고 사례를 참고해야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1243,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>법과 사회, 인간과 심리, 사회문제 탐구, 운동과 건강</t>
+          <t>법과 사회, 인간과 심리, 사회문제 탐구, 운동과 건강, 스포츠 생활1, 화법과 언어</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1205,7 +1256,9 @@
           <t>법과 사회: 형 집행 법령에 따라 일하므로 → 법의 원리와 형사 절차를 배워요.
 인간과 심리: 수용자를 상담하고 교화해야 해서 → 사람의 마음과 행동 원리를 배워요.
 사회문제 탐구: 범죄와 재범의 원인을 알아야 해서 → 사회 문제를 조사하고 분석해요.
-운동과 건강: 체력과 안전 관리가 필요해서 → 체력 관리와 건강한 운동법을 배워요.</t>
+운동과 건강: 체력과 안전 관리가 필요해서 → 체력 관리와 건강한 운동법을 배워요.
+스포츠 생활1: 돌발 상황에 대응할 체력이 필요해서 → 꾸준한 운동으로 체력을 길러요.
+화법과 언어: 수용자를 상담하고 지도해야 해서 → 상대를 존중하며 대화하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1280,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>세계시민과 지리, 국제경제, 국제정치, 기후변화와 지속가능한 세계, 영어 발표와 토론</t>
+          <t>세계시민과 지리, 국제경제, 국제정치, 기후변화와 지속가능한 세계, 영어 발표와 토론, 영어 I, 영어 독해와 작문, 확률과 통계</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1241,7 +1294,10 @@
 국제경제: 개도국의 경제 발전을 돕는 일이라 → 무역·국제 금융과 경제 격차를 배워요.
 국제정치: 국제기구·각국 정부와 협력해서 → 국제 관계와 국제기구의 역할을 배워요.
 기후변화와 지속가능한 세계: 지속가능발전이 핵심 과제라 → 기후 위기와 지속가능한 발전을 배워요.
-영어 발표와 토론: 국제 회의와 협상이 많아서 → 영어로 발표하고 토론하는 법을 배워요.</t>
+영어 발표와 토론: 국제 회의와 협상이 많아서 → 영어로 발표하고 토론하는 법을 배워요.
+영어 I: 현지 주민·국제기구와 영어로 일해서 → 영어 의사소통의 기초를 다져요.
+영어 독해와 작문: 사업 제안서와 보고서를 영어로 써야 해서 → 영어 글을 읽고 쓰는 법을 배워요.
+확률과 통계: 현지 조사 자료로 사업을 평가해야 해서 → 자료를 정리하고 분석하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1319,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>운동과 건강, 국제정치, 동아시아 역사 기행, 한국지리 탐구, 물리학</t>
+          <t>운동과 건강, 국제정치, 동아시아 역사 기행, 한국지리 탐구, 물리학, 스포츠 생활1, 스포츠 과학, 영어 I</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1277,7 +1333,10 @@
 국제정치: 안보는 주변국 관계와 이어져서 → 국제 관계와 안보 문제를 배워요.
 동아시아 역사 기행: 한반도 안보의 역사를 알아야 해서 → 동아시아 국가 간 역사와 갈등을 배워요.
 한국지리 탐구: 작전에 지형 이해가 중요해서 → 우리 국토의 지형과 지역 특성을 배워요.
-물리학: 첨단 무기·장비를 다루므로 → 힘과 운동, 전기 등의 원리를 배워요.</t>
+물리학: 첨단 무기·장비를 다루므로 → 힘과 운동, 전기 등의 원리를 배워요.
+스포츠 생활1: 훈련과 작전에 강한 체력이 필요해서 → 꾸준한 운동으로 기초 체력을 길러요.
+스포츠 과학: 부대원의 체력을 과학적으로 관리해야 해서 → 운동과 신체 원리를 배워요.
+영어 I: 연합 훈련에서 외국군과 소통해야 해서 → 기본 영어 의사소통을 배워요.</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1358,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>지구과학, 지구시스템과학, 기후변화와 환경생태, 매체 의사소통</t>
+          <t>지구과학, 지구시스템과학, 기후변화와 환경생태, 매체 의사소통, 화법과 언어, 확률과 통계</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1312,7 +1371,9 @@
           <t>지구과학: 날씨 변화의 원리를 알아야 해서 → 대기와 해양, 기상 현상을 배워요.
 지구시스템과학: 기압·전선 등을 깊이 이해해야 해서 → 대기·해양의 상호작용을 깊이 배워요.
 기후변화와 환경생태: 이상 기후 소식도 전하므로 → 기후 변화와 생태계 영향을 배워요.
-매체 의사소통: 방송으로 정보를 전달하므로 → 매체에 맞게 말하고 표현하는 법을 배워요.</t>
+매체 의사소통: 방송으로 정보를 전달하므로 → 매체에 맞게 말하고 표현하는 법을 배워요.
+화법과 언어: 방송에서 날씨를 또렷이 전달해야 해서 → 정확한 발음과 말하기 방법을 배워요.
+확률과 통계: 강수 확률 같은 수치를 설명해야 해서 → 확률과 자료 해석 방법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1395,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>사회와 문화, 세계시민과 지리, 인간과 심리, 세계 문화와 영어, 중국어</t>
+          <t>사회와 문화, 세계시민과 지리, 인간과 심리, 세계 문화와 영어, 중국어, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1348,7 +1409,9 @@
 세계시민과 지리: 이주민의 출신 지역을 알아야 해서 → 세계 여러 지역의 생활과 문화를 배워요.
 인간과 심리: 적응을 돕는 상담을 해야 해서 → 사람의 마음과 행동 원리를 배워요.
 세계 문화와 영어: 다양한 문화권과 소통하므로 → 영어로 세계 여러 문화를 배워요.
-중국어: 중국 출신 이주민이 많아서 → 중국어 기초 의사소통을 배워요.</t>
+중국어: 중국 출신 이주민이 많아서 → 중국어 기초 의사소통을 배워요.
+화법과 언어: 이주민과 쉬운 말로 소통해야 해서 → 상대에 맞춘 말하기와 공감 대화를 배워요.
+영어 I: 여러 나라 사람과 대화하는 일이 많아서 → 기본 영어 의사소통을 배워요.</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1433,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>인간과 심리, 법과 사회, 논리와 사고, 사회문제 탐구, 실용 통계</t>
+          <t>인간과 심리, 법과 사회, 논리와 사고, 사회문제 탐구, 실용 통계, 확률과 통계, 독서와 작문, 영어 I</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1384,7 +1447,10 @@
 법과 사회: 수사는 법 절차에 따라 하므로 → 법의 원리와 형사 절차를 배워요.
 논리와 사고: 증거로 범인을 추리해야 해서 → 논리적 추론과 비판적 사고를 배워요.
 사회문제 탐구: 범죄의 사회적 배경을 알아야 해서 → 사회 문제를 조사하고 분석해요.
-실용 통계: 범죄 자료를 분석해 유형을 찾으므로 → 자료를 수집하고 통계로 해석해요.</t>
+실용 통계: 범죄 자료를 분석해 유형을 찾으므로 → 자료를 수집하고 통계로 해석해요.
+확률과 통계: 범죄 자료로 범인 특성을 추정해야 해서 → 자료로 가능성을 따지는 통계적 추론을 배워요.
+독서와 작문: 분석 결과를 보고서로 써야 해서 → 근거를 들어 논리적으로 쓰는 법을 배워요.
+영어 I: 해외 범죄 심리 연구를 참고해야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1472,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>법과 사회, 정치, 경제, 언어생활과 한자, 논리와 사고</t>
+          <t>법과 사회, 정치, 경제, 언어생활과 한자, 논리와 사고, 독서와 작문, 화법과 언어</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1420,7 +1486,9 @@
 정치: 법이 만들어지는 과정을 알아야 해서 → 민주 정치와 헌법 원리를 배워요.
 경제: 부동산·금전 거래를 많이 다뤄서 → 시장과 경제 활동의 원리를 배워요.
 언어생활과 한자: 법률 용어에 한자어가 많아서 → 한자어의 뜻과 쓰임을 배워요.
-논리와 사고: 법 조문을 논리적으로 해석해야 해서 → 논증과 추론하는 법을 배워요.</t>
+논리와 사고: 법 조문을 논리적으로 해석해야 해서 → 논증과 추론하는 법을 배워요.
+독서와 작문: 법률 서류를 정확하게 작성해야 해서 → 목적에 맞게 정확한 글 쓰는 법을 배워요.
+화법과 언어: 의뢰인에게 절차를 쉽게 설명해야 해서 → 알기 쉽게 설명하는 말하기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1510,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>실용 통계, 사회와 문화, 사회문제 탐구, 정보, 인공지능 수학</t>
+          <t>실용 통계, 사회와 문화, 사회문제 탐구, 정보, 인공지능 수학, 확률과 통계, 대수, 독서와 작문</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1456,7 +1524,10 @@
 사회와 문화: 조사 방법론의 기초가 되어서 → 사회 현상과 자료 수집 방법을 배워요.
 사회문제 탐구: 조사할 주제를 정해야 해서 → 사회 문제를 조사하고 분석해요.
 정보: 분석 프로그램으로 자료를 처리해서 → 프로그래밍과 자료 처리를 배워요.
-인공지능 수학: 대량 자료 분석이 늘고 있어서 → 데이터 분석에 쓰이는 수학을 배워요.</t>
+인공지능 수학: 대량 자료 분석이 늘고 있어서 → 데이터 분석에 쓰이는 수학을 배워요.
+확률과 통계: 표본 조사로 전체 여론을 추정해야 해서 → 표본과 통계적 추정을 배워요.
+대수: 분석 공식과 수치 계산을 다뤄야 해서 → 식과 함수로 수량 관계를 다루는 법을 배워요.
+독서와 작문: 조사 결과를 보고서로 정리해야 해서 → 자료를 근거로 글 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1549,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>운동과 건강, 화학, 물리학, 생명과학</t>
+          <t>운동과 건강, 화학, 물리학, 생명과학, 스포츠 생활1, 스포츠 생활2, 스포츠 과학</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1491,7 +1562,10 @@
           <t>운동과 건강: 체력 시험과 현장 활동이 힘들어서 → 체력 관리와 건강한 운동법을 배워요.
 화학: 불이 붙고 번지는 원리를 알아야 해서 → 물질의 성질과 화학 반응을 배워요.
 물리학: 구조 장비와 건물 붕괴를 이해해야 해서 → 힘과 운동, 에너지의 원리를 배워요.
-생명과학: 응급 처치를 해야 해서 → 사람 몸의 구조와 기능을 배워요.</t>
+생명과학: 응급 처치를 해야 해서 → 사람 몸의 구조와 기능을 배워요.
+스포츠 생활1: 무거운 장비를 메고 구조해야 해서 → 꾸준한 운동으로 근력과 체력을 길러요.
+스포츠 생활2: 체력 시험과 현장 출동에 대비해야 해서 → 운동을 습관으로 만들어 체력을 키워요.
+스포츠 과학: 부상 없이 오래 활동해야 해서 → 운동과 신체 회복의 원리를 배워요.</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1587,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>실용 통계, 정치, 사회와 문화, 정보</t>
+          <t>실용 통계, 정치, 사회와 문화, 정보, 확률과 통계, 대수, 화법과 언어</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1526,7 +1600,10 @@
           <t>실용 통계: 표본과 오차를 정확히 다뤄야 해서 → 표본 조사와 통계적 해석을 배워요.
 정치: 선거·정책 여론을 주로 다뤄서 → 민주 정치와 선거 제도를 배워요.
 사회와 문화: 조사 설계의 기초가 필요해서 → 사회 현상 탐구 방법을 배워요.
-정보: 조사 자료를 프로그램으로 분석해서 → 프로그래밍과 자료 처리를 배워요.</t>
+정보: 조사 자료를 프로그램으로 분석해서 → 프로그래밍과 자료 처리를 배워요.
+확률과 통계: 표본으로 국민 전체 생각을 추정해야 해서 → 표본 조사와 오차, 통계적 추정을 배워요.
+대수: 조사 결과를 수치로 계산해야 해서 → 식과 함수로 수량 관계를 다루는 법을 배워요.
+화법과 언어: 설문 문항을 오해 없이 만들어야 해서 → 정확하고 중립적인 언어 표현을 배워요.</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1625,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>인간과 심리, 사회문제 탐구, 법과 사회, 생명과학</t>
+          <t>인간과 심리, 사회문제 탐구, 법과 사회, 생명과학, 화법과 언어, 독서와 작문, 스포츠 문화</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1561,7 +1638,10 @@
           <t>인간과 심리: 내담자의 마음을 이해해야 해서 → 사람의 마음과 상담의 기초를 배워요.
 사회문제 탐구: 장애인의 사회적 어려움을 알아야 해서 → 사회 문제를 조사하고 대안을 찾아요.
 법과 사회: 복지 제도와 권리를 안내해야 해서 → 인권과 사회 보장 관련 법을 배워요.
-생명과학: 장애의 의학적 특성을 이해해야 해서 → 사람 몸의 구조와 기능을 배워요.</t>
+생명과학: 장애의 의학적 특성을 이해해야 해서 → 사람 몸의 구조와 기능을 배워요.
+화법과 언어: 내담자의 마음을 듣고 상담해야 해서 → 공감하며 대화하는 방법을 배워요.
+독서와 작문: 상담 기록과 재활 계획서를 써야 해서 → 내용을 정확히 정리하는 글쓰기를 배워요.
+스포츠 문화: 장애인 스포츠로 재활을 도울 수 있어서 → 다양한 스포츠의 가치와 문화를 배워요.</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1663,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>정치, 실용 통계, 매체 의사소통, 인간과 심리, 사회문제 탐구</t>
+          <t>정치, 실용 통계, 매체 의사소통, 인간과 심리, 사회문제 탐구, 확률과 통계, 화법과 언어, 독서와 작문</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1597,7 +1677,10 @@
 실용 통계: 여론조사 결과로 전략을 세워서 → 자료를 통계로 분석하고 해석해요.
 매체 의사소통: 미디어 홍보 전략을 짜야 해서 → 매체별 특성과 소통 방법을 배워요.
 인간과 심리: 유권자의 마음을 읽어야 해서 → 사람의 심리와 행동 원리를 배워요.
-사회문제 탐구: 공약이 될 사회 문제를 찾아야 해서 → 사회 문제를 조사하고 분석해요.</t>
+사회문제 탐구: 공약이 될 사회 문제를 찾아야 해서 → 사회 문제를 조사하고 분석해요.
+확률과 통계: 여론 조사로 선거 판세를 읽어야 해서 → 자료를 분석하고 추론하는 법을 배워요.
+화법과 언어: 후보의 연설과 메시지를 다듬어야 해서 → 청중을 설득하는 말하기 전략을 배워요.
+독서와 작문: 선거 전략 보고서를 써야 해서 → 논리적으로 설득하는 글쓰기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1702,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>정치, 국제정치, 독서 토론과 글쓰기, 논리와 사고, 역사로 탐구하는 현대 세계</t>
+          <t>정치, 국제정치, 독서 토론과 글쓰기, 논리와 사고, 역사로 탐구하는 현대 세계, 화법과 언어, 확률과 통계, 영어 I</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1633,7 +1716,10 @@
 국제정치: 외교·안보 이슈도 다루므로 → 국제 관계와 국제 질서를 배워요.
 독서 토론과 글쓰기: 칼럼과 토론이 주된 일이라 → 근거를 들어 말하고 쓰는 법을 익혀요.
 논리와 사고: 균형 잡힌 분석이 필요해서 → 논증과 비판적 사고를 배워요.
-역사로 탐구하는 현대 세계: 정치 현상의 배경을 알아야 해서 → 현대 세계의 형성을 역사로 탐구해요.</t>
+역사로 탐구하는 현대 세계: 정치 현상의 배경을 알아야 해서 → 현대 세계의 형성을 역사로 탐구해요.
+화법과 언어: 방송에서 견해를 논리적으로 말해야 해서 → 근거를 들어 설득하는 말하기를 배워요.
+확률과 통계: 여론 조사 결과를 해석해야 해서 → 통계 자료를 바르게 읽는 법을 배워요.
+영어 I: 해외 정치 소식을 직접 살펴야 해서 → 영어 기사를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1741,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>인간과 심리, 인간과 경제활동, 사회와 문화, 직무 의사소통</t>
+          <t>인간과 심리, 인간과 경제활동, 사회와 문화, 직무 의사소통, 화법과 언어, 확률과 통계, 독서와 작문</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1668,7 +1754,10 @@
           <t>인간과 심리: 내담자의 적성과 마음을 이해해야 해서 → 성격·심리와 상담의 기초를 배워요.
 인간과 경제활동: 직업과 노동 시장을 안내해야 해서 → 일과 직업, 경제생활을 배워요.
 사회와 문화: 사회 변화에 따른 직업 흐름을 알아야 해서 → 사회 구조와 사회 변동을 배워요.
-직무 의사소통: 상담과 면접 지도를 하므로 → 직업 현장의 의사소통 방법을 배워요.</t>
+직무 의사소통: 상담과 면접 지도를 하므로 → 직업 현장의 의사소통 방법을 배워요.
+화법과 언어: 구직자의 고민을 듣고 조언해야 해서 → 공감하며 대화하는 방법을 배워요.
+확률과 통계: 적성 검사 결과를 해석해야 해서 → 검사 점수와 자료를 해석하는 법을 배워요.
+독서와 작문: 자기소개서 작성을 도와줘야 해서 → 목적에 맞게 글 쓰고 고치는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1779,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>교육의 이해, 인간과 심리, 사회문제 탐구, 운동과 건강</t>
+          <t>교육의 이해, 인간과 심리, 사회문제 탐구, 운동과 건강, 스포츠 생활1, 화법과 언어, 스포츠 문화</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1703,7 +1792,10 @@
           <t>교육의 이해: 청소년 교육 프로그램을 기획해서 → 교육의 의미와 원리를 배워요.
 인간과 심리: 청소년의 고민을 이해해야 해서 → 발달과 심리의 기초를 배워요.
 사회문제 탐구: 청소년 문제를 함께 다루므로 → 사회 문제를 조사하고 대안을 찾아요.
-운동과 건강: 체육·야외 활동을 이끌기도 해서 → 운동 방법과 건강 관리를 배워요.</t>
+운동과 건강: 체육·야외 활동을 이끌기도 해서 → 운동 방법과 건강 관리를 배워요.
+스포츠 생활1: 캠프·야외 활동을 이끌어야 해서 → 여러 운동을 익히고 체력을 길러요.
+화법과 언어: 청소년과 마음을 열고 대화해야 해서 → 공감하며 대화하는 방법을 배워요.
+스포츠 문화: 스포츠로 협동심을 기르는 활동이 많아서 → 스포츠의 가치와 문화를 배워요.</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1817,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>실생활 영어 회화, 법과 사회, 국제정치, 중국어 회화, 세계시민과 지리</t>
+          <t>실생활 영어 회화, 법과 사회, 국제정치, 중국어 회화, 세계시민과 지리, 영어 I, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1739,7 +1831,9 @@
 법과 사회: 출입국 관련 법에 따라 심사해서 → 법의 기본 원리와 적용을 배워요.
 국제정치: 나라 사이의 비자 협정을 알아야 해서 → 국제 관계와 국제 질서를 배워요.
 중국어 회화: 중국어권 입국자가 많아서 → 중국어로 대화하는 법을 배워요.
-세계시민과 지리: 여러 나라 사람을 만나므로 → 세계 여러 지역의 특성을 배워요.</t>
+세계시민과 지리: 여러 나라 사람을 만나므로 → 세계 여러 지역의 특성을 배워요.
+영어 I: 외국인과 매일 영어로 대화해야 해서 → 기본 영어 의사소통을 배워요.
+영어Ⅱ: 여러 나라 서류와 질문을 이해해야 해서 → 더 다양한 영어 표현과 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1855,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>매체 의사소통, 언어생활 탐구, 독서 토론과 글쓰기, 인간과 심리, 문학과 영상</t>
+          <t>매체 의사소통, 언어생활 탐구, 독서 토론과 글쓰기, 인간과 심리, 문학과 영상, 문학, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1775,7 +1869,10 @@
 언어생활 탐구: 말맛을 살린 표현이 중요해서 → 국어의 소리·단어·문장을 탐구해요.
 독서 토론과 글쓰기: 많은 문안을 쓰고 다듬어야 해서 → 글을 쓰고 고쳐 쓰는 법을 연습해요.
 인간과 심리: 소비자의 마음을 움직여야 해서 → 사람의 심리와 행동 원리를 배워요.
-문학과 영상: 광고 영상의 이야기를 함께 만들어서 → 문학과 영상의 표현 방식을 배워요.</t>
+문학과 영상: 광고 영상의 이야기를 함께 만들어서 → 문학과 영상의 표현 방식을 배워요.
+문학: 짧은 문구에 감성을 담아야 해서 → 시의 비유와 함축적 표현을 배워요.
+화법과 언어: 귀에 쏙 들어오는 말을 만들어야 해서 → 단어의 느낌과 말의 효과를 배워요.
+영어 I: 광고에 영어 문구도 자주 쓰여서 → 자연스러운 영어 표현을 배워요.</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1894,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>경제, 미적분Ⅱ, 경제 수학, 실용 통계, 국제경제</t>
+          <t>경제, 미적분Ⅱ, 경제 수학, 실용 통계, 국제경제, 미적분 I, 확률과 통계, 영어 독해와 작문</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1811,7 +1908,10 @@
 미적분Ⅱ: 경제 모형은 미분으로 분석하므로 → 여러 함수의 미분과 적분을 배워요.
 경제 수학: 경제 지표를 수학으로 다뤄서 → 경제에 쓰이는 수학적 개념을 배워요.
 실용 통계: 경제 자료를 실증 분석해야 해서 → 자료를 통계로 분석하고 해석해요.
-국제경제: 무역·환율도 연구 대상이라 → 국제 무역과 환율의 원리를 배워요.</t>
+국제경제: 무역·환율도 연구 대상이라 → 국제 무역과 환율의 원리를 배워요.
+미적분 I: 경제 변화를 수학 모델로 분석해야 해서 → 변화율과 미분의 원리를 배워요.
+확률과 통계: 경제 자료로 가설을 검증해야 해서 → 자료 분석과 통계적 추론을 배워요.
+영어 독해와 작문: 영어 논문을 읽고 써야 해서 → 영어 글을 읽고 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1933,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>법과 사회, 경제, 금융과 경제생활, 도시의 미래 탐구, 한국지리 탐구</t>
+          <t>법과 사회, 경제, 금융과 경제생활, 도시의 미래 탐구, 한국지리 탐구, 화법과 언어, 대수, 독서와 작문</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1847,7 +1947,10 @@
 경제: 부동산 시장의 흐름을 읽어야 해서 → 시장의 수요·공급 원리를 배워요.
 금융과 경제생활: 대출·세금 상담도 하므로 → 금융 상품과 세금의 기초를 배워요.
 도시의 미래 탐구: 개발 계획이 집값에 영향을 줘서 → 도시 개발과 공간 변화를 배워요.
-한국지리 탐구: 지역별 입지를 분석해야 해서 → 우리 국토의 지역 특성을 배워요.</t>
+한국지리 탐구: 지역별 입지를 분석해야 해서 → 우리 국토의 지역 특성을 배워요.
+화법과 언어: 고객에게 매물과 계약을 설명해야 해서 → 신뢰를 주는 설명과 말하기를 배워요.
+대수: 대출 이자와 세금을 계산해야 해서 → 수열·지수로 금액을 계산하는 법을 배워요.
+독서와 작문: 계약서를 꼼꼼히 읽고 써야 해서 → 글을 정확히 읽고 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1972,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>국제경제, 법과 사회, 경제, 직무 영어, 경제 수학</t>
+          <t>국제경제, 법과 사회, 경제, 직무 영어, 경제 수학, 영어 I, 대수, 독서와 작문</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1883,7 +1986,10 @@
 법과 사회: 관세법에 따라 업무를 처리해서 → 법의 원리와 적용을 배워요.
 경제: 시장과 거래의 원리를 알아야 해서 → 기본적인 경제 원리를 배워요.
 직무 영어: 영문 무역 서류를 다뤄서 → 업무에 쓰이는 영어를 배워요.
-경제 수학: 관세와 환율을 계산해야 해서 → 경제에 쓰이는 수학을 배워요.</t>
+경제 수학: 관세와 환율을 계산해야 해서 → 경제에 쓰이는 수학을 배워요.
+영어 I: 수출입 서류가 대부분 영어로 되어 있어서 → 영어 문서를 읽는 기본 독해를 배워요.
+대수: 관세와 환율을 정확히 계산해야 해서 → 식과 지수를 다루는 계산 원리를 배워요.
+독서와 작문: 통관 서류를 정확히 작성해야 해서 → 정확하고 논리적인 글쓰기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -1905,7 +2011,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>직무 영어, 영어 발표와 토론, 세계 문화와 영어, 국제정치, 직무 의사소통</t>
+          <t>직무 영어, 영어 발표와 토론, 세계 문화와 영어, 국제정치, 직무 의사소통, 영어 I, 영어Ⅱ, 화법과 언어</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1919,7 +2025,10 @@
 영어 발표와 토론: 회의 진행과 발표를 지원해서 → 영어로 발표하고 토론하는 법을 배워요.
 세계 문화와 영어: 여러 나라 참가자를 맞이해서 → 영어로 세계 여러 문화를 배워요.
 국제정치: 국제기구·정부 회의를 많이 열어서 → 국제 관계와 국제기구를 배워요.
-직무 의사소통: 여러 업체와 일정을 조율해서 → 직장 속 의사소통 방법을 배워요.</t>
+직무 의사소통: 여러 업체와 일정을 조율해서 → 직장 속 의사소통 방법을 배워요.
+영어 I: 외국 참가자와 영어로 소통해야 해서 → 기본 영어 의사소통을 배워요.
+영어Ⅱ: 해외 기관과 일정을 협의해야 해서 → 더 다양한 영어 표현을 배워요.
+화법과 언어: 행사 진행과 안내를 맡아야 해서 → 상황에 맞는 말하기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -1941,7 +2050,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>미적분Ⅱ, 경제 수학, 실용 통계, 금융과 경제생활, 경제</t>
+          <t>미적분Ⅱ, 경제 수학, 실용 통계, 금융과 경제생활, 경제, 확률과 통계, 대수</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1955,7 +2064,9 @@
 경제 수학: 이자·수익률 계산이 기본이라 → 경제·금융에 쓰이는 수학을 배워요.
 실용 통계: 위험을 확률로 예측해야 해서 → 자료를 통계로 분석하고 해석해요.
 금융과 경제생활: 금융 상품의 구조를 알아야 해서 → 예금·보험·투자 상품을 배워요.
-경제: 금리와 시장 변화를 읽어야 해서 → 시장과 경제 정책의 원리를 배워요.</t>
+경제: 금리와 시장 변화를 읽어야 해서 → 시장과 경제 정책의 원리를 배워요.
+확률과 통계: 고객 위험과 수익 가능성을 따져야 해서 → 확률과 통계적 추론을 배워요.
+대수: 이자와 수익률을 계산해야 해서 → 지수·로그·수열로 복리를 계산해요.</t>
         </is>
       </c>
     </row>
@@ -1977,7 +2088,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>실용 통계, 미적분Ⅱ, 경제 수학, 경제, 국제경제</t>
+          <t>실용 통계, 미적분Ⅱ, 경제 수학, 경제, 국제경제, 확률과 통계, 대수, 영어 I</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1991,7 +2102,10 @@
 미적분Ⅱ: 금융 위험 모형을 다뤄서 → 다양한 함수의 미분과 적분을 배워요.
 경제 수학: 손실과 수익을 계산해야 해서 → 경제·금융에 쓰이는 수학을 배워요.
 경제: 경기 변화가 위험 요인이 되어서 → 경기 변동과 경제 정책을 배워요.
-국제경제: 환율·국제 시장 위험도 관리해서 → 환율과 국제 금융의 원리를 배워요.</t>
+국제경제: 환율·국제 시장 위험도 관리해서 → 환율과 국제 금융의 원리를 배워요.
+확률과 통계: 손실이 생길 가능성을 예측해야 해서 → 확률 분포와 통계적 추론을 배워요.
+대수: 위험 지표를 수식으로 계산해야 해서 → 지수·로그 함수를 다루는 법을 배워요.
+영어 I: 해외 시장 위험 자료를 살펴야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2127,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>직무 수학, 실용 통계, 정보, 국제경제, 한국지리 탐구</t>
+          <t>직무 수학, 실용 통계, 정보, 국제경제, 한국지리 탐구, 확률과 통계, 대수, 영어 I</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2027,7 +2141,10 @@
 실용 통계: 수요를 예측해 재고를 관리해서 → 자료를 통계로 분석하고 예측해요.
 정보: 물류 관리 시스템을 사용하므로 → 프로그래밍과 자료 처리를 배워요.
 국제경제: 수출입 물류도 많이 다뤄서 → 국제 무역의 흐름을 배워요.
-한국지리 탐구: 물류 센터 입지와 운송로를 정해서 → 국토의 교통과 지역 특성을 배워요.</t>
+한국지리 탐구: 물류 센터 입지와 운송로를 정해서 → 국토의 교통과 지역 특성을 배워요.
+확률과 통계: 수요를 예측해 재고를 맞춰야 해서 → 자료로 예측하는 통계 방법을 배워요.
+대수: 운송비와 시간을 계산해야 해서 → 식과 함수로 수량을 계산하는 법을 배워요.
+영어 I: 해외 운송 업체와 연락해야 해서 → 기본 영어 의사소통을 배워요.</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2166,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>법과 사회, 금융과 경제생활, 실용 통계, 생명과학</t>
+          <t>법과 사회, 금융과 경제생활, 실용 통계, 생명과학, 확률과 통계, 독서와 작문</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2062,7 +2179,9 @@
           <t>법과 사회: 약관과 법률을 따져야 해서 → 계약과 손해 배상 관련 법을 배워요.
 금융과 경제생활: 보험 상품을 이해해야 해서 → 보험 등 금융 상품의 원리를 배워요.
 실용 통계: 사고 위험과 확률을 다뤄서 → 자료를 통계로 분석하고 해석해요.
-생명과학: 질병·상해 서류를 검토해야 해서 → 사람 몸의 구조와 질병을 배워요.</t>
+생명과학: 질병·상해 서류를 검토해야 해서 → 사람 몸의 구조와 질병을 배워요.
+확률과 통계: 사고 확률로 보험 위험을 판단해야 해서 → 확률과 통계적 추론을 배워요.
+독서와 작문: 서류를 검토하고 심사 의견을 써야 해서 → 글을 꼼꼼히 읽고 근거 있게 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2203,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>실용 통계, 정보, 인공지능 수학, 경제, 직무 의사소통</t>
+          <t>실용 통계, 정보, 인공지능 수학, 경제, 직무 의사소통, 확률과 통계, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2098,7 +2217,10 @@
 정보: 데이터를 프로그램으로 다뤄서 → 프로그래밍과 자료 처리를 배워요.
 인공지능 수학: 예측 분석 도구를 활용해서 → 데이터 분석에 쓰이는 수학을 배워요.
 경제: 기업 활동과 시장을 이해해야 해서 → 시장과 기업 활동의 원리를 배워요.
-직무 의사소통: 분석 결과를 보고·설득해야 해서 → 직장 속 보고와 발표 방법을 배워요.</t>
+직무 의사소통: 분석 결과를 보고·설득해야 해서 → 직장 속 보고와 발표 방법을 배워요.
+확률과 통계: 데이터로 문제의 원인을 찾아야 해서 → 자료 분석과 통계적 추론을 배워요.
+화법과 언어: 분석 결과를 경영진에게 발표해야 해서 → 핵심을 전달하는 발표 방법을 배워요.
+영어 I: 글로벌 기업 자료를 다루는 일이 많아서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2242,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>경제, 실용 통계, 인간과 심리, 사회와 문화, 미술과 매체</t>
+          <t>경제, 실용 통계, 인간과 심리, 사회와 문화, 미술과 매체, 확률과 통계, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2134,7 +2256,10 @@
 실용 통계: 판매 데이터를 분석해야 해서 → 자료를 통계로 분석하고 해석해요.
 인간과 심리: 소비자의 구매 심리를 알아야 해서 → 사람의 심리와 행동 원리를 배워요.
 사회와 문화: 유행과 생활 문화를 읽어야 해서 → 문화 현상을 분석하는 법을 배워요.
-미술과 매체: 상품 디자인을 보는 안목이 필요해서 → 시각 매체로 표현하는 법을 배워요.</t>
+미술과 매체: 상품 디자인을 보는 안목이 필요해서 → 시각 매체로 표현하는 법을 배워요.
+확률과 통계: 판매 자료로 잘 팔릴 상품을 골라야 해서 → 자료를 정리하고 경향을 읽는 법을 배워요.
+화법과 언어: 협력 업체와 협상해야 해서 → 설득하고 협상하는 말하기를 배워요.
+영어 I: 해외 상품과 트렌드를 살펴야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2281,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>실용 통계, 경제, 사회와 문화, 정보, 인공지능 수학</t>
+          <t>실용 통계, 경제, 사회와 문화, 정보, 인공지능 수학, 확률과 통계, 대수, 독서와 작문</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2170,7 +2295,10 @@
 경제: 시장 구조와 수요를 알아야 해서 → 시장과 수요·공급의 원리를 배워요.
 사회와 문화: 설문 조사 설계의 기초가 되어서 → 사회 현상과 자료 수집 방법을 배워요.
 정보: 대량의 조사 자료를 처리해서 → 프로그래밍과 자료 처리를 배워요.
-인공지능 수학: 빅데이터 분석이 늘고 있어서 → 데이터 분석에 쓰이는 수학을 배워요.</t>
+인공지능 수학: 빅데이터 분석이 늘고 있어서 → 데이터 분석에 쓰이는 수학을 배워요.
+확률과 통계: 표본 조사로 소비자 생각을 추정해야 해서 → 표본 조사와 통계적 추정을 배워요.
+대수: 분석 지표를 수식으로 계산해야 해서 → 식과 함수로 수량 관계를 다뤄요.
+독서와 작문: 분석 보고서를 써야 해서 → 자료를 근거로 글 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2320,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 매체 의사소통, 정보, 실용 통계, 경제</t>
+          <t>미술과 매체, 매체 의사소통, 정보, 실용 통계, 경제, 독서와 작문, 확률과 통계, 영어 I</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2206,7 +2334,10 @@
 매체 의사소통: SNS로 홍보하고 고객과 소통해서 → 매체별 특성과 소통 방법을 배워요.
 정보: 쇼핑몰 사이트를 관리해야 해서 → 컴퓨터와 프로그래밍의 기초를 배워요.
 실용 통계: 판매·방문 데이터를 분석해서 → 자료를 통계로 분석하고 해석해요.
-경제: 가격과 수익을 따져야 해서 → 시장과 소비자 선택의 원리를 배워요.</t>
+경제: 가격과 수익을 따져야 해서 → 시장과 소비자 선택의 원리를 배워요.
+독서와 작문: 눈길을 끄는 상품 설명을 써야 해서 → 읽는 사람을 고려한 글쓰기를 배워요.
+확률과 통계: 방문·구매 자료로 판매를 늘려야 해서 → 자료를 정리하고 해석하는 법을 배워요.
+영어 I: 해외 판매와 해외 상품을 다룰 수 있어서 → 기본 영어 의사소통을 배워요.</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2359,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>경제, 직무 수학, 실용 통계, 인간과 경제활동, 정보</t>
+          <t>경제, 직무 수학, 실용 통계, 인간과 경제활동, 정보, 확률과 통계, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2242,7 +2373,10 @@
 직무 수학: 재고와 원가를 계산해야 해서 → 실무에 쓰이는 수학을 배워요.
 실용 통계: 판매량을 예측해야 해서 → 자료를 통계로 분석하고 예측해요.
 인간과 경제활동: 소비자와 기업의 활동을 알아야 해서 → 생산·소비 등 경제 활동을 배워요.
-정보: 재고 관리 시스템을 사용해서 → 컴퓨터와 자료 처리를 배워요.</t>
+정보: 재고 관리 시스템을 사용해서 → 컴퓨터와 자료 처리를 배워요.
+확률과 통계: 판매 자료로 재고량을 정해야 해서 → 자료로 수요를 예측하는 법을 배워요.
+화법과 언어: 거래처와 조건을 협상해야 해서 → 설득하고 협상하는 말하기를 배워요.
+영어 I: 해외 상품을 들여오는 일이 있어서 → 기본 영어 의사소통을 배워요.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2398,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>금융과 경제생활, 경제, 경제 수학, 실용 통계, 직무 의사소통</t>
+          <t>금융과 경제생활, 경제, 경제 수학, 실용 통계, 직무 의사소통, 대수, 화법과 언어, 확률과 통계</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2278,7 +2412,10 @@
 경제: 금리·환율 변화를 이해해야 해서 → 시장과 국민 경제의 원리를 배워요.
 경제 수학: 이자와 수익률을 계산해야 해서 → 이자 계산 등 경제 속 수학을 배워요.
 실용 통계: 고객·금융 자료를 분석하므로 → 자료 정리와 통계적 해석을 배워요.
-직무 의사소통: 고객 상담이 핵심 업무라서 → 직장에서의 말하기·설명 방법을 배워요.</t>
+직무 의사소통: 고객 상담이 핵심 업무라서 → 직장에서의 말하기·설명 방법을 배워요.
+대수: 예금·대출 이자를 정확히 계산해야 해서 → 지수와 수열로 복리를 계산하는 법을 배워요.
+화법과 언어: 고객에게 금융 상품을 설명해야 해서 → 친절하고 알기 쉬운 말하기를 배워요.
+확률과 통계: 대출 심사에 고객 자료를 분석해야 해서 → 자료를 정리하고 판단하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2437,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>인간과 심리, 사회와 문화, 법과 사회, 직무 의사소통, 실용 통계</t>
+          <t>인간과 심리, 사회와 문화, 법과 사회, 직무 의사소통, 실용 통계, 화법과 언어, 독서와 작문, 확률과 통계</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2314,7 +2451,10 @@
 사회와 문화: 조직 문화와 구성원을 다뤄서 → 집단·조직과 사회 구조를 배워요.
 법과 사회: 근로계약과 노동법을 지켜야 해서 → 생활 속 법과 근로자 권리를 배워요.
 직무 의사소통: 면접·상담·공지를 자주 하므로 → 직장 내 말하기·글쓰기를 배워요.
-실용 통계: 인사 평가·설문 결과를 분석해서 → 자료 수집과 통계 분석을 배워요.</t>
+실용 통계: 인사 평가·설문 결과를 분석해서 → 자료 수집과 통계 분석을 배워요.
+화법과 언어: 채용 면접과 직원 상담을 해야 해서 → 질문하고 경청하는 대화법을 배워요.
+독서와 작문: 채용 공고와 인사 규정을 써야 해서 → 정확하고 명료한 글쓰기를 배워요.
+확률과 통계: 직원 평가 자료를 분석해야 해서 → 자료를 정리하고 해석하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2476,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>경제 수학, 실용 통계, 경제, 금융과 경제생활, 국제경제</t>
+          <t>경제 수학, 실용 통계, 경제, 금융과 경제생활, 국제경제, 확률과 통계, 대수, 영어 I</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2350,7 +2490,10 @@
 실용 통계: 재무 자료로 추세를 예측하므로 → 자료 분석과 통계적 추론을 배워요.
 경제: 기업 실적이 경기와 연결돼 있어서 → 시장·경기·금리의 원리를 배워요.
 금융과 경제생활: 주식·채권 등 금융상품을 다뤄서 → 금융 시장과 투자의 기초를 배워요.
-국제경제: 환율·무역이 기업 가치에 영향을 줘서 → 무역과 환율, 국제 금융을 배워요.</t>
+국제경제: 환율·무역이 기업 가치에 영향을 줘서 → 무역과 환율, 국제 금융을 배워요.
+확률과 통계: 시장 자료로 투자 위험을 판단해야 해서 → 자료 분석과 통계적 추론을 배워요.
+대수: 수익률과 성장률을 계산해야 해서 → 지수·로그 함수와 수열을 배워요.
+영어 I: 해외 기업 재무 자료를 읽어야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2515,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>금융과 경제생활, 경제, 경제 수학, 인간과 심리, 직무 의사소통</t>
+          <t>금융과 경제생활, 경제, 경제 수학, 인간과 심리, 직무 의사소통, 대수, 화법과 언어, 확률과 통계</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2386,7 +2529,10 @@
 경제: 금리·물가가 자산에 영향을 줘서 → 경제 흐름과 시장 원리를 배워요.
 경제 수학: 이자와 수익을 계산해 비교해야 해서 → 복리 등 경제 속 수학을 배워요.
 인간과 심리: 고객의 성향과 고민을 이해해야 해서 → 마음과 의사결정의 심리를 배워요.
-직무 의사소통: 금융 정보를 쉽게 설명해야 해서 → 상담·설명하는 의사소통 방법을 배워요.</t>
+직무 의사소통: 금융 정보를 쉽게 설명해야 해서 → 상담·설명하는 의사소통 방법을 배워요.
+대수: 저축과 투자의 미래 가치를 계산해야 해서 → 지수와 수열로 복리를 계산해요.
+화법과 언어: 고객과 상담하며 계획을 설명해야 해서 → 신뢰를 주는 상담 대화법을 배워요.
+확률과 통계: 투자의 위험과 수익을 비교해야 해서 → 확률과 자료 해석 방법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2554,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>경제, 경제 수학, 실용 통계, 국제경제, 금융과 경제생활, 독서 토론과 글쓰기</t>
+          <t>경제, 경제 수학, 실용 통계, 국제경제, 금융과 경제생활, 독서 토론과 글쓰기, 확률과 통계, 영어 I</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2423,7 +2569,9 @@
 실용 통계: 주가·실적 자료로 전망을 세워서 → 자료 분석과 예측 방법을 배워요.
 국제경제: 해외 시장과 환율도 분석해야 해서 → 무역·환율·국제 금융을 배워요.
 금융과 경제생활: 주식·채권 시장을 다뤄서 → 금융 시장과 투자의 기초를 배워요.
-독서 토론과 글쓰기: 분석 보고서를 써야 해서 → 근거를 갖춘 논리적 글쓰기를 배워요.</t>
+독서 토론과 글쓰기: 분석 보고서를 써야 해서 → 근거를 갖춘 논리적 글쓰기를 배워요.
+확률과 통계: 기업 자료로 주가를 전망해야 해서 → 자료 분석과 통계적 추론을 배워요.
+영어 I: 해외 기업과 시장 보고서를 읽어야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2593,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>미적분Ⅱ, 실용 통계, 인공지능 수학, 경제 수학, 정보</t>
+          <t>미적분Ⅱ, 실용 통계, 인공지능 수학, 경제 수학, 정보, 미적분 I, 확률과 통계, 대수</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2459,7 +2607,10 @@
 실용 통계: 시장 데이터의 확률적 움직임을 다뤄서 → 통계적 추정과 자료 분석을 배워요.
 인공지능 수학: 머신러닝으로 투자 전략을 세우므로 → 인공지능에 쓰이는 수학을 배워요.
 경제 수학: 수익률과 위험을 수치로 다뤄서 → 경제·금융 현상을 수학으로 분석해요.
-정보: 모델을 코드로 구현해야 해서 → 프로그래밍과 자료 처리를 배워요.</t>
+정보: 모델을 코드로 구현해야 해서 → 프로그래밍과 자료 처리를 배워요.
+미적분 I: 가격 변화를 수학 모델로 다뤄야 해서 → 극한과 미분의 원리를 배워요.
+확률과 통계: 시장의 불확실성을 확률로 다뤄야 해서 → 확률 분포와 통계적 추론을 배워요.
+대수: 수익률을 지수·로그로 계산해야 해서 → 지수·로그 함수와 수열을 배워요.</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2632,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>미술 감상과 비평, 미술과 매체, 사회와 문화, 경제, 실생활 영어 회화</t>
+          <t>미술 감상과 비평, 미술과 매체, 사회와 문화, 경제, 실생활 영어 회화, 영어 I, 영어Ⅱ, 확률과 통계</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2495,7 +2646,10 @@
 미술과 매체: 패션 트렌드가 이미지·영상으로 퍼져서 → 다양한 매체의 시각 표현을 배워요.
 사회와 문화: 유행은 사회 변화와 맞물려 있어서 → 문화와 소비 현상을 탐구해요.
 경제: 가격과 수요를 따져 상품을 사야 해서 → 수요·공급과 시장 원리를 배워요.
-실생활 영어 회화: 해외 브랜드와 직접 거래해서 → 실용적인 영어 회화를 연습해요.</t>
+실생활 영어 회화: 해외 브랜드와 직접 거래해서 → 실용적인 영어 회화를 연습해요.
+영어 I: 해외 브랜드와 직접 거래해야 해서 → 기본 영어 의사소통을 배워요.
+영어Ⅱ: 해외 패션쇼와 계약 자료를 봐야 해서 → 더 다양한 영어 표현과 독해를 배워요.
+확률과 통계: 판매 자료로 구매량을 정해야 해서 → 자료를 정리하고 경향을 읽는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2671,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>경제, 금융과 경제생활, 경제 수학, 실용 통계, 국제경제</t>
+          <t>경제, 금융과 경제생활, 경제 수학, 실용 통계, 국제경제, 확률과 통계, 대수, 영어 I</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2531,7 +2685,10 @@
 금융과 경제생활: 다양한 금융상품에 투자하므로 → 금융 시장과 위험 관리를 배워요.
 경제 수학: 수익률과 위험을 계산해야 해서 → 경제 현상을 수학으로 분석해요.
 실용 통계: 시장 자료로 투자 판단을 하므로 → 자료 분석과 통계적 추론을 배워요.
-국제경제: 해외 자산에도 투자해서 → 환율·무역·국제 금융을 배워요.</t>
+국제경제: 해외 자산에도 투자해서 → 환율·무역·국제 금융을 배워요.
+확률과 통계: 수익과 위험을 숫자로 관리해야 해서 → 확률과 통계적 추론을 배워요.
+대수: 복리 수익률을 계산해야 해서 → 지수·로그 함수와 수열을 배워요.
+영어 I: 해외 시장 정보를 직접 읽어야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2710,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>정보, 인공지능 기초, 금융과 경제생활, 실용 통계, 인공지능 수학</t>
+          <t>정보, 인공지능 기초, 금융과 경제생활, 실용 통계, 인공지능 수학, 확률과 통계, 대수, 영어 I</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2567,7 +2724,10 @@
 인공지능 기초: 신용 평가·이상거래 탐지에 AI를 써서 → 인공지능의 원리와 활용을 배워요.
 금융과 경제생활: 결제·대출·투자 서비스를 설계해서 → 금융 제도와 금융상품을 배워요.
 실용 통계: 금융 빅데이터를 분석해야 해서 → 자료 분석과 통계적 해석을 배워요.
-인공지능 수학: 금융 AI 모델을 이해해야 해서 → 인공지능에 쓰이는 수학을 배워요.</t>
+인공지능 수학: 금융 AI 모델을 이해해야 해서 → 인공지능에 쓰이는 수학을 배워요.
+확률과 통계: 금융 빅데이터를 분석해야 해서 → 자료 분석과 통계적 추론을 배워요.
+대수: 암호화와 이자 계산에 수학이 쓰여서 → 지수·로그 함수와 수열을 배워요.
+영어 I: 최신 IT 기술 문서가 영어로 되어 있어서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2749,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>물리학, 화학, 생명과학, 지구과학, 융합과학 탐구, 교육의 이해</t>
+          <t>물리학, 화학, 생명과학, 지구과학, 융합과학 탐구, 교육의 이해, 미적분 I, 화법과 언어</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2604,7 +2764,9 @@
 생명과학: 생명 단원을 가르치므로 → 세포·유전·항상성 등 생명 현상을 배워요.
 지구과학: 지구·우주 단원도 가르쳐서 → 지구의 변화와 우주의 원리를 배워요.
 융합과학 탐구: 학생 탐구 활동을 지도해야 해서 → 탐구 설계와 실험·자료 분석을 해 봐요.
-교육의 이해: 학생을 가르치는 직업이라 → 교육의 의미와 학습 원리를 배워요.</t>
+교육의 이해: 학생을 가르치는 직업이라 → 교육의 의미와 학습 원리를 배워요.
+미적분 I: 과학 공식을 수학으로 설명해야 해서 → 변화율과 미분의 원리를 배워요.
+화법과 언어: 어려운 개념을 쉽게 가르쳐야 해서 → 알기 쉽게 설명하는 말하기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2788,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>교육의 이해, 인간과 심리, 사회와 문화, 실용 통계, 직무 의사소통</t>
+          <t>교육의 이해, 인간과 심리, 사회와 문화, 실용 통계, 직무 의사소통, 화법과 언어, 확률과 통계, 독서와 작문</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2640,7 +2802,10 @@
 인간과 심리: 학생의 성향과 고민을 파악해야 해서 → 발달·동기·상담 심리를 배워요.
 사회와 문화: 교육은 사회 변화와 맞물려 있어서 → 사회 구조와 교육 문제를 탐구해요.
 실용 통계: 입시·성적 자료를 분석해야 해서 → 자료 정리와 통계 해석을 배워요.
-직무 의사소통: 상담과 설명회가 주된 업무라서 → 상담·발표 등 직무 말하기를 배워요.</t>
+직무 의사소통: 상담과 설명회가 주된 업무라서 → 상담·발표 등 직무 말하기를 배워요.
+화법과 언어: 학생·학부모와 상담해야 해서 → 공감하며 설명하는 대화법을 배워요.
+확률과 통계: 입시 자료와 성적을 분석해야 해서 → 자료를 정리하고 해석하는 법을 배워요.
+독서와 작문: 교육 계획서와 자기소개서를 다뤄야 해서 → 목적에 맞게 글 쓰고 고치는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2827,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>교육의 이해, 매체 의사소통, 미술과 매체, 소프트웨어와 생활, 인간과 심리</t>
+          <t>교육의 이해, 매체 의사소통, 미술과 매체, 소프트웨어와 생활, 인간과 심리, 독서와 작문, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2676,7 +2841,10 @@
 매체 의사소통: 영상·온라인으로 내용을 전달해서 → 매체 자료를 분석하고 만드는 법을 배워요.
 미술과 매체: 보기 좋은 화면과 자료가 중요해서 → 디지털 매체로 시각 표현을 해 봐요.
 소프트웨어와 생활: 디지털 학습 도구를 다뤄서 → 소프트웨어로 문제 해결하는 법을 배워요.
-인간과 심리: 학습자의 흥미와 이해를 고려해서 → 동기·인지 등 사람의 심리를 배워요.</t>
+인간과 심리: 학습자의 흥미와 이해를 고려해서 → 동기·인지 등 사람의 심리를 배워요.
+독서와 작문: 교재와 강의 원고를 써야 해서 → 읽는 사람을 고려한 글쓰기를 배워요.
+화법과 언어: 강의 영상의 말을 다듬어야 해서 → 알기 쉽게 설명하는 말하기를 배워요.
+영어 I: 해외 교육 콘텐츠를 참고해야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2866,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>교육의 이해, 인간과 심리, 미술과 매체, 수학과 문화</t>
+          <t>교육의 이해, 인간과 심리, 미술과 매체, 수학과 문화, 독서와 작문, 대수, 문학</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2711,7 +2879,10 @@
           <t>교육의 이해: 학습 원리에 맞는 교재를 만들어서 → 교육과 학습의 원리를 배워요.
 인간과 심리: 아이의 발달 수준을 고려해야 해서 → 발달과 인지 심리를 배워요.
 미술과 매체: 교구 디자인과 시각 자료가 중요해서 → 다양한 매체로 조형 표현을 해 봐요.
-수학과 문화: 수학 교구를 많이 개발하므로 → 생활·문화 속 수학 원리를 탐구해요.</t>
+수학과 문화: 수학 교구를 많이 개발하므로 → 생활·문화 속 수학 원리를 탐구해요.
+독서와 작문: 교재의 설명 글을 써야 해서 → 쉽고 정확한 글쓰기를 배워요.
+대수: 수학 교구의 원리를 설계해야 해서 → 식과 함수, 수열의 원리를 배워요.
+문학: 동화·이야기로 교재를 꾸미기도 해서 → 이야기의 구성과 표현을 배워요.</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2904,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>교육의 이해, 인간과 심리, 직무 의사소통, 실용 통계, 사회와 문화</t>
+          <t>교육의 이해, 인간과 심리, 직무 의사소통, 실용 통계, 사회와 문화, 화법과 언어, 확률과 통계, 독서와 작문</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2747,7 +2918,10 @@
 인간과 심리: 직원의 동기와 성장을 도와야 해서 → 동기·학습·대인관계 심리를 배워요.
 직무 의사소통: 강의와 발표를 자주 진행해서 → 직장 내 발표·소통 방법을 배워요.
 실용 통계: 교육 효과를 설문으로 평가해서 → 자료 수집과 통계 분석을 배워요.
-사회와 문화: 조직 문화와 변화를 이해해야 해서 → 집단·조직과 사회 변화를 탐구해요.</t>
+사회와 문화: 조직 문화와 변화를 이해해야 해서 → 집단·조직과 사회 변화를 탐구해요.
+화법과 언어: 직원 앞에서 강의하고 진행해야 해서 → 청중을 이끄는 발표 방법을 배워요.
+확률과 통계: 교육 효과를 자료로 평가해야 해서 → 자료를 정리하고 분석하는 법을 배워요.
+독서와 작문: 교육 프로그램 기획서를 써야 해서 → 논리적으로 설득하는 글쓰기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2943,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>미술 감상과 비평, 미술과 매체, 교육의 이해, 인간과 심리</t>
+          <t>미술 감상과 비평, 미술과 매체, 교육의 이해, 인간과 심리, 화법과 언어, 문학</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2782,7 +2956,9 @@
           <t>미술 감상과 비평: 작품 감상 수업을 해야 해서 → 작품을 보고 해석·비평하는 법을 배워요.
 미술과 매체: 다양한 재료와 디지털 표현을 가르쳐서 → 여러 매체를 활용한 표현을 배워요.
 교육의 이해: 학생을 가르치는 직업이라 → 교육의 의미와 학습 원리를 배워요.
-인간과 심리: 학생의 감정과 표현을 이해해야 해서 → 사람의 마음과 발달을 배워요.</t>
+인간과 심리: 학생의 감정과 표현을 이해해야 해서 → 사람의 마음과 발달을 배워요.
+화법과 언어: 작품을 감상하고 설명해 줘야 해서 → 알기 쉽게 설명하는 말하기를 배워요.
+문학: 그림과 이야기를 연결한 수업을 해서 → 작품을 해석하고 감상하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2980,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>미술 감상과 비평, 미술과 매체, 교육의 이해, 세계사, 직무 의사소통</t>
+          <t>미술 감상과 비평, 미술과 매체, 교육의 이해, 세계사, 직무 의사소통, 화법과 언어, 영어 I, 독서와 작문</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2818,7 +2994,10 @@
 미술과 매체: 체험 활동과 전시 매체를 다뤄서 → 다양한 매체의 미술 표현을 배워요.
 교육의 이해: 관람객 대상 교육을 설계해서 → 교육의 원리와 방법을 배워요.
 세계사: 작품의 시대 배경을 알아야 해서 → 세계 여러 지역의 역사를 배워요.
-직무 의사소통: 관람객 앞에서 설명하는 일이 많아서 → 직무 상황의 말하기를 배워요.</t>
+직무 의사소통: 관람객 앞에서 설명하는 일이 많아서 → 직무 상황의 말하기를 배워요.
+화법과 언어: 관람객에게 작품을 해설해야 해서 → 듣는 사람에 맞춘 말하기를 배워요.
+영어 I: 외국인 관람객에게도 안내해야 해서 → 기본 영어 의사소통을 배워요.
+독서와 작문: 교육 프로그램 자료를 만들어야 해서 → 쉽고 정확한 글쓰기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -2840,7 +3019,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>교육의 이해, 인간과 심리, 직무 의사소통</t>
+          <t>교육의 이해, 인간과 심리, 직무 의사소통, 화법과 언어, 스포츠 생활1, 독서와 작문</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2852,7 +3031,10 @@
         <is>
           <t>교육의 이해: 학생을 직접 가르치는 일이라 → 교육과 학습의 원리를 배워요.
 인간과 심리: 다양한 학생의 흥미를 끌어야 해서 → 동기와 발달 심리를 배워요.
-직무 의사소통: 수업 안내와 학부모 상담을 해서 → 직무 상황의 말하기·글쓰기를 배워요.</t>
+직무 의사소통: 수업 안내와 학부모 상담을 해서 → 직무 상황의 말하기·글쓰기를 배워요.
+화법과 언어: 학생들에게 알기 쉽게 설명해야 해서 → 상대에 맞춘 설명과 말하기를 배워요.
+스포츠 생활1: 예체능 프로그램을 맡을 수도 있어서 → 여러 운동을 익히고 체력을 길러요.
+독서와 작문: 수업 계획서와 활동지를 만들어야 해서 → 목적에 맞는 글쓰기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -2874,7 +3056,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>주제 탐구 독서, 독서 토론과 글쓰기, 교육의 이해, 정보, 매체 의사소통</t>
+          <t>주제 탐구 독서, 독서 토론과 글쓰기, 교육의 이해, 정보, 매체 의사소통, 문학, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2888,7 +3070,10 @@
 독서 토론과 글쓰기: 독서 토론 활동을 이끌어서 → 읽고 토론하고 쓰는 법을 배워요.
 교육의 이해: 학생을 가르치는 교사라서 → 교육의 의미와 학습 원리를 배워요.
 정보: 도서관 자료를 디지털로 관리해서 → 자료 처리와 정보 활용을 배워요.
-매체 의사소통: 정보 활용·미디어 교육을 해서 → 매체 정보를 비판적으로 읽는 법을 배워요.</t>
+매체 의사소통: 정보 활용·미디어 교육을 해서 → 매체 정보를 비판적으로 읽는 법을 배워요.
+문학: 학생에게 좋은 책을 추천해야 해서 → 문학 작품을 해석하고 감상하는 법을 배워요.
+화법과 언어: 독서 수업과 토론을 이끌어야 해서 → 토론을 진행하는 말하기를 배워요.
+영어 I: 영어 원서와 자료도 다뤄야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -2910,7 +3095,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>사회와 문화, 정치, 경제, 법과 사회, 세계시민과 지리, 교육의 이해</t>
+          <t>사회와 문화, 정치, 경제, 법과 사회, 세계시민과 지리, 교육의 이해, 화법과 언어, 확률과 통계</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2925,7 +3110,9 @@
 경제: 경제 단원을 가르쳐서 → 시장과 국민 경제의 원리를 배워요.
 법과 사회: 법 단원을 가르치므로 → 헌법과 생활 속 법을 배워요.
 세계시민과 지리: 지리와 세계 문제도 가르쳐서 → 세계의 지역과 지구촌 문제를 배워요.
-교육의 이해: 학생을 가르치는 직업이라 → 교육의 의미와 학습 원리를 배워요.</t>
+교육의 이해: 학생을 가르치는 직업이라 → 교육의 의미와 학습 원리를 배워요.
+화법과 언어: 사회 개념을 쉽게 설명해야 해서 → 알기 쉽게 설명하는 말하기를 배워요.
+확률과 통계: 사회 통계 자료를 가르쳐야 해서 → 통계 자료를 바르게 해석하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -2947,7 +3134,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>미적분Ⅱ, 기하, 수학과제 탐구, 실용 통계, 교육의 이해</t>
+          <t>미적분Ⅱ, 기하, 수학과제 탐구, 실용 통계, 교육의 이해, 대수, 미적분 I, 확률과 통계</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2961,7 +3148,10 @@
 기하: 도형·벡터 단원을 가르쳐서 → 이차곡선·벡터·공간도형을 배워요.
 수학과제 탐구: 학생 수학 탐구를 지도해야 해서 → 수학 과제를 탐구·발표하는 법을 배워요.
 실용 통계: 통계 단원과 성적 분석에 필요해서 → 자료 분석과 통계적 추론을 배워요.
-교육의 이해: 학생을 가르치는 직업이라 → 교육의 의미와 학습 원리를 배워요.</t>
+교육의 이해: 학생을 가르치는 직업이라 → 교육의 의미와 학습 원리를 배워요.
+대수: 고등 수학의 기초 개념을 가르쳐야 해서 → 지수·로그·삼각함수·수열을 배워요.
+미적분 I: 미분과 적분을 가르쳐야 해서 → 극한, 미분, 적분의 원리를 배워요.
+확률과 통계: 확률과 통계를 가르쳐야 해서 → 경우의 수, 확률, 통계를 배워요.</t>
         </is>
       </c>
     </row>
@@ -2983,7 +3173,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>언어생활 탐구, 직무 의사소통, 독서 토론과 글쓰기, 매체 의사소통, 인간과 심리</t>
+          <t>언어생활 탐구, 직무 의사소통, 독서 토론과 글쓰기, 매체 의사소통, 인간과 심리, 화법과 언어, 문학, 스포츠 생활1</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2997,7 +3187,10 @@
 직무 의사소통: 면접·발표 코칭을 많이 해서 → 직무 상황의 말하기 전략을 배워요.
 독서 토론과 글쓰기: 논리적으로 말하는 힘이 필요해서 → 토론과 논리적 글쓰기를 배워요.
 매체 의사소통: 영상·온라인 발표도 지도해서 → 매체를 활용한 표현과 소통을 배워요.
-인간과 심리: 발표 불안을 다뤄 줘야 해서 → 감정·불안 등 사람의 심리를 배워요.</t>
+인간과 심리: 발표 불안을 다뤄 줘야 해서 → 감정·불안 등 사람의 심리를 배워요.
+화법과 언어: 효과적인 말하기를 가르쳐야 해서 → 말하기 전략과 국어의 말소리를 배워요.
+문학: 감동을 주는 연설 표현이 필요해서 → 비유와 표현 기법을 배워요.
+스포츠 생활1: 오랜 강의를 버틸 체력이 필요해서 → 꾸준한 운동으로 체력을 길러요.</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3212,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>인간과 심리, 교육의 이해, 생명과학, 사회와 문화, 실용 통계</t>
+          <t>인간과 심리, 교육의 이해, 생명과학, 사회와 문화, 실용 통계, 화법과 언어, 확률과 통계, 문학</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3033,7 +3226,10 @@
 교육의 이해: 놀이·교육 프로그램을 계획해서 → 교육과 학습의 원리를 배워요.
 생명과학: 뇌와 신체 발달을 이해해야 해서 → 사람 몸과 신경계의 기초를 배워요.
 사회와 문화: 가족·사회 환경이 발달에 영향을 줘서 → 가족과 사회화 과정을 탐구해요.
-실용 통계: 발달 검사 결과를 해석해야 해서 → 자료 분석과 통계 해석을 배워요.</t>
+실용 통계: 발달 검사 결과를 해석해야 해서 → 자료 분석과 통계 해석을 배워요.
+화법과 언어: 아이의 언어 발달을 살펴야 해서 → 말소리와 언어 습득의 원리를 배워요.
+확률과 통계: 발달 검사 결과를 해석해야 해서 → 검사 점수와 자료를 해석하는 법을 배워요.
+문학: 동화로 아이 정서를 도울 수 있어서 → 이야기를 해석하고 감상하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3251,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>심화 영어, 심화 영어 독해와 작문, 영어 발표와 토론, 실생활 영어 회화, 교육의 이해</t>
+          <t>심화 영어, 심화 영어 독해와 작문, 영어 발표와 토론, 실생활 영어 회화, 교육의 이해, 영어 I, 영어Ⅱ, 화법과 언어</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3069,7 +3265,10 @@
 심화 영어 독해와 작문: 독해·작문 수업을 맡아서 → 긴 글 읽기와 영어 글쓰기를 배워요.
 영어 발표와 토론: 말하기 수업을 진행해서 → 영어로 발표·토론하는 법을 배워요.
 실생활 영어 회화: 회화 수업이 많아서 → 생활 속 영어 회화를 연습해요.
-교육의 이해: 가르치는 일이 핵심이라 → 교육과 학습의 원리를 배워요.</t>
+교육의 이해: 가르치는 일이 핵심이라 → 교육과 학습의 원리를 배워요.
+영어 I: 영어 기본기를 탄탄히 가르쳐야 해서 → 영어 어휘와 문장 구조를 배워요.
+영어Ⅱ: 수준 높은 영어 수업을 해야 해서 → 더 다양한 영어 표현과 독해를 배워요.
+화법과 언어: 학생 눈높이에 맞게 설명해야 해서 → 알기 쉽게 설명하는 말하기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3290,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>세계사, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 한문, 교육의 이해</t>
+          <t>세계사, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 한문, 교육의 이해, 화법과 언어, 독서와 작문, 문학</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3105,7 +3304,10 @@
 동아시아 역사 기행: 한·중·일 관계사를 다뤄서 → 동아시아의 교류와 갈등을 탐구해요.
 역사로 탐구하는 현대 세계: 오늘의 문제를 역사로 설명해서 → 현대 세계의 형성 과정을 배워요.
 한문: 옛 사료를 읽어야 할 때가 많아서 → 한자와 한문 문장의 기초를 배워요.
-교육의 이해: 학생을 가르치는 직업이라 → 교육의 의미와 학습 원리를 배워요.</t>
+교육의 이해: 학생을 가르치는 직업이라 → 교육의 의미와 학습 원리를 배워요.
+화법과 언어: 역사 이야기를 흥미롭게 들려줘야 해서 → 청중을 사로잡는 말하기를 배워요.
+독서와 작문: 사료를 읽고 수업 자료를 만들어야 해서 → 자료를 읽고 정리하는 글쓰기를 배워요.
+문학: 작품으로 시대 분위기를 전하기도 해서 → 작품 속 시대 배경을 해석하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3329,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>화학, 생명과학, 세포와 물질대사, 운동과 건강, 교육의 이해</t>
+          <t>화학, 생명과학, 세포와 물질대사, 운동과 건강, 교육의 이해, 확률과 통계, 화법과 언어, 대수</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3141,7 +3343,10 @@
 생명과학: 소화·흡수와 건강을 다뤄서 → 사람 몸의 구조와 기능을 배워요.
 세포와 물질대사: 영양소가 에너지로 쓰이는 과정을 알아야 해서 → 세포 호흡과 물질대사를 배워요.
 운동과 건강: 건강한 생활 습관을 교육해서 → 운동·영양과 건강 관리를 배워요.
-교육의 이해: 식생활 교육을 하는 교사라서 → 교육의 의미와 학습 원리를 배워요.</t>
+교육의 이해: 식생활 교육을 하는 교사라서 → 교육의 의미와 학습 원리를 배워요.
+확률과 통계: 학생들의 영양 섭취 자료를 분석해야 해서 → 자료를 정리하고 해석하는 법을 배워요.
+화법과 언어: 학생들에게 식생활 교육을 해야 해서 → 알기 쉽게 설명하는 말하기를 배워요.
+대수: 식단의 열량과 영양소를 계산해야 해서 → 식과 비율로 수량을 계산하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3368,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>심화 영어, 영미 문학 읽기, 심화 영어 독해와 작문, 영어 발표와 토론, 교육의 이해</t>
+          <t>심화 영어, 영미 문학 읽기, 심화 영어 독해와 작문, 영어 발표와 토론, 교육의 이해, 영어 I, 영어Ⅱ, 영어 독해와 작문</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3177,7 +3382,10 @@
 영미 문학 읽기: 영어 문학 작품도 가르쳐서 → 영미 소설·시를 읽고 감상해요.
 심화 영어 독해와 작문: 독해·작문 수업을 맡아서 → 긴 글 읽기와 영어 글쓰기를 배워요.
 영어 발표와 토론: 말하기 수업을 지도해서 → 영어로 발표·토론하는 법을 배워요.
-교육의 이해: 학생을 가르치는 직업이라 → 교육의 의미와 학습 원리를 배워요.</t>
+교육의 이해: 학생을 가르치는 직업이라 → 교육의 의미와 학습 원리를 배워요.
+영어 I: 영어의 기본 문법과 어휘를 가르쳐야 해서 → 영어 어휘와 문장 구조를 배워요.
+영어Ⅱ: 수준 높은 영어 독해를 가르쳐야 해서 → 더 다양한 영어 표현과 독해를 배워요.
+영어 독해와 작문: 학생들의 영어 글쓰기를 지도해야 해서 → 영어 글을 읽고 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3407,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>일본어, 중국어, 일본어 회화, 중국어 회화, 일본 문화, 중국 문화</t>
+          <t>일본어, 중국어, 일본어 회화, 중국어 회화, 일본 문화, 중국 문화, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3214,7 +3422,9 @@
 일본어 회화: 말하기 수업을 지도해야 해서 → 실제 상황의 일본어 회화를 익혀요.
 중국어 회화: 말하기 수업을 지도해야 해서 → 실제 상황의 중국어 회화를 익혀요.
 일본 문화: 언어와 함께 문화도 가르쳐서 → 일본의 생활과 문화를 배워요.
-중국 문화: 언어와 함께 문화도 가르쳐서 → 중국의 생활과 문화를 배워요.</t>
+중국 문화: 언어와 함께 문화도 가르쳐서 → 중국의 생활과 문화를 배워요.
+화법과 언어: 외국어와 국어를 비교해 가르쳐야 해서 → 국어의 문법과 말소리 원리를 배워요.
+영어 I: 외국어 교재와 자료를 폭넓게 봐야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3446,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>심화 영어 독해와 작문, 세계 문화와 영어, 실생활 영어 회화, 세계시민과 지리, 직무 의사소통</t>
+          <t>심화 영어 독해와 작문, 세계 문화와 영어, 실생활 영어 회화, 세계시민과 지리, 직무 의사소통, 영어 I, 영어Ⅱ, 영어 독해와 작문</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3250,7 +3460,10 @@
 세계 문화와 영어: 나라별 교육·문화를 안내해서 → 영어로 세계 여러 문화를 배워요.
 실생활 영어 회화: 해외 학교와 연락을 주고받아서 → 실용적인 영어 회화를 연습해요.
 세계시민과 지리: 유학 국가 정보를 알려 줘야 해서 → 세계 여러 지역의 특징을 배워요.
-직무 의사소통: 학생·학부모 상담이 주 업무라서 → 상담·설명하는 말하기를 배워요.</t>
+직무 의사소통: 학생·학부모 상담이 주 업무라서 → 상담·설명하는 말하기를 배워요.
+영어 I: 해외 학교와 영어로 연락해야 해서 → 기본 영어 의사소통을 배워요.
+영어Ⅱ: 해외 학교 입학 요강을 읽어야 해서 → 더 다양한 영어 표현과 독해를 배워요.
+영어 독해와 작문: 영어 에세이 첨삭을 도와야 해서 → 영어 글을 읽고 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3485,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>음악 감상과 비평, 음악과 미디어, 교육의 이해</t>
+          <t>음악 감상과 비평, 음악과 미디어, 교육의 이해, 문학, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -3284,7 +3497,10 @@
         <is>
           <t>음악 감상과 비평: 감상 수업을 진행해야 해서 → 음악을 듣고 해석·비평하는 법을 배워요.
 음악과 미디어: 디지털 음악 수업도 늘고 있어서 → 미디어를 활용한 음악 제작을 배워요.
-교육의 이해: 학생을 가르치는 직업이라 → 교육의 의미와 학습 원리를 배워요.</t>
+교육의 이해: 학생을 가르치는 직업이라 → 교육의 의미와 학습 원리를 배워요.
+문학: 노랫말과 시를 함께 다뤄야 해서 → 시의 운율과 표현을 배워요.
+화법과 언어: 음악을 쉽게 설명해야 해서 → 알기 쉽게 설명하는 말하기를 배워요.
+영어 I: 외국 노래와 음악 자료를 다뤄야 해서 → 기본 영어 표현과 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3522,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>인간과 심리, 교육의 이해, 사회와 문화, 실용 통계</t>
+          <t>인간과 심리, 교육의 이해, 사회와 문화, 실용 통계, 화법과 언어, 문학, 확률과 통계</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -3319,7 +3535,10 @@
           <t>인간과 심리: 학생의 마음을 이해하는 일이라 → 정서·성격·상담 심리를 배워요.
 교육의 이해: 학교 안에서 일하는 교사라서 → 교육의 의미와 학교 제도를 배워요.
 사회와 문화: 가정·또래 환경이 고민에 영향을 줘서 → 가족·집단과 사회 문제를 탐구해요.
-실용 통계: 심리검사 결과를 해석해야 해서 → 자료 분석과 통계 해석을 배워요.</t>
+실용 통계: 심리검사 결과를 해석해야 해서 → 자료 분석과 통계 해석을 배워요.
+화법과 언어: 학생의 마음을 듣고 상담해야 해서 → 공감하며 대화하는 방법을 배워요.
+문학: 작품으로 마음을 돌보는 상담도 해서 → 작품 속 인물의 감정을 해석하는 법을 배워요.
+확률과 통계: 심리 검사 결과를 해석해야 해서 → 검사 점수와 자료를 해석하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3560,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>정보, 인공지능 기초, 소프트웨어와 생활, 인공지능 수학, 교육의 이해</t>
+          <t>정보, 인공지능 기초, 소프트웨어와 생활, 인공지능 수학, 교육의 이해, 대수, 확률과 통계, 영어 I</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -3355,7 +3574,10 @@
 인공지능 기초: AI 교육이 강조되고 있어서 → 인공지능의 원리와 활용을 배워요.
 소프트웨어와 생활: 생활 속 문제 해결을 지도해서 → 소프트웨어로 문제를 해결해 봐요.
 인공지능 수학: AI의 원리를 설명해야 해서 → 인공지능에 쓰이는 수학을 배워요.
-교육의 이해: 학생을 가르치는 직업이라 → 교육의 의미와 학습 원리를 배워요.</t>
+교육의 이해: 학생을 가르치는 직업이라 → 교육의 의미와 학습 원리를 배워요.
+대수: 알고리즘에 수학적 사고가 필요해서 → 수열과 함수, 수학적 귀납법을 배워요.
+확률과 통계: 인공지능과 데이터를 가르쳐야 해서 → 자료 분석과 확률의 원리를 배워요.
+영어 I: 프로그래밍 자료가 영어로 되어 있어서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3599,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>운동과 건강, 생명과학, 교육의 이해, 인간과 심리</t>
+          <t>운동과 건강, 생명과학, 교육의 이해, 인간과 심리, 스포츠 생활1, 스포츠 과학, 스포츠 문화</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3390,7 +3612,10 @@
           <t>운동과 건강: 체육 수업의 핵심이라 → 운동 방법과 건강 관리를 배워요.
 생명과학: 운동할 때 몸의 변화를 알아야 해서 → 근육·호흡·순환 등 몸의 원리를 배워요.
 교육의 이해: 학생을 가르치는 직업이라 → 교육의 의미와 학습 원리를 배워요.
-인간과 심리: 학생의 의욕과 협동을 이끌어야 해서 → 동기와 대인관계 심리를 배워요.</t>
+인간과 심리: 학생의 의욕과 협동을 이끌어야 해서 → 동기와 대인관계 심리를 배워요.
+스포츠 생활1: 여러 종목을 직접 시범 보여야 해서 → 다양한 운동 기능을 익혀요.
+스포츠 과학: 운동을 과학적으로 지도해야 해서 → 운동과 신체 원리를 배워요.
+스포츠 문화: 스포츠의 가치를 가르쳐야 해서 → 스포츠의 역사와 문화를 배워요.</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3637,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>교육의 이해, 인간과 심리, 주제 탐구 독서, 수학과 문화, 융합과학 탐구</t>
+          <t>교육의 이해, 인간과 심리, 주제 탐구 독서, 수학과 문화, 융합과학 탐구, 화법과 언어, 문학, 스포츠 생활1</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -3426,7 +3651,10 @@
 인간과 심리: 어린이의 발달을 이해해야 해서 → 발달·정서 심리를 배워요.
 주제 탐구 독서: 국어·독서 지도를 맡아서 → 주제를 정해 깊이 읽는 법을 배워요.
 수학과 문화: 수학을 쉽고 재미있게 가르쳐야 해서 → 생활·문화 속 수학을 탐구해요.
-융합과학 탐구: 과학 실험·탐구 수업도 해서 → 탐구 설계와 실험 활동을 경험해요.</t>
+융합과학 탐구: 과학 실험·탐구 수업도 해서 → 탐구 설계와 실험 활동을 경험해요.
+화법과 언어: 어린이 눈높이로 설명해야 해서 → 상대에 맞춘 말하기를 배워요.
+문학: 국어 시간에 동시와 동화를 가르쳐서 → 문학 작품을 해석하고 감상하는 법을 배워요.
+스포츠 생활1: 체육 수업도 직접 맡아야 해서 → 여러 운동을 익히고 체력을 길러요.</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3676,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>교육의 이해, 인간과 심리, 생명과학, 사회와 문화</t>
+          <t>교육의 이해, 인간과 심리, 생명과학, 사회와 문화, 화법과 언어, 스포츠 생활1, 독서와 작문</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -3461,7 +3689,10 @@
           <t>교육의 이해: 개별화 교육을 설계해야 해서 → 교육의 원리와 방법을 배워요.
 인간과 심리: 학생의 행동과 정서를 이해해야 해서 → 발달·행동 심리를 배워요.
 생명과학: 장애의 원인과 신체 특성을 알아야 해서 → 사람 몸과 신경계의 기초를 배워요.
-사회와 문화: 장애인 인권과 통합 교육을 다뤄서 → 사회적 소수자와 차별 문제를 탐구해요.</t>
+사회와 문화: 장애인 인권과 통합 교육을 다뤄서 → 사회적 소수자와 차별 문제를 탐구해요.
+화법과 언어: 학생 특성에 맞춰 소통해야 해서 → 상대에 맞춘 말하기와 대화법을 배워요.
+스포츠 생활1: 학생의 신체 활동을 도와야 해서 → 여러 운동을 익히고 체력을 길러요.
+독서와 작문: 개별 교육 계획서를 써야 해서 → 정확하고 체계적인 글쓰기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3714,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>교육의 이해, 사회와 문화, 인간과 심리, 직무 의사소통, 실용 통계</t>
+          <t>교육의 이해, 사회와 문화, 인간과 심리, 직무 의사소통, 실용 통계, 화법과 언어, 독서와 작문, 확률과 통계</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -3497,7 +3728,10 @@
 사회와 문화: 지역 사회의 요구를 파악해야 해서 → 사회 구조와 사회 변화를 탐구해요.
 인간과 심리: 성인 학습자의 동기를 이해해야 해서 → 학습 동기와 발달 심리를 배워요.
 직무 의사소통: 홍보·안내·회의가 많아서 → 직무 상황의 말하기·글쓰기를 배워요.
-실용 통계: 수요 조사와 만족도를 분석해서 → 설문 자료 분석 방법을 배워요.</t>
+실용 통계: 수요 조사와 만족도를 분석해서 → 설문 자료 분석 방법을 배워요.
+화법과 언어: 주민 앞에서 프로그램을 안내해야 해서 → 상황에 맞는 발표와 말하기를 배워요.
+독서와 작문: 프로그램 기획서와 보고서를 써야 해서 → 논리적으로 정리하는 글쓰기를 배워요.
+확률과 통계: 수요 조사와 만족도를 분석해야 해서 → 자료를 정리하고 해석하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3753,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>인간과 심리, 교육의 이해, 언어생활 탐구, 생명과학</t>
+          <t>인간과 심리, 교육의 이해, 언어생활 탐구, 생명과학, 화법과 언어, 대수, 독서와 작문</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -3532,7 +3766,10 @@
           <t>인간과 심리: 아동의 인지·정서 특성을 파악해서 → 인지·발달 심리를 배워요.
 교육의 이해: 맞춤 학습 계획을 세워야 해서 → 교육과 학습의 원리를 배워요.
 언어생활 탐구: 읽기·쓰기 지도가 많아서 → 국어의 말소리·글자·문법을 탐구해요.
-생명과학: 뇌 발달과 학습의 관계를 알아야 해서 → 신경계 등 몸의 원리를 배워요.</t>
+생명과학: 뇌 발달과 학습의 관계를 알아야 해서 → 신경계 등 몸의 원리를 배워요.
+화법과 언어: 읽기·말하기의 어려움을 살펴야 해서 → 말소리와 문법의 원리를 배워요.
+대수: 셈하기를 단계별로 가르쳐야 해서 → 수와 식의 원리를 체계적으로 배워요.
+독서와 작문: 읽기·쓰기 지도법을 알아야 해서 → 읽기와 글쓰기의 과정을 배워요.</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3791,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>교육의 이해, 직무 의사소통, 인간과 심리</t>
+          <t>교육의 이해, 직무 의사소통, 인간과 심리, 화법과 언어, 미적분 I, 영어 I</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -3566,7 +3803,10 @@
         <is>
           <t>교육의 이해: 가르치는 일이 핵심이라 → 교육과 학습의 원리를 배워요.
 직무 의사소통: 수업 설명과 학부모 상담을 해서 → 직무 상황의 말하기·글쓰기를 배워요.
-인간과 심리: 학생의 의욕을 높여야 해서 → 학습 동기와 발달 심리를 배워요.</t>
+인간과 심리: 학생의 의욕을 높여야 해서 → 학습 동기와 발달 심리를 배워요.
+화법과 언어: 학생을 집중시키는 강의가 필요해서 → 알기 쉽게 설명하는 말하기를 배워요.
+미적분 I: 입시 수학을 가르칠 수 있어서 → 극한, 미분, 적분의 원리를 배워요.
+영어 I: 입시 영어를 가르칠 수 있어서 → 영어 어휘와 문장 구조를 배워요.</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3828,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 생명과학 실험, 기후변화와 환경생태, 생물의 유전, 화학</t>
+          <t>생명과학, 생명과학 실험, 기후변화와 환경생태, 생물의 유전, 화학, 확률과 통계, 영어 I, 독서와 작문</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -3602,7 +3842,10 @@
 생명과학 실험: 채집·관찰·실험이 일상이라서 → 생물 실험과 관찰 방법을 익혀요.
 기후변화와 환경생태: 곤충 분포가 기후에 따라 변해서 → 기후변화와 생태계 변화를 배워요.
 생물의 유전: 종 분류와 유전 연구를 하므로 → 유전 원리와 유전자 분석을 배워요.
-화학: 살충제·페로몬 등 물질을 다뤄서 → 물질의 성질과 화학 반응을 배워요.</t>
+화학: 살충제·페로몬 등 물질을 다뤄서 → 물질의 성질과 화학 반응을 배워요.
+확률과 통계: 곤충 개체 수를 조사·분석해야 해서 → 표본 조사와 자료 분석을 배워요.
+영어 I: 해외 곤충 연구 논문을 읽어야 해서 → 영어 자료를 읽는 기본 독해를 배워요.
+독서와 작문: 연구 결과를 보고서로 써야 해서 → 근거를 들어 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3867,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>과학의 역사와 문화, 물리학, 융합과학 탐구, 매체 의사소통, 독서 토론과 글쓰기</t>
+          <t>과학의 역사와 문화, 물리학, 융합과학 탐구, 매체 의사소통, 독서 토론과 글쓰기, 화법과 언어, 영어 I, 확률과 통계</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -3638,7 +3881,10 @@
 물리학: 기초 과학 원리를 설명해야 해서 → 힘·에너지 등 자연의 기본 원리를 배워요.
 융합과학 탐구: 여러 분야를 넘나들며 소개해서 → 과학 분야를 융합해 탐구해요.
 매체 의사소통: 영상·SNS로 과학을 알려서 → 매체 콘텐츠를 기획·제작하는 법을 배워요.
-독서 토론과 글쓰기: 과학 글과 대본을 써야 해서 → 읽고 토론하며 글 쓰는 법을 배워요.</t>
+독서 토론과 글쓰기: 과학 글과 대본을 써야 해서 → 읽고 토론하며 글 쓰는 법을 배워요.
+화법과 언어: 강연에서 과학을 쉽게 전해야 해서 → 청중을 사로잡는 말하기를 배워요.
+영어 I: 해외 과학 뉴스를 빠르게 읽어야 해서 → 영어 자료를 읽는 기본 독해를 배워요.
+확률과 통계: 과학 자료와 그래프를 설명해야 해서 → 자료를 바르게 해석하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3906,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>화학, 생명과학, 생물의 유전, 화학 실험, 생명과학 실험, 법과 사회</t>
+          <t>화학, 생명과학, 생물의 유전, 화학 실험, 생명과학 실험, 법과 사회, 확률과 통계, 독서와 작문</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -3675,7 +3921,9 @@
 생물의 유전: DNA로 신원을 확인하므로 → 유전 원리와 DNA 분석 기술을 배워요.
 화학 실험: 정밀한 성분 분석을 해야 해서 → 화학 실험 기법과 안전을 익혀요.
 생명과학 실험: 생체 시료를 실험으로 분석해서 → 생물 실험과 관찰 방법을 익혀요.
-법과 사회: 증거가 재판에 쓰이므로 → 형사 절차와 법의 기본을 배워요.</t>
+법과 사회: 증거가 재판에 쓰이므로 → 형사 절차와 법의 기본을 배워요.
+확률과 통계: DNA 일치 확률 같은 증거를 판단해야 해서 → 확률과 통계적 추론을 배워요.
+독서와 작문: 감정 결과를 보고서로 써야 해서 → 정확하고 객관적인 글쓰기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3945,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 화학, 화학 실험, 생명과학 실험, 실용 통계</t>
+          <t>생명과학, 화학, 화학 실험, 생명과학 실험, 실용 통계, 확률과 통계, 독서와 작문, 스포츠 생활1</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -3711,7 +3959,10 @@
 화학: 잔류 농약과 성분을 검사해서 → 물질의 성질과 화학 반응을 배워요.
 화학 실험: 성분 분석 실험을 하므로 → 화학 실험 기법과 안전을 익혀요.
 생명과학 실험: 병해·미생물을 검사해서 → 생물 실험과 관찰 방법을 익혀요.
-실용 통계: 표본 검사 결과로 판정해서 → 표본 조사와 통계 분석을 배워요.</t>
+실용 통계: 표본 검사 결과로 판정해서 → 표본 조사와 통계 분석을 배워요.
+확률과 통계: 표본으로 농산물 품질을 판정해야 해서 → 표본 조사와 통계적 추정을 배워요.
+독서와 작문: 검사 결과를 보고서로 남겨야 해서 → 정확하고 객관적인 글쓰기를 배워요.
+스포츠 생활1: 산지와 시장을 다니며 검사해야 해서 → 꾸준한 운동으로 체력을 길러요.</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3984,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 생물의 유전, 세포와 물질대사, 화학, 생명과학 실험, 기후변화와 환경생태</t>
+          <t>생명과학, 생물의 유전, 세포와 물질대사, 화학, 생명과학 실험, 기후변화와 환경생태, 확률과 통계, 영어 I</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -3748,7 +3999,9 @@
 세포와 물질대사: 광합성과 생장을 연구해서 → 광합성과 물질대사의 원리를 배워요.
 화학: 비료·토양 성분을 다뤄서 → 물질의 성질과 화학 반응을 배워요.
 생명과학 실험: 재배·실험이 연구의 기본이라 → 생물 실험과 탐구 방법을 익혀요.
-기후변화와 환경생태: 기후에 강한 작물을 개발해서 → 기후변화와 생태계 변화를 배워요.</t>
+기후변화와 환경생태: 기후에 강한 작물을 개발해서 → 기후변화와 생태계 변화를 배워요.
+확률과 통계: 재배 실험 결과를 비교해야 해서 → 자료 분석과 통계적 추론을 배워요.
+영어 I: 해외 농업 논문을 읽어야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -3770,7 +4023,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 화학, 경제, 기후변화와 환경생태, 직무 의사소통</t>
+          <t>생명과학, 화학, 경제, 기후변화와 환경생태, 직무 의사소통, 화법과 언어, 확률과 통계, 대수</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -3784,7 +4037,10 @@
 화학: 비료와 토양 관리를 안내해서 → 물질의 성질과 화학 반응을 배워요.
 경제: 농가 경영과 판로를 조언해서 → 시장과 수요·공급의 원리를 배워요.
 기후변화와 환경생태: 기후 변화에 맞춘 농사가 필요해서 → 기후변화와 생태계를 배워요.
-직무 의사소통: 농민과 상담하는 일이 많아서 → 상담·설명하는 말하기를 배워요.</t>
+직무 의사소통: 농민과 상담하는 일이 많아서 → 상담·설명하는 말하기를 배워요.
+화법과 언어: 농민에게 기술을 쉽게 설명해야 해서 → 알기 쉽게 설명하는 말하기를 배워요.
+확률과 통계: 수확량과 판매 자료를 분석해야 해서 → 자료를 정리하고 해석하는 법을 배워요.
+대수: 농가 수익과 비용을 계산해야 해서 → 식과 함수로 수량을 계산하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -3806,7 +4062,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 도시의 미래 탐구, 기후변화와 환경생태, 교육의 이해</t>
+          <t>생명과학, 도시의 미래 탐구, 기후변화와 환경생태, 교육의 이해, 화법과 언어, 스포츠 생활1, 확률과 통계</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3819,7 +4075,10 @@
           <t>생명과학: 작물을 기르는 원리를 알아야 해서 → 식물의 생장과 생명 현상을 배워요.
 도시의 미래 탐구: 도시 공간을 활용하는 일이라 → 도시 문제와 지속가능한 도시를 탐구해요.
 기후변화와 환경생태: 도시 열섬 등 환경 문제도 다뤄서 → 기후변화와 생태계 변화를 배워요.
-교육의 이해: 시민 대상 교육을 많이 해서 → 교육의 원리와 방법을 배워요.</t>
+교육의 이해: 시민 대상 교육을 많이 해서 → 교육의 원리와 방법을 배워요.
+화법과 언어: 시민 대상 교육을 진행해야 해서 → 알기 쉽게 설명하는 말하기를 배워요.
+스포츠 생활1: 텃밭을 가꾸는 몸 쓰는 일이 많아서 → 꾸준한 운동으로 체력을 길러요.
+확률과 통계: 작물 생육 자료를 정리해야 해서 → 자료를 정리하고 해석하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -3841,7 +4100,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 세포와 물질대사, 생명과학 실험, 기후변화와 환경생태</t>
+          <t>생명과학, 세포와 물질대사, 생명과학 실험, 기후변화와 환경생태, 스포츠 생활1, 화법과 언어, 확률과 통계</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3854,7 +4113,10 @@
           <t>생명과학: 동물의 몸과 행동을 이해해야 해서 → 생물의 구조·기능과 생태를 배워요.
 세포와 물질대사: 먹이와 영양을 관리해야 해서 → 영양소와 물질대사의 원리를 배워요.
 생명과학 실험: 동물을 관찰하고 기록해야 해서 → 생물 관찰과 실험 방법을 익혀요.
-기후변화와 환경생태: 멸종위기종 보전에도 참여해서 → 생태계와 생물 다양성을 배워요.</t>
+기후변화와 환경생태: 멸종위기종 보전에도 참여해서 → 생태계와 생물 다양성을 배워요.
+스포츠 생활1: 동물을 돌보는 힘든 일이 많아서 → 꾸준한 운동으로 체력을 길러요.
+화법과 언어: 관람객에게 동물을 설명해야 해서 → 듣는 사람에 맞춘 말하기를 배워요.
+확률과 통계: 동물의 건강 기록을 관리해야 해서 → 자료를 정리하고 해석하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -3876,7 +4138,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 생태와 환경, 인간과 심리, 운동과 건강</t>
+          <t>생명과학, 생태와 환경, 인간과 심리, 운동과 건강, 스포츠 생활1, 화법과 언어, 스포츠 과학</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3889,7 +4151,10 @@
           <t>생명과학: 숲의 식물과 인체 반응을 알아야 해서 → 생명 현상과 몸의 원리를 배워요.
 생태와 환경: 숲 생태계를 이해해야 해서 → 생태계와 환경 보전을 배워요.
 인간과 심리: 스트레스 해소를 돕는 일이라 → 스트레스와 마음 건강을 배워요.
-운동과 건강: 걷기·체조 등 활동을 지도해서 → 운동과 건강 관리 방법을 배워요.</t>
+운동과 건강: 걷기·체조 등 활동을 지도해서 → 운동과 건강 관리 방법을 배워요.
+스포츠 생활1: 숲길을 걸으며 프로그램을 이끌어야 해서 → 꾸준한 운동으로 체력을 길러요.
+화법과 언어: 참가자의 마음을 편하게 이끌어야 해서 → 공감하며 대화하는 방법을 배워요.
+스포츠 과학: 몸 건강을 돕는 활동을 짜야 해서 → 운동과 신체 원리를 배워요.</t>
         </is>
       </c>
     </row>
@@ -3911,7 +4176,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 생명과학 실험, 생물의 유전, 세포와 물질대사, 화학, 화학 실험</t>
+          <t>생명과학, 생명과학 실험, 생물의 유전, 세포와 물질대사, 화학, 화학 실험, 확률과 통계, 영어 I</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -3926,7 +4191,9 @@
 생물의 유전: 유전자 검사·분석을 많이 해서 → 유전 원리와 유전자 기술을 배워요.
 세포와 물질대사: 세포·효소 실험을 다뤄서 → 세포 구조와 물질대사를 배워요.
 화학: 시약과 용액을 정확히 다뤄야 해서 → 물질의 성질과 화학 반응을 배워요.
-화학 실험: 시료를 분석하는 실험을 해서 → 화학 실험 기법과 안전을 익혀요.</t>
+화학 실험: 시료를 분석하는 실험을 해서 → 화학 실험 기법과 안전을 익혀요.
+확률과 통계: 실험 결과의 신뢰도를 따져야 해서 → 자료 분석과 통계적 추론을 배워요.
+영어 I: 실험 매뉴얼이 영어인 경우가 많아서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -3948,7 +4215,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 생물의 유전, 정보, 실용 통계, 인공지능 기초</t>
+          <t>생명과학, 생물의 유전, 정보, 실용 통계, 인공지능 기초, 확률과 통계, 미적분 I, 영어 독해와 작문</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3962,7 +4229,10 @@
 생물의 유전: 유전체 데이터를 주로 다뤄서 → 유전자와 유전 정보의 원리를 배워요.
 정보: 데이터를 프로그램으로 분석해서 → 프로그래밍과 자료 처리를 배워요.
 실용 통계: 실험 데이터의 의미를 판단해야 해서 → 자료 분석과 통계적 추론을 배워요.
-인공지능 기초: 단백질 구조 예측 등에 AI를 써서 → 인공지능의 원리와 활용을 배워요.</t>
+인공지능 기초: 단백질 구조 예측 등에 AI를 써서 → 인공지능의 원리와 활용을 배워요.
+확률과 통계: 유전체 데이터의 의미를 찾아야 해서 → 확률과 통계적 추론을 배워요.
+미적분 I: 생명 현상을 수학 모델로 다뤄야 해서 → 변화율과 미분의 원리를 배워요.
+영어 독해와 작문: 영어 논문을 읽고 써야 해서 → 영어 글을 읽고 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -3984,7 +4254,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 기후변화와 환경생태, 지구과학, 생명과학 실험, 한국지리 탐구</t>
+          <t>생명과학, 기후변화와 환경생태, 지구과학, 생명과학 실험, 한국지리 탐구, 확률과 통계, 스포츠 생활1, 독서와 작문</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3998,7 +4268,10 @@
 기후변화와 환경생태: 환경 변화가 생태계에 미치는 영향을 알아야 해서 → 기후변화와 생태계 변화를 배워요.
 지구과학: 토양·물·지형을 함께 살펴야 해서 → 지구의 구조와 환경 변화를 배워요.
 생명과학 실험: 현장 조사와 시료 분석을 해서 → 생물 관찰과 실험 방법을 익혀요.
-한국지리 탐구: 우리나라 국토를 대상으로 일해서 → 한국의 지형·기후·환경을 탐구해요.</t>
+한국지리 탐구: 우리나라 국토를 대상으로 일해서 → 한국의 지형·기후·환경을 탐구해요.
+확률과 통계: 생물 분포를 조사·분석해야 해서 → 표본 조사와 자료 분석을 배워요.
+스포츠 생활1: 산과 하천을 다니며 조사해야 해서 → 꾸준한 운동으로 체력을 길러요.
+독서와 작문: 복원 계획서를 써야 해서 → 근거를 들어 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4293,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 기후변화와 환경생태, 생태와 환경, 지구과학, 생명과학 실험, 실용 통계</t>
+          <t>생명과학, 기후변화와 환경생태, 생태와 환경, 지구과학, 생명과학 실험, 실용 통계, 확률과 통계, 영어 독해와 작문</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4035,7 +4308,9 @@
 생태와 환경: 생태계 보전 방안을 고민해야 해서 → 인간과 자연의 관계와 환경 문제를 배워요.
 지구과학: 서식지의 기후·토양·물을 이해해야 해서 → 대기·해양·지각의 기초를 배워요.
 생명과학 실험: 야외 조사와 실험을 직접 해야 해서 → 생물 관찰과 실험 설계를 경험해요.
-실용 통계: 조사 자료로 결론을 내야 하므로 → 자료 정리와 통계적 분석을 배워요.</t>
+실용 통계: 조사 자료로 결론을 내야 하므로 → 자료 정리와 통계적 분석을 배워요.
+확률과 통계: 개체 수 조사로 결론을 내야 해서 → 자료 정리와 통계적 추론을 배워요.
+영어 독해와 작문: 해외 생태 논문을 읽고 써야 해서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4332,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 세포와 물질대사, 생물의 유전, 지구과학, 화학, 생명과학 실험</t>
+          <t>생명과학, 세포와 물질대사, 생물의 유전, 지구과학, 화학, 생명과학 실험, 확률과 통계, 대수</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -4072,7 +4347,9 @@
 생물의 유전: 우수 품종 개량과 질병 연구에 필요해서 → 유전의 원리와 유전자 기술을 배워요.
 지구과학: 바다의 수온·해류가 어장에 영향을 주므로 → 해양과 대기의 기초를 배워요.
 화학: 양식장 수질을 관리해야 해서 → 물질의 성질과 화학 반응의 기초를 배워요.
-생명과학 실험: 시료 채집과 분석을 직접 해야 해서 → 생물 실험 방법과 탐구 설계를 경험해요.</t>
+생명과학 실험: 시료 채집과 분석을 직접 해야 해서 → 생물 실험 방법과 탐구 설계를 경험해요.
+확률과 통계: 어획량·자원량 자료를 분석해서 → 자료 정리와 통계적 추론을 배워요.
+대수: 어류 개체 수 증감을 예측해야 해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4371,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 정보, 인공지능 기초, 화학, 물리학</t>
+          <t>생명과학, 정보, 인공지능 기초, 화학, 물리학, 확률과 통계, 미적분 I</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -4108,7 +4385,9 @@
 정보: 재배 환경을 프로그램으로 제어하므로 → 프로그래밍과 자료 처리를 배워요.
 인공지능 기초: 생육 데이터를 분석해 자동 관리하므로 → 인공지능의 원리와 활용을 배워요.
 화학: 양액과 비료 농도를 맞춰야 해서 → 물질의 성질과 용액의 기초를 배워요.
-물리학: 센서·조명·냉난방 장치를 다루므로 → 빛·전기·열 등 물리의 기초를 배워요.</t>
+물리학: 센서·조명·냉난방 장치를 다루므로 → 빛·전기·열 등 물리의 기초를 배워요.
+확률과 통계: 센서 데이터로 재배 환경을 판단해서 → 자료 정리와 통계적 추론을 배워요.
+미적분 I: 온도·습도 변화를 제어해야 해서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4409,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 세포와 물질대사, 생물의 유전, 화학, 생명과학 실험</t>
+          <t>생명과학, 세포와 물질대사, 생물의 유전, 화학, 생명과학 실험, 확률과 통계, 영어 독해와 작문</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -4144,7 +4423,9 @@
 세포와 물질대사: 병든 식물의 생리 변화를 분석해서 → 세포 구조와 물질대사를 배워요.
 생물의 유전: 병에 강한 품종과 병원균 유전자를 연구해서 → 유전의 원리와 유전자 기술을 배워요.
 화학: 농약과 방제 물질을 다루므로 → 물질의 성질과 화학 반응의 기초를 배워요.
-생명과학 실험: 병원균을 배양하고 진단해야 해서 → 생물 실험 방법과 탐구 설계를 경험해요.</t>
+생명과학 실험: 병원균을 배양하고 진단해야 해서 → 생물 실험 방법과 탐구 설계를 경험해요.
+확률과 통계: 병 발생률과 방제 효과를 비교해서 → 자료 정리와 통계적 추론을 배워요.
+영어 독해와 작문: 해외 병해 연구를 읽고 발표해서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4447,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 생물의 유전, 세포와 물질대사, 생명과학 실험, 실용 통계</t>
+          <t>생명과학, 생물의 유전, 세포와 물질대사, 생명과학 실험, 실용 통계, 확률과 통계, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4180,7 +4461,9 @@
 생물의 유전: 품종 개량의 핵심이 유전이므로 → 유전의 원리와 유전자 기술을 배워요.
 세포와 물질대사: 작물의 성장과 품질을 높여야 해서 → 세포 호흡·광합성 등 물질대사를 배워요.
 생명과학 실험: 교배와 재배 실험을 반복하므로 → 실험 설계와 관찰 방법을 경험해요.
-실용 통계: 품종 비교 결과를 판단해야 해서 → 자료 분석과 통계적 추론을 배워요.</t>
+실용 통계: 품종 비교 결과를 판단해야 해서 → 자료 분석과 통계적 추론을 배워요.
+확률과 통계: 유전 형질이 나타날 확률을 따져서 → 자료 정리와 통계적 추론을 배워요.
+영어Ⅱ: 해외 품종 연구 자료를 읽어야 해서 → 다양한 주제의 영어 글 이해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4485,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>화학, 생명과학, 화학 반응의 세계, 세포와 물질대사, 화학 실험, 법과 사회</t>
+          <t>화학, 생명과학, 화학 반응의 세계, 세포와 물질대사, 화학 실험, 법과 사회, 확률과 통계, 독서와 작문</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -4217,7 +4500,9 @@
 화학 반응의 세계: 식품이 변질되는 원리를 알아야 해서 → 산·염기, 산화·환원 반응을 깊이 배워요.
 세포와 물질대사: 미생물 증식과 영양소 변화를 이해해야 해서 → 세포와 물질대사의 원리를 배워요.
 화학 실험: 시료를 직접 검사·분석하므로 → 실험 기구 사용과 분석 방법을 익혀요.
-법과 사회: 식품 안전 기준과 법규를 적용해서 → 법의 원리와 생활 속 법을 배워요.</t>
+법과 사회: 식품 안전 기준과 법규를 적용해서 → 법의 원리와 생활 속 법을 배워요.
+확률과 통계: 검사 결과로 위해 여부를 판단해서 → 자료 정리와 통계적 추론을 배워요.
+독서와 작문: 안전 기준 보고서를 작성해야 해서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4524,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 화학, 생명과학 실험, 생태와 환경, 미술 감상과 비평</t>
+          <t>생명과학, 화학, 생명과학 실험, 생태와 환경, 미술 감상과 비평, 스포츠 생활1, 확률과 통계</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -4253,7 +4538,9 @@
 화학: 비료와 토양 상태를 관리해야 해서 → 물질의 성질과 화학 반응의 기초를 배워요.
 생명과학 실험: 재배 조건을 바꿔 가며 키워 봐야 해서 → 관찰과 실험 설계를 경험해요.
 생태와 환경: 식물과 주변 환경을 함께 가꾸므로 → 생태계와 환경 문제를 배워요.
-미술 감상과 비평: 정원·꽃 장식의 아름다움을 고려해서 → 조형미를 보는 안목을 길러요.</t>
+미술 감상과 비평: 정원·꽃 장식의 아름다움을 고려해서 → 조형미를 보는 안목을 길러요.
+스포츠 생활1: 야외에서 오래 몸을 쓰는 일이라서 → 꾸준한 운동 습관과 기초 체력을 길러요.
+확률과 통계: 생육 기록으로 재배법을 개선해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4562,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>인간과 심리, 생명과학, 생태와 환경, 사회와 문화</t>
+          <t>인간과 심리, 생명과학, 생태와 환경, 사회와 문화, 화법과 언어, 문학</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -4288,7 +4575,9 @@
           <t>인간과 심리: 대상자의 마음을 이해하고 도와야 해서 → 인간의 마음과 행동의 원리를 배워요.
 생명과학: 치료에 쓸 식물을 잘 길러야 해서 → 식물과 생명 현상의 기초를 배워요.
 생태와 환경: 자연과의 교감이 치유의 바탕이라 → 인간과 자연의 관계를 배워요.
-사회와 문화: 노인·장애인 등 다양한 대상자를 만나서 → 사회 집단과 복지의 기초를 배워요.</t>
+사회와 문화: 노인·장애인 등 다양한 대상자를 만나서 → 사회 집단과 복지의 기초를 배워요.
+화법과 언어: 참여자와 공감하며 대화해야 해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.
+문학: 사람의 마음과 사연을 이해해야 해서 → 작품 속 인물과 삶을 깊이 이해하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4599,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 지구과학, 기후변화와 환경생태, 생태와 환경, 한국지리 탐구</t>
+          <t>생명과학, 지구과학, 기후변화와 환경생태, 생태와 환경, 한국지리 탐구, 스포츠 생활1, 확률과 통계</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -4324,7 +4613,9 @@
 지구과학: 산림의 토양·지형·기후를 알아야 해서 → 지권과 대기의 기초를 배워요.
 기후변화와 환경생태: 숲은 기후변화 대응의 핵심이라 → 기후변화와 생태계 변화를 배워요.
 생태와 환경: 산림 생태계를 보전해야 해서 → 생태계와 환경 문제를 배워요.
-한국지리 탐구: 우리 산지의 특성을 알아야 해서 → 국토의 지형과 기후를 탐구해요.</t>
+한국지리 탐구: 우리 산지의 특성을 알아야 해서 → 국토의 지형과 기후를 탐구해요.
+스포츠 생활1: 산을 오르며 현장 조사를 해서 → 꾸준한 운동 습관과 기초 체력을 길러요.
+확률과 통계: 산림 자원량을 조사·분석해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4637,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>화학, 물질과 에너지, 화학 반응의 세계, 화학 실험, 생명과학</t>
+          <t>화학, 물질과 에너지, 화학 반응의 세계, 화학 실험, 생명과학, 대수, 문학</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -4360,7 +4651,9 @@
 물질과 에너지: 향 성분의 휘발과 혼합을 다루므로 → 물질의 상태와 용액의 성질을 배워요.
 화학 반응의 세계: 향이 변하거나 반응하는 원리를 알아야 해서 → 화학 반응을 깊이 배워요.
 화학 실험: 향료를 직접 배합하고 분석하므로 → 실험 기구 사용과 분석 방법을 익혀요.
-생명과학: 사람이 냄새를 느끼는 원리를 알아야 해서 → 감각과 신경의 기초를 배워요.</t>
+생명과학: 사람이 냄새를 느끼는 원리를 알아야 해서 → 감각과 신경의 기초를 배워요.
+대수: 향료 배합 비율을 정밀히 계산해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
+문학: 향으로 이야기와 감성을 표현해서 → 작품 속 인물과 삶을 깊이 이해하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4675,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>지구과학, 지구시스템과학, 화학, 물리학, 행성우주과학</t>
+          <t>지구과학, 지구시스템과학, 화학, 물리학, 행성우주과학, 미적분 I, 스포츠 생활1</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -4396,7 +4689,9 @@
 지구시스템과학: 지구 내부와 지표의 상호작용을 봐야 해서 → 지구 시스템을 깊이 배워요.
 화학: 암석·광물의 성분을 분석해서 → 원소와 화학 결합의 기초를 배워요.
 물리학: 지진파 등으로 지구 내부를 탐사해서 → 파동과 힘의 기초를 배워요.
-행성우주과학: 다른 행성의 지질과 비교하기도 해서 → 행성과 우주의 구성을 배워요.</t>
+행성우주과학: 다른 행성의 지질과 비교하기도 해서 → 행성과 우주의 구성을 배워요.
+미적분 I: 지층 변화 속도를 계산해야 해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+스포츠 생활1: 산과 들로 야외 답사를 다녀서 → 꾸준한 운동 습관과 기초 체력을 길러요.</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4713,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 생물의 유전, 세포와 물질대사, 화학, 생명과학 실험</t>
+          <t>생명과학, 생물의 유전, 세포와 물질대사, 화학, 생명과학 실험, 확률과 통계, 대수</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -4432,7 +4727,9 @@
 생물의 유전: 우수한 가축 품종을 개량해야 해서 → 유전의 원리와 유전자 기술을 배워요.
 세포와 물질대사: 사료와 성장의 관계를 연구해서 → 영양과 물질대사의 원리를 배워요.
 화학: 사료 성분과 축사 환경을 분석해서 → 물질의 성질과 화학 반응의 기초를 배워요.
-생명과학 실험: 사육 실험과 시료 분석을 해야 해서 → 생물 실험 방법과 탐구 설계를 경험해요.</t>
+생명과학 실험: 사육 실험과 시료 분석을 해야 해서 → 생물 실험 방법과 탐구 설계를 경험해요.
+확률과 통계: 사육 실험 결과를 비교·분석해서 → 자료 정리와 통계적 추론을 배워요.
+대수: 가축 성장 추세를 예측해야 해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4751,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>화학, 생명과학, 생태와 환경, 법과 사회, 기후변화와 지속가능한 세계</t>
+          <t>화학, 생명과학, 생태와 환경, 법과 사회, 기후변화와 지속가능한 세계, 독서와 작문, 확률과 통계</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -4468,7 +4765,9 @@
 생명과학: 작물·토양 생물의 상태를 판단해서 → 생명 현상과 생태계의 기초를 배워요.
 생태와 환경: 친환경 농업의 목적을 이해해야 해서 → 인간과 자연의 관계와 환경 문제를 배워요.
 법과 사회: 인증 기준과 관련 법규를 적용하므로 → 법의 원리와 생활 속 법을 배워요.
-기후변화와 지속가능한 세계: 지속가능한 생산을 평가하는 일이라 → 지속가능 발전과 환경 정책을 배워요.</t>
+기후변화와 지속가능한 세계: 지속가능한 생산을 평가하는 일이라 → 지속가능 발전과 환경 정책을 배워요.
+독서와 작문: 심사 보고서를 정확히 작성해서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.
+확률과 통계: 시료 검사 결과를 판단해야 해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4789,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>지구과학, 지구시스템과학, 물리학, 화학, 기후변화와 환경생태, 미적분Ⅱ</t>
+          <t>지구과학, 지구시스템과학, 물리학, 화학, 기후변화와 환경생태, 미적분Ⅱ, 미적분 I, 영어 독해와 작문</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -4505,7 +4804,9 @@
 물리학: 파도와 해류의 움직임을 분석해서 → 힘과 운동, 파동의 기초를 배워요.
 화학: 바닷물의 성분과 오염을 분석해서 → 물질의 성질과 용액의 기초를 배워요.
 기후변화와 환경생태: 바다는 기후변화와 밀접해서 → 기후변화와 생태계 변화를 배워요.
-미적분Ⅱ: 해양 자료를 수치 모델로 분석해서 → 미분·적분의 심화 내용을 배워요.</t>
+미적분Ⅱ: 해양 자료를 수치 모델로 분석해서 → 미분·적분의 심화 내용을 배워요.
+미적분 I: 해류·수온 변화를 수식으로 다뤄서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+영어 독해와 작문: 국제 공동 연구로 논문을 써서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4828,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>화학, 화학 반응의 세계, 물질과 에너지, 생명과학, 화학 실험</t>
+          <t>화학, 화학 반응의 세계, 물질과 에너지, 생명과학, 화학 실험, 확률과 통계, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -4541,7 +4842,9 @@
 화학 반응의 세계: 성분의 안정성과 반응을 따져야 해서 → 산·염기, 산화·환원 반응을 배워요.
 물질과 에너지: 크림·로션 같은 제형을 만들어야 해서 → 물질의 상태와 용액의 성질을 배워요.
 생명과학: 피부 구조와 반응을 이해해야 해서 → 세포와 인체의 기초를 배워요.
-화학 실험: 원료를 배합하고 시험해야 해서 → 실험 기구 사용과 분석 방법을 익혀요.</t>
+화학 실험: 원료를 배합하고 시험해야 해서 → 실험 기구 사용과 분석 방법을 익혀요.
+확률과 통계: 임상 시험 결과로 효과를 검증해서 → 자료 정리와 통계적 추론을 배워요.
+영어Ⅱ: 해외 원료·규제 자료를 읽어서 → 다양한 주제의 영어 글 이해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4866,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>화학, 화학 실험, 화학 반응의 세계, 물질과 에너지, 실용 통계</t>
+          <t>화학, 화학 실험, 화학 반응의 세계, 물질과 에너지, 실용 통계, 대수, 독서와 작문</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -4577,7 +4880,9 @@
 화학 실험: 분석 실험을 매일 직접 하므로 → 실험 기구 사용과 분석 방법을 익혀요.
 화학 반응의 세계: 적정·산화환원 분석을 자주 해서 → 산·염기, 산화·환원 반응을 깊이 배워요.
 물질과 에너지: 용액 농도와 물질 상태를 다뤄서 → 물질의 상태와 용액의 성질을 배워요.
-실용 통계: 측정값의 오차와 신뢰도를 판단해서 → 자료 분석과 통계의 기초를 배워요.</t>
+실용 통계: 측정값의 오차와 신뢰도를 판단해서 → 자료 분석과 통계의 기초를 배워요.
+대수: 농도와 희석 비율을 계산해야 해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
+독서와 작문: 시험 성적서를 정확히 써야 해서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4904,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>화학, 화학 반응의 세계, 물질과 에너지, 화학 실험, 물리학, 미적분Ⅱ</t>
+          <t>화학, 화학 반응의 세계, 물질과 에너지, 화학 실험, 물리학, 미적분Ⅱ, 미적분 I, 영어 독해와 작문</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -4614,7 +4919,9 @@
 물질과 에너지: 물질의 상태와 에너지 변화를 다루므로 → 물질의 상태와 열화학을 배워요.
 화학 실험: 가설을 실험으로 확인해야 해서 → 실험 설계와 분석 방법을 익혀요.
 물리학: 원자·분자 구조를 이해해야 해서 → 에너지와 물질의 물리적 기초를 배워요.
-미적분Ⅱ: 반응 속도 등을 수식으로 다뤄서 → 미분·적분의 심화 내용을 배워요.</t>
+미적분Ⅱ: 반응 속도 등을 수식으로 다뤄서 → 미분·적분의 심화 내용을 배워요.
+미적분 I: 반응 속도 변화를 수식으로 다뤄서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+영어 독해와 작문: 연구 결과를 영어 논문으로 써서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4943,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>기하, 정보, 물리학, 물질과 에너지, 미술과 매체</t>
+          <t>기하, 정보, 물리학, 물질과 에너지, 미술과 매체, 미적분 I, 영어 I</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -4650,7 +4957,9 @@
 정보: 모델링·출력 프로그램을 다루므로 → 프로그래밍과 자료 처리를 배워요.
 물리학: 출력물의 강도와 구조를 따져야 해서 → 힘과 운동, 열의 기초를 배워요.
 물질과 에너지: 플라스틱·금속 등 재료를 녹여 쓰므로 → 물질의 상태와 성질을 배워요.
-미술과 매체: 조형물과 디자인을 만들기도 해서 → 다양한 매체로 표현하는 법을 배워요.</t>
+미술과 매체: 조형물과 디자인을 만들기도 해서 → 다양한 매체로 표현하는 법을 배워요.
+미적분 I: 곡면과 부피를 계산해 출력해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+영어 I: 해외 장비 매뉴얼을 읽어야 해서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4981,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>기하, 정보, 물리학, 역학과 에너지</t>
+          <t>기하, 정보, 물리학, 역학과 에너지, 미적분 I, 영어 I</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -4685,7 +4994,9 @@
           <t>기하: 도면은 정확한 도형과 좌표로 그리므로 → 공간도형과 벡터를 배워요.
 정보: 설계 프로그램을 능숙히 다뤄야 해서 → 컴퓨터와 프로그래밍의 기초를 배워요.
 물리학: 부품이 받는 힘을 고려해야 해서 → 힘과 운동의 기초를 배워요.
-역학과 에너지: 기계 구조의 움직임을 이해해야 해서 → 역학과 에너지를 깊이 배워요.</t>
+역학과 에너지: 기계 구조의 움직임을 이해해야 해서 → 역학과 에너지를 깊이 배워요.
+미적분 I: 곡선 형태와 면적을 계산해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+영어 I: 영문 도면과 규격을 읽어야 해서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4707,7 +5018,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>물리학, 역학과 에너지, 기하, 법과 사회, 직무 의사소통</t>
+          <t>물리학, 역학과 에너지, 기하, 법과 사회, 직무 의사소통, 독서와 작문, 스포츠 생활1</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -4721,7 +5032,9 @@
 역학과 에너지: 구조 안전성을 검토해야 해서 → 힘의 평형과 에너지를 깊이 배워요.
 기하: 도면을 정확히 읽어야 해서 → 공간도형과 좌표를 배워요.
 법과 사회: 건설 관련 법규와 기준을 적용하므로 → 법의 원리와 생활 속 법을 배워요.
-직무 의사소통: 시공자·발주자와 협의하고 보고해서 → 업무 보고와 협의 방법을 배워요.</t>
+직무 의사소통: 시공자·발주자와 협의하고 보고해서 → 업무 보고와 협의 방법을 배워요.
+독서와 작문: 감리 보고서를 정확히 작성해서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.
+스포츠 생활1: 건설 현장을 다니며 점검해서 → 꾸준한 운동 습관과 기초 체력을 길러요.</t>
         </is>
       </c>
     </row>
@@ -4743,7 +5056,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>물리학, 역학과 에너지, 기하, 지구과학, 직무 의사소통</t>
+          <t>물리학, 역학과 에너지, 기하, 지구과학, 직무 의사소통, 스포츠 생활1, 화법과 언어</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -4757,7 +5070,9 @@
 역학과 에너지: 안전한 시공 방법을 판단해야 해서 → 힘의 평형과 에너지를 깊이 배워요.
 기하: 도면을 읽고 측량해야 해서 → 공간도형과 좌표를 배워요.
 지구과학: 지반과 기상 조건이 공사에 영향을 주므로 → 지권과 대기의 기초를 배워요.
-직무 의사소통: 현장 인력과 협력해야 해서 → 업무 상황의 의사소통 방법을 배워요.</t>
+직무 의사소통: 현장 인력과 협력해야 해서 → 업무 상황의 의사소통 방법을 배워요.
+스포츠 생활1: 현장을 누비며 공사를 관리해서 → 꾸준한 운동 습관과 기초 체력을 길러요.
+화법과 언어: 작업자와 소통하며 지휘해야 해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4779,7 +5094,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>물리학, 기하, 경제 수학, 경제, 직무 의사소통</t>
+          <t>물리학, 기하, 경제 수학, 경제, 직무 의사소통, 대수, 독서와 작문</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -4793,7 +5108,9 @@
 기하: 도면과 공간 계획을 검토해야 해서 → 공간도형과 좌표를 배워요.
 경제 수학: 사업비와 수익을 계산해야 해서 → 경제 문제를 수학으로 분석하는 법을 배워요.
 경제: 사업의 경제성을 판단해야 해서 → 시장과 경제 원리를 배워요.
-직무 의사소통: 여러 참여자를 조율하는 일이라 → 협의·보고 등 업무 의사소통을 배워요.</t>
+직무 의사소통: 여러 참여자를 조율하는 일이라 → 협의·보고 등 업무 의사소통을 배워요.
+대수: 공사비·일정 변화를 계산해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
+독서와 작문: 사업 계획서와 보고서를 써서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4815,7 +5132,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>기하, 직무 수학, 경제 수학, 정보, 물리학</t>
+          <t>기하, 직무 수학, 경제 수학, 정보, 물리학, 대수, 미적분 I</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -4829,7 +5146,9 @@
 직무 수학: 수량과 비용을 정확히 계산해야 해서 → 실무에 쓰이는 수학을 배워요.
 경제 수학: 공사비와 물가 변동을 따져야 해서 → 경제 문제를 수학으로 분석하는 법을 배워요.
 정보: 적산 프로그램과 스프레드시트를 써서 → 자료 처리와 프로그래밍을 배워요.
-물리학: 구조와 자재의 쓰임을 이해해야 해서 → 힘과 운동의 기초를 배워요.</t>
+물리학: 구조와 자재의 쓰임을 이해해야 해서 → 힘과 운동의 기초를 배워요.
+대수: 자재 물량과 비용을 계산해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
+미적분 I: 곡면 구조의 면적·부피를 구해서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4851,7 +5170,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>물리학, 전자기와 양자, 역학과 에너지, 미적분Ⅱ, 정보, 물리학 실험</t>
+          <t>물리학, 전자기와 양자, 역학과 에너지, 미적분Ⅱ, 정보, 물리학 실험, 미적분 I, 확률과 통계</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -4866,7 +5185,9 @@
 역학과 에너지: 압력·진동 등을 측정해서 → 역학과 에너지를 깊이 배워요.
 미적분Ⅱ: 측정 신호를 수식으로 분석해서 → 미분·적분의 심화 내용을 배워요.
 정보: 측정 데이터를 프로그램으로 처리해서 → 프로그래밍과 자료 처리를 배워요.
-물리학 실험: 측정과 오차 분석이 핵심이라 → 측정 실험과 자료 분석을 경험해요.</t>
+물리학 실험: 측정과 오차 분석이 핵심이라 → 측정 실험과 자료 분석을 경험해요.
+미적분 I: 신호의 변화율을 분석해야 해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+확률과 통계: 측정 오차를 통계로 줄여야 해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4888,7 +5209,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>실용 통계, 미적분Ⅱ, 물리학, 정보, 도시의 미래 탐구</t>
+          <t>실용 통계, 미적분Ⅱ, 물리학, 정보, 도시의 미래 탐구, 확률과 통계, 미적분 I</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -4902,7 +5223,9 @@
 미적분Ⅱ: 교통 흐름을 수학 모델로 다뤄서 → 미분·적분의 심화 내용을 배워요.
 물리학: 차량의 속도·제동을 고려해야 해서 → 힘과 운동의 기초를 배워요.
 정보: 교통 시뮬레이션 프로그램을 써서 → 프로그래밍과 자료 처리를 배워요.
-도시의 미래 탐구: 교통은 도시 계획과 맞물리므로 → 도시 문제와 미래 도시를 탐구해요.</t>
+도시의 미래 탐구: 교통은 도시 계획과 맞물리므로 → 도시 문제와 미래 도시를 탐구해요.
+확률과 통계: 교통량 자료로 정책을 세워서 → 자료 정리와 통계적 추론을 배워요.
+미적분 I: 차량 흐름의 변화를 분석해서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4924,7 +5247,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>물리학, 역학과 에너지, 미적분Ⅱ, 기하, 정보</t>
+          <t>물리학, 역학과 에너지, 미적분Ⅱ, 기하, 정보, 미적분 I, 대수</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -4938,7 +5261,9 @@
 역학과 에너지: 하중과 진동을 계산해야 해서 → 힘의 평형과 에너지를 깊이 배워요.
 미적분Ⅱ: 구조 계산에 미적분이 쓰여서 → 미분·적분의 심화 내용을 배워요.
 기하: 구조의 형태와 힘의 방향을 다뤄서 → 공간도형과 벡터를 배워요.
-정보: 구조 해석 프로그램을 사용해서 → 프로그래밍과 자료 처리를 배워요.</t>
+정보: 구조 해석 프로그램을 사용해서 → 프로그래밍과 자료 처리를 배워요.
+미적분 I: 하중과 변형을 수식으로 계산해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+대수: 구조 안전 계수를 계산해야 해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -4960,7 +5285,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>화학, 물리학, 직무 의사소통, 직무 영어, 경제</t>
+          <t>화학, 물리학, 직무 의사소통, 직무 영어, 경제, 화법과 언어, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -4974,7 +5299,9 @@
 물리학: 장비의 작동 원리를 설명해야 해서 → 힘·전기 등 물리의 기초를 배워요.
 직무 의사소통: 고객에게 제품을 설명·제안해야 해서 → 발표와 협상 등 업무 의사소통을 배워요.
 직무 영어: 해외 고객과 기술 자료를 다뤄서 → 업무에 쓰이는 영어를 배워요.
-경제: 시장과 고객의 요구를 파악해야 해서 → 시장과 경제 원리를 배워요.</t>
+경제: 시장과 고객의 요구를 파악해야 해서 → 시장과 경제 원리를 배워요.
+화법과 언어: 고객에게 기술을 쉽게 설명해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.
+영어Ⅱ: 해외 고객과 소통해야 해서 → 다양한 주제의 영어 글 이해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -4996,7 +5323,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>물리학, 전자기와 양자, 화학, 물질과 에너지, 생명과학, 미적분Ⅱ</t>
+          <t>물리학, 전자기와 양자, 화학, 물질과 에너지, 생명과학, 미적분Ⅱ, 대수, 영어 독해와 작문</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -5011,7 +5338,9 @@
 화학: 원자·분자 구조를 설계해야 해서 → 화학 결합과 물질 구조를 배워요.
 물질과 에너지: 소재의 성질을 이해해야 해서 → 물질의 상태와 성질을 깊이 배워요.
 생명과학: 나노 의약·바이오 소재에도 쓰여서 → 세포와 생명 현상의 기초를 배워요.
-미적분Ⅱ: 물리 현상을 수식으로 분석해서 → 미분·적분의 심화 내용을 배워요.</t>
+미적분Ⅱ: 물리 현상을 수식으로 분석해서 → 미분·적분의 심화 내용을 배워요.
+대수: 극미세 단위를 지수로 다뤄서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
+영어 독해와 작문: 최신 해외 논문을 읽고 써서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5362,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>물리학, 역학과 에너지, 기후변화와 지속가능한 세계, 생태와 환경, 기하</t>
+          <t>물리학, 역학과 에너지, 기후변화와 지속가능한 세계, 생태와 환경, 기하, 미적분 I, 확률과 통계</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -5047,7 +5376,9 @@
 역학과 에너지: 건물 에너지 효율을 계산해서 → 에너지 전환과 열역학을 깊이 배워요.
 기후변화와 지속가능한 세계: 탄소 감축이 목표라서 → 기후변화 대응과 지속가능 발전을 배워요.
 생태와 환경: 자연과 어우러진 건축을 계획해서 → 생태계와 환경 문제를 배워요.
-기하: 건물 형태와 배치를 설계해서 → 공간도형과 좌표를 배워요.</t>
+기하: 건물 형태와 배치를 설계해서 → 공간도형과 좌표를 배워요.
+미적분 I: 에너지 소비 변화를 분석해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+확률과 통계: 건물 에너지 자료를 평가해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5400,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>도시의 미래 탐구, 한국지리 탐구, 사회문제 탐구, 사회와 문화, 실용 통계</t>
+          <t>도시의 미래 탐구, 한국지리 탐구, 사회문제 탐구, 사회와 문화, 실용 통계, 화법과 언어, 독서와 작문</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -5083,7 +5414,9 @@
 한국지리 탐구: 지역의 특성을 분석해야 해서 → 국토와 지역의 특징을 탐구해요.
 사회문제 탐구: 인구 감소·주거 문제를 다뤄서 → 사회 문제를 조사·분석하는 법을 배워요.
 사회와 문화: 주민 공동체와 함께 일하므로 → 사회 구조와 공동체를 배워요.
-실용 통계: 인구·주거 자료로 계획을 세워서 → 자료 분석과 통계를 배워요.</t>
+실용 통계: 인구·주거 자료로 계획을 세워서 → 자료 분석과 통계를 배워요.
+화법과 언어: 주민 의견을 듣고 조율해야 해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.
+독서와 작문: 재생 계획서를 설득력 있게 써서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5438,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>물리학, 역학과 에너지, 전자기와 양자, 정보, 인공지능 기초</t>
+          <t>물리학, 역학과 에너지, 전자기와 양자, 정보, 인공지능 기초, 미적분 I, 영어 I</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -5119,7 +5452,9 @@
 역학과 에너지: 비행 안정성과 배터리 효율을 다뤄서 → 역학과 에너지를 깊이 배워요.
 전자기와 양자: 모터·센서·통신 장치를 다루므로 → 전자기 현상의 원리를 배워요.
 정보: 비행 제어 프로그램을 다뤄서 → 프로그래밍과 자료 처리를 배워요.
-인공지능 기초: 자율 비행과 영상 분석에 쓰여서 → 인공지능의 원리와 활용을 배워요.</t>
+인공지능 기초: 자율 비행과 영상 분석에 쓰여서 → 인공지능의 원리와 활용을 배워요.
+미적분 I: 비행 속도와 경로를 계산해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+영어 I: 해외 기체 매뉴얼을 읽어야 해서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5476,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>물리학, 전자기와 양자, 화학, 물질과 에너지, 미적분Ⅱ</t>
+          <t>물리학, 전자기와 양자, 화학, 물질과 에너지, 미적분Ⅱ, 미적분 I, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -5155,7 +5490,9 @@
 전자기와 양자: 발광 소자와 반도체 원리를 알아야 해서 → 전자기와 양자 현상을 배워요.
 화학: 유기 발광 소재 등을 다뤄서 → 물질의 구조와 화학 결합을 배워요.
 물질과 에너지: 소재의 성질을 이해해야 해서 → 물질의 상태와 성질을 깊이 배워요.
-미적분Ⅱ: 소자 특성을 수식으로 분석해서 → 미분·적분의 심화 내용을 배워요.</t>
+미적분Ⅱ: 소자 특성을 수식으로 분석해서 → 미분·적분의 심화 내용을 배워요.
+미적분 I: 빛과 전류 변화를 수식으로 다뤄서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+영어Ⅱ: 해외 기술 자료를 읽어야 해서 → 다양한 주제의 영어 글 이해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -5177,7 +5514,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>물리학, 역학과 에너지, 전자기와 양자, 미적분Ⅱ, 정보</t>
+          <t>물리학, 역학과 에너지, 전자기와 양자, 미적분Ⅱ, 정보, 미적분 I, 영어 I</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -5191,7 +5528,9 @@
 역학과 에너지: 기계 장치의 움직임을 설계해서 → 역학과 에너지를 깊이 배워요.
 전자기와 양자: 모터·센서 등 전자 부품을 써서 → 전자기 현상의 원리를 배워요.
 미적분Ⅱ: 제어 이론에 미적분이 쓰여서 → 미분·적분의 심화 내용을 배워요.
-정보: 장비를 프로그램으로 제어하므로 → 프로그래밍과 자료 처리를 배워요.</t>
+정보: 장비를 프로그램으로 제어하므로 → 프로그래밍과 자료 처리를 배워요.
+미적분 I: 로봇 움직임을 수식으로 제어해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+영어 I: 해외 부품 사양서를 읽어서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5552,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>물리학, 전자기와 양자, 화학, 미적분Ⅱ, 물질과 에너지, 정보</t>
+          <t>물리학, 전자기와 양자, 화학, 미적분Ⅱ, 물질과 에너지, 정보, 미적분 I, 확률과 통계</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -5228,7 +5567,9 @@
 화학: 공정에서 박막·식각 반응을 다뤄서 → 물질 구조와 화학 반응을 배워요.
 미적분Ⅱ: 회로와 소자 특성을 수식으로 분석해서 → 미분·적분의 심화 내용을 배워요.
 물질과 에너지: 반도체 소재를 이해해야 해서 → 물질의 상태와 성질을 깊이 배워요.
-정보: 회로 설계·공정 데이터를 다뤄서 → 프로그래밍과 자료 처리를 배워요.</t>
+정보: 회로 설계·공정 데이터를 다뤄서 → 프로그래밍과 자료 처리를 배워요.
+미적분 I: 전자 소자 특성을 수식으로 다뤄서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+확률과 통계: 공정 수율과 불량률을 분석해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5591,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>화학, 화학 반응의 세계, 물질과 에너지, 물리학, 전자기와 양자</t>
+          <t>화학, 화학 반응의 세계, 물질과 에너지, 물리학, 전자기와 양자, 미적분 I, 확률과 통계</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -5264,7 +5605,9 @@
 화학 반응의 세계: 충전·방전이 산화·환원 반응이라 → 산화·환원과 전기화학을 배워요.
 물질과 에너지: 전극·전해질 소재를 다뤄서 → 물질의 상태와 에너지 변화를 배워요.
 물리학: 전류·전압과 발열을 다뤄야 해서 → 전기와 에너지의 기초를 배워요.
-전자기와 양자: 배터리 관리 회로를 이해해야 해서 → 전기 회로와 전자기 현상을 배워요.</t>
+전자기와 양자: 배터리 관리 회로를 이해해야 해서 → 전기 회로와 전자기 현상을 배워요.
+미적분 I: 충전·방전 변화를 분석해야 해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+확률과 통계: 성능 시험 자료를 분석해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5629,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>물리학, 전자기와 양자, 역학과 에너지, 물리학 실험</t>
+          <t>물리학, 전자기와 양자, 역학과 에너지, 물리학 실험, 확률과 통계, 영어 I</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -5299,7 +5642,9 @@
           <t>물리학: 초음파·방사선은 물리 현상이라 → 파동과 에너지의 기초를 배워요.
 전자기와 양자: 방사선·자기 검사 원리를 알아야 해서 → 전자기와 양자 현상을 배워요.
 역학과 에너지: 재료의 균열과 강도를 판단해서 → 힘과 에너지를 깊이 배워요.
-물리학 실험: 검사 장비로 직접 측정해서 → 측정 실험과 자료 분석을 경험해요.</t>
+물리학 실험: 검사 장비로 직접 측정해서 → 측정 실험과 자료 분석을 경험해요.
+확률과 통계: 검사 신호로 결함을 판정해서 → 자료 정리와 통계적 추론을 배워요.
+영어 I: 국제 검사 규격을 읽어야 해서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5666,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>화학, 물리학, 생명과학, 법과 사회, 직무 의사소통</t>
+          <t>화학, 물리학, 생명과학, 법과 사회, 직무 의사소통, 확률과 통계, 화법과 언어</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -5335,7 +5680,9 @@
 물리학: 기계·전기 사고 위험을 판단해서 → 힘과 운동, 전기의 기초를 배워요.
 생명과학: 유해 환경이 몸에 주는 영향을 알아야 해서 → 인체와 질병의 기초를 배워요.
 법과 사회: 산업안전 법규를 지키게 해야 해서 → 법의 원리와 생활 속 법을 배워요.
-직무 의사소통: 근로자에게 안전 교육을 해야 해서 → 설명과 보고 등 업무 의사소통을 배워요.</t>
+직무 의사소통: 근로자에게 안전 교육을 해야 해서 → 설명과 보고 등 업무 의사소통을 배워요.
+확률과 통계: 사고 통계로 위험을 예측해서 → 자료 정리와 통계적 추론을 배워요.
+화법과 언어: 작업자에게 안전 교육을 해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5357,7 +5704,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>실용 통계, 경제 수학, 직무 수학, 정보, 화학</t>
+          <t>실용 통계, 경제 수학, 직무 수학, 정보, 화학, 확률과 통계, 대수</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -5371,7 +5718,9 @@
 경제 수학: 원가와 생산량을 최적화해야 해서 → 경제 문제를 수학으로 분석하는 법을 배워요.
 직무 수학: 생산 일정과 수량을 계산해서 → 실무에 쓰이는 수학을 배워요.
 정보: 생산 데이터를 시스템으로 관리해서 → 프로그래밍과 자료 처리를 배워요.
-화학: 화학·섬유 공정을 관리하기도 해서 → 물질의 성질과 화학 반응의 기초를 배워요.</t>
+화학: 화학·섬유 공정을 관리하기도 해서 → 물질의 성질과 화학 반응의 기초를 배워요.
+확률과 통계: 불량률과 생산량을 관리해서 → 자료 정리와 통계적 추론을 배워요.
+대수: 생산 계획과 원가를 계산해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5742,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>물리학, 역학과 에너지, 전자기와 양자, 미적분Ⅱ, 기하</t>
+          <t>물리학, 역학과 에너지, 전자기와 양자, 미적분Ⅱ, 기하, 미적분 I, 영어 I</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -5407,7 +5756,9 @@
 역학과 에너지: 냉난방·배관의 에너지 흐름을 다뤄서 → 열역학과 유체를 깊이 배워요.
 전자기와 양자: 전기 설비와 모터를 관리해서 → 전기 회로와 전자기 현상을 배워요.
 미적분Ⅱ: 설비 용량을 계산해야 해서 → 미분·적분의 심화 내용을 배워요.
-기하: 배관·설비 도면을 읽어야 해서 → 공간도형과 좌표를 배워요.</t>
+기하: 배관·설비 도면을 읽어야 해서 → 공간도형과 좌표를 배워요.
+미적분 I: 유체·열의 흐름을 계산해야 해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+영어 I: 해외 설비 매뉴얼을 읽어서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5780,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>화학, 물질과 에너지, 화학 반응의 세계, 화학 실험, 물리학</t>
+          <t>화학, 물질과 에너지, 화학 반응의 세계, 화학 실험, 물리학, 확률과 통계, 대수</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -5443,7 +5794,9 @@
 물질과 에너지: 섬유의 성질과 가공을 다뤄서 → 물질의 상태와 성질을 깊이 배워요.
 화학 반응의 세계: 염색·가공 반응을 다뤄서 → 다양한 화학 반응을 깊이 배워요.
 화학 실험: 원단을 직접 시험·분석해서 → 실험 기구 사용과 분석 방법을 익혀요.
-물리학: 섬유의 강도·신축성을 평가해서 → 힘과 운동의 기초를 배워요.</t>
+물리학: 섬유의 강도·신축성을 평가해서 → 힘과 운동의 기초를 배워요.
+확률과 통계: 섬유 품질 시험 결과를 분석해서 → 자료 정리와 통계적 추론을 배워요.
+대수: 원료 배합 비율을 계산해야 해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5818,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>정보, 인공지능 기초, 인공지능 수학, 실용 통계, 물리학</t>
+          <t>정보, 인공지능 기초, 인공지능 수학, 실용 통계, 물리학, 확률과 통계, 미적분 I</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -5479,7 +5832,9 @@
 인공지능 기초: 생산 데이터를 분석·예측하므로 → 인공지능의 원리와 활용을 배워요.
 인공지능 수학: 데이터 분석 모델은 수학으로 작동해서 → 인공지능에 쓰이는 수학을 배워요.
 실용 통계: 공정 데이터로 품질을 관리해서 → 자료 분석과 통계의 기초를 배워요.
-물리학: 센서·로봇 등 설비를 이해해야 해서 → 힘과 운동, 전기의 기초를 배워요.</t>
+물리학: 센서·로봇 등 설비를 이해해야 해서 → 힘과 운동, 전기의 기초를 배워요.
+확률과 통계: 공정 데이터로 이상을 찾아내서 → 자료 정리와 통계적 추론을 배워요.
+미적분 I: 공정 변화를 실시간 제어해서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5856,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>화학, 생명과학, 화학 반응의 세계, 세포와 물질대사, 화학 실험</t>
+          <t>화학, 생명과학, 화학 반응의 세계, 세포와 물질대사, 화학 실험, 확률과 통계, 미적분 I</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -5515,7 +5870,9 @@
 생명과학: 발효·미생물을 이용해서 → 미생물과 생명 현상의 기초를 배워요.
 화학 반응의 세계: 가공·저장 중 성분 변화를 알아야 해서 → 산·염기, 산화·환원 반응을 배워요.
 세포와 물질대사: 발효와 영양소 변화를 이해해야 해서 → 효소와 물질대사의 원리를 배워요.
-화학 실험: 식품을 직접 분석·시험해서 → 실험 기구 사용과 분석 방법을 익혀요.</t>
+화학 실험: 식품을 직접 분석·시험해서 → 실험 기구 사용과 분석 방법을 익혀요.
+확률과 통계: 품질 검사 결과를 분석해서 → 자료 정리와 통계적 추론을 배워요.
+미적분 I: 살균 온도·시간 변화를 다뤄서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5537,7 +5894,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>물리학, 전자기와 양자, 역학과 에너지, 미적분Ⅱ, 화학</t>
+          <t>물리학, 전자기와 양자, 역학과 에너지, 미적분Ⅱ, 화학, 대수, 미적분 I</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -5551,7 +5908,9 @@
 전자기와 양자: 핵분열과 방사선을 이해해야 해서 → 원자와 양자 현상을 배워요.
 역학과 에너지: 발전 과정의 열에너지를 다뤄서 → 열역학과 에너지 전환을 깊이 배워요.
 미적분Ⅱ: 원자로 계산에 미적분이 쓰여서 → 미분·적분의 심화 내용을 배워요.
-화학: 핵연료와 방사성 물질을 다뤄서 → 원소와 물질의 기초를 배워요.</t>
+화학: 핵연료와 방사성 물질을 다뤄서 → 원소와 물질의 기초를 배워요.
+대수: 방사선 붕괴를 지수·로그로 다뤄서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
+미적분 I: 에너지 변화를 정밀히 계산해서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5573,7 +5932,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>물리학, 생명과학, 전자기와 양자, 정보, 미적분Ⅱ</t>
+          <t>물리학, 생명과학, 전자기와 양자, 정보, 미적분Ⅱ, 미적분 I, 확률과 통계</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -5587,7 +5946,9 @@
 생명과학: 인체에 쓰일 기기를 만들어서 → 인체 구조와 생명 현상의 기초를 배워요.
 전자기와 양자: 영상·센서 장비를 다뤄서 → 전자기와 양자 현상을 배워요.
 정보: 기기를 제어하는 소프트웨어를 만들어서 → 프로그래밍과 자료 처리를 배워요.
-미적분Ⅱ: 생체 신호를 수식으로 분석해서 → 미분·적분의 심화 내용을 배워요.</t>
+미적분Ⅱ: 생체 신호를 수식으로 분석해서 → 미분·적분의 심화 내용을 배워요.
+미적분 I: 생체 신호 변화를 분석해야 해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+확률과 통계: 임상 시험으로 안전성을 검증해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5609,7 +5970,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>인간과 심리, 실용 통계, 생명과학, 물리학, 정보</t>
+          <t>인간과 심리, 실용 통계, 생명과학, 물리학, 정보, 확률과 통계, 스포츠 과학</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -5623,7 +5984,9 @@
 실용 통계: 사용자 실험 결과를 분석해서 → 자료 분석과 통계의 기초를 배워요.
 생명과학: 인체 구조와 피로를 고려해야 해서 → 인체와 생명 현상의 기초를 배워요.
 물리학: 몸에 가해지는 힘을 분석해서 → 힘과 운동의 기초를 배워요.
-정보: 사용자 데이터와 화면 설계를 다뤄서 → 프로그래밍과 자료 처리를 배워요.</t>
+정보: 사용자 데이터와 화면 설계를 다뤄서 → 프로그래밍과 자료 처리를 배워요.
+확률과 통계: 사람의 신체 치수를 분석해서 → 자료 정리와 통계적 추론을 배워요.
+스포츠 과학: 몸의 움직임과 피로를 이해해서 → 몸의 움직임과 체력 향상 원리를 배워요.</t>
         </is>
       </c>
     </row>
@@ -5645,7 +6008,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>미적분Ⅱ, 물리학, 전자기와 양자, 역학과 에너지, 정보</t>
+          <t>미적분Ⅱ, 물리학, 전자기와 양자, 역학과 에너지, 정보, 미적분 I, 대수</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -5659,7 +6022,9 @@
 물리학: 제어 대상의 움직임을 알아야 해서 → 힘과 운동, 전기의 기초를 배워요.
 전자기와 양자: 전기 회로와 모터를 제어해서 → 전자기 현상의 원리를 배워요.
 역학과 에너지: 기계 시스템의 운동을 분석해서 → 역학과 에너지를 깊이 배워요.
-정보: 제어 알고리즘을 프로그램으로 구현해서 → 프로그래밍과 자료 처리를 배워요.</t>
+정보: 제어 알고리즘을 프로그램으로 구현해서 → 프로그래밍과 자료 처리를 배워요.
+미적분 I: 시스템 변화를 수식으로 제어해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+대수: 반복 신호를 수열로 분석해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5681,7 +6046,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>물리학, 역학과 에너지, 전자기와 양자, 미적분Ⅱ, 화학</t>
+          <t>물리학, 역학과 에너지, 전자기와 양자, 미적분Ⅱ, 화학, 미적분 I, 확률과 통계</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -5695,7 +6060,9 @@
 역학과 에너지: 주행·충돌·연비를 분석해서 → 역학과 에너지 전환을 깊이 배워요.
 전자기와 양자: 전기차 모터·전장 부품을 다뤄서 → 전자기 현상의 원리를 배워요.
 미적분Ⅱ: 차량 성능을 수식으로 계산해서 → 미분·적분의 심화 내용을 배워요.
-화학: 배터리·연료·소재를 다뤄서 → 물질의 성질과 화학 반응의 기초를 배워요.</t>
+화학: 배터리·연료·소재를 다뤄서 → 물질의 성질과 화학 반응의 기초를 배워요.
+미적분 I: 속도·가속도 변화를 계산해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+확률과 통계: 주행 시험 자료를 분석해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5717,7 +6084,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>물리학, 역학과 에너지, 전자기와 양자, 물리학 실험</t>
+          <t>물리학, 역학과 에너지, 전자기와 양자, 물리학 실험, 영어 I, 스포츠 생활1</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -5730,7 +6097,9 @@
           <t>물리학: 엔진·제동 장치의 원리를 알아야 해서 → 힘과 운동, 열의 기초를 배워요.
 역학과 에너지: 동력 전달 장치를 다뤄서 → 역학과 에너지 전환을 배워요.
 전자기와 양자: 전기·전자 장치 고장을 진단해서 → 전기 회로와 전자기 현상을 배워요.
-물리학 실험: 측정 장비로 차량을 점검해서 → 측정과 실험 방법을 경험해요.</t>
+물리학 실험: 측정 장비로 차량을 점검해서 → 측정과 실험 방법을 경험해요.
+영어 I: 영문 정비 매뉴얼을 읽어야 해서 → 영어 글의 핵심을 파악하는 법을 배워요.
+스포츠 생활1: 무거운 부품을 다루며 일해서 → 꾸준한 운동 습관과 기초 체력을 길러요.</t>
         </is>
       </c>
     </row>
@@ -5752,7 +6121,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>정보, 인공지능 기초, 인공지능 수학, 미적분Ⅱ, 기하, 물리학</t>
+          <t>정보, 인공지능 기초, 인공지능 수학, 미적분Ⅱ, 기하, 물리학, 확률과 통계, 미적분 I</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -5767,7 +6136,9 @@
 인공지능 수학: 인식 모델이 수학으로 작동해서 → 인공지능에 쓰이는 수학을 배워요.
 미적분Ⅱ: 차량 움직임을 예측·제어해서 → 미분·적분의 심화 내용을 배워요.
 기하: 센서 위치와 경로를 계산해서 → 벡터와 공간 좌표를 배워요.
-물리학: 차량의 운동과 센서 원리를 알아야 해서 → 힘과 운동, 빛의 기초를 배워요.</t>
+물리학: 차량의 운동과 센서 원리를 알아야 해서 → 힘과 운동, 빛의 기초를 배워요.
+확률과 통계: 센서 정보로 상황을 예측해서 → 자료 정리와 통계적 추론을 배워요.
+미적분 I: 차량 움직임을 실시간 계산해서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5789,7 +6160,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>물리학, 전자기와 양자, 역학과 에너지, 미적분Ⅱ, 물리학 실험</t>
+          <t>물리학, 전자기와 양자, 역학과 에너지, 미적분Ⅱ, 물리학 실험, 미적분 I, 대수</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -5803,7 +6174,9 @@
 전자기와 양자: 전동기·변압기가 전자기 원리로 작동해서 → 전기장·자기장과 전자기 유도를 깊이 배워요.
 역학과 에너지: 발전과 에너지 변환을 이해해야 해서 → 에너지의 전환과 보존을 깊이 배워요.
 미적분Ⅱ: 교류 회로 계산에 수학이 필요해서 → 삼각함수·지수함수의 미적분을 배워요.
-물리학 실험: 측정·점검이 실무의 핵심이라 → 실험 설계와 측정·분석을 경험해요.</t>
+물리학 실험: 측정·점검이 실무의 핵심이라 → 실험 설계와 측정·분석을 경험해요.
+미적분 I: 전류·전압 변화를 계산해야 해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+대수: 교류 전기의 주기를 다뤄서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5825,7 +6198,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 기후변화와 환경생태, 도시의 미래 탐구, 미술과 매체, 기하</t>
+          <t>생명과학, 기후변화와 환경생태, 도시의 미래 탐구, 미술과 매체, 기하, 문학, 미적분 I</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -5839,7 +6212,9 @@
 기후변화와 환경생태: 생태적으로 건강한 녹지를 설계해야 해서 → 생태계와 환경 변화를 깊이 배워요.
 도시의 미래 탐구: 도시 공원·녹지를 계획하므로 → 도시 공간과 지속가능한 도시를 탐구해요.
 미술과 매체: 설계안을 시각적으로 표현해야 해서 → 다양한 매체로 조형 표현을 배워요.
-기하: 부지 도면과 공간 배치를 다루므로 → 도형·좌표·벡터를 배워요.</t>
+기하: 부지 도면과 공간 배치를 다루므로 → 도형·좌표·벡터를 배워요.
+문학: 공간에 이야기와 정서를 담아서 → 작품 속 인물과 삶을 깊이 이해하는 법을 배워요.
+미적분 I: 지형 곡면과 면적을 계산해서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -5861,7 +6236,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>물리학, 역학과 에너지, 미적분Ⅱ, 기하, 지구과학</t>
+          <t>물리학, 역학과 에너지, 미적분Ⅱ, 기하, 지구과학, 미적분 I, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -5875,7 +6250,9 @@
 역학과 에너지: 선체에 걸리는 힘과 엔진 효율을 다뤄서 → 역학과 열에너지를 깊이 배워요.
 미적분Ⅱ: 선체 형상·유체 계산에 수학이 쓰여서 → 심화 미분·적분을 배워요.
 기하: 3차원 선체를 설계하므로 → 공간도형과 벡터를 배워요.
-지구과학: 파도·해류 속에서 운항하므로 → 해양과 대기의 움직임을 배워요.</t>
+지구과학: 파도·해류 속에서 운항하므로 → 해양과 대기의 움직임을 배워요.
+미적분 I: 선체 곡면과 부력을 계산해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+영어Ⅱ: 해외 선주와 소통해야 해서 → 다양한 주제의 영어 글 이해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -5897,7 +6274,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>기하, 한국지리 탐구, 지구과학, 물리학, 정보</t>
+          <t>기하, 한국지리 탐구, 지구과학, 물리학, 정보, 대수, 스포츠 생활1</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -5911,7 +6288,9 @@
 한국지리 탐구: 국토의 지형과 토지를 다뤄서 → 우리나라 지형과 지도 읽기를 배워요.
 지구과학: 지구 모양과 지형을 이해해야 해서 → 지구의 구조와 지각 변동을 배워요.
 물리학: 레이저·위성 측량 장비를 다뤄서 → 빛과 파동, 운동의 원리를 배워요.
-정보: 측량 자료를 컴퓨터로 처리해서 → 프로그래밍과 자료 처리를 배워요.</t>
+정보: 측량 자료를 컴퓨터로 처리해서 → 프로그래밍과 자료 처리를 배워요.
+대수: 거리·각도를 정확히 계산해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
+스포츠 생활1: 장비를 들고 현장을 다녀서 → 꾸준한 운동 습관과 기초 체력을 길러요.</t>
         </is>
       </c>
     </row>
@@ -5933,7 +6312,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>물리학, 역학과 에너지, 기하, 미적분Ⅱ, 지구과학</t>
+          <t>물리학, 역학과 에너지, 기하, 미적분Ⅱ, 지구과학, 미적분 I, 스포츠 생활1</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -5947,7 +6326,9 @@
 역학과 에너지: 다리·건물이 버티는 원리를 알아야 해서 → 역학을 깊이 배워요.
 기하: 설계 도면과 구조 형태를 다뤄서 → 도형·벡터·공간 개념을 배워요.
 미적분Ⅱ: 구조 계산에 수학이 쓰여서 → 심화 미분·적분을 배워요.
-지구과학: 지반 위에 시설을 지어서 → 암석·지각과 지형 변화를 배워요.</t>
+지구과학: 지반 위에 시설을 지어서 → 암석·지각과 지형 변화를 배워요.
+미적분 I: 하중과 지반 변화를 계산해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+스포츠 생활1: 야외 현장에서 오래 일해서 → 꾸준한 운동 습관과 기초 체력을 길러요.</t>
         </is>
       </c>
     </row>
@@ -5969,7 +6350,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>실용 통계, 화학, 화학 실험, 생명과학, 물리학</t>
+          <t>실용 통계, 화학, 화학 실험, 생명과학, 물리학, 확률과 통계, 독서와 작문</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -5983,7 +6364,9 @@
 화학: 원료·제품의 성분을 분석하므로 → 물질의 구성과 화학 반응의 기초를 배워요.
 화학 실험: 시료를 직접 검사·측정해서 → 실험 기구 사용과 분석 방법을 익혀요.
 생명과학: 식품·바이오 제품의 위생을 다뤄서 → 미생물과 생명 현상의 기초를 배워요.
-물리학: 기계·전자 제품의 성능을 시험해서 → 힘·전기·파동의 원리를 배워요.</t>
+물리학: 기계·전자 제품의 성능을 시험해서 → 힘·전기·파동의 원리를 배워요.
+확률과 통계: 불량률을 통계로 관리해야 해서 → 자료 정리와 통계적 추론을 배워요.
+독서와 작문: 품질 보고서를 정확히 써야 해서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6388,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>물리학, 화학, 역학과 에너지, 물질과 에너지, 미적분Ⅱ, 직무 영어</t>
+          <t>물리학, 화학, 역학과 에너지, 물질과 에너지, 미적분Ⅱ, 직무 영어, 미적분 I, 확률과 통계</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -6020,7 +6403,9 @@
 역학과 에너지: 열·압력을 다루는 설비가 많아서 → 역학과 열에너지를 깊이 배워요.
 물질과 에너지: 공정 물질의 상태 변화를 다뤄서 → 물질의 상태와 에너지 출입을 배워요.
 미적분Ⅱ: 공정 설계에 계산이 많아서 → 심화 미분·적분을 배워요.
-직무 영어: 해외 공사와 협업이 많아서 → 업무에 쓰이는 영어를 배워요.</t>
+직무 영어: 해외 공사와 협업이 많아서 → 업무에 쓰이는 영어를 배워요.
+미적분 I: 유체·열 흐름을 계산해야 해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+확률과 통계: 설비 운전 자료를 분석해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6427,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>물리학, 역학과 에너지, 전자기와 양자, 물리학 실험, 직무 영어</t>
+          <t>물리학, 역학과 에너지, 전자기와 양자, 물리학 실험, 직무 영어, 영어Ⅱ, 미적분 I</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -6056,7 +6441,9 @@
 역학과 에너지: 엔진과 기체에 큰 힘이 작용해서 → 역학과 열역학을 깊이 배워요.
 전자기와 양자: 항공 전자 장비를 정비해서 → 전기·자기와 전자기 유도를 배워요.
 물리학 실험: 장비를 직접 점검·측정해서 → 측정과 실험 기능을 익혀요.
-직무 영어: 정비 매뉴얼이 영어로 되어 있어서 → 업무용 영어 읽기를 배워요.</t>
+직무 영어: 정비 매뉴얼이 영어로 되어 있어서 → 업무용 영어 읽기를 배워요.
+영어Ⅱ: 영문 정비 교범을 읽어야 해서 → 다양한 주제의 영어 글 이해를 배워요.
+미적분 I: 기체 힘과 운동을 이해해야 해서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6465,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>화학, 화학 반응의 세계, 물질과 에너지, 화학 실험, 법과 사회</t>
+          <t>화학, 화학 반응의 세계, 물질과 에너지, 화학 실험, 법과 사회, 확률과 통계, 화법과 언어</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -6092,7 +6479,9 @@
 화학 반응의 세계: 폭발·누출 같은 사고를 예방해야 해서 → 산화·환원 등 반응을 깊이 배워요.
 물질과 에너지: 보관 중 상태 변화를 관리해서 → 물질의 상태와 용액을 배워요.
 화학 실험: 안전한 취급 습관이 필수라서 → 실험 안전과 시약 다루는 법을 익혀요.
-법과 사회: 화학물질 관련 법을 지켜야 해서 → 법의 원리와 사회 속 법을 배워요.</t>
+법과 사회: 화학물질 관련 법을 지켜야 해서 → 법의 원리와 사회 속 법을 배워요.
+확률과 통계: 유해 물질 측정값을 판단해서 → 자료 정리와 통계적 추론을 배워요.
+화법과 언어: 작업자에게 안전 수칙을 알려서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6503,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>화학, 기후변화와 환경생태, 기후변화와 지속가능한 세계, 지구과학, 실용 통계</t>
+          <t>화학, 기후변화와 환경생태, 기후변화와 지속가능한 세계, 지구과학, 실용 통계, 확률과 통계, 독서와 작문</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -6128,7 +6517,9 @@
 기후변화와 환경생태: 환경 영향을 과학적으로 판단해서 → 기후 변화와 생태계를 배워요.
 기후변화와 지속가능한 세계: 기업의 친환경 전략을 제안해서 → 지속가능 발전과 환경 정책을 배워요.
 지구과학: 대기·물·토양 환경을 다뤄서 → 지구 환경 시스템을 배워요.
-실용 통계: 측정 자료로 보고서를 써야 해서 → 자료 분석과 통계 활용을 배워요.</t>
+실용 통계: 측정 자료로 보고서를 써야 해서 → 자료 분석과 통계 활용을 배워요.
+확률과 통계: 오염 측정 자료를 분석해서 → 자료 정리와 통계적 추론을 배워요.
+독서와 작문: 환경 진단 보고서를 써야 해서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6541,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 기후변화와 환경생태, 지구과학, 화학, 실용 통계</t>
+          <t>생명과학, 기후변화와 환경생태, 지구과학, 화학, 실용 통계, 확률과 통계, 독서와 작문</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -6164,7 +6555,9 @@
 기후변화와 환경생태: 생태계 변화를 예측해야 해서 → 환경 변화와 생태계 반응을 배워요.
 지구과학: 지형·수질·대기를 조사하므로 → 지구 환경의 구성과 변화를 배워요.
 화학: 오염 물질 농도를 분석해서 → 물질의 성질과 반응을 배워요.
-실용 통계: 조사 자료로 영향을 예측해서 → 자료 분석과 통계적 추론을 배워요.</t>
+실용 통계: 조사 자료로 영향을 예측해서 → 자료 분석과 통계적 추론을 배워요.
+확률과 통계: 환경 조사 자료로 영향을 예측해서 → 자료 정리와 통계적 추론을 배워요.
+독서와 작문: 평가서를 논리적으로 써야 해서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6579,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>한국지리 탐구, 정보, 도시의 미래 탐구, 실용 통계, 지구과학</t>
+          <t>한국지리 탐구, 정보, 도시의 미래 탐구, 실용 통계, 지구과학, 확률과 통계, 대수</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -6200,7 +6593,9 @@
 정보: 공간 데이터를 프로그램으로 처리해서 → 프로그래밍과 자료 처리를 배워요.
 도시의 미래 탐구: 도시 계획에 GIS가 쓰여서 → 도시 문제와 공간 계획을 탐구해요.
 실용 통계: 공간 자료를 분석해야 해서 → 자료 정리와 통계 분석을 배워요.
-지구과학: 지형·기상 자료도 다뤄서 → 지구의 지형과 대기 현상을 배워요.</t>
+지구과학: 지형·기상 자료도 다뤄서 → 지구의 지형과 대기 현상을 배워요.
+확률과 통계: 공간 데이터를 분석해야 해서 → 자료 정리와 통계적 추론을 배워요.
+대수: 좌표 변환과 축척을 계산해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6617,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>정보, 소프트웨어와 생활, 인간과 심리, 실용 통계, 직무 의사소통</t>
+          <t>정보, 소프트웨어와 생활, 인간과 심리, 실용 통계, 직무 의사소통, 독서와 작문, 확률과 통계</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -6236,7 +6631,9 @@
 소프트웨어와 생활: 생활 속 문제를 서비스로 풀어서 → 소프트웨어로 문제 해결하는 법을 배워요.
 인간과 심리: 사용자의 마음을 이해해야 해서 → 사람의 행동과 심리를 배워요.
 실용 통계: 이용 데이터로 서비스를 개선해서 → 자료 분석과 해석을 배워요.
-직무 의사소통: 기획안을 설명하고 조율해서 → 업무 상황의 말하기·쓰기를 배워요.</t>
+직무 의사소통: 기획안을 설명하고 조율해서 → 업무 상황의 말하기·쓰기를 배워요.
+독서와 작문: 서비스 기획서를 논리적으로 써서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.
+확률과 통계: 사용자 데이터로 개선점을 찾아서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6655,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>정보, 물리학, 전자기와 양자, 인공지능 기초, 소프트웨어와 생활</t>
+          <t>정보, 물리학, 전자기와 양자, 인공지능 기초, 소프트웨어와 생활, 영어 I, 확률과 통계</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -6272,7 +6669,9 @@
 물리학: 센서와 전자 회로를 다뤄서 → 전기·파동의 기초 원리를 배워요.
 전자기와 양자: 무선 통신·센서가 전자기 원리라서 → 전자기파와 양자 현상을 배워요.
 인공지능 기초: 스마트 기기에 AI가 쓰여서 → 인공지능의 원리와 활용을 배워요.
-소프트웨어와 생활: 생활 속 문제를 기술로 풀어서 → 소프트웨어로 문제 해결하는 법을 배워요.</t>
+소프트웨어와 생활: 생활 속 문제를 기술로 풀어서 → 소프트웨어로 문제 해결하는 법을 배워요.
+영어 I: 영문 개발 문서를 읽어야 해서 → 영어 글의 핵심을 파악하는 법을 배워요.
+확률과 통계: 센서 데이터를 분석해야 해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6693,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 인간과 심리, 미술 감상과 비평, 정보, 소프트웨어와 생활</t>
+          <t>미술과 매체, 인간과 심리, 미술 감상과 비평, 정보, 소프트웨어와 생활, 확률과 통계, 화법과 언어</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -6308,7 +6707,9 @@
 인간과 심리: 사용자 행동을 이해해야 해서 → 사람의 인지와 심리를 배워요.
 미술 감상과 비평: 좋은 디자인을 보는 눈이 필요해서 → 작품 분석과 비평을 배워요.
 정보: 개발 과정과 구현을 이해해야 해서 → 프로그래밍 기초를 배워요.
-소프트웨어와 생활: 서비스로 생활 속 문제를 풀어서 → 소프트웨어로 문제 해결하는 법을 배워요.</t>
+소프트웨어와 생활: 서비스로 생활 속 문제를 풀어서 → 소프트웨어로 문제 해결하는 법을 배워요.
+확률과 통계: 사용성 테스트 결과를 분석해서 → 자료 정리와 통계적 추론을 배워요.
+화법과 언어: 사용자 인터뷰를 진행해야 해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6731,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>정보, 기하, 미술과 매체, 물리학</t>
+          <t>정보, 기하, 미술과 매체, 물리학, 미적분 I, 문학</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -6343,7 +6744,9 @@
           <t>정보: 콘텐츠를 프로그램으로 구현해서 → 프로그래밍과 알고리즘을 배워요.
 기하: 3차원 가상 공간을 만들어서 → 공간좌표와 벡터를 배워요.
 미술과 매체: 몰입감 있는 화면을 디자인해서 → 디지털 매체 표현을 배워요.
-물리학: 가상 물체의 움직임을 구현해서 → 힘과 운동, 빛의 원리를 배워요.</t>
+물리학: 가상 물체의 움직임을 구현해서 → 힘과 운동, 빛의 원리를 배워요.
+미적분 I: 3D 공간 움직임을 계산해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+문학: 몰입감 있는 이야기를 만들어서 → 작품 속 인물과 삶을 깊이 이해하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6768,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>정보, 물리학, 전자기와 양자, 직무 영어</t>
+          <t>정보, 물리학, 전자기와 양자, 직무 영어, 대수, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -6378,7 +6781,9 @@
           <t>정보: 네트워크 원리를 알아야 해서 → 컴퓨팅 시스템과 네트워크를 배워요.
 물리학: 신호가 전선·전파로 전달돼서 → 전기와 파동의 기초를 배워요.
 전자기와 양자: 무선·광통신을 다뤄서 → 전자기파와 빛의 성질을 배워요.
-직무 영어: 장비 문서와 자격증이 영어라서 → 업무용 영어를 배워요.</t>
+직무 영어: 장비 문서와 자격증이 영어라서 → 업무용 영어를 배워요.
+대수: IP 주소와 2진수 계산을 다뤄서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
+영어Ⅱ: 영문 장비 문서를 읽어야 해서 → 다양한 주제의 영어 글 이해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6805,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>정보, 실용 통계, 인공지능 수학, 논리와 사고</t>
+          <t>정보, 실용 통계, 인공지능 수학, 논리와 사고, 확률과 통계, 영어 I</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -6413,7 +6818,9 @@
           <t>정보: 데이터를 구조화해 저장해서 → 자료 구조와 프로그래밍을 배워요.
 실용 통계: 쌓인 데이터를 분석·활용해서 → 자료 정리와 통계 분석을 배워요.
 인공지능 수학: 데이터 처리에 수학이 쓰여서 → 벡터·행렬 등 자료 표현 수학을 배워요.
-논리와 사고: 데이터 검색 조건이 논리 구조라서 → 논리적 추론 방법을 배워요.</t>
+논리와 사고: 데이터 검색 조건이 논리 구조라서 → 논리적 추론 방법을 배워요.
+확률과 통계: 대용량 데이터를 분석·관리해서 → 자료 정리와 통계적 추론을 배워요.
+영어 I: 영문 기술 문서를 읽어야 해서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6842,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>정보, 수학과제 탐구, 금융과 경제생활, 논리와 사고</t>
+          <t>정보, 수학과제 탐구, 금융과 경제생활, 논리와 사고, 대수, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -6448,7 +6855,9 @@
           <t>정보: 분산 시스템을 프로그래밍해서 → 프로그래밍과 알고리즘을 배워요.
 수학과제 탐구: 암호 기술이 수학에 기반해서 → 수학 주제를 스스로 깊이 탐구해요.
 금융과 경제생활: 가상자산·금융 서비스에 쓰여서 → 금융의 원리와 경제생활을 배워요.
-논리와 사고: 거래 규칙을 코드로 설계해서 → 논리적 사고와 추론을 배워요.</t>
+논리와 사고: 거래 규칙을 코드로 설계해서 → 논리적 사고와 추론을 배워요.
+대수: 암호 기술의 수학 원리를 다뤄서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
+영어Ⅱ: 해외 개발 커뮤니티와 소통해서 → 다양한 주제의 영어 글 이해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6879,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 미술 감상과 비평, 정보, 매체 의사소통</t>
+          <t>미술과 매체, 미술 감상과 비평, 정보, 매체 의사소통, 영어 I, 화법과 언어</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -6483,7 +6892,9 @@
           <t>미술과 매체: 디지털 이미지로 화면을 만들어서 → 매체를 활용한 시각 표현을 배워요.
 미술 감상과 비평: 색·구도 감각이 필요해서 → 조형 요소와 작품 분석을 배워요.
 정보: 웹 구현 방식을 알아야 해서 → 프로그래밍 기초를 배워요.
-매체 의사소통: 정보를 효과적으로 전달해야 해서 → 매체 언어와 소통 방식을 배워요.</t>
+매체 의사소통: 정보를 효과적으로 전달해야 해서 → 매체 언어와 소통 방식을 배워요.
+영어 I: 해외 디자인 자료를 참고해서 → 영어 글의 핵심을 파악하는 법을 배워요.
+화법과 언어: 고객 요구를 듣고 시안을 설명해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6505,7 +6916,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>인공지능 수학, 정보, 인공지능 기초, 미적분Ⅱ, 실용 통계, 기하</t>
+          <t>인공지능 수학, 정보, 인공지능 기초, 미적분Ⅱ, 실용 통계, 기하, 확률과 통계, 미적분 I</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -6520,7 +6931,9 @@
 인공지능 기초: AI 전반을 이해해야 해서 → 기계학습의 원리와 활용을 배워요.
 미적분Ⅱ: 학습 과정이 미분으로 이뤄져서 → 심화 미분·적분을 배워요.
 실용 통계: 데이터의 특성을 파악해야 해서 → 자료 분석과 통계적 추론을 배워요.
-기하: 데이터를 벡터로 다뤄서 → 벡터와 공간 개념을 배워요.</t>
+기하: 데이터를 벡터로 다뤄서 → 벡터와 공간 개념을 배워요.
+확률과 통계: AI가 확률로 예측하는 원리라서 → 자료 정리와 통계적 추론을 배워요.
+미적분 I: AI 학습이 미분으로 이뤄져서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6955,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>정보, 물리학, 전자기와 양자, 물리학 실험, 미적분Ⅱ</t>
+          <t>정보, 물리학, 전자기와 양자, 물리학 실험, 미적분Ⅱ, 대수, 영어 I</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -6556,7 +6969,9 @@
 물리학: 회로와 센서를 이해해야 해서 → 전기와 운동의 기초를 배워요.
 전자기와 양자: 반도체·전자 부품을 다뤄서 → 전자기 현상과 양자 원리를 배워요.
 물리학 실험: 하드웨어를 직접 시험해서 → 측정과 실험 분석을 익혀요.
-미적분Ⅱ: 신호 처리·제어에 수학이 쓰여서 → 심화 미분·적분을 배워요.</t>
+미적분Ⅱ: 신호 처리·제어에 수학이 쓰여서 → 심화 미분·적분을 배워요.
+대수: 2진수와 비트 연산을 다뤄서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
+영어 I: 영문 칩 데이터시트를 읽어서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6993,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>정보, 수학과제 탐구, 논리와 사고, 인공지능 기초, 법과 사회</t>
+          <t>정보, 수학과제 탐구, 논리와 사고, 인공지능 기초, 법과 사회, 대수, 확률과 통계</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -6592,7 +7007,9 @@
 수학과제 탐구: 암호가 수학에 기반해서 → 수학 주제를 스스로 깊이 탐구해요.
 논리와 사고: 공격 경로를 추론해야 해서 → 논리적 분석과 추론을 배워요.
 인공지능 기초: AI 기반 공격·탐지가 늘어서 → 인공지능의 원리를 배워요.
-법과 사회: 개인정보 보호 법령을 지켜야 해서 → 법의 원리와 권리 보호를 배워요.</t>
+법과 사회: 개인정보 보호 법령을 지켜야 해서 → 법의 원리와 권리 보호를 배워요.
+대수: 암호의 수학 원리를 이해해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
+확률과 통계: 공격 패턴 데이터를 분석해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6614,7 +7031,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>물리학, 전자기와 양자, 정보, 미적분Ⅱ, 물리학 실험</t>
+          <t>물리학, 전자기와 양자, 정보, 미적분Ⅱ, 물리학 실험, 대수, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -6628,7 +7045,9 @@
 전자기와 양자: 반도체 소자가 양자 원리를 따라서 → 전자기와 양자 현상을 배워요.
 정보: 하드웨어와 소프트웨어가 맞물려서 → 컴퓨터 구조와 프로그래밍을 배워요.
 미적분Ⅱ: 회로 해석에 수학이 쓰여서 → 심화 미분·적분을 배워요.
-물리학 실험: 회로를 직접 측정·시험해서 → 실험 설계와 측정을 익혀요.</t>
+물리학 실험: 회로를 직접 측정·시험해서 → 실험 설계와 측정을 익혀요.
+대수: 2진수와 회로 논리를 다뤄서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
+영어Ⅱ: 영문 부품 사양서를 읽어서 → 다양한 주제의 영어 글 이해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -6650,7 +7069,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>정보, 소프트웨어와 생활, 인공지능 기초, 직무 영어</t>
+          <t>정보, 소프트웨어와 생활, 인공지능 기초, 직무 영어, 영어Ⅱ, 확률과 통계</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -6663,7 +7082,9 @@
           <t>정보: 서버와 네트워크를 다뤄서 → 컴퓨팅 시스템과 프로그래밍을 배워요.
 소프트웨어와 생활: 서비스가 생활에 쓰이는 방식을 알아야 해서 → 소프트웨어로 문제 해결하는 법을 배워요.
 인공지능 기초: AI 서비스가 클라우드에서 돌아가서 → 인공지능의 원리를 배워요.
-직무 영어: 기술 문서가 대부분 영어라서 → 업무용 영어 읽기를 배워요.</t>
+직무 영어: 기술 문서가 대부분 영어라서 → 업무용 영어 읽기를 배워요.
+영어Ⅱ: 영문 기술 문서를 매일 읽어서 → 다양한 주제의 영어 글 이해를 배워요.
+확률과 통계: 서버 사용량을 분석·예측해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6685,7 +7106,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>물리학, 전자기와 양자, 미적분Ⅱ, 정보, 물리학 실험</t>
+          <t>물리학, 전자기와 양자, 미적분Ⅱ, 정보, 물리학 실험, 미적분 I, 대수</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -6699,7 +7120,9 @@
 전자기와 양자: 전파·광통신을 다뤄서 → 전자기파와 빛의 성질을 배워요.
 미적분Ⅱ: 신호 분석에 삼각함수가 쓰여서 → 삼각함수 등의 미적분을 배워요.
 정보: 데이터 전송 방식을 알아야 해서 → 네트워크와 프로그래밍을 배워요.
-물리학 실험: 장비 성능을 측정해서 → 측정과 실험 분석을 익혀요.</t>
+물리학 실험: 장비 성능을 측정해서 → 측정과 실험 분석을 익혀요.
+미적분 I: 전파 신호의 변화를 분석해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
+대수: 신호 세기를 로그로 다뤄서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6721,7 +7144,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 세포와 물질대사, 화학, 생명과학 실험</t>
+          <t>생명과학, 세포와 물질대사, 화학, 생명과학 실험, 화법과 언어, 스포츠 생활1</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -6734,7 +7157,9 @@
           <t>생명과학: 동물의 몸과 질병을 알아야 해서 → 생명 현상과 항상성의 기초를 배워요.
 세포와 물질대사: 영양·대사 상태를 살펴야 해서 → 세포와 물질대사의 원리를 배워요.
 화학: 약품·소독제를 다뤄서 → 물질의 성질과 반응을 배워요.
-생명과학 실험: 검사 보조를 맡아서 → 실험 기구 사용과 관찰을 익혀요.</t>
+생명과학 실험: 검사 보조를 맡아서 → 실험 기구 사용과 관찰을 익혀요.
+화법과 언어: 보호자에게 돌봄법을 설명해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.
+스포츠 생활1: 동물을 안고 다루는 일이 많아서 → 꾸준한 운동 습관과 기초 체력을 길러요.</t>
         </is>
       </c>
     </row>
@@ -6756,7 +7181,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>물리학, 전자기와 양자, 생명과학, 물리학 실험, 화학</t>
+          <t>물리학, 전자기와 양자, 생명과학, 물리학 실험, 화학, 대수, 화법과 언어</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -6770,7 +7195,9 @@
 전자기와 양자: 엑스선·MRI가 전자기 원리라서 → 전자기파와 원자 구조를 배워요.
 생명과학: 촬영 부위의 인체 구조를 알아야 해서 → 사람 몸의 구조와 기능을 배워요.
 물리학 실험: 장비를 정확히 다뤄야 해서 → 측정과 실험 기능을 익혀요.
-화학: 방사성 동위원소·조영제를 다뤄서 → 원자와 물질의 기초를 배워요.</t>
+화학: 방사성 동위원소·조영제를 다뤄서 → 원자와 물질의 기초를 배워요.
+대수: 방사선 감쇠를 지수로 계산해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
+화법과 언어: 환자에게 검사 과정을 안내해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6792,7 +7219,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>경제, 법과 사회, 실용 통계, 사회와 문화, 직무 의사소통</t>
+          <t>경제, 법과 사회, 실용 통계, 사회와 문화, 직무 의사소통, 확률과 통계, 독서와 작문</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -6806,7 +7233,9 @@
 법과 사회: 의료법·건강보험 제도를 따라서 → 법의 원리와 사회 제도를 배워요.
 실용 통계: 환자·진료 자료로 운영을 개선해서 → 자료 분석과 해석을 배워요.
 사회와 문화: 다양한 환자·직원을 상대해서 → 사회 구조와 집단을 이해해요.
-직무 의사소통: 부서 간 조율이 많아서 → 업무 상황의 소통 방법을 배워요.</t>
+직무 의사소통: 부서 간 조율이 많아서 → 업무 상황의 소통 방법을 배워요.
+확률과 통계: 병원 운영 자료를 분석해서 → 자료 정리와 통계적 추론을 배워요.
+독서와 작문: 행정 문서와 보고서를 써서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6828,7 +7257,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 운동과 건강, 교육의 이해, 인간과 심리, 세포와 물질대사</t>
+          <t>생명과학, 운동과 건강, 교육의 이해, 인간과 심리, 세포와 물질대사, 화법과 언어, 스포츠 과학</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -6842,7 +7271,9 @@
 운동과 건강: 건강 습관을 지도해서 → 운동과 건강 관리 방법을 배워요.
 교육의 이해: 사람들을 가르치는 일이라 → 교육의 원리와 방법을 배워요.
 인간과 심리: 행동 변화를 이끌어야 해서 → 사람의 마음과 행동을 배워요.
-세포와 물질대사: 영양·비만 교육도 하므로 → 물질대사와 에너지 이용을 배워요.</t>
+세포와 물질대사: 영양·비만 교육도 하므로 → 물질대사와 에너지 이용을 배워요.
+화법과 언어: 건강 정보를 쉽게 강의해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.
+스포츠 과학: 운동과 건강의 원리를 알려서 → 몸의 움직임과 체력 향상 원리를 배워요.</t>
         </is>
       </c>
     </row>
@@ -6864,7 +7295,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 화학, 생명과학 실험, 실용 통계, 세포와 물질대사</t>
+          <t>생명과학, 화학, 생명과학 실험, 실용 통계, 세포와 물질대사, 확률과 통계, 영어 독해와 작문</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -6878,7 +7309,9 @@
 화학: 식품·환경 시료를 분석해서 → 물질의 성질과 반응을 배워요.
 생명과학 실험: 검사·실험이 주 업무라서 → 실험 설계와 분석 방법을 익혀요.
 실용 통계: 건강 조사 자료를 분석해서 → 자료 분석과 통계적 추론을 배워요.
-세포와 물질대사: 영양·대사 연구를 해서 → 세포와 물질대사의 원리를 배워요.</t>
+세포와 물질대사: 영양·대사 연구를 해서 → 세포와 물질대사의 원리를 배워요.
+확률과 통계: 질병 자료로 원인을 밝혀서 → 자료 정리와 통계적 추론을 배워요.
+영어 독해와 작문: 연구 결과를 논문으로 써서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6900,7 +7333,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 정보, 실용 통계, 법과 사회, 직무 영어</t>
+          <t>생명과학, 정보, 실용 통계, 법과 사회, 직무 영어, 확률과 통계, 영어 I</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -6914,7 +7347,9 @@
 정보: 의료 정보를 전산으로 다뤄서 → 데이터 처리와 프로그래밍을 배워요.
 실용 통계: 진료 통계를 작성해서 → 자료 정리와 통계 분석을 배워요.
 법과 사회: 개인정보·의료법을 지켜야 해서 → 법의 원리와 권리 보호를 배워요.
-직무 영어: 진단명·의학 용어가 영어라서 → 업무용 영어를 배워요.</t>
+직무 영어: 진단명·의학 용어가 영어라서 → 업무용 영어를 배워요.
+확률과 통계: 의료 데이터를 통계로 정리해서 → 자료 정리와 통계적 추론을 배워요.
+영어 I: 영문 의학 용어를 다뤄야 해서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6936,7 +7371,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>화학, 생명과학, 화학 반응의 세계, 세포와 물질대사, 생물의 유전, 화학 실험</t>
+          <t>화학, 생명과학, 화학 반응의 세계, 세포와 물질대사, 생물의 유전, 화학 실험, 확률과 통계, 영어 독해와 작문</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -6951,7 +7386,9 @@
 화학 반응의 세계: 약물을 합성해야 해서 → 산·염기, 산화·환원 반응을 깊이 배워요.
 세포와 물질대사: 약이 세포에 작용해서 → 세포 구조와 물질대사를 배워요.
 생물의 유전: 유전자 표적 치료제가 늘어서 → 유전 원리와 유전자 기술을 배워요.
-화학 실험: 실험으로 물질을 검증해서 → 합성·분석 실험 방법을 익혀요.</t>
+화학 실험: 실험으로 물질을 검증해서 → 합성·분석 실험 방법을 익혀요.
+확률과 통계: 임상 시험으로 약효를 검증해서 → 자료 정리와 통계적 추론을 배워요.
+영어 독해와 작문: 해외 논문을 읽고 써야 해서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -6973,7 +7410,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>인간과 심리, 교육의 이해, 생명과학, 사회와 문화</t>
+          <t>인간과 심리, 교육의 이해, 생명과학, 사회와 문화, 문학, 화법과 언어</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -6986,7 +7423,9 @@
           <t>인간과 심리: 아이의 불안을 이해해야 해서 → 발달과 마음의 원리를 배워요.
 교육의 이해: 놀이로 치료 과정을 알려 줘서 → 교육의 원리와 방법을 배워요.
 생명과학: 질병과 치료를 쉽게 설명해야 해서 → 인체와 질병의 기초를 배워요.
-사회와 문화: 다양한 가족을 지원해서 → 가족과 사회 구조를 이해해요.</t>
+사회와 문화: 다양한 가족을 지원해서 → 가족과 사회 구조를 이해해요.
+문학: 동화로 아이의 마음을 이해해서 → 작품 속 인물과 삶을 깊이 이해하는 법을 배워요.
+화법과 언어: 아이 눈높이에 맞춰 말해야 해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7447,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>물리학, 전자기와 양자, 생명과학, 물리학 실험</t>
+          <t>물리학, 전자기와 양자, 생명과학, 물리학 실험, 대수, 화법과 언어</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -7021,7 +7460,9 @@
           <t>물리학: 렌즈가 빛을 굴절시켜서 → 빛과 파동의 기초를 배워요.
 전자기와 양자: 빛의 성질을 깊이 알아야 해서 → 빛의 파동성과 입자성을 배워요.
 생명과학: 눈의 구조와 시각을 알아야 해서 → 신경계와 감각의 기초를 배워요.
-물리학 실험: 굴절·초점을 정확히 재야 해서 → 실험으로 측정하는 법을 익혀요.</t>
+물리학 실험: 굴절·초점을 정확히 재야 해서 → 실험으로 측정하는 법을 익혀요.
+대수: 렌즈 도수를 정확히 계산해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
+화법과 언어: 고객에게 시력 상태를 설명해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7484,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>언어생활 탐구, 인간과 심리, 생명과학, 교육의 이해</t>
+          <t>언어생활 탐구, 인간과 심리, 생명과학, 교육의 이해, 화법과 언어, 문학</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -7056,7 +7497,9 @@
           <t>언어생활 탐구: 말소리와 언어 구조를 다뤄서 → 음운·문법 등 국어의 원리를 배워요.
 인간과 심리: 내담자의 마음을 이해해야 해서 → 발달과 심리의 원리를 배워요.
 생명과학: 발성·청각 기관을 알아야 해서 → 신경계와 인체 구조를 배워요.
-교육의 이해: 단계적으로 훈련시켜야 해서 → 학습과 교육의 원리를 배워요.</t>
+교육의 이해: 단계적으로 훈련시켜야 해서 → 학습과 교육의 원리를 배워요.
+화법과 언어: 말소리와 언어 구조를 분석해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.
+문학: 이야기로 표현력을 키워 줘서 → 작품 속 인물과 삶을 깊이 이해하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7521,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 화학, 세포와 물질대사, 화학 실험, 운동과 건강</t>
+          <t>생명과학, 화학, 세포와 물질대사, 화학 실험, 운동과 건강, 대수, 화법과 언어</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -7092,7 +7535,9 @@
 화학: 영양소가 화학 물질이라서 → 물질의 구성과 반응을 배워요.
 세포와 물질대사: 영양소가 에너지로 바뀌는 과정이라 → 세포 호흡과 물질대사를 배워요.
 화학 실험: 식품 성분을 분석하기도 해서 → 실험 방법과 분석을 익혀요.
-운동과 건강: 체중·건강 관리를 지도해서 → 운동과 건강 관리 방법을 배워요.</t>
+운동과 건강: 체중·건강 관리를 지도해서 → 운동과 건강 관리 방법을 배워요.
+대수: 열량과 영양소를 계산해야 해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
+화법과 언어: 식습관 상담을 해야 해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7559,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 화학, 생명과학 실험, 화학 실험, 생태와 환경</t>
+          <t>생명과학, 화학, 생명과학 실험, 화학 실험, 생태와 환경, 확률과 통계, 화법과 언어</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -7128,7 +7573,9 @@
 화학: 소독제·오염 물질을 다뤄서 → 물질의 성질과 반응을 배워요.
 생명과학 실험: 미생물 검사를 해서 → 미생물 관찰과 실험 방법을 익혀요.
 화학 실험: 수질·식품을 분석해서 → 시료 분석 실험을 익혀요.
-생태와 환경: 생활 환경을 관리해서 → 환경 문제와 생태적 삶을 배워요.</t>
+생태와 환경: 생활 환경을 관리해서 → 환경 문제와 생태적 삶을 배워요.
+확률과 통계: 위생 검사 결과를 판단해서 → 자료 정리와 통계적 추론을 배워요.
+화법과 언어: 시민에게 위생 수칙을 알려서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7597,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 세포와 물질대사, 운동과 건강, 화학</t>
+          <t>생명과학, 세포와 물질대사, 운동과 건강, 화학, 스포츠 생활1, 스포츠 과학, 화법과 언어</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -7163,7 +7610,10 @@
           <t>생명과학: 위급한 몸 상태를 판단해야 해서 → 순환·호흡 등 인체 기능을 배워요.
 세포와 물질대사: 쇼크·호흡 곤란을 이해해야 해서 → 세포 호흡과 물질대사를 배워요.
 운동과 건강: 체력과 응급 처치가 필수라서 → 체력 관리와 안전·응급 처치를 배워요.
-화학: 응급 약물을 다뤄서 → 물질의 성질과 반응을 배워요.</t>
+화학: 응급 약물을 다뤄서 → 물질의 성질과 반응을 배워요.
+스포츠 생활1: 환자를 옮기는 강한 체력이 필요해서 → 꾸준한 운동 습관과 기초 체력을 길러요.
+스포츠 과학: 몸의 손상과 회복을 이해해서 → 몸의 움직임과 체력 향상 원리를 배워요.
+화법과 언어: 위급할 때 정확히 소통해야 해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7185,7 +7635,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 화학, 세포와 물질대사, 생물의 유전, 화학 반응의 세계, 생명과학 실험</t>
+          <t>생명과학, 화학, 세포와 물질대사, 생물의 유전, 화학 반응의 세계, 생명과학 실험, 확률과 통계, 영어 독해와 작문</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -7200,7 +7650,9 @@
 세포와 물질대사: 질병이 세포에서 시작돼서 → 세포와 물질대사를 깊이 배워요.
 생물의 유전: 유전체 연구가 핵심이라 → 유전 원리와 유전자 기술을 배워요.
 화학 반응의 세계: 약물·생체 반응을 분석해서 → 화학 반응을 깊이 배워요.
-생명과학 실험: 실험으로 가설을 검증해서 → 실험 설계와 분석을 익혀요.</t>
+생명과학 실험: 실험으로 가설을 검증해서 → 실험 설계와 분석을 익혀요.
+확률과 통계: 실험 결과를 통계로 검증해서 → 자료 정리와 통계적 추론을 배워요.
+영어 독해와 작문: 연구를 영어 논문으로 발표해서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7674,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>물리학, 전자기와 양자, 미적분Ⅱ, 생명과학, 물리학 실험</t>
+          <t>물리학, 전자기와 양자, 미적분Ⅱ, 생명과학, 물리학 실험, 대수, 영어 독해와 작문</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -7236,7 +7688,9 @@
 전자기와 양자: 방사선이 원자 수준의 현상이라 → 전자기파와 양자 현상을 배워요.
 미적분Ⅱ: 방사선량을 정밀하게 계산해서 → 지수함수 등 심화 미적분을 배워요.
 생명과학: 방사선이 인체에 주는 영향을 알아야 해서 → 세포와 인체의 기초를 배워요.
-물리학 실험: 선량을 측정·검증해서 → 정밀 측정과 분석을 익혀요.</t>
+물리학 실험: 선량을 측정·검증해서 → 정밀 측정과 분석을 익혀요.
+대수: 방사선량을 지수·로그로 계산해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
+영어 독해와 작문: 해외 의학물리 논문을 읽어서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7712,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>실생활 영어 회화, 직무 의사소통, 생명과학, 중국어 회화, 인간과 심리</t>
+          <t>실생활 영어 회화, 직무 의사소통, 생명과학, 중국어 회화, 인간과 심리, 화법과 언어, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -7272,7 +7726,9 @@
 직무 의사소통: 환자와 의료진을 연결해서 → 업무 상황의 말하기·듣기를 배워요.
 생명과학: 진료 내용을 이해·설명해야 해서 → 인체와 질병의 기초를 배워요.
 중국어 회화: 중국어권 환자도 많이 찾아와서 → 생활 중국어 회화를 배워요.
-인간과 심리: 불안한 환자를 응대해서 → 사람의 마음과 감정을 배워요.</t>
+인간과 심리: 불안한 환자를 응대해서 → 사람의 마음과 감정을 배워요.
+화법과 언어: 환자에게 진료 과정을 안내해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.
+영어Ⅱ: 외국인 환자와 소통해야 해서 → 다양한 주제의 영어 글 이해를 배워요.</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7750,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 화학, 세포와 물질대사, 생물의 유전, 화학 반응의 세계, 미적분Ⅱ</t>
+          <t>생명과학, 화학, 세포와 물질대사, 생물의 유전, 화학 반응의 세계, 미적분Ⅱ, 확률과 통계, 영어 독해와 작문</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -7309,7 +7765,9 @@
 세포와 물질대사: 질병이 세포 수준에서 생겨서 → 세포와 물질대사를 깊이 배워요.
 생물의 유전: 유전 질환을 진단·상담해서 → 유전 원리와 유전자 기술을 배워요.
 화학 반응의 세계: 약이 몸에서 작용하는 원리라서 → 산·염기, 산화·환원을 깊이 배워요.
-미적분Ⅱ: 의학 연구에 수리 역량이 필요해서 → 심화 미분·적분을 배워요.</t>
+미적분Ⅱ: 의학 연구에 수리 역량이 필요해서 → 심화 미분·적분을 배워요.
+확률과 통계: 검사 수치로 진단을 내려야 해서 → 자료 정리와 통계적 추론을 배워요.
+영어 독해와 작문: 최신 의학 논문을 읽어야 해서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7789,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>화학, 생명과학, 법과 사회, 실용 통계, 심화 영어 독해와 작문</t>
+          <t>화학, 생명과학, 법과 사회, 실용 통계, 심화 영어 독해와 작문, 독서와 작문, 확률과 통계</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -7345,7 +7803,9 @@
 생명과학: 약효·부작용 자료를 이해해서 → 인체와 면역의 기초를 배워요.
 법과 사회: 약사법 등 규정을 따라야 해서 → 법의 원리와 제도를 배워요.
 실용 통계: 임상시험 결과를 해석해서 → 통계적 추론과 자료 해석을 배워요.
-심화 영어 독해와 작문: 해외 허가 문서를 다뤄서 → 전문적인 영어 읽기·쓰기를 배워요.</t>
+심화 영어 독해와 작문: 해외 허가 문서를 다뤄서 → 전문적인 영어 읽기·쓰기를 배워요.
+독서와 작문: 허가 서류를 정확히 작성해서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.
+확률과 통계: 임상 자료의 타당성을 검토해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7827,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 화학, 생명과학 실험, 화학 실험, 세포와 물질대사, 생물의 유전</t>
+          <t>생명과학, 화학, 생명과학 실험, 화학 실험, 세포와 물질대사, 생물의 유전, 확률과 통계, 대수</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -7382,7 +7842,9 @@
 생명과학 실험: 검사가 곧 실험이라 → 현미경 관찰과 실험 방법을 익혀요.
 화학 실험: 정확한 시약 조제가 필요해서 → 용액 조제와 분석 실험을 익혀요.
 세포와 물질대사: 혈액·조직 세포를 분석해서 → 세포 구조와 대사를 배워요.
-생물의 유전: 유전자 검사도 맡아서 → 유전 원리와 유전자 분석을 배워요.</t>
+생물의 유전: 유전자 검사도 맡아서 → 유전 원리와 유전자 분석을 배워요.
+확률과 통계: 검사 수치의 정상 범위를 판단해서 → 자료 정리와 통계적 추론을 배워요.
+대수: 시약 농도와 희석을 계산해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7866,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>인간과 심리, 생명과학, 실용 통계, 사회와 문화</t>
+          <t>인간과 심리, 생명과학, 실용 통계, 사회와 문화, 확률과 통계, 문학, 화법과 언어</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -7417,7 +7879,10 @@
           <t>인간과 심리: 심리학이 직업의 기본이라서 → 마음과 행동의 원리를 배워요.
 생명과학: 뇌·신경과 마음이 연결돼서 → 신경계와 호르몬의 기초를 배워요.
 실용 통계: 심리 검사 점수를 해석해서 → 자료 분석과 통계 해석을 배워요.
-사회와 문화: 개인의 문제가 환경과 연결돼서 → 사회 구조와 문화를 이해해요.</t>
+사회와 문화: 개인의 문제가 환경과 연결돼서 → 사회 구조와 문화를 이해해요.
+확률과 통계: 심리검사 점수를 해석해야 해서 → 자료 정리와 통계적 추론을 배워요.
+문학: 다양한 삶과 감정을 이해해서 → 작품 속 인물과 삶을 깊이 이해하는 법을 배워요.
+화법과 언어: 내담자와 공감하며 대화해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7904,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 화학, 실용 통계, 윤리문제 탐구, 직무 영어</t>
+          <t>생명과학, 화학, 실용 통계, 윤리문제 탐구, 직무 영어, 확률과 통계, 화법과 언어</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -7453,7 +7918,9 @@
 화학: 약물 정보를 이해해야 해서 → 물질과 화학 반응의 기초를 배워요.
 실용 통계: 임상 자료를 정확히 관리해서 → 자료 수집·분석을 배워요.
 윤리문제 탐구: 참여자 권리 보호가 중요해서 → 생명 윤리 등 윤리 문제를 탐구해요.
-직무 영어: 해외 제약사와 문서를 주고받아서 → 업무용 영어를 배워요.</t>
+직무 영어: 해외 제약사와 문서를 주고받아서 → 업무용 영어를 배워요.
+확률과 통계: 임상 시험 자료를 관리해서 → 자료 정리와 통계적 추론을 배워요.
+화법과 언어: 참여자에게 연구를 설명해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7475,7 +7942,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 인간과 심리, 운동과 건강, 물리학</t>
+          <t>생명과학, 인간과 심리, 운동과 건강, 물리학, 스포츠 과학, 화법과 언어</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -7488,7 +7955,9 @@
           <t>생명과학: 신경·근육 기능을 알아야 해서 → 인체 구조와 신경계를 배워요.
 인간과 심리: 환자의 의욕을 북돋워야 해서 → 마음과 행동의 원리를 배워요.
 운동과 건강: 신체 활동으로 재활을 도와서 → 운동과 건강 관리를 배워요.
-물리학: 몸의 움직임을 분석해야 해서 → 힘과 운동의 원리를 배워요.</t>
+물리학: 몸의 움직임을 분석해야 해서 → 힘과 운동의 원리를 배워요.
+스포츠 과학: 몸의 움직임과 재활 원리를 알아서 → 몸의 움직임과 체력 향상 원리를 배워요.
+화법과 언어: 환자를 격려하며 치료해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7979,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 화학, 직무 의사소통, 경제, 인간과 심리</t>
+          <t>생명과학, 화학, 직무 의사소통, 경제, 인간과 심리, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -7524,7 +7993,9 @@
 화학: 약 성분을 이해해야 해서 → 물질과 화학 반응의 기초를 배워요.
 직무 의사소통: 제품을 설득력 있게 소개해서 → 업무 상황의 말하기를 배워요.
 경제: 시장과 판매 전략을 이해해서 → 시장 원리와 경제 활동을 배워요.
-인간과 심리: 고객의 요구를 파악해서 → 사람의 마음과 행동을 배워요.</t>
+인간과 심리: 고객의 요구를 파악해서 → 사람의 마음과 행동을 배워요.
+화법과 언어: 의료진을 설득력 있게 만나서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.
+영어 I: 해외 약품 자료를 읽어야 해서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7546,7 +8017,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 물리학, 인간과 심리, 언어생활 탐구, 실용 통계</t>
+          <t>생명과학, 물리학, 인간과 심리, 언어생활 탐구, 실용 통계, 확률과 통계, 화법과 언어</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -7560,7 +8031,9 @@
 물리학: 소리의 크기·높낮이를 측정하므로 → 파동과 소리의 성질을 배워요.
 인간과 심리: 청각 장애로 힘든 마음을 이해해야 해서 → 인간의 감정과 심리를 배워요.
 언어생활 탐구: 말소리를 듣고 구별하는 훈련을 하므로 → 국어의 말소리와 발음 원리를 배워요.
-실용 통계: 청력 검사 결과를 해석해야 해서 → 자료를 정리하고 분석하는 법을 배워요.</t>
+실용 통계: 청력 검사 결과를 해석해야 해서 → 자료를 정리하고 분석하는 법을 배워요.
+확률과 통계: 청력 검사 수치를 비교·해석해야 해서 → 자료 정리와 통계적 추론을 배워요.
+화법과 언어: 환자에게 결과를 쉽게 설명해야 해서 → 상황에 맞는 말하기와 언어 원리를 배워요.</t>
         </is>
       </c>
     </row>
@@ -7582,7 +8055,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>화학, 생명과학, 물리학, 기하, 물질과 에너지</t>
+          <t>화학, 생명과학, 물리학, 기하, 물질과 에너지, 미적분 I, 영어 I</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -7596,7 +8069,9 @@
 생명과학: 치아와 턱의 구조를 알아야 해서 → 사람 몸의 구조와 기능을 배워요.
 물리학: 씹는 힘을 견디는 보철물을 만들어야 해서 → 힘과 운동, 물체의 성질을 배워요.
 기하: 3D 스캔·CAD로 치아 모양을 설계하므로 → 공간도형과 좌표를 배워요.
-물질과 에너지: 재료를 녹이고 굳히는 과정을 다뤄서 → 물질의 상태 변화와 성질을 깊이 배워요.</t>
+물질과 에너지: 재료를 녹이고 굳히는 과정을 다뤄서 → 물질의 상태 변화와 성질을 깊이 배워요.
+미적분 I: 보철물의 곡면과 치수를 정밀하게 다뤄서 → 함수의 변화와 그래프 해석을 배워요.
+영어 I: 최신 재료·장비 설명서를 읽어야 해서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -7618,7 +8093,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 화학, 세포와 물질대사, 생명과학 실험, 직무 의사소통</t>
+          <t>생명과학, 화학, 세포와 물질대사, 생명과학 실험, 직무 의사소통, 화법과 언어, 확률과 통계</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -7632,7 +8107,9 @@
 화학: 불소·소독약 등 약품을 다루므로 → 물질의 성질과 화학 반응의 기초를 배워요.
 세포와 물질대사: 세균이 충치를 만드는 과정을 알아야 해서 → 세포와 물질대사의 원리를 배워요.
 생명과학 실험: 위생·감염 관리가 중요해서 → 실험 도구 사용과 안전 수칙을 익혀요.
-직무 의사소통: 환자에게 관리법을 설명해야 해서 → 업무 상황에 맞는 말하기를 배워요.</t>
+직무 의사소통: 환자에게 관리법을 설명해야 해서 → 업무 상황에 맞는 말하기를 배워요.
+화법과 언어: 환자에게 구강 관리법을 안내해야 해서 → 정확하고 친절한 말하기를 배워요.
+확률과 통계: 구강 검진 자료를 기록·관리해야 해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7654,7 +8131,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 화학, 세포와 물질대사, 화학 반응의 세계, 생물의 유전, 미적분Ⅱ</t>
+          <t>생명과학, 화학, 세포와 물질대사, 화학 반응의 세계, 생물의 유전, 미적분Ⅱ, 확률과 통계, 영어 독해와 작문</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -7669,7 +8146,9 @@
 세포와 물질대사: 염증·치유 과정을 알아야 해서 → 세포 호흡과 물질대사의 원리를 배워요.
 화학 반응의 세계: 약이 몸에서 작용하는 원리를 알아야 해서 → 산·염기, 산화·환원 반응을 배워요.
 생물의 유전: 유전성 구강 질환을 이해해야 해서 → 유전의 원리와 유전자 기술을 배워요.
-미적분Ⅱ: 치의예과 진학에 수학 역량이 중요해서 → 심화된 미분·적분을 배워요.</t>
+미적분Ⅱ: 치의예과 진학에 수학 역량이 중요해서 → 심화된 미분·적분을 배워요.
+확률과 통계: 치료 효과와 임상 자료를 판단해야 해서 → 확률과 통계적 추론을 배워요.
+영어 독해와 작문: 최신 치의학 논문을 읽어야 해서 → 영어 글을 읽고 요약하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7691,7 +8170,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 화학, 한문, 세포와 물질대사, 한문 고전 읽기</t>
+          <t>생명과학, 화학, 한문, 세포와 물질대사, 한문 고전 읽기, 독서와 작문, 확률과 통계</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -7705,7 +8184,9 @@
 화학: 한약재의 성분과 효능을 다루므로 → 물질의 성질과 화학 반응의 기초를 배워요.
 한문: 한의학 원전이 한문으로 쓰여 있어서 → 한자와 한문 문장의 기초를 배워요.
 세포와 물질대사: 몸의 대사 상태를 판단해야 해서 → 세포 호흡과 물질대사의 원리를 배워요.
-한문 고전 읽기: 동의보감 같은 고전을 읽어야 해서 → 한문 고전을 해석하는 힘을 길러요.</t>
+한문 고전 읽기: 동의보감 같은 고전을 읽어야 해서 → 한문 고전을 해석하는 힘을 길러요.
+독서와 작문: 한의학 고전과 진료 기록을 다뤄서 → 깊이 읽고 논리적으로 쓰는 법을 배워요.
+확률과 통계: 치료 효과를 객관적으로 검증해야 해서 → 자료 분석과 통계적 추론을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7727,7 +8208,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 기하, 정보, 미술 감상과 비평, 소프트웨어와 생활</t>
+          <t>미술과 매체, 기하, 정보, 미술 감상과 비평, 소프트웨어와 생활, 미적분 I, 영어 I</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -7741,7 +8222,9 @@
 기하: 입체를 좌표와 도형으로 다루므로 → 공간도형·벡터·좌표를 배워요.
 정보: 모델링 프로그램과 데이터를 다루므로 → 컴퓨팅 사고와 프로그래밍 기초를 배워요.
 미술 감상과 비평: 형태·색감 보는 눈이 필요해서 → 작품을 분석하고 평가하는 법을 배워요.
-소프트웨어와 생활: 다양한 디자인 툴을 활용해서 → 생활 속 소프트웨어 활용을 배워요.</t>
+소프트웨어와 생활: 다양한 디자인 툴을 활용해서 → 생활 속 소프트웨어 활용을 배워요.
+미적분 I: 곡면과 움직임을 수학적으로 다뤄서 → 함수와 변화율의 개념을 배워요.
+영어 I: 3D 툴과 해외 튜토리얼이 영어라서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -7763,7 +8246,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>경제, 인간과 심리, 실용 통계, 법과 사회, 매체 의사소통</t>
+          <t>경제, 인간과 심리, 실용 통계, 법과 사회, 매체 의사소통, 확률과 통계, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -7777,7 +8260,9 @@
 인간과 심리: 선수의 컨디션·멘탈을 챙겨야 해서 → 인간의 감정과 동기를 배워요.
 실용 통계: 경기 기록으로 팀 전력을 분석해서 → 자료를 정리하고 해석하는 법을 배워요.
 법과 사회: 선수 계약과 권리를 다뤄야 해서 → 계약 등 생활 속 법을 배워요.
-매체 의사소통: 방송·SNS로 팀을 홍보하므로 → 매체 특성에 맞는 소통을 배워요.</t>
+매체 의사소통: 방송·SNS로 팀을 홍보하므로 → 매체 특성에 맞는 소통을 배워요.
+확률과 통계: 선수 경기 기록을 분석해 전략을 짜서 → 자료 정리와 통계 해석을 배워요.
+영어Ⅱ: 해외 리그·구단과 소통할 일이 많아서 → 다양한 영어 글과 표현을 익혀요.</t>
         </is>
       </c>
     </row>
@@ -7799,7 +8284,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>음악 감상과 비평, 경제, 매체 의사소통, 사회와 문화, 직무 의사소통</t>
+          <t>음악 감상과 비평, 경제, 매체 의사소통, 사회와 문화, 직무 의사소통, 독서와 작문, 화법과 언어</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -7813,7 +8298,9 @@
 경제: 예산을 짜고 수익을 계산해야 해서 → 시장과 경제 활동의 원리를 배워요.
 매체 의사소통: 공연을 알리는 홍보가 중요해서 → 매체 특성에 맞는 소통을 배워요.
 사회와 문화: 관객의 취향과 문화 흐름을 읽어야 해서 → 사회 현상과 대중문화를 배워요.
-직무 의사소통: 출연진·스태프와 협의가 많아서 → 업무 상황에 맞는 말하기를 배워요.</t>
+직무 의사소통: 출연진·스태프와 협의가 많아서 → 업무 상황에 맞는 말하기를 배워요.
+독서와 작문: 기획서와 홍보 글을 직접 써야 해서 → 설득력 있는 글쓰기를 배워요.
+화법과 언어: 아티스트·관계자와 협의가 많아서 → 상황에 맞는 말하기와 협상을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7835,7 +8322,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>미술 감상과 비평, 미술과 매체, 화학, 동아시아 역사 기행</t>
+          <t>미술 감상과 비평, 미술과 매체, 화학, 동아시아 역사 기행, 문학, 화법과 언어</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -7848,7 +8335,9 @@
           <t>미술 감상과 비평: 조형미를 보는 안목이 필요해서 → 작품을 분석하고 평가하는 법을 배워요.
 미술과 매체: 다양한 재료로 작품을 표현해서 → 여러 매체를 활용한 표현을 배워요.
 화학: 유약·염료·금속의 변화를 다루므로 → 물질의 성질과 화학 반응의 기초를 배워요.
-동아시아 역사 기행: 전통 공예의 뿌리를 알아야 해서 → 동아시아의 역사와 문화를 배워요.</t>
+동아시아 역사 기행: 전통 공예의 뿌리를 알아야 해서 → 동아시아의 역사와 문화를 배워요.
+문학: 작품에 담을 이야기와 감성이 중요해서 → 문학 작품의 표현과 정서를 배워요.
+화법과 언어: 전시·판매 때 작품을 소개해야 해서 → 효과적으로 말하고 설명하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7870,7 +8359,7 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 문학과 영상, 매체 의사소통, 인간과 심리, 음악과 미디어</t>
+          <t>미술과 매체, 문학과 영상, 매체 의사소통, 인간과 심리, 음악과 미디어, 문학, 화법과 언어</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -7884,7 +8373,9 @@
 문학과 영상: 짧은 영상에 이야기를 담아야 해서 → 문학과 영상의 서사 표현을 배워요.
 매체 의사소통: 광고는 대중에게 메시지를 전하므로 → 매체의 특성과 소통 방식을 배워요.
 인간과 심리: 소비자의 마음을 움직여야 해서 → 인간의 감정과 행동을 배워요.
-음악과 미디어: 광고 음악·효과음을 함께 고르므로 → 미디어 속 음악의 역할을 배워요.</t>
+음악과 미디어: 광고 음악·효과음을 함께 고르므로 → 미디어 속 음악의 역할을 배워요.
+문학: 짧은 영상에 이야기를 담아야 해서 → 서사 구조와 비유 표현을 배워요.
+화법과 언어: 광고주에게 아이디어를 발표해야 해서 → 설득력 있는 말하기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -7906,7 +8397,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>음악 감상과 비평, 교육의 이해, 음악과 미디어, 한문</t>
+          <t>음악 감상과 비평, 교육의 이해, 음악과 미디어, 한문, 화법과 언어, 문학</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -7919,7 +8410,9 @@
           <t>음악 감상과 비평: 국악의 특징을 설명해야 해서 → 음악을 감상하고 분석하는 법을 배워요.
 교육의 이해: 배우는 사람에 맞게 가르쳐야 해서 → 교육의 원리와 방법을 배워요.
 음악과 미디어: 영상·디지털 수업 자료를 만들어서 → 미디어 속 음악 활용을 배워요.
-한문: 판소리·정가의 가사에 한자어가 많아서 → 한자와 한문 문장의 기초를 배워요.</t>
+한문: 판소리·정가의 가사에 한자어가 많아서 → 한자와 한문 문장의 기초를 배워요.
+화법과 언어: 학생에게 장단과 기법을 설명해야 해서 → 알기 쉽게 말하는 법을 배워요.
+문학: 판소리·민요 가사를 이해해야 해서 → 고전 시가와 문학 표현을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7941,7 +8434,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>음악 감상과 비평, 음악과 미디어, 한문, 동아시아 역사 기행</t>
+          <t>음악 감상과 비평, 음악과 미디어, 한문, 동아시아 역사 기행, 문학, 영어 I</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -7954,7 +8447,9 @@
           <t>음악 감상과 비평: 여러 연주를 듣고 해석해야 해서 → 음악을 감상하고 평가하는 법을 배워요.
 음악과 미디어: 국악을 영상·음원으로 알리므로 → 미디어 속 음악 활용을 배워요.
 한문: 옛 노랫말에 한자어가 많아서 → 한자와 한문 문장의 기초를 배워요.
-동아시아 역사 기행: 국악의 역사적 배경을 알아야 해서 → 동아시아의 역사와 문화를 배워요.</t>
+동아시아 역사 기행: 국악의 역사적 배경을 알아야 해서 → 동아시아의 역사와 문화를 배워요.
+문학: 판소리 사설과 가사를 해석해야 해서 → 고전 문학의 정서와 표현을 배워요.
+영어 I: 해외 공연에서 국악을 알릴 기회가 많아서 → 기초 영어 표현을 익혀요.</t>
         </is>
       </c>
     </row>
@@ -7976,7 +8471,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 미술 감상과 비평, 음악과 미디어, 정보, 문학과 영상</t>
+          <t>미술과 매체, 미술 감상과 비평, 음악과 미디어, 정보, 문학과 영상, 미적분 I, 영어 I</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -7990,7 +8485,9 @@
 미술 감상과 비평: 색·구도 보는 감각이 필요해서 → 작품을 분석하고 평가하는 법을 배워요.
 음악과 미디어: 음악 리듬에 맞춰 움직임을 만들어서 → 미디어 속 음악의 역할을 배워요.
 정보: 그래픽 프로그램과 코드를 다루므로 → 컴퓨팅 사고와 프로그래밍 기초를 배워요.
-문학과 영상: 영상의 흐름과 연출을 알아야 해서 → 영상의 서사와 표현 방식을 배워요.</t>
+문학과 영상: 영상의 흐름과 연출을 알아야 해서 → 영상의 서사와 표현 방식을 배워요.
+미적분 I: 움직임의 속도 변화(이징)를 조절해서 → 함수와 변화율의 개념을 배워요.
+영어 I: 툴 사용법과 해외 레퍼런스가 영어라서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -8012,7 +8509,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>미술 감상과 비평, 미술과 매체, 문학과 영상, 기하, 세계사</t>
+          <t>미술 감상과 비평, 미술과 매체, 문학과 영상, 기하, 세계사, 문학, 대수</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -8026,7 +8523,9 @@
 미술과 매체: 모형·디지털로 무대를 표현해서 → 다양한 매체를 활용한 표현을 배워요.
 문학과 영상: 대본을 읽고 장면을 구상해야 해서 → 작품의 서사와 장면 표현을 배워요.
 기하: 무대 도면과 공간을 설계하므로 → 공간도형과 좌표를 배워요.
-세계사: 작품 속 시대 배경을 고증해야 해서 → 세계 여러 시대의 역사를 배워요.</t>
+세계사: 작품 속 시대 배경을 고증해야 해서 → 세계 여러 시대의 역사를 배워요.
+문학: 작품의 주제와 분위기를 무대로 옮겨서 → 희곡·소설을 해석하는 방법을 배워요.
+대수: 도면의 치수와 비율을 계산해야 해서 → 수와 식을 다루는 계산력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8547,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>미술 감상과 비평, 세계사, 문학과 영상, 미술과 매체, 화학</t>
+          <t>미술 감상과 비평, 세계사, 문학과 영상, 미술과 매체, 화학, 문학, 화법과 언어</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -8062,7 +8561,9 @@
 세계사: 시대별 복식을 고증해야 해서 → 세계 여러 시대의 역사와 문화를 배워요.
 문학과 영상: 인물의 성격을 의상으로 표현해서 → 작품 속 인물과 서사를 배워요.
 미술과 매체: 디자인 스케치를 여러 방식으로 그려서 → 다양한 매체를 활용한 표현을 배워요.
-화학: 옷감과 염색 재료를 다루므로 → 물질의 성질과 화학 반응의 기초를 배워요.</t>
+화학: 옷감과 염색 재료를 다루므로 → 물질의 성질과 화학 반응의 기초를 배워요.
+문학: 인물의 성격을 의상으로 표현해야 해서 → 작품 속 인물과 시대 해석을 배워요.
+화법과 언어: 연출가와 콘셉트를 맞춰야 해서 → 생각을 정확히 전달하는 말하기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8585,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>운동과 건강, 교육의 이해, 음악 감상과 비평, 생명과학, 인간과 심리</t>
+          <t>운동과 건강, 교육의 이해, 음악 감상과 비평, 생명과학, 인간과 심리, 스포츠 과학, 화법과 언어</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -8098,7 +8599,9 @@
 교육의 이해: 수준에 맞게 가르쳐야 해서 → 교육의 원리와 방법을 배워요.
 음악 감상과 비평: 음악에 맞춰 동작을 지도해서 → 음악을 감상하고 분석하는 법을 배워요.
 생명과학: 근육·뼈의 움직임을 알아야 해서 → 사람 몸의 구조와 기능을 배워요.
-인간과 심리: 수강생의 자신감을 키워야 해서 → 인간의 감정과 동기를 배워요.</t>
+인간과 심리: 수강생의 자신감을 키워야 해서 → 인간의 감정과 동기를 배워요.
+스포츠 과학: 부상 없이 동작을 지도해야 해서 → 운동 원리와 신체 관리법을 배워요.
+화법과 언어: 동작을 말로 정확히 설명해야 해서 → 알기 쉽게 말하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -8120,7 +8623,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>운동과 건강, 음악 감상과 비평, 생명과학, 음악과 미디어</t>
+          <t>운동과 건강, 음악 감상과 비평, 생명과학, 음악과 미디어, 스포츠 과학, 스포츠 생활1, 문학</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -8133,7 +8636,10 @@
           <t>운동과 건강: 체력과 몸 관리가 기본이라 → 운동 원리와 건강 관리를 배워요.
 음악 감상과 비평: 음악을 해석해 춤으로 표현해서 → 음악을 감상하고 분석하는 법을 배워요.
 생명과학: 근육·뼈의 움직임을 이해해야 해서 → 사람 몸의 구조와 기능을 배워요.
-음악과 미디어: 영상·미디어 공연이 늘어나서 → 미디어 속 음악과 예술 활용을 배워요.</t>
+음악과 미디어: 영상·미디어 공연이 늘어나서 → 미디어 속 음악과 예술 활용을 배워요.
+스포츠 과학: 몸을 정밀하게 쓰고 부상을 막아야 해서 → 운동 원리와 체력 관리법을 배워요.
+스포츠 생활1: 기초 체력과 유연성이 필수라서 → 꾸준한 신체 활동과 체력 관리를 익혀요.
+문학: 작품의 이야기를 몸으로 표현해서 → 작품 속 정서와 주제 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -8155,7 +8661,7 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>음악 감상과 비평, 문학과 영상, 운동과 건강, 음악과 미디어, 인간과 심리</t>
+          <t>음악 감상과 비평, 문학과 영상, 운동과 건강, 음악과 미디어, 인간과 심리, 문학, 스포츠 생활1, 화법과 언어</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -8169,7 +8675,10 @@
 문학과 영상: 대본 속 인물을 이해해야 해서 → 작품의 인물과 서사를 배워요.
 운동과 건강: 노래하며 춤추는 체력이 필요해서 → 운동 원리와 건강 관리를 배워요.
 음악과 미디어: 공연 영상·음원 활동도 많아서 → 미디어 속 음악의 역할을 배워요.
-인간과 심리: 인물의 감정을 깊이 표현해야 해서 → 인간의 감정과 심리를 배워요.</t>
+인간과 심리: 인물의 감정을 깊이 표현해야 해서 → 인간의 감정과 심리를 배워요.
+문학: 대본 속 인물을 깊이 이해해야 해서 → 작품의 인물·갈등 해석을 배워요.
+스포츠 생활1: 노래하며 춤추는 체력이 필요해서 → 기초 체력과 신체 활동을 익혀요.
+화법과 언어: 정확한 발음과 대사 전달이 중요해서 → 말소리와 말하기 원리를 배워요.</t>
         </is>
       </c>
     </row>
@@ -8191,7 +8700,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>인간과 심리, 미술 감상과 비평, 미술과 매체, 사회와 문화, 교육의 이해</t>
+          <t>인간과 심리, 미술 감상과 비평, 미술과 매체, 사회와 문화, 교육의 이해, 화법과 언어, 확률과 통계</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -8205,7 +8714,9 @@
 미술 감상과 비평: 작품 속 감정을 읽어 내야 해서 → 작품을 분석하고 해석하는 법을 배워요.
 미술과 매체: 다양한 재료로 활동을 이끌어서 → 여러 매체를 활용한 표현을 배워요.
 사회와 문화: 내담자의 가정·사회 환경을 이해해서 → 사회 구조와 문화 현상을 배워요.
-교육의 이해: 아동·청소년 상담이 많아서 → 성장과 교육의 원리를 배워요.</t>
+교육의 이해: 아동·청소년 상담이 많아서 → 성장과 교육의 원리를 배워요.
+화법과 언어: 내담자와 공감하며 대화해야 해서 → 경청하고 공감하는 말하기를 배워요.
+확률과 통계: 치료 효과를 기록·평가해야 해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8738,7 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>화학, 미술 감상과 비평, 화학 실험, 세계사, 동아시아 역사 기행</t>
+          <t>화학, 미술 감상과 비평, 화학 실험, 세계사, 동아시아 역사 기행, 영어 독해와 작문, 독서와 작문</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -8241,7 +8752,9 @@
 미술 감상과 비평: 작품의 원래 표현을 알아야 해서 → 작품을 분석하고 평가하는 법을 배워요.
 화학 실험: 재료를 분석하고 시험해야 해서 → 화학 실험 방법과 안전 수칙을 익혀요.
 세계사: 서양 미술품의 시대 배경을 알아야 해서 → 세계 여러 시대의 역사를 배워요.
-동아시아 역사 기행: 우리 문화재를 다루는 일이 많아서 → 동아시아의 역사와 문화를 배워요.</t>
+동아시아 역사 기행: 우리 문화재를 다루는 일이 많아서 → 동아시아의 역사와 문화를 배워요.
+영어 독해와 작문: 해외 복원 사례와 논문을 참고해서 → 영어 글을 읽고 정리하는 법을 배워요.
+독서와 작문: 복원 과정을 보고서로 남겨야 해서 → 정확하고 논리적인 글쓰기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8776,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 미술 감상과 비평, 인간과 심리, 경제</t>
+          <t>미술과 매체, 미술 감상과 비평, 인간과 심리, 경제, 화법과 언어, 확률과 통계</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -8276,7 +8789,9 @@
           <t>미술과 매체: 공간을 시각적으로 꾸미는 일이라 → 다양한 매체를 활용한 표현을 배워요.
 미술 감상과 비평: 색·구도 감각이 필요해서 → 작품을 분석하고 평가하는 법을 배워요.
 인간과 심리: 소비자의 마음을 끌어야 해서 → 인간의 감정과 행동을 배워요.
-경제: 판매와 유행의 흐름을 읽어야 해서 → 시장과 소비 활동의 원리를 배워요.</t>
+경제: 판매와 유행의 흐름을 읽어야 해서 → 시장과 소비 활동의 원리를 배워요.
+화법과 언어: 매장 콘셉트를 팀에 설명해야 해서 → 생각을 분명하게 전달하는 법을 배워요.
+확률과 통계: 진열 변화에 따른 매출을 분석해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8813,7 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 미술 감상과 비평, 물리학, 문학과 영상</t>
+          <t>미술과 매체, 미술 감상과 비평, 물리학, 문학과 영상, 문학, 영어 I</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -8311,7 +8826,9 @@
           <t>미술과 매체: 사진은 대표적인 시각 매체라서 → 사진·영상 등 매체 표현을 배워요.
 미술 감상과 비평: 구도·빛을 보는 안목이 필요해서 → 작품을 분석하고 평가하는 법을 배워요.
 물리학: 렌즈와 빛을 다루는 일이라 → 빛과 파동의 성질을 배워요.
-문학과 영상: 사진 한 장에 이야기를 담아야 해서 → 이미지와 서사 표현을 배워요.</t>
+문학과 영상: 사진 한 장에 이야기를 담아야 해서 → 이미지와 서사 표현을 배워요.
+문학: 한 장의 사진에 이야기를 담아야 해서 → 작품의 주제와 정서 표현을 배워요.
+영어 I: 해외 공모전·작가 활동 기회가 있어서 → 기초 영어 독해와 표현을 익혀요.</t>
         </is>
       </c>
     </row>
@@ -8333,7 +8850,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 미술 감상과 비평, 물리학, 정보, 문학과 영상</t>
+          <t>미술과 매체, 미술 감상과 비평, 물리학, 정보, 문학과 영상, 영어 I, 대수</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -8347,7 +8864,9 @@
 미술 감상과 비평: 색채 감각이 핵심이라 → 작품의 색과 표현을 분석하는 법을 배워요.
 물리학: 빛과 색의 원리를 알아야 해서 → 빛의 성질과 파동을 배워요.
 정보: 보정 프로그램과 영상 데이터를 다뤄서 → 컴퓨팅 사고와 자료 처리를 배워요.
-문학과 영상: 장면의 감정을 색으로 살려야 해서 → 영상의 서사와 표현 방식을 배워요.</t>
+문학과 영상: 장면의 감정을 색으로 살려야 해서 → 영상의 서사와 표현 방식을 배워요.
+영어 I: 보정 프로그램과 자료가 영어라서 → 기초 영어 독해 능력을 키워요.
+대수: 감마 곡선 등 색값을 수식으로 다뤄서 → 지수·로그 함수를 배워요.</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8888,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>언어생활 탐구, 문학과 영상, 매체 의사소통, 인간과 심리</t>
+          <t>언어생활 탐구, 문학과 영상, 매체 의사소통, 인간과 심리, 화법과 언어, 문학</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -8382,7 +8901,9 @@
           <t>언어생활 탐구: 정확한 발음이 기본이라 → 국어의 말소리와 표준 발음을 배워요.
 문학과 영상: 대본 속 인물을 이해해야 해서 → 작품의 인물과 서사를 배워요.
 매체 의사소통: 방송·광고 등 매체로 전달하므로 → 매체 특성에 맞는 표현을 배워요.
-인간과 심리: 목소리로 감정을 표현해야 해서 → 인간의 감정과 심리를 배워요.</t>
+인간과 심리: 목소리로 감정을 표현해야 해서 → 인간의 감정과 심리를 배워요.
+화법과 언어: 정확한 발음과 억양이 생명이라서 → 말소리와 말하기 원리를 배워요.
+문학: 대본 속 인물의 감정을 살려야 해서 → 작품의 정서와 인물 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8925,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>미술 감상과 비평, 미술과 매체, 사회와 문화, 인간과 심리</t>
+          <t>미술 감상과 비평, 미술과 매체, 사회와 문화, 인간과 심리, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -8417,7 +8938,9 @@
           <t>미술 감상과 비평: 색·형태 조화를 보는 눈이 필요해서 → 작품을 분석하고 평가하는 법을 배워요.
 미술과 매체: 화보·영상 속 연출을 다뤄서 → 다양한 매체를 활용한 표현을 배워요.
 사회와 문화: 유행과 대중문화를 읽어야 해서 → 사회 현상과 대중문화를 배워요.
-인간과 심리: 고객의 개성과 원하는 이미지를 파악해서 → 인간의 감정과 심리를 배워요.</t>
+인간과 심리: 고객의 개성과 원하는 이미지를 파악해서 → 인간의 감정과 심리를 배워요.
+화법과 언어: 고객의 취향을 듣고 제안해야 해서 → 경청하고 설득하는 말하기를 배워요.
+영어 I: 해외 패션 트렌드를 빠르게 읽어야 해서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8962,7 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>경제, 운동과 건강, 실용 통계, 법과 사회, 매체 의사소통</t>
+          <t>경제, 운동과 건강, 실용 통계, 법과 사회, 매체 의사소통, 확률과 통계, 스포츠 문화, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -8453,7 +8976,10 @@
 운동과 건강: 선수 관리에 운동 지식이 필요해서 → 운동 원리와 건강 관리를 배워요.
 실용 통계: 경기·관중 기록을 분석하므로 → 자료를 정리하고 해석하는 법을 배워요.
 법과 사회: 선수 계약과 규정을 다뤄서 → 계약 등 생활 속 법을 배워요.
-매체 의사소통: 팬과 언론에 구단을 알려야 해서 → 매체 특성에 맞는 소통을 배워요.</t>
+매체 의사소통: 팬과 언론에 구단을 알려야 해서 → 매체 특성에 맞는 소통을 배워요.
+확률과 통계: 선수 기록과 관중 자료를 분석해서 → 자료 정리와 통계 해석을 배워요.
+스포츠 문화: 스포츠 산업과 팬 문화를 이해해야 해서 → 스포츠의 사회·문화적 의미를 배워요.
+영어Ⅱ: 외국인 선수와 소통해야 해서 → 다양한 영어 표현을 익혀요.</t>
         </is>
       </c>
     </row>
@@ -8475,7 +9001,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>실용 통계, 정보, 인공지능 수학, 인공지능 기초, 운동과 건강</t>
+          <t>실용 통계, 정보, 인공지능 수학, 인공지능 기초, 운동과 건강, 확률과 통계, 미적분 I, 영어 I</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -8489,7 +9015,10 @@
 정보: 데이터를 프로그램으로 처리하므로 → 프로그래밍과 자료 처리를 배워요.
 인공지능 수학: 경기 예측 모델을 만들어야 해서 → 인공지능에 쓰이는 수학을 배워요.
 인공지능 기초: 영상·센서 데이터 분석에 AI를 써서 → 인공지능의 원리와 활용을 배워요.
-운동과 건강: 종목과 선수 몸을 이해해야 해서 → 운동 원리와 체력 요소를 배워요.</t>
+운동과 건강: 종목과 선수 몸을 이해해야 해서 → 운동 원리와 체력 요소를 배워요.
+확률과 통계: 경기 결과를 예측·분석하는 일이라서 → 확률 분포와 통계적 추론을 배워요.
+미적분 I: 선수 움직임의 속도 변화를 분석해서 → 미분으로 변화율 구하는 법을 배워요.
+영어 I: 분석 도구와 해외 자료가 영어라서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -8511,7 +9040,7 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>운동과 건강, 경제, 법과 사회, 직무 의사소통</t>
+          <t>운동과 건강, 경제, 법과 사회, 직무 의사소통, 스포츠 생활1, 확률과 통계</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -8524,7 +9053,9 @@
           <t>운동과 건강: 이용자의 안전한 운동을 도와야 해서 → 운동 원리와 안전 관리를 배워요.
 경제: 시설 운영비와 수익을 관리해서 → 시장과 경제 활동의 원리를 배워요.
 법과 사회: 안전 규정과 이용 약관을 지켜야 해서 → 생활 속 법과 제도를 배워요.
-직무 의사소통: 이용객·직원과 소통이 많아서 → 업무 상황에 맞는 말하기를 배워요.</t>
+직무 의사소통: 이용객·직원과 소통이 많아서 → 업무 상황에 맞는 말하기를 배워요.
+스포츠 생활1: 이용자 프로그램을 직접 운영해서 → 다양한 스포츠 활동을 익혀요.
+확률과 통계: 이용률·운영비 자료를 관리해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -8546,7 +9077,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>운동과 건강, 현대사회와 윤리, 인간과 심리, 실생활 영어 회화</t>
+          <t>운동과 건강, 현대사회와 윤리, 인간과 심리, 실생활 영어 회화, 스포츠 생활1, 스포츠 문화, 화법과 언어</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -8559,7 +9090,10 @@
           <t>운동과 건강: 경기 내내 뛰는 체력이 필요해서 → 운동 원리와 체력 관리를 배워요.
 현대사회와 윤리: 공정한 판정이 핵심이라 → 공정성과 직업 윤리를 배워요.
 인간과 심리: 선수의 흥분을 다스려야 해서 → 인간의 감정과 행동을 배워요.
-실생활 영어 회화: 국제 대회에서 소통해야 해서 → 생활 속 영어 회화를 연습해요.</t>
+실생활 영어 회화: 국제 대회에서 소통해야 해서 → 생활 속 영어 회화를 연습해요.
+스포츠 생활1: 경기 내내 선수와 함께 뛰어야 해서 → 기초 체력과 경기 규칙을 익혀요.
+스포츠 문화: 공정성과 스포츠맨십을 지켜야 해서 → 스포츠의 가치와 윤리를 배워요.
+화법과 언어: 판정을 분명하게 설명해야 해서 → 정확하고 단호한 말하기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -8581,7 +9115,7 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>법과 사회, 경제, 실생활 영어 회화, 직무 영어, 운동과 건강</t>
+          <t>법과 사회, 경제, 실생활 영어 회화, 직무 영어, 운동과 건강, 화법과 언어, 영어Ⅱ, 스포츠 문화</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -8595,7 +9129,10 @@
 경제: 연봉·후원 금액을 따져야 해서 → 시장과 경제 활동의 원리를 배워요.
 실생활 영어 회화: 해외 구단과도 소통해서 → 생활 속 영어 회화를 연습해요.
 직무 영어: 영어 계약·이메일을 다루므로 → 업무에 쓰이는 영어를 배워요.
-운동과 건강: 선수의 몸 상태를 이해해야 해서 → 운동 원리와 건강 관리를 배워요.</t>
+운동과 건강: 선수의 몸 상태를 이해해야 해서 → 운동 원리와 건강 관리를 배워요.
+화법과 언어: 구단과 연봉 협상을 해야 해서 → 설득하고 협상하는 말하기를 배워요.
+영어Ⅱ: 해외 이적 계약을 다뤄야 해서 → 다양한 영어 글 이해력을 키워요.
+스포츠 문화: 스포츠 산업의 흐름을 알아야 해서 → 스포츠의 사회·문화적 의미를 배워요.</t>
         </is>
       </c>
     </row>
@@ -8617,7 +9154,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>운동과 건강, 매체 의사소통, 언어생활 탐구, 실용 통계</t>
+          <t>운동과 건강, 매체 의사소통, 언어생활 탐구, 실용 통계, 화법과 언어, 스포츠 문화, 확률과 통계</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -8630,7 +9167,10 @@
           <t>운동과 건강: 종목과 경기 원리를 알아야 해서 → 운동 원리와 체력 요소를 배워요.
 매체 의사소통: 방송으로 경기를 전달하므로 → 매체 특성에 맞는 말하기를 배워요.
 언어생활 탐구: 정확하고 바른 말을 써야 해서 → 국어의 발음과 표현을 배워요.
-실용 통계: 기록으로 경기를 분석해 설명해서 → 자료를 정리하고 해석하는 법을 배워요.</t>
+실용 통계: 기록으로 경기를 분석해 설명해서 → 자료를 정리하고 해석하는 법을 배워요.
+화법과 언어: 경기 상황을 생생히 전달해야 해서 → 생동감 있는 말하기를 배워요.
+스포츠 문화: 종목의 역사와 의미를 알려줘서 → 스포츠의 역사와 문화를 배워요.
+확률과 통계: 기록을 근거로 경기를 분석해서 → 통계 자료 해석법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -8652,7 +9192,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>인간과 심리, 운동과 건강, 생명과학, 실용 통계</t>
+          <t>인간과 심리, 운동과 건강, 생명과학, 실용 통계, 스포츠 과학, 화법과 언어, 확률과 통계</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -8665,7 +9205,10 @@
           <t>인간과 심리: 선수의 마음을 이해해야 해서 → 인간의 감정과 동기를 배워요.
 운동과 건강: 운동 상황을 알아야 상담할 수 있어서 → 운동 원리와 건강 관리를 배워요.
 생명과학: 긴장할 때 몸의 반응을 알아야 해서 → 신경계와 호르몬 작용을 배워요.
-실용 통계: 심리 검사 결과를 해석해야 해서 → 자료를 정리하고 분석하는 법을 배워요.</t>
+실용 통계: 심리 검사 결과를 해석해야 해서 → 자료를 정리하고 분석하는 법을 배워요.
+스포츠 과학: 선수의 몸과 마음을 함께 봐야 해서 → 운동 수행의 과학 원리를 배워요.
+화법과 언어: 선수와 신뢰 있는 대화를 해야 해서 → 경청하고 공감하는 말하기를 배워요.
+확률과 통계: 심리 검사 결과를 해석해야 해서 → 자료 분석과 통계 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -8687,7 +9230,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>물리학, 역학과 에너지, 화학, 운동과 건강, 기하</t>
+          <t>물리학, 역학과 에너지, 화학, 운동과 건강, 기하, 미적분 I, 스포츠 과학, 확률과 통계</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -8701,7 +9244,10 @@
 역학과 에너지: 공·라켓의 움직임을 분석해서 → 운동과 에너지를 깊이 배워요.
 화학: 고무·섬유 같은 신소재를 다루므로 → 물질의 성질과 화학 반응의 기초를 배워요.
 운동과 건강: 사용자의 운동 동작을 이해해야 해서 → 운동 원리와 체력 요소를 배워요.
-기하: 제품 모양을 설계해야 해서 → 공간도형과 좌표를 배워요.</t>
+기하: 제품 모양을 설계해야 해서 → 공간도형과 좌표를 배워요.
+미적분 I: 공·라켓의 운동을 분석해서 → 미분으로 속도 변화 구하는 법을 배워요.
+스포츠 과학: 선수 동작에 맞는 용품을 설계해서 → 운동 동작의 과학 원리를 배워요.
+확률과 통계: 제품 테스트 결과를 비교해야 해서 → 실험 자료의 통계 분석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -8723,7 +9269,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>음악 감상과 비평, 음악과 미디어, 교육의 이해, 인간과 심리</t>
+          <t>음악 감상과 비평, 음악과 미디어, 교육의 이해, 인간과 심리, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -8736,7 +9282,9 @@
           <t>음악 감상과 비평: 다양한 장르를 설명해야 해서 → 음악을 감상하고 분석하는 법을 배워요.
 음악과 미디어: 녹음·편곡 프로그램을 쓰므로 → 미디어를 활용한 음악 제작을 배워요.
 교육의 이해: 수강생 수준에 맞게 가르쳐야 해서 → 교육의 원리와 방법을 배워요.
-인간과 심리: 수강생의 동기를 키워야 해서 → 인간의 감정과 동기를 배워요.</t>
+인간과 심리: 수강생의 동기를 키워야 해서 → 인간의 감정과 동기를 배워요.
+화법과 언어: 학생에게 발성과 연주법을 설명해서 → 알기 쉽게 말하는 법을 배워요.
+영어 I: 팝 가사와 해외 교재를 다뤄서 → 기초 영어 독해와 발음을 익혀요.</t>
         </is>
       </c>
     </row>
@@ -8758,7 +9306,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>음악 감상과 비평, 운동과 건강, 음악과 미디어, 미술 감상과 비평</t>
+          <t>음악 감상과 비평, 운동과 건강, 음악과 미디어, 미술 감상과 비평, 스포츠 과학, 문학, 스포츠 생활1</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -8771,7 +9319,10 @@
           <t>음악 감상과 비평: 음악을 분석해 동작을 짜야 해서 → 음악을 감상하고 분석하는 법을 배워요.
 운동과 건강: 무리 없는 동작을 만들어야 해서 → 운동 원리와 부상 예방을 배워요.
 음악과 미디어: 뮤직비디오·영상 무대가 많아서 → 미디어 속 음악의 역할을 배워요.
-미술 감상과 비평: 무대 위 구도와 대형을 짜야 해서 → 시각적 구성을 분석하는 법을 배워요.</t>
+미술 감상과 비평: 무대 위 구도와 대형을 짜야 해서 → 시각적 구성을 분석하는 법을 배워요.
+스포츠 과학: 무용수가 다치지 않는 동작을 짜야 해서 → 신체 움직임의 원리를 배워요.
+문학: 노래 가사와 주제를 동작에 담아서 → 작품의 주제와 정서 해석을 배워요.
+스포츠 생활1: 직접 시범을 보일 체력이 필요해서 → 기초 체력과 신체 활동을 익혀요.</t>
         </is>
       </c>
     </row>
@@ -8793,7 +9344,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 미술 감상과 비평, 문학과 영상, 정보</t>
+          <t>미술과 매체, 미술 감상과 비평, 문학과 영상, 정보, 문학, 미적분 I</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -8806,7 +9357,9 @@
           <t>미술과 매체: 그림을 움직이는 영상으로 만들어서 → 디지털 매체를 활용한 표현을 배워요.
 미술 감상과 비평: 그림 실력과 안목이 바탕이라 → 작품을 분석하고 평가하는 법을 배워요.
 문학과 영상: 이야기를 장면으로 풀어야 해서 → 문학과 영상의 서사 표현을 배워요.
-정보: 애니메이션 프로그램을 다루므로 → 컴퓨팅 사고와 프로그래밍 기초를 배워요.</t>
+정보: 애니메이션 프로그램을 다루므로 → 컴퓨팅 사고와 프로그래밍 기초를 배워요.
+문학: 캐릭터와 이야기에 생명을 불어넣어서 → 서사와 인물 표현을 배워요.
+미적분 I: 움직임의 속도 변화를 자연스럽게 그려서 → 함수와 변화율의 개념을 배워요.</t>
         </is>
       </c>
     </row>
@@ -8828,7 +9381,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>매체 의사소통, 법과 사회, 경제, 직무 의사소통, 사회와 문화</t>
+          <t>매체 의사소통, 법과 사회, 경제, 직무 의사소통, 사회와 문화, 화법과 언어, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -8842,7 +9395,9 @@
 법과 사회: 출연 계약과 초상권을 다뤄서 → 계약과 권리 등 생활 속 법을 배워요.
 경제: 출연료와 수익을 관리해야 해서 → 시장과 경제 활동의 원리를 배워요.
 직무 의사소통: 방송사·광고주와 협의가 많아서 → 업무 상황에 맞는 말하기를 배워요.
-사회와 문화: 대중의 관심과 유행을 읽어야 해서 → 사회 현상과 대중문화를 배워요.</t>
+사회와 문화: 대중의 관심과 유행을 읽어야 해서 → 사회 현상과 대중문화를 배워요.
+화법과 언어: 방송사·광고주와 협상해야 해서 → 설득하고 협상하는 말하기를 배워요.
+영어Ⅱ: 해외 활동 일정을 조율해야 해서 → 다양한 영어 표현을 익혀요.</t>
         </is>
       </c>
     </row>
@@ -8864,7 +9419,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 문학과 영상, 매체 의사소통, 음악과 미디어, 정보</t>
+          <t>미술과 매체, 문학과 영상, 매체 의사소통, 음악과 미디어, 정보, 독서와 작문, 확률과 통계</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -8878,7 +9433,9 @@
 문학과 영상: 재미있는 이야기 구성이 중요해서 → 문학과 영상의 서사 표현을 배워요.
 매체 의사소통: 시청자와 소통하는 일이라 → 매체의 특성과 소통 방식을 배워요.
 음악과 미디어: 배경음악·효과음을 넣어야 해서 → 미디어 속 음악의 역할을 배워요.
-정보: 편집 프로그램과 데이터를 다뤄서 → 컴퓨팅 사고와 자료 처리를 배워요.</t>
+정보: 편집 프로그램과 데이터를 다뤄서 → 컴퓨팅 사고와 자료 처리를 배워요.
+독서와 작문: 기획안과 대본을 직접 써야 해서 → 구성력 있는 글쓰기를 배워요.
+확률과 통계: 조회수·시청 지표를 분석해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -8900,7 +9457,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 문학과 영상, 음악과 미디어, 정보, 미술 감상과 비평</t>
+          <t>미술과 매체, 문학과 영상, 음악과 미디어, 정보, 미술 감상과 비평, 문학, 영어 I</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -8914,7 +9471,9 @@
 문학과 영상: 장면 순서로 이야기를 만들어서 → 영상의 서사와 편집 표현을 배워요.
 음악과 미디어: 음악과 화면을 맞춰야 해서 → 미디어 속 음악의 역할을 배워요.
 정보: 편집 프로그램과 파일을 다루므로 → 컴퓨팅 사고와 자료 처리를 배워요.
-미술 감상과 비평: 화면의 구도·색감을 판단해서 → 작품을 분석하고 평가하는 법을 배워요.</t>
+미술 감상과 비평: 화면의 구도·색감을 판단해서 → 작품을 분석하고 평가하는 법을 배워요.
+문학: 장면을 이어 이야기의 흐름을 만들어서 → 서사 구조와 전개 방식을 배워요.
+영어 I: 편집 프로그램과 해외 자료가 영어라서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -8936,7 +9495,7 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>문학과 영상, 미술과 매체, 인간과 심리, 음악과 미디어, 사회와 문화</t>
+          <t>문학과 영상, 미술과 매체, 인간과 심리, 음악과 미디어, 사회와 문화, 문학, 독서와 작문, 화법과 언어</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -8950,7 +9509,10 @@
 미술과 매체: 장면의 화면 구성을 정해야 해서 → 영상 등 다양한 매체 표현을 배워요.
 인간과 심리: 인물의 감정을 깊이 그려야 해서 → 인간의 감정과 심리를 배워요.
 음악과 미디어: 영화 음악으로 분위기를 살려서 → 미디어 속 음악의 역할을 배워요.
-사회와 문화: 사회를 담은 이야기를 만들어서 → 사회 현상과 문화를 배워요.</t>
+사회와 문화: 사회를 담은 이야기를 만들어서 → 사회 현상과 문화를 배워요.
+문학: 인물과 이야기를 깊이 해석해야 해서 → 서사와 인물 표현 방식을 배워요.
+독서와 작문: 시나리오를 쓰고 다듬어야 해서 → 구성력 있는 글쓰기를 배워요.
+화법과 언어: 배우·스태프를 이끌어야 해서 → 생각을 정확히 전달하는 말하기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -8972,7 +9534,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>문학과 영상, 인간과 심리, 언어생활 탐구, 운동과 건강</t>
+          <t>문학과 영상, 인간과 심리, 언어생활 탐구, 운동과 건강, 문학, 화법과 언어, 스포츠 생활1</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -8985,7 +9547,10 @@
           <t>문학과 영상: 대본 속 인물을 이해해야 해서 → 작품의 인물과 서사를 배워요.
 인간과 심리: 인물의 감정을 진짜처럼 표현해서 → 인간의 감정과 심리를 배워요.
 언어생활 탐구: 정확한 발음과 대사 전달이 중요해서 → 국어의 말소리와 표현을 배워요.
-운동과 건강: 촬영을 견딜 체력과 몸 관리가 필요해서 → 운동 원리와 건강 관리를 배워요.</t>
+운동과 건강: 촬영을 견딜 체력과 몸 관리가 필요해서 → 운동 원리와 건강 관리를 배워요.
+문학: 배역의 감정과 삶을 이해해야 해서 → 작품 속 인물과 갈등 해석을 배워요.
+화법과 언어: 대사를 정확하고 자연스럽게 해야 해서 → 발음과 말하기 원리를 배워요.
+스포츠 생활1: 액션과 장시간 촬영을 버텨야 해서 → 기초 체력과 신체 활동을 익혀요.</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9572,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>인간과 심리, 미술 감상과 비평, 음악 감상과 비평, 미술과 매체, 사회와 문화</t>
+          <t>인간과 심리, 미술 감상과 비평, 음악 감상과 비평, 미술과 매체, 사회와 문화, 화법과 언어, 확률과 통계</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -9021,7 +9586,9 @@
 미술 감상과 비평: 작품 속 감정을 읽어야 해서 → 작품을 분석하고 해석하는 법을 배워요.
 음악 감상과 비평: 음악을 치료에 활용하므로 → 음악을 감상하고 분석하는 법을 배워요.
 미술과 매체: 여러 재료로 활동을 이끌어서 → 다양한 매체를 활용한 표현을 배워요.
-사회와 문화: 내담자의 생활 환경을 이해해서 → 사회 구조와 문화 현상을 배워요.</t>
+사회와 문화: 내담자의 생활 환경을 이해해서 → 사회 구조와 문화 현상을 배워요.
+화법과 언어: 내담자의 마음을 듣고 공감해야 해서 → 경청과 공감의 말하기를 배워요.
+확률과 통계: 치료 효과를 기록·평가해야 해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9610,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 세포와 물질대사, 운동과 건강, 화학, 생명과학 실험</t>
+          <t>생명과학, 세포와 물질대사, 운동과 건강, 화학, 생명과학 실험, 스포츠 과학, 확률과 통계, 영어 독해와 작문</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -9057,7 +9624,10 @@
 세포와 물질대사: 에너지가 만들어지는 과정을 알아야 해서 → 세포 호흡과 물질대사를 배워요.
 운동과 건강: 운동 효과를 연구하는 학문이라 → 운동 원리와 체력 요소를 배워요.
 화학: 체내 물질 변화를 이해해야 해서 → 물질의 성질과 화학 반응의 기초를 배워요.
-생명과학 실험: 실험으로 몸의 변화를 측정해서 → 실험 설계와 측정 방법을 익혀요.</t>
+생명과학 실험: 실험으로 몸의 변화를 측정해서 → 실험 설계와 측정 방법을 익혀요.
+스포츠 과학: 운동할 때 몸의 변화를 연구해서 → 운동 수행의 과학 원리를 배워요.
+확률과 통계: 실험 데이터를 분석해 결론을 내서 → 통계적 추론과 자료 분석을 배워요.
+영어 독해와 작문: 해외 논문을 읽고 써야 해서 → 영어 글 읽기와 쓰기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9649,7 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>운동과 건강, 생명과학, 인간과 심리, 실생활 영어 회화</t>
+          <t>운동과 건강, 생명과학, 인간과 심리, 실생활 영어 회화, 스포츠 과학, 스포츠 생활2, 영어 I</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -9092,7 +9662,10 @@
           <t>운동과 건강: 체계적인 훈련과 몸 관리가 기본이라 → 운동 원리와 건강 관리를 배워요.
 생명과학: 몸의 회복과 영양을 이해해야 해서 → 사람 몸의 구조와 기능을 배워요.
 인간과 심리: 경기 중 긴장을 다스려야 해서 → 인간의 감정과 동기를 배워요.
-실생활 영어 회화: 해외 대회·전지훈련이 있어서 → 생활 속 영어 회화를 연습해요.</t>
+실생활 영어 회화: 해외 대회·전지훈련이 있어서 → 생활 속 영어 회화를 연습해요.
+스포츠 과학: 훈련 효과를 높이고 부상을 막아야 해서 → 운동 원리와 컨디션 관리를 배워요.
+스포츠 생활2: 꾸준한 체력 훈련이 기본이라서 → 다양한 운동과 체력 관리를 익혀요.
+영어 I: 해외 대회와 전지훈련에 나가서 → 기초 영어 의사소통을 익혀요.</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9687,7 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>운동과 건강, 생명과학, 세포와 물질대사, 물리학</t>
+          <t>운동과 건강, 생명과학, 세포와 물질대사, 물리학, 스포츠 과학, 확률과 통계, 화법과 언어</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -9127,7 +9700,10 @@
           <t>운동과 건강: 운동 프로그램을 짜는 일이라 → 운동 원리와 체력 요소를 배워요.
 생명과학: 심장·근육 등 몸의 기능을 알아야 해서 → 항상성과 몸의 기능을 배워요.
 세포와 물질대사: 운동과 에너지 소비를 계산해서 → 세포 호흡과 물질대사를 배워요.
-물리학: 바른 자세와 동작을 분석해야 해서 → 힘과 운동의 기초를 배워요.</t>
+물리학: 바른 자세와 동작을 분석해야 해서 → 힘과 운동의 기초를 배워요.
+스포츠 과학: 개인 맞춤 운동을 처방해야 해서 → 운동 원리와 체력 측정법을 배워요.
+확률과 통계: 체력 측정 결과를 비교·분석해서 → 자료 정리와 통계 해석을 배워요.
+화법과 언어: 고객에게 운동법을 설명해야 해서 → 알기 쉽게 설명하는 말하기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9725,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 문학과 영상, 독서 토론과 글쓰기, 미술 감상과 비평</t>
+          <t>미술과 매체, 문학과 영상, 독서 토론과 글쓰기, 미술 감상과 비평, 문학, 화법과 언어</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -9162,7 +9738,9 @@
           <t>미술과 매체: 디지털 드로잉으로 작업해서 → 디지털 매체를 활용한 표현을 배워요.
 문학과 영상: 이야기를 칸과 장면으로 풀어야 해서 → 문학과 영상의 서사 표현을 배워요.
 독서 토론과 글쓰기: 탄탄한 스토리를 써야 해서 → 읽고 토론하며 글 쓰는 법을 배워요.
-미술 감상과 비평: 그림 실력과 안목이 바탕이라 → 작품을 분석하고 평가하는 법을 배워요.</t>
+미술 감상과 비평: 그림 실력과 안목이 바탕이라 → 작품을 분석하고 평가하는 법을 배워요.
+문학: 독자를 끌어당기는 이야기를 만들어서 → 서사 구조와 인물 표현을 배워요.
+화법과 언어: 대사 한 줄로 캐릭터를 살려야 해서 → 상황에 맞는 언어 표현을 배워요.</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9762,7 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>매체 의사소통, 미술과 매체, 음악과 미디어, 문학과 영상, 사회와 문화</t>
+          <t>매체 의사소통, 미술과 매체, 음악과 미디어, 문학과 영상, 사회와 문화, 화법과 언어, 독서와 작문, 확률과 통계</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -9198,7 +9776,10 @@
 미술과 매체: 촬영·편집으로 영상을 만들어서 → 영상 등 다양한 매체 표현을 배워요.
 음악과 미디어: 배경음악·효과음을 넣어야 해서 → 미디어 속 음악의 역할을 배워요.
 문학과 영상: 재미있는 이야기 구성이 중요해서 → 문학과 영상의 서사 표현을 배워요.
-사회와 문화: 유행과 시청자 관심을 읽어야 해서 → 사회 현상과 대중문화를 배워요.</t>
+사회와 문화: 유행과 시청자 관심을 읽어야 해서 → 사회 현상과 대중문화를 배워요.
+화법과 언어: 카메라 앞에서 말로 소통해서 → 전달력 있는 말하기를 배워요.
+독서와 작문: 영상 대본과 기획을 직접 써서 → 구성력 있는 글쓰기를 배워요.
+확률과 통계: 조회수·구독자 지표를 분석해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -9220,7 +9801,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>음악 감상과 비평, 음악과 미디어, 경제, 매체 의사소통, 법과 사회</t>
+          <t>음악 감상과 비평, 음악과 미디어, 경제, 매체 의사소통, 법과 사회, 독서와 작문, 영어Ⅱ, 확률과 통계</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -9234,7 +9815,10 @@
 음악과 미디어: 음원·영상으로 음악을 알리므로 → 미디어 속 음악의 역할을 배워요.
 경제: 제작비와 수익을 따져야 해서 → 시장과 경제 활동의 원리를 배워요.
 매체 의사소통: 음반 홍보가 중요해서 → 매체 특성에 맞는 소통을 배워요.
-법과 사회: 저작권과 계약을 다뤄야 해서 → 권리와 계약 등 생활 속 법을 배워요.</t>
+법과 사회: 저작권과 계약을 다뤄야 해서 → 권리와 계약 등 생활 속 법을 배워요.
+독서와 작문: 앨범 기획서와 소개 글을 써야 해서 → 설득력 있는 글쓰기를 배워요.
+영어Ⅱ: 해외 시장 진출과 협업이 많아서 → 다양한 영어 표현을 익혀요.
+확률과 통계: 음원 차트와 판매 자료를 분석해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -9256,7 +9840,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>음악과 미디어, 음악 감상과 비평, 물리학</t>
+          <t>음악과 미디어, 음악 감상과 비평, 물리학, 대수, 영어 I, 문학</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -9268,7 +9852,10 @@
         <is>
           <t>음악과 미디어: 녹음·믹싱 장비와 프로그램을 다뤄서 → 미디어를 활용한 음악 제작을 배워요.
 음악 감상과 비평: 여러 장르의 사운드를 알아야 해서 → 음악을 감상하고 분석하는 법을 배워요.
-물리학: 소리를 녹음하고 다듬는 일이라 → 파동과 소리의 성질을 배워요.</t>
+물리학: 소리를 녹음하고 다듬는 일이라 → 파동과 소리의 성질을 배워요.
+대수: 음의 주파수가 지수적으로 변해서 → 지수·로그 함수를 배워요.
+영어 I: 장비와 프로그램이 영어로 되어 있어서 → 기초 영어 독해 능력을 키워요.
+문학: 가사의 메시지를 다듬어야 해서 → 시적 표현과 정서를 배워요.</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9877,7 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>인간과 심리, 음악 감상과 비평, 음악과 미디어, 생명과학, 사회와 문화</t>
+          <t>인간과 심리, 음악 감상과 비평, 음악과 미디어, 생명과학, 사회와 문화, 화법과 언어, 확률과 통계</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -9304,7 +9891,9 @@
 음악 감상과 비평: 상황에 맞는 음악을 골라 써야 해서 → 다양한 음악을 듣고 분석·평가해요.
 음악과 미디어: 치료용 음악을 만들고 편집하기도 해서 → 디지털 매체로 음악을 만들고 다뤄요.
 생명과학: 음악이 몸과 뇌에 주는 영향을 알아야 해서 → 신경계·항상성 등 몸의 원리를 배워요.
-사회와 문화: 아동·노인·장애인 등 다양한 대상을 만나서 → 사회 집단과 문화의 다양성을 배워요.</t>
+사회와 문화: 아동·노인·장애인 등 다양한 대상을 만나서 → 사회 집단과 문화의 다양성을 배워요.
+화법과 언어: 내담자와 공감하며 대화해야 해서 → 경청하고 공감하는 말하기를 배워요.
+확률과 통계: 치료 효과를 기록·평가해야 해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9915,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 기하, 미술 감상과 비평, 물리학</t>
+          <t>미술과 매체, 기하, 미술 감상과 비평, 물리학, 대수, 화법과 언어</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -9339,7 +9928,9 @@
           <t>미술과 매체: 디자인 시안을 시각적으로 보여 줘야 해서 → 다양한 매체로 조형 표현을 배워요.
 기하: 공간의 치수와 도면을 다뤄야 해서 → 도형과 공간좌표, 벡터를 배워요.
 미술 감상과 비평: 색채·조형 감각이 중요해서 → 작품을 분석하며 미적 안목을 길러요.
-물리학: 조명·소재·구조의 특성을 고려해야 해서 → 힘과 빛, 에너지의 기초를 배워요.</t>
+물리학: 조명·소재·구조의 특성을 고려해야 해서 → 힘과 빛, 에너지의 기초를 배워요.
+대수: 공간 치수와 자재 수량을 계산해서 → 수와 식의 계산력을 키워요.
+화법과 언어: 고객에게 디자인을 제안해야 해서 → 설득력 있는 말하기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -9361,7 +9952,7 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 미술 감상과 비평, 문학과 영상, 매체 의사소통</t>
+          <t>미술과 매체, 미술 감상과 비평, 문학과 영상, 매체 의사소통, 문학, 영어 I</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -9374,7 +9965,9 @@
           <t>미술과 매체: 디지털·손그림으로 작업하므로 → 다양한 매체를 활용한 표현을 배워요.
 미술 감상과 비평: 여러 화풍을 알아야 해서 → 작품을 감상하고 표현 방식을 분석해요.
 문학과 영상: 글의 내용을 그림으로 옮겨야 해서 → 문학 작품을 해석하고 영상으로 표현해요.
-매체 의사소통: 매체에 맞게 그림을 전달해야 해서 → 매체별 소통 방식과 표현을 배워요.</t>
+매체 의사소통: 매체에 맞게 그림을 전달해야 해서 → 매체별 소통 방식과 표현을 배워요.
+문학: 글의 내용을 그림으로 옮겨야 해서 → 작품의 주제와 정서 해석을 배워요.
+영어 I: 해외 클라이언트와 작업할 수 있어서 → 기초 영어 독해와 표현을 익혀요.</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9989,7 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 기하, 물리학, 미술 감상과 비평</t>
+          <t>미술과 매체, 기하, 물리학, 미술 감상과 비평, 미적분 I, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -9409,7 +10002,9 @@
           <t>미술과 매체: 스케치·3D로 디자인을 표현해야 해서 → 다양한 매체로 조형 표현을 배워요.
 기하: 차체의 곡면과 비례를 다뤄야 해서 → 도형, 공간좌표와 벡터를 배워요.
 물리학: 공기저항 등 주행 성능을 고려해야 해서 → 힘과 운동의 기본 원리를 배워요.
-미술 감상과 비평: 색채·조형 감각이 중요해서 → 작품을 분석하며 미적 안목을 길러요.</t>
+미술 감상과 비평: 색채·조형 감각이 중요해서 → 작품을 분석하며 미적 안목을 길러요.
+미적분 I: 차체의 매끄러운 곡선을 설계해서 → 함수와 미분의 기초를 배워요.
+영어Ⅱ: 해외 디자인 센터와 협업이 많아서 → 다양한 영어 표현을 익혀요.</t>
         </is>
       </c>
     </row>
@@ -9431,7 +10026,7 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 미술 감상과 비평, 사회와 문화, 경제</t>
+          <t>미술과 매체, 미술 감상과 비평, 사회와 문화, 경제, 화법과 언어, 확률과 통계</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -9444,7 +10039,9 @@
           <t>미술과 매체: 제품 아이디어를 그려 보여 줘야 해서 → 다양한 매체로 조형 표현을 배워요.
 미술 감상과 비평: 색채·조형 감각이 중요해서 → 작품을 분석하며 미적 안목을 길러요.
 사회와 문화: 유행과 소비자 취향을 읽어야 해서 → 사회 변화와 대중문화를 배워요.
-경제: 잘 팔리는 상품을 기획해야 해서 → 시장과 소비의 원리를 배워요.</t>
+경제: 잘 팔리는 상품을 기획해야 해서 → 시장과 소비의 원리를 배워요.
+화법과 언어: 디자인 콘셉트를 발표해야 해서 → 효과적인 말하기를 배워요.
+확률과 통계: 판매 자료로 인기 상품을 분석해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -9466,7 +10063,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>미술 감상과 비평, 미술과 매체, 화학, 인간과 철학</t>
+          <t>미술 감상과 비평, 미술과 매체, 화학, 인간과 철학, 문학, 독서와 작문</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -9479,7 +10076,9 @@
           <t>미술 감상과 비평: 자신의 작품 세계를 넓혀야 해서 → 작품을 감상·비평하며 안목을 길러요.
 미술과 매체: 다양한 재료와 기법을 써야 해서 → 매체별 조형 표현 방법을 배워요.
 화학: 재료의 성질을 알고 다뤄야 해서 → 물질의 성질과 화학 반응을 배워요.
-인간과 철학: 작품에 담을 주제를 깊이 고민해야 해서 → 인간과 삶에 대한 사유를 배워요.</t>
+인간과 철학: 작품에 담을 주제를 깊이 고민해야 해서 → 인간과 삶에 대한 사유를 배워요.
+문학: 작품에 담을 주제를 깊이 고민해서 → 문학 속 주제와 상징 해석을 배워요.
+독서와 작문: 작가 노트와 전시 소개를 써야 해서 → 생각을 글로 정리하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -9501,7 +10100,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>물리학, 미술과 매체, 문학과 영상, 전자기와 양자</t>
+          <t>물리학, 미술과 매체, 문학과 영상, 전자기와 양자, 대수, 문학</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -9514,7 +10113,9 @@
           <t>물리학: 빛의 성질과 전기를 이해해야 해서 → 빛·파동과 전기의 기초를 배워요.
 미술과 매체: 색과 빛으로 장면을 표현해야 해서 → 매체를 활용한 시각 표현을 배워요.
 문학과 영상: 작품의 장면과 정서를 읽어야 해서 → 작품을 해석하고 영상으로 표현해요.
-전자기와 양자: 조명 장비와 전기 회로를 다뤄서 → 전자기 현상과 빛의 원리를 깊이 배워요.</t>
+전자기와 양자: 조명 장비와 전기 회로를 다뤄서 → 전자기 현상과 빛의 원리를 깊이 배워요.
+대수: 조도와 밝기 변화를 수치로 다뤄서 → 지수·로그 등 함수 계산을 배워요.
+문학: 장면의 분위기를 빛으로 표현해서 → 작품의 정서와 분위기 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -9536,7 +10137,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 미술 감상과 비평, 화학, 기하</t>
+          <t>미술과 매체, 미술 감상과 비평, 화학, 기하, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -9549,7 +10150,9 @@
           <t>미술과 매체: 작은 장신구를 정교하게 표현해야 해서 → 다양한 매체로 조형 표현을 배워요.
 미술 감상과 비평: 색채·조형 감각이 중요해서 → 작품을 분석하며 미적 안목을 길러요.
 화학: 금속과 보석의 성질을 다뤄야 해서 → 물질의 구조와 성질을 배워요.
-기하: 정교한 형태와 비율을 설계해야 해서 → 도형과 공간의 성질을 배워요.</t>
+기하: 정교한 형태와 비율을 설계해야 해서 → 도형과 공간의 성질을 배워요.
+화법과 언어: 고객의 사연을 듣고 디자인해서 → 경청하고 제안하는 말하기를 배워요.
+영어 I: 해외 보석 시장 정보를 참고해서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -9571,7 +10174,7 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>문학과 영상, 미술과 매체, 물리학, 매체 의사소통</t>
+          <t>문학과 영상, 미술과 매체, 물리학, 매체 의사소통, 대수, 영어 I</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -9584,7 +10187,9 @@
           <t>문학과 영상: 대본 속 장면을 영상으로 옮겨야 해서 → 서사를 해석하고 영상 언어를 배워요.
 미술과 매체: 화면 구도와 색감을 정해야 해서 → 사진·영상 등 매체 표현을 배워요.
 물리학: 렌즈와 빛을 다루는 일이라 → 빛의 굴절·반사 등 파동의 원리를 배워요.
-매체 의사소통: 영상으로 관객과 소통해야 해서 → 매체의 특성과 표현 방식을 배워요.</t>
+매체 의사소통: 영상으로 관객과 소통해야 해서 → 매체의 특성과 표현 방식을 배워요.
+대수: 조리개·셔터값이 배수로 변해서 → 지수·로그 함수를 배워요.
+영어 I: 촬영 장비 매뉴얼이 영어라서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -9606,7 +10211,7 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>미술 감상과 비평, 미술과 매체, 인간과 심리, 화학</t>
+          <t>미술 감상과 비평, 미술과 매체, 인간과 심리, 화학, 확률과 통계, 화법과 언어</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -9619,7 +10224,9 @@
           <t>미술 감상과 비평: 색채 감각과 안목이 핵심이라 → 작품의 색과 조형 요소를 분석해요.
 미술과 매체: 색 조합을 시안으로 보여 줘야 해서 → 다양한 매체로 시각 표현을 배워요.
 인간과 심리: 색이 주는 느낌을 알아야 해서 → 지각·감정 등 인간 심리를 배워요.
-화학: 염료·안료의 특성을 이해해야 해서 → 물질의 성질과 반응을 배워요.</t>
+화학: 염료·안료의 특성을 이해해야 해서 → 물질의 성질과 반응을 배워요.
+확률과 통계: 색 선호도 조사를 분석해야 해서 → 자료 정리와 통계 해석을 배워요.
+화법과 언어: 색채 기획을 고객에게 설명해서 → 설득력 있는 말하기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -9641,7 +10248,7 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 미술 감상과 비평, 화학, 수학과 문화</t>
+          <t>미술과 매체, 미술 감상과 비평, 화학, 수학과 문화, 대수, 영어 I</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -9654,7 +10261,9 @@
           <t>미술과 매체: 무늬와 색을 디자인해야 해서 → 다양한 매체로 조형 표현을 배워요.
 미술 감상과 비평: 색채·조형 감각이 중요해서 → 작품을 분석하며 미적 안목을 길러요.
 화학: 섬유와 염료의 성질을 알아야 해서 → 물질의 구조와 성질을 배워요.
-수학과 문화: 반복 무늬의 규칙을 만들어야 해서 → 문화 속 대칭·패턴의 수학을 배워요.</t>
+수학과 문화: 반복 무늬의 규칙을 만들어야 해서 → 문화 속 대칭·패턴의 수학을 배워요.
+대수: 반복 무늬의 규칙을 설계해서 → 수열과 규칙성을 배워요.
+영어 I: 해외 섬유 박람회 정보를 읽어서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -9676,7 +10285,7 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 미술 감상과 비평, 사회와 문화, 경제</t>
+          <t>미술과 매체, 미술 감상과 비평, 사회와 문화, 경제, 영어Ⅱ, 화법과 언어</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -9689,7 +10298,9 @@
           <t>미술과 매체: 옷의 디자인을 그려 표현해야 해서 → 다양한 매체로 조형 표현을 배워요.
 미술 감상과 비평: 색채·조형 감각이 중요해서 → 작품을 분석하며 미적 안목을 길러요.
 사회와 문화: 유행과 소비자 취향을 읽어야 해서 → 사회 변화와 대중문화를 배워요.
-경제: 잘 팔리는 옷을 기획해야 해서 → 시장과 소비의 원리를 배워요.</t>
+경제: 잘 팔리는 옷을 기획해야 해서 → 시장과 소비의 원리를 배워요.
+영어Ⅱ: 해외 패션쇼·브랜드와 교류해서 → 다양한 영어 표현을 익혀요.
+화법과 언어: 컬렉션 콘셉트를 발표해야 해서 → 설득력 있는 말하기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -9711,7 +10322,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>기하, 직무 수학, 미술과 매체</t>
+          <t>기하, 직무 수학, 미술과 매체, 대수, 미적분 I</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -9723,7 +10334,9 @@
         <is>
           <t>기하: 평면 패턴을 입체로 바꿔 생각해야 해서 → 도형과 공간의 성질을 배워요.
 직무 수학: 치수를 재고 비율을 계산해야 해서 → 실무에 쓰는 측정·비율 계산을 배워요.
-미술과 매체: 디자인 의도를 이해해야 해서 → 조형 요소와 시각 표현을 배워요.</t>
+미술과 매체: 디자인 의도를 이해해야 해서 → 조형 요소와 시각 표현을 배워요.
+대수: 치수를 비율대로 늘리고 줄여서 → 수와 식, 수열의 계산을 배워요.
+미적분 I: 몸의 곡선에 맞는 패턴을 그려서 → 곡선과 함수의 성질을 배워요.</t>
         </is>
       </c>
     </row>
@@ -9745,7 +10358,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>운동과 건강, 인간과 심리, 논리와 사고, 정보</t>
+          <t>운동과 건강, 인간과 심리, 논리와 사고, 정보, 스포츠 생활1, 확률과 통계, 영어 I</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -9758,7 +10371,10 @@
           <t>운동과 건강: 오래 앉아 훈련해 체력 관리가 중요해서 → 체력과 건강 관리 방법을 배워요.
 인간과 심리: 경기 중 긴장을 다스려야 해서 → 스트레스·감정 조절 등 심리를 배워요.
 논리와 사고: 상황 판단과 전략 수립이 핵심이라 → 논리적·비판적 사고를 연습해요.
-정보: 게임의 작동 원리를 알면 도움이 돼서 → 컴퓨팅 원리와 프로그래밍을 배워요.</t>
+정보: 게임의 작동 원리를 알면 도움이 돼서 → 컴퓨팅 원리와 프로그래밍을 배워요.
+스포츠 생활1: 장시간 경기를 버틸 체력이 필요해서 → 기초 체력과 건강 관리를 익혀요.
+확률과 통계: 승률과 전략을 데이터로 따져서 → 확률과 통계적 판단을 배워요.
+영어 I: 해외 선수와 대회에서 소통해서 → 기초 영어 의사소통을 익혀요.</t>
         </is>
       </c>
     </row>
@@ -9780,7 +10396,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>운동과 건강, 생명과학, 인간과 심리, 직무 의사소통</t>
+          <t>운동과 건강, 생명과학, 인간과 심리, 직무 의사소통, 스포츠 과학, 화법과 언어, 스포츠 생활2</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -9793,7 +10409,10 @@
           <t>운동과 건강: 직접 시범을 보이고 운동을 지도해서 → 체력과 건강 관리 방법을 배워요.
 생명과학: 근육·뼈 등 몸의 구조를 알아야 해서 → 사람 몸의 구조와 기능을 배워요.
 인간과 심리: 회원의 마음 상태까지 살펴야 해서 → 스트레스·정서 등 심리를 배워요.
-직무 의사소통: 동작을 쉽고 정확히 설명해야 해서 → 업무 상황의 말하기·듣기를 배워요.</t>
+직무 의사소통: 동작을 쉽고 정확히 설명해야 해서 → 업무 상황의 말하기·듣기를 배워요.
+스포츠 과학: 바른 자세와 근육 사용을 지도해서 → 운동 원리와 신체 구조를 배워요.
+화법과 언어: 동작을 말로 정확히 안내해서 → 알기 쉽게 설명하는 말하기를 배워요.
+스포츠 생활2: 직접 시범을 보일 체력이 필요해서 → 다양한 운동과 체력 관리를 익혀요.</t>
         </is>
       </c>
     </row>
@@ -9815,7 +10434,7 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 미술 감상과 비평, 동아시아 역사 기행, 사회와 문화</t>
+          <t>미술과 매체, 미술 감상과 비평, 동아시아 역사 기행, 사회와 문화, 문학, 영어 I</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -9828,7 +10447,9 @@
           <t>미술과 매체: 한복의 선과 색을 표현해야 해서 → 다양한 매체로 조형 표현을 배워요.
 미술 감상과 비평: 색채·조형 감각이 중요해서 → 작품을 분석하며 미적 안목을 길러요.
 동아시아 역사 기행: 시대별 복식의 배경을 알아야 해서 → 동아시아 역사와 문화 교류를 배워요.
-사회와 문화: 전통을 현대 취향에 맞게 풀어야 해서 → 문화 변동과 대중문화를 배워요.</t>
+사회와 문화: 전통을 현대 취향에 맞게 풀어야 해서 → 문화 변동과 대중문화를 배워요.
+문학: 전통 미감과 정서를 이해해야 해서 → 고전 문학 속 우리 문화를 배워요.
+영어 I: 한복을 해외에 알릴 기회가 많아서 → 기초 영어 표현을 익혀요.</t>
         </is>
       </c>
     </row>
@@ -9850,7 +10471,7 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>미술 감상과 비평, 미술과 매체, 인간과 철학, 세계사</t>
+          <t>미술 감상과 비평, 미술과 매체, 인간과 철학, 세계사, 문학, 독서와 작문</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -9863,7 +10484,9 @@
           <t>미술 감상과 비평: 자신의 작품 세계를 넓혀야 해서 → 작품을 감상·비평하며 안목을 길러요.
 미술과 매체: 다양한 재료와 기법을 써야 해서 → 매체별 조형 표현 방법을 배워요.
 인간과 철학: 작품에 담을 주제를 깊이 고민해야 해서 → 인간과 삶에 대한 사유를 배워요.
-세계사: 미술사의 흐름을 이해해야 해서 → 시대별 세계의 역사와 문화를 배워요.</t>
+세계사: 미술사의 흐름을 이해해야 해서 → 시대별 세계의 역사와 문화를 배워요.
+문학: 그림에 담을 주제와 감정을 고민해서 → 문학 속 주제와 상징 해석을 배워요.
+독서와 작문: 작가 노트와 전시 서문을 써야 해서 → 생각을 글로 정리하는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -9885,7 +10508,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>운동과 건강, 법과 사회, 인간과 심리, 실생활 영어 회화</t>
+          <t>운동과 건강, 법과 사회, 인간과 심리, 실생활 영어 회화, 스포츠 생활1, 스포츠 과학, 영어 I</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -9898,7 +10521,10 @@
           <t>운동과 건강: 강한 체력과 순발력이 필요해서 → 체력과 건강 관리 방법을 배워요.
 법과 사회: 법이 허용하는 범위에서 대응해야 해서 → 생활 속 법과 권리를 배워요.
 인간과 심리: 수상한 사람의 행동을 살펴야 해서 → 인간 행동과 심리의 원리를 배워요.
-실생활 영어 회화: 외국 귀빈을 경호하기도 해서 → 생활 속 영어 회화를 연습해요.</t>
+실생활 영어 회화: 외국 귀빈을 경호하기도 해서 → 생활 속 영어 회화를 연습해요.
+스포츠 생활1: 강한 체력과 순발력이 필수라서 → 기초 체력과 신체 활동을 익혀요.
+스포츠 과학: 위기 상황에 빠르게 대응해야 해서 → 체력 훈련의 과학 원리를 배워요.
+영어 I: 외국 귀빈을 경호하기도 해서 → 기초 영어 의사소통을 익혀요.</t>
         </is>
       </c>
     </row>
@@ -9920,7 +10546,7 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>직무 의사소통, 인간과 심리, 법과 사회, 실생활 영어 회화</t>
+          <t>직무 의사소통, 인간과 심리, 법과 사회, 실생활 영어 회화, 화법과 언어, 독서와 작문</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -9933,7 +10559,9 @@
           <t>직무 의사소통: 고객과 정확히 소통해야 해서 → 업무 상황의 말하기·듣기를 배워요.
 인간과 심리: 고객의 감정을 이해해야 해서 → 감정·행동 등 인간 심리를 배워요.
 법과 사회: 환불·계약 등 소비자 문제를 다뤄서 → 소비자 권리와 생활 법을 배워요.
-실생활 영어 회화: 외국인 손님도 응대해야 해서 → 생활 속 영어 회화를 연습해요.</t>
+실생활 영어 회화: 외국인 손님도 응대해야 해서 → 생활 속 영어 회화를 연습해요.
+화법과 언어: 고객의 불만을 듣고 해결해야 해서 → 공감하고 정확한 말하기를 배워요.
+독서와 작문: 상담 내용과 안내문을 글로 써서 → 정확하고 간결한 글쓰기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -9955,7 +10583,7 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 미술 감상과 비평, 화학, 생명과학</t>
+          <t>미술과 매체, 미술 감상과 비평, 화학, 생명과학, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -9968,7 +10596,9 @@
           <t>미술과 매체: 작은 손톱 위에 그림을 표현해서 → 다양한 매체로 조형 표현을 배워요.
 미술 감상과 비평: 색채·조형 감각이 중요해서 → 작품을 분석하며 미적 안목을 길러요.
 화학: 젤·리무버 등 화학 제품을 다뤄서 → 물질의 성질과 화학 반응을 배워요.
-생명과학: 손톱과 피부 건강을 살펴야 해서 → 몸의 구조와 질병의 기초를 배워요.</t>
+생명과학: 손톱과 피부 건강을 살펴야 해서 → 몸의 구조와 질병의 기초를 배워요.
+화법과 언어: 시술 중 고객과 대화하며 상담해서 → 친절하고 센스 있는 말하기를 배워요.
+영어 I: 해외 트렌드와 제품 정보를 찾아서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -9990,7 +10620,7 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 미술 감상과 비평, 화학, 생명과학</t>
+          <t>미술과 매체, 미술 감상과 비평, 화학, 생명과학, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -10003,7 +10633,9 @@
           <t>미술과 매체: 얼굴에 색과 형태를 표현해야 해서 → 조형 요소와 다양한 표현을 배워요.
 미술 감상과 비평: 색채·조형 감각이 중요해서 → 작품을 분석하며 미적 안목을 길러요.
 화학: 화장품 성분을 이해해야 해서 → 물질의 성질과 화학 반응을 배워요.
-생명과학: 피부 상태에 맞게 화장해야 해서 → 피부·면역 등 몸의 기초를 배워요.</t>
+생명과학: 피부 상태에 맞게 화장해야 해서 → 피부·면역 등 몸의 기초를 배워요.
+화법과 언어: 고객이 원하는 이미지를 파악해서 → 경청하고 제안하는 말하기를 배워요.
+영어 I: 해외 화장품 성분·트렌드를 읽어서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -10025,7 +10657,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>화학, 직무 의사소통, 실생활 영어 회화</t>
+          <t>화학, 직무 의사소통, 실생활 영어 회화, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -10037,7 +10669,9 @@
         <is>
           <t>화학: 로스팅·추출은 화학 변화라서 → 물질의 성질과 화학 반응을 배워요.
 직무 의사소통: 손님 취향을 듣고 메뉴를 추천해서 → 업무 상황의 말하기·듣기를 배워요.
-실생활 영어 회화: 외국인 손님도 응대해야 해서 → 생활 속 영어 회화를 연습해요.</t>
+실생활 영어 회화: 외국인 손님도 응대해야 해서 → 생활 속 영어 회화를 연습해요.
+화법과 언어: 손님에게 커피 맛을 설명해서 → 친절하고 알기 쉬운 말하기를 배워요.
+영어 I: 원두 산지 정보와 대회 자료가 영어라서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10693,7 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 인간과 심리, 직무 의사소통</t>
+          <t>생명과학, 인간과 심리, 직무 의사소통, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -10071,7 +10705,9 @@
         <is>
           <t>생명과학: 동물의 몸과 본능을 이해해야 해서 → 자극과 반응 등 생명 현상을 배워요.
 인간과 심리: 학습·행동 원리를 응용하므로 → 행동과 학습에 관한 심리를 배워요.
-직무 의사소통: 보호자를 교육·상담해야 해서 → 업무 상황의 설명·상담 화법을 배워요.</t>
+직무 의사소통: 보호자를 교육·상담해야 해서 → 업무 상황의 설명·상담 화법을 배워요.
+화법과 언어: 보호자에게 교정법을 설명해야 해서 → 알기 쉽게 설명하는 말하기를 배워요.
+영어 I: 해외 동물행동학 자료를 참고해서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -10093,7 +10729,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>매체 의사소통, 미술과 매체, 화학, 사회와 문화</t>
+          <t>매체 의사소통, 미술과 매체, 화학, 사회와 문화, 독서와 작문, 확률과 통계</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -10106,7 +10742,9 @@
           <t>매체 의사소통: 콘텐츠로 시청자와 소통해서 → 매체 특성과 콘텐츠 제작을 배워요.
 미술과 매체: 보기 좋은 영상·이미지를 만들어야 해서 → 사진·영상 등 매체 표현을 배워요.
 화학: 화장품 성분을 정확히 소개해야 해서 → 물질의 성질과 화학 반응을 배워요.
-사회와 문화: 유행과 소비자 반응을 읽어야 해서 → 대중문화와 사회 변화를 배워요.</t>
+사회와 문화: 유행과 소비자 반응을 읽어야 해서 → 대중문화와 사회 변화를 배워요.
+독서와 작문: 콘텐츠 기획안과 대본을 써서 → 구성력 있는 글쓰기를 배워요.
+확률과 통계: 조회수와 소비자 반응을 분석해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -10128,7 +10766,7 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>물리학, 지구과학, 기하, 직무 영어</t>
+          <t>물리학, 지구과학, 기하, 직무 영어, 영어Ⅱ, 대수, 스포츠 생활1</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -10141,7 +10779,10 @@
           <t>물리학: 배의 운동과 항해 장비를 이해해야 해서 → 힘과 운동, 파동의 기초를 배워요.
 지구과학: 날씨와 바다 상태를 읽어야 해서 → 대기와 해양의 변화를 배워요.
 기하: 배의 위치와 방향을 계산해야 해서 → 벡터와 공간좌표를 배워요.
-직무 영어: 국제 항해에서는 영어로 교신해서 → 업무에 쓰는 실용 영어를 배워요.</t>
+직무 영어: 국제 항해에서는 영어로 교신해서 → 업무에 쓰는 실용 영어를 배워요.
+영어Ⅱ: 국제 항해의 공용어가 영어라서 → 다양한 영어 표현과 독해를 익혀요.
+대수: 항로를 계산할 때 삼각함수를 써서 → 삼각함수와 계산법을 배워요.
+스포츠 생활1: 긴 항해를 견딜 체력이 필요해서 → 기초 체력 관리를 익혀요.</t>
         </is>
       </c>
     </row>
@@ -10163,7 +10804,7 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>화학, 세계시민과 지리, 직무 의사소통, 실생활 영어 회화</t>
+          <t>화학, 세계시민과 지리, 직무 의사소통, 실생활 영어 회화, 화법과 언어, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -10176,7 +10817,9 @@
           <t>화학: 발효와 맛·향 성분을 이해해야 해서 → 물질의 성질과 화학 반응을 배워요.
 세계시민과 지리: 산지의 기후·토양이 맛을 좌우해서 → 세계 각 지역의 자연과 문화를 배워요.
 직무 의사소통: 손님 취향을 듣고 추천해야 해서 → 업무 상황의 말하기·듣기를 배워요.
-실생활 영어 회화: 외국 손님과 와인 용어를 접해서 → 생활 속 영어 회화를 연습해요.</t>
+실생활 영어 회화: 외국 손님과 와인 용어를 접해서 → 생활 속 영어 회화를 연습해요.
+화법과 언어: 와인의 맛과 향을 말로 표현해서 → 풍부한 언어 표현을 배워요.
+영어Ⅱ: 와인 산지·라벨 정보가 외국어라서 → 다양한 영어 글 독해를 익혀요.</t>
         </is>
       </c>
     </row>
@@ -10198,7 +10841,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>여행지리, 세계시민과 지리, 경제, 실생활 영어 회화, 일본어</t>
+          <t>여행지리, 세계시민과 지리, 경제, 실생활 영어 회화, 일본어, 독서와 작문, 영어Ⅱ, 확률과 통계</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -10212,7 +10855,10 @@
 세계시민과 지리: 여러 나라의 상품을 만들어서 → 세계 지역의 특징과 문화를 배워요.
 경제: 가격과 수익을 따져야 해서 → 시장과 수요·공급의 원리를 배워요.
 실생활 영어 회화: 해외 현지 업체와 연락해서 → 생활 속 영어 회화를 연습해요.
-일본어: 일본은 대표적인 인기 여행지라서 → 일본어 기초 의사소통을 배워요.</t>
+일본어: 일본은 대표적인 인기 여행지라서 → 일본어 기초 의사소통을 배워요.
+독서와 작문: 여행 상품 소개 글을 써야 해서 → 매력 있게 쓰는 글쓰기를 배워요.
+영어Ⅱ: 해외 현지 업체와 연락해야 해서 → 다양한 영어 표현을 익혀요.
+확률과 통계: 여행 수요를 분석해 상품을 짜서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -10234,7 +10880,7 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>직무 의사소통, 실생활 영어 회화, 인간과 심리, 운동과 건강</t>
+          <t>직무 의사소통, 실생활 영어 회화, 인간과 심리, 운동과 건강, 화법과 언어, 영어 I, 스포츠 생활1</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -10247,7 +10893,10 @@
           <t>직무 의사소통: 승객 안내와 방송을 해야 해서 → 업무 상황의 말하기·듣기를 배워요.
 실생활 영어 회화: 외국인 승객도 안내해서 → 생활 속 영어 회화를 연습해요.
 인간과 심리: 다양한 승객을 응대해야 해서 → 감정과 행동 등 인간 심리를 배워요.
-운동과 건강: 오래 서서 일하고 이동이 많아서 → 체력과 건강 관리 방법을 배워요.</t>
+운동과 건강: 오래 서서 일하고 이동이 많아서 → 체력과 건강 관리 방법을 배워요.
+화법과 언어: 승객 안내 방송과 응대를 해서 → 정확하고 친절한 말하기를 배워요.
+영어 I: 외국인 승객을 안내해야 해서 → 기초 영어 표현을 익혀요.
+스포츠 생활1: 오래 서서 이동하며 일해서 → 기초 체력 관리를 익혀요.</t>
         </is>
       </c>
     </row>
@@ -10269,7 +10918,7 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>경제, 경제 수학, 금융과 경제생활, 직무 의사소통</t>
+          <t>경제, 경제 수학, 금융과 경제생활, 직무 의사소통, 확률과 통계, 화법과 언어</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -10282,7 +10931,9 @@
           <t>경제: 매출과 원가를 관리해야 해서 → 시장과 기업 활동의 원리를 배워요.
 경제 수학: 매출·비용을 계산하고 분석해서 → 경제 현상에 쓰이는 수학을 배워요.
 금융과 경제생활: 매장의 돈 관리를 책임져서 → 금융 생활과 자산 관리를 배워요.
-직무 의사소통: 직원과 손님을 함께 상대해서 → 업무 상황의 말하기·듣기를 배워요.</t>
+직무 의사소통: 직원과 손님을 함께 상대해서 → 업무 상황의 말하기·듣기를 배워요.
+확률과 통계: 매출과 재고 자료를 관리해서 → 자료 정리와 통계 해석을 배워요.
+화법과 언어: 직원과 손님을 모두 상대해서 → 상황에 맞는 말하기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10955,7 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>화학, 생명과학, 세포와 물질대사, 매체 의사소통</t>
+          <t>화학, 생명과학, 세포와 물질대사, 매체 의사소통, 독서와 작문, 영어 I</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -10317,7 +10968,9 @@
           <t>화학: 조리는 재료의 화학 변화라서 → 물질의 성질과 화학 반응을 배워요.
 생명과학: 음식과 건강의 관계를 다뤄서 → 사람 몸의 기능과 항상성을 배워요.
 세포와 물질대사: 영양소가 몸에서 쓰이는 원리를 알아야 해서 → 세포 호흡과 물질대사를 배워요.
-매체 의사소통: 방송·SNS로 요리를 알리므로 → 매체 특성과 콘텐츠 표현을 배워요.</t>
+매체 의사소통: 방송·SNS로 요리를 알리므로 → 매체 특성과 콘텐츠 표현을 배워요.
+독서와 작문: 레시피와 요리책을 써야 해서 → 정확하고 읽기 쉬운 글쓰기를 배워요.
+영어 I: 세계 요리 자료를 찾아봐서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -10339,7 +10992,7 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>지구과학, 물리학, 기하, 직무 영어</t>
+          <t>지구과학, 물리학, 기하, 직무 영어, 영어Ⅱ, 대수, 확률과 통계</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -10352,7 +11005,10 @@
           <t>지구과학: 비행 경로의 날씨를 판단해야 해서 → 대기와 날씨 변화를 배워요.
 물리학: 연료·무게 등 비행 조건을 따져서 → 힘과 운동의 기초를 배워요.
 기하: 항로와 방향을 다뤄야 해서 → 벡터와 공간좌표를 배워요.
-직무 영어: 항공 업무는 영어로 진행돼서 → 업무에 쓰는 실용 영어를 배워요.</t>
+직무 영어: 항공 업무는 영어로 진행돼서 → 업무에 쓰는 실용 영어를 배워요.
+영어Ⅱ: 국제 항공 정보가 영어로 오가서 → 다양한 영어 표현과 독해를 익혀요.
+대수: 연료와 운항 거리를 정확히 계산해서 → 수와 식, 함수 계산을 배워요.
+확률과 통계: 기상 확률로 운항 여부를 판단해서 → 확률과 자료 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -10374,7 +11030,7 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>직무 의사소통, 인간과 심리, 미술 감상과 비평, 금융과 경제생활</t>
+          <t>직무 의사소통, 인간과 심리, 미술 감상과 비평, 금융과 경제생활, 화법과 언어, 독서와 작문</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -10387,7 +11043,9 @@
           <t>직무 의사소통: 고객 상담과 업체 조율이 많아서 → 업무 상황의 상담·협상 화법을 배워요.
 인간과 심리: 고객의 바람을 세심히 파악해야 해서 → 감정과 욕구 등 인간 심리를 배워요.
 미술 감상과 비평: 식장 연출과 꾸밈 감각이 필요해서 → 미적 요소를 분석하며 안목을 길러요.
-금융과 경제생활: 예산에 맞게 계획을 짜야 해서 → 예산·소비 등 금융 생활을 배워요.</t>
+금융과 경제생활: 예산에 맞게 계획을 짜야 해서 → 예산·소비 등 금융 생활을 배워요.
+화법과 언어: 신랑신부의 바람을 듣고 조율해서 → 경청하고 설득하는 말하기를 배워요.
+독서와 작문: 견적서와 진행 계획서를 써서 → 정확한 실용 글쓰기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -10409,7 +11067,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>화학, 생명과학, 직무 수학, 미술과 매체</t>
+          <t>화학, 생명과학, 직무 수학, 미술과 매체, 대수, 영어 I</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -10422,7 +11080,9 @@
           <t>화학: 반죽과 굽기가 화학 반응이라서 → 물질의 성질과 화학 반응을 배워요.
 생명과학: 효모 발효와 위생을 이해해야 해서 → 세포와 미생물 등 생명 현상을 배워요.
 직무 수학: 재료 배합 비율을 계산해야 해서 → 실무에 쓰는 비율·단위 계산을 배워요.
-미술과 매체: 보기 좋은 모양과 장식이 중요해서 → 조형 요소와 다양한 표현을 배워요.</t>
+미술과 매체: 보기 좋은 모양과 장식이 중요해서 → 조형 요소와 다양한 표현을 배워요.
+대수: 배합 비율로 양을 늘리고 줄여서 → 수와 식의 계산력을 키워요.
+영어 I: 해외 레시피와 제과 용어를 읽어서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -10444,7 +11104,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>화학, 생명과학, 세계시민과 지리, 경제</t>
+          <t>화학, 생명과학, 세계시민과 지리, 경제, 영어 I, 스포츠 생활1</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -10457,7 +11117,9 @@
           <t>화학: 조리는 재료의 화학 변화라서 → 물질의 성질과 화학 반응을 배워요.
 생명과학: 식재료 위생과 영양을 알아야 해서 → 생명 현상과 몸의 기능을 배워요.
 세계시민과 지리: 세계 각국의 음식을 다뤄서 → 세계 지역의 자연과 생활 문화를 배워요.
-경제: 원가와 메뉴 가격을 관리해야 해서 → 시장과 경제 활동의 원리를 배워요.</t>
+경제: 원가와 메뉴 가격을 관리해야 해서 → 시장과 경제 활동의 원리를 배워요.
+영어 I: 해외 레시피와 식재료 정보를 봐서 → 기초 영어 독해 능력을 키워요.
+스포츠 생활1: 뜨거운 주방에서 오래 서서 일해서 → 기초 체력 관리를 익혀요.</t>
         </is>
       </c>
     </row>
@@ -10479,7 +11141,7 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>물리학, 역학과 에너지, 전자기와 양자, 운동과 건강</t>
+          <t>물리학, 역학과 에너지, 전자기와 양자, 운동과 건강, 미적분 I, 화법과 언어</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -10492,7 +11154,9 @@
           <t>물리학: 열차의 가속·제동 원리를 알아야 해서 → 힘과 운동, 전기의 기초를 배워요.
 역학과 에너지: 무거운 열차의 운동을 다뤄서 → 운동과 에너지를 깊이 배워요.
 전자기와 양자: 전기로 움직이는 열차가 많아서 → 전기·자기 현상을 깊이 배워요.
-운동과 건강: 오랜 시간 집중력과 체력이 필요해서 → 체력과 건강 관리 방법을 배워요.</t>
+운동과 건강: 오랜 시간 집중력과 체력이 필요해서 → 체력과 건강 관리 방법을 배워요.
+미적분 I: 열차의 가속·제동 거리를 판단해서 → 미분으로 속도 변화를 배워요.
+화법과 언어: 관제실과 정확히 교신해야 해서 → 정확하게 말하고 듣는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -10514,7 +11178,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>실생활 영어 회화, 중국어 회화, 일본어 회화, 실용 통계</t>
+          <t>실생활 영어 회화, 중국어 회화, 일본어 회화, 실용 통계, 확률과 통계, 영어Ⅱ, 화법과 언어</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -10527,7 +11191,10 @@
           <t>실생활 영어 회화: 외국인 손님이 대부분이라 → 생활 속 영어 회화를 연습해요.
 중국어 회화: 중국인 손님이 많아서 → 중국어로 말하고 듣는 연습을 해요.
 일본어 회화: 일본인 손님도 많아서 → 일본어로 말하고 듣는 연습을 해요.
-실용 통계: 게임 속 확률을 이해해야 해서 → 확률과 통계의 실생활 활용을 배워요.</t>
+실용 통계: 게임 속 확률을 이해해야 해서 → 확률과 통계의 실생활 활용을 배워요.
+확률과 통계: 게임마다 확률 계산이 핵심이라서 → 경우의 수와 확률을 배워요.
+영어Ⅱ: 외국인 고객이 대부분이라서 → 다양한 영어 표현을 익혀요.
+화법과 언어: 고객과 매너 있게 대화해야 해서 → 품위 있는 말하기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -10549,7 +11216,7 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>실생활 영어 회화, 세계 문화와 영어, 직무 의사소통, 운동과 건강</t>
+          <t>실생활 영어 회화, 세계 문화와 영어, 직무 의사소통, 운동과 건강, 영어Ⅱ, 스포츠 생활1, 화법과 언어</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -10562,7 +11229,10 @@
           <t>실생활 영어 회화: 외국인 승객을 영어로 응대해서 → 생활 속 영어 회화를 연습해요.
 세계 문화와 영어: 여러 나라 승객과 동료를 만나서 → 영어로 세계 문화를 이해해요.
 직무 의사소통: 승객 안내와 문제 해결이 많아서 → 업무 상황의 말하기·듣기를 배워요.
-운동과 건강: 긴 항해 동안 체력이 필요해서 → 체력과 건강 관리 방법을 배워요.</t>
+운동과 건강: 긴 항해 동안 체력이 필요해서 → 체력과 건강 관리 방법을 배워요.
+영어Ⅱ: 세계 각국 승객과 소통해서 → 다양한 영어 표현을 익혀요.
+스포츠 생활1: 비상 대응과 장시간 근무를 해서 → 기초 체력과 신체 활동을 익혀요.
+화법과 언어: 승객을 친절하게 안내해야 해서 → 상황에 맞는 말하기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -10584,7 +11254,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 미술 감상과 비평, 화학, 매체 의사소통</t>
+          <t>미술과 매체, 미술 감상과 비평, 화학, 매체 의사소통, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -10597,7 +11267,9 @@
           <t>미술과 매체: 사진·영상 속 음식을 연출해서 → 매체를 활용한 시각 표현을 배워요.
 미술 감상과 비평: 색과 구도 감각이 중요해서 → 작품의 조형 요소를 분석해요.
 화학: 음식의 색·모양 변화를 다뤄서 → 물질의 성질과 화학 반응을 배워요.
-매체 의사소통: 광고·방송 매체에 맞춰 작업해서 → 매체별 표현과 소통을 배워요.</t>
+매체 의사소통: 광고·방송 매체에 맞춰 작업해서 → 매체별 표현과 소통을 배워요.
+화법과 언어: 촬영팀과 콘셉트를 맞춰야 해서 → 생각을 정확히 전달하는 법을 배워요.
+영어 I: 해외 푸드 트렌드를 참고해서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -10619,7 +11291,7 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 미술 감상과 비평, 생명과학, 생태와 환경</t>
+          <t>미술과 매체, 미술 감상과 비평, 생명과학, 생태와 환경, 문학, 화법과 언어</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -10632,7 +11304,9 @@
           <t>미술과 매체: 꽃으로 형태와 색을 표현해서 → 다양한 매체로 조형 표현을 배워요.
 미술 감상과 비평: 색채·조형 감각이 중요해서 → 작품을 분석하며 미적 안목을 길러요.
 생명과학: 꽃을 싱싱하게 관리해야 해서 → 생물의 구조와 생명 현상을 배워요.
-생태와 환경: 식물이 자라는 환경을 이해해야 해서 → 생태계와 환경 문제를 배워요.</t>
+생태와 환경: 식물이 자라는 환경을 이해해야 해서 → 생태계와 환경 문제를 배워요.
+문학: 꽃말과 감성을 작품에 담아서 → 문학의 상징과 정서 표현을 배워요.
+화법과 언어: 고객의 사연을 듣고 꽃을 제안해서 → 경청하고 제안하는 말하기를 배워요.</t>
         </is>
       </c>
     </row>
@@ -10654,7 +11328,7 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>생명과학, 화학, 세포와 물질대사, 직무 의사소통</t>
+          <t>생명과학, 화학, 세포와 물질대사, 직무 의사소통, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -10667,7 +11341,9 @@
           <t>생명과학: 피부 구조와 질환을 알아야 해서 → 몸의 구조와 면역 등 생명 현상을 배워요.
 화학: 화장품 성분이 피부에 작용해서 → 물질의 성질과 화학 반응을 배워요.
 세포와 물질대사: 피부 재생 원리를 이해해야 해서 → 세포의 구조와 물질대사를 배워요.
-직무 의사소통: 고객과 상담하며 관리해서 → 업무 상황의 상담 화법을 배워요.</t>
+직무 의사소통: 고객과 상담하며 관리해서 → 업무 상황의 상담 화법을 배워요.
+화법과 언어: 고객 피부 상태를 상담해야 해서 → 친절하고 정확한 말하기를 배워요.
+영어 I: 화장품 성분 표기를 읽어야 해서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -10689,7 +11365,7 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>실생활 영어 회화, 직무 영어, 세계 문화와 영어, 중국어 회화, 운동과 건강</t>
+          <t>실생활 영어 회화, 직무 영어, 세계 문화와 영어, 중국어 회화, 운동과 건강, 스포츠 생활1, 화법과 언어, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -10703,7 +11379,10 @@
 직무 영어: 기내 방송과 업무를 영어로 해서 → 업무에 쓰는 실용 영어를 배워요.
 세계 문화와 영어: 여러 나라 승객을 만나서 → 영어로 세계 문화를 이해해요.
 중국어 회화: 중국어권 승객도 많아서 → 중국어로 말하고 듣는 연습을 해요.
-운동과 건강: 비상 상황 대응과 체력이 필요해서 → 체력과 건강 관리 방법을 배워요.</t>
+운동과 건강: 비상 상황 대응과 체력이 필요해서 → 체력과 건강 관리 방법을 배워요.
+스포츠 생활1: 비상 탈출 훈련과 체력 검사가 있어서 → 기초 체력과 신체 활동을 익혀요.
+화법과 언어: 기내 방송과 승객 응대를 해서 → 정확하고 품위 있는 말하기를 배워요.
+영어Ⅱ: 국제선 기내 안내가 영어라서 → 다양한 영어 표현을 익혀요.</t>
         </is>
       </c>
     </row>
@@ -10725,7 +11404,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>직무 영어, 물리학, 지구과학, 기하</t>
+          <t>직무 영어, 물리학, 지구과학, 기하, 영어Ⅱ, 대수, 화법과 언어</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -10738,7 +11417,10 @@
           <t>직무 영어: 조종사와 영어로 교신해서 → 업무에 쓰는 실용 영어를 배워요.
 물리학: 항공기의 속도와 움직임을 판단해서 → 힘과 운동의 기초를 배워요.
 지구과학: 날씨가 항공 안전을 좌우해서 → 대기와 날씨 변화를 배워요.
-기하: 여러 항공기의 위치를 공간에서 파악해서 → 벡터와 공간좌표를 배워요.</t>
+기하: 여러 항공기의 위치를 공간에서 파악해서 → 벡터와 공간좌표를 배워요.
+영어Ⅱ: 조종사와 영어로 교신해서 → 다양한 영어 표현과 듣기를 익혀요.
+대수: 항공기 간격과 고도를 계산해서 → 수와 식, 삼각함수를 배워요.
+화법과 언어: 짧고 정확한 지시가 생명이라서 → 정확하게 말하고 듣는 법을 배워요.</t>
         </is>
       </c>
     </row>
@@ -10760,7 +11442,7 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>물리학, 역학과 에너지, 지구과학, 직무 영어, 기하</t>
+          <t>물리학, 역학과 에너지, 지구과학, 직무 영어, 기하, 영어Ⅱ, 미적분 I, 스포츠 생활1</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -10774,7 +11456,10 @@
 역학과 에너지: 비행 중 속도·고도를 조절해서 → 운동과 에너지를 깊이 배워요.
 지구과학: 날씨가 비행 안전을 좌우해서 → 대기와 날씨 변화를 배워요.
 직무 영어: 관제탑과 영어로 교신해서 → 업무에 쓰는 실용 영어를 배워요.
-기하: 항로와 방향을 계산해야 해서 → 벡터와 공간좌표를 배워요.</t>
+기하: 항로와 방향을 계산해야 해서 → 벡터와 공간좌표를 배워요.
+영어Ⅱ: 관제와 교신이 모두 영어라서 → 다양한 영어 표현과 듣기를 익혀요.
+미적분 I: 속도·고도 변화를 순간 판단해서 → 미분으로 변화율을 배워요.
+스포츠 생활1: 엄격한 신체검사를 통과해야 해서 → 기초 체력 관리를 익혀요.</t>
         </is>
       </c>
     </row>
@@ -10796,7 +11481,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>실생활 영어 회화, 직무 영어, 직무 의사소통, 일본어 회화</t>
+          <t>실생활 영어 회화, 직무 영어, 직무 의사소통, 일본어 회화, 화법과 언어, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -10809,7 +11494,9 @@
           <t>실생활 영어 회화: 외국인 승객을 영어로 응대해서 → 생활 속 영어 회화를 연습해요.
 직무 영어: 항공 업무 용어가 영어라서 → 업무에 쓰는 실용 영어를 배워요.
 직무 의사소통: 승객 안내와 문제 해결이 많아서 → 업무 상황의 말하기·듣기를 배워요.
-일본어 회화: 일본인 승객도 자주 만나서 → 일본어로 말하고 듣는 연습을 해요.</t>
+일본어 회화: 일본인 승객도 자주 만나서 → 일본어로 말하고 듣는 연습을 해요.
+화법과 언어: 탑승 수속과 안내를 맡아서 → 친절하고 정확한 말하기를 배워요.
+영어Ⅱ: 외국인 승객 응대가 많아서 → 다양한 영어 표현을 익혀요.</t>
         </is>
       </c>
     </row>
@@ -10831,7 +11518,7 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>물리학, 역학과 에너지, 법과 사회, 직무 영어</t>
+          <t>물리학, 역학과 에너지, 법과 사회, 직무 영어, 영어 독해와 작문, 독서와 작문, 확률과 통계</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -10844,7 +11531,10 @@
           <t>물리학: 항공기의 작동 원리를 알아야 해서 → 힘과 운동, 전기의 기초를 배워요.
 역학과 에너지: 기체 구조와 성능을 점검해서 → 운동과 에너지를 깊이 배워요.
 법과 사회: 항공 안전 법규를 근거로 점검해서 → 법의 원리와 사회 속 법을 배워요.
-직무 영어: 국제 기준과 문서가 영어라서 → 업무에 쓰는 실용 영어를 배워요.</t>
+직무 영어: 국제 기준과 문서가 영어라서 → 업무에 쓰는 실용 영어를 배워요.
+영어 독해와 작문: 국제 안전 기준 문서를 다뤄서 → 영어 문서 읽기와 쓰기를 배워요.
+독서와 작문: 점검 보고서를 써야 해서 → 논리적인 보고서 쓰기를 배워요.
+확률과 통계: 사고 위험을 자료로 평가해서 → 확률과 통계 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -10866,7 +11556,7 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>직무 의사소통, 매체 의사소통, 경제, 실생활 영어 회화</t>
+          <t>직무 의사소통, 매체 의사소통, 경제, 실생활 영어 회화, 독서와 작문, 화법과 언어, 확률과 통계</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -10879,7 +11569,10 @@
           <t>직무 의사소통: 여러 업체·사람과 협의해야 해서 → 업무 상황의 회의·협상 화법을 배워요.
 매체 의사소통: 행사를 널리 알려야 해서 → 매체 특성과 홍보 표현을 배워요.
 경제: 예산과 수익을 계획해야 해서 → 시장과 경제 활동의 원리를 배워요.
-실생활 영어 회화: 국제 행사도 많아서 → 생활 속 영어 회화를 연습해요.</t>
+실생활 영어 회화: 국제 행사도 많아서 → 생활 속 영어 회화를 연습해요.
+독서와 작문: 기획서와 제안서를 써야 해서 → 설득력 있는 글쓰기를 배워요.
+화법과 언어: 행사 진행과 협의를 해야 해서 → 상황에 맞는 말하기를 배워요.
+확률과 통계: 참가자 설문 결과를 분석해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
     </row>
@@ -10901,7 +11594,7 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>미술과 매체, 미술 감상과 비평, 화학, 직무 의사소통</t>
+          <t>미술과 매체, 미술 감상과 비평, 화학, 직무 의사소통, 화법과 언어, 영어 I</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -10914,7 +11607,9 @@
           <t>미술과 매체: 머리 모양으로 형태와 색을 표현해서 → 다양한 매체로 조형 표현을 배워요.
 미술 감상과 비평: 색채·조형 감각이 중요해서 → 작품을 분석하며 미적 안목을 길러요.
 화학: 염색·펌은 화학 반응을 이용해서 → 물질의 성질과 화학 반응을 배워요.
-직무 의사소통: 고객 취향을 듣고 스타일을 제안해서 → 업무 상황의 말하기·듣기를 배워요.</t>
+직무 의사소통: 고객 취향을 듣고 스타일을 제안해서 → 업무 상황의 말하기·듣기를 배워요.
+화법과 언어: 고객이 원하는 스타일을 파악해서 → 경청하고 제안하는 말하기를 배워요.
+영어 I: 해외 헤어 트렌드를 참고해서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
     </row>
@@ -10936,7 +11631,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>실생활 영어 회화, 직무 영어, 세계 문화와 영어, 직무 의사소통, 경제</t>
+          <t>실생활 영어 회화, 직무 영어, 세계 문화와 영어, 직무 의사소통, 경제, 화법과 언어, 영어Ⅱ</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -10950,7 +11645,9 @@
 직무 영어: 예약·안내 업무를 영어로 해서 → 업무에 쓰는 실용 영어를 배워요.
 세계 문화와 영어: 여러 나라 손님을 만나서 → 영어로 세계 문화를 이해해요.
 직무 의사소통: 손님의 요청을 정확히 처리해야 해서 → 업무 상황의 말하기·듣기를 배워요.
-경제: 객실 가격과 수익을 관리해서 → 시장과 기업 활동의 원리를 배워요.</t>
+경제: 객실 가격과 수익을 관리해서 → 시장과 기업 활동의 원리를 배워요.
+화법과 언어: 투숙객을 품위 있게 응대해서 → 상황에 맞는 존중의 말하기를 배워요.
+영어Ⅱ: 외국인 투숙객과 소통이 많아서 → 다양한 영어 표현을 익혀요.</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>· 과목명은 2026·2027 과목데이터의 선택과목 이름과 똑같이 적어야 화면에서 연결됩니다(2학년 이상 지정 과목은 모두 배우므로 넣지 않았습니다).</t>
+          <t>· 과목명은 2026·2027 과목데이터의 과목 이름과 똑같이 적어야 화면에서 연결됩니다. 선택과목 뒤에 2·3학년 지정 과목(문학·대수·확률과 통계·영어 I 등)도 넣었습니다 → 화면에 「모두 배우는 지정 과목도 이 직업과 이어져요」로 따로 보입니다.</t>
         </is>
       </c>
     </row>

--- a/sheet/AI직업데이터.xlsx
+++ b/sheet/AI직업데이터.xlsx
@@ -2744,7 +2744,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>과학 교과 교육과, 물리학과, 화학과, 생명과학과</t>
+          <t>과학교육과, 물리학과, 화학과, 생명과학과</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>사회 교과 교육과, 사회학과, 정치외교학과, 경제학과</t>
+          <t>일반사회교육과, 역사교육과, 사회학과, 정치외교학과</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>영어영문학과, 언어 교과 교육과, 통번역학과, 서양어학과</t>
+          <t>영어영문학과, 영어교육과, 통번역학과, 서양어학과</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>언어 교과 교육과, 동양어학과, 서양어학과</t>
+          <t>영어교육과, 중국어교육과, 일본어교육과, 동양어학과</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>수학교육과, 과학 교과 교육과, 사회 교과 교육과, 언어 교과 교육과</t>
+          <t>수학교육과, 국어교육과, 영어교육과, 과학교육과</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>물리학과, 생명과학과, 과학 교과 교육과, 신문방송학과</t>
+          <t>물리학과, 생명과학과, 과학교육과, 신문방송학과</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">

--- a/sheet/AI직업데이터.xlsx
+++ b/sheet/AI직업데이터.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F294"/>
+  <dimension ref="A1:G294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -458,6 +458,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,6 +490,11 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>과목별 추천 이유</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>학과별 추천 이유</t>
         </is>
       </c>
     </row>
@@ -529,6 +535,14 @@
 영어 I: 해외 고고학 연구 자료를 참고해야 해서 → 기본 영어 독해 실력을 키워요.</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>고고학과: 유적 발굴 방법과 유물 분석을 직접 배워 고고학 연구에 써요.
+사학과: 역사 자료를 해석하는 법을 배워 유물의 시대적 의미를 밝혀요.
+인류학과: 옛사람들의 문화와 생활 방식을 연구하는 방법을 배워요.
+문화재보존학과: 유물을 과학적으로 분석·보존하는 법을 배워 발굴 조사에 써요.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -565,6 +579,13 @@
 논리와 사고: 글의 논리적 오류를 찾아야 해서 → 논증 구조와 오류 판별법을 배워요.
 화법과 언어: 맞춤법과 문법 오류를 정확히 짚어야 해서 → 국어의 음운·문법 규칙을 체계적으로 배워요.
 독서와 작문: 글의 흐름과 논리를 다듬어야 해서 → 글의 구조를 분석하고 고쳐 쓰는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>국어국문학과: 맞춤법과 문법, 바른 문장을 깊이 배워 원고 오류를 바로잡아요.
+문예창작학과: 글쓰기와 합평을 통해 문장을 읽기 쉽게 다듬는 감각을 길러요.
+신문방송학과: 기사 작성과 사실 확인을 배워 정확한 글을 만드는 데 써요.</t>
         </is>
       </c>
     </row>
@@ -606,6 +627,13 @@
 독서와 작문: 대본을 여러 번 고쳐 완성해야 해서 → 글을 계획하고 고쳐 쓰는 과정을 배워요.</t>
         </is>
       </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>문예창작학과: 희곡·시나리오 창작 실습으로 이야기와 대사 쓰는 법을 배워요.
+연극영화학과: 연기·연출을 함께 배워 무대와 화면에 맞는 대본을 써요.
+국어국문학과: 문학 작품 분석과 문장력을 길러 깊이 있는 이야기를 써요.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -641,6 +669,13 @@
 법과 사회: 기록물 관련 법령에 따라 일하므로 → 법의 기본 원리와 사회 속 법을 배워요.
 독서와 작문: 기록의 내용을 요약해 목록을 만들어야 해서 → 핵심을 파악해 간결하게 정리하는 법을 배워요.
 확률과 통계: 많은 기록물을 분류·관리해야 해서 → 자료를 기준에 따라 정리·분석하는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>문헌정보학과: 기록 관리와 정보 조직을 배워 기록물을 체계적으로 분류해요.
+사학과: 역사 기록을 읽고 해석하는 법을 배워 중요한 기록을 가려내요.
+기록관리학과: 기록의 수집·분류·보존 방법을 전문적으로 배워 바로 실무에 써요.</t>
         </is>
       </c>
     </row>
@@ -679,6 +714,14 @@
 미술 감상과 비평: 원래의 미적 가치를 살려야 해서 → 미술 작품을 감상하고 분석해요.
 독서와 작문: 보존 처리 과정을 보고서로 남겨야 해서 → 과정과 결과를 정확히 기록하는 글쓰기를 배워요.
 영어 I: 해외 보존 기술 자료를 읽어야 해서 → 전문 자료를 읽는 기본 영어 독해를 배워요.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>문화재보존학과: 문화재 보존 과학과 복원 기술을 직접 실습하며 배워요.
+고고학과: 유물의 시대와 제작 방식을 배워 복원의 기준을 세울 수 있어요.
+화학과: 물질의 성분과 화학 반응을 배워 문화재 손상 원인을 분석해요.
+공예과(조형학과): 도자·금속·목공 등 전통 재료 다루는 기술을 익혀 복원에 써요.</t>
         </is>
       </c>
     </row>
@@ -720,6 +763,14 @@
 확률과 통계: 관객 반응과 흥행 자료를 살펴야 해서 → 자료를 정리하고 경향을 읽는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>문화콘텐츠학과: 역사·문화를 콘텐츠로 바꾸는 기획과 제작 과정을 배워요.
+문예창작학과: 이야기 창작을 배워 콘텐츠에 담을 매력적인 스토리를 만들어요.
+미디어학과: 영상·디지털 미디어 제작을 배워 콘텐츠를 다양한 매체로 펼쳐요.
+경영학과: 마케팅과 사업 운영을 배워 콘텐츠를 상품으로 기획해요.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -759,6 +810,14 @@
 스포츠 생활1: 유적지를 오래 걸으며 안내해야 해서 → 꾸준한 운동으로 체력을 기르는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>사학과: 한국사와 세계사를 깊이 배워 문화유산의 역사를 설명해요.
+고고학과: 유적과 유물의 의미를 배워 유적지 해설에 바로 써요.
+문화재보존학과: 문화재의 가치와 보존 방법을 배워 깊이 있게 해설해요.
+관광경영학과: 관광 서비스와 안내 기법을 배워 방문객을 친절하게 안내해요.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -795,6 +854,14 @@
 화학: 안료·재료를 과학적으로 분석하기도 해서 → 물질의 성질과 화학 반응을 배워요.
 독서와 작문: 감정 결과를 감정서로 정확히 써야 해서 → 근거를 들어 논리적으로 글 쓰는 법을 배워요.
 영어 I: 해외 경매 자료와 작품 기록을 봐야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>미술사학과: 시대별 미술 양식과 작가를 배워 작품의 진위와 가치를 판단해요.
+회화과: 그림 재료와 기법을 직접 익혀 작품의 제작 방식을 알아봐요.
+고고학과: 고미술품의 시대와 제작 배경을 배워 감정에 활용해요.
+문화재보존학과: 작품 재료를 과학적으로 분석하는 법을 배워 진위 감정에 써요.</t>
         </is>
       </c>
     </row>
@@ -836,6 +903,14 @@
 문학: 드라마·교양 프로그램의 이야기를 짜야 해서 → 작품의 구성과 표현 방식을 배워요.</t>
         </is>
       </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>문예창작학과: 대본·구성 글쓰기 실습으로 방송 원고 쓰는 힘을 길러요.
+국어국문학과: 정확하고 자연스러운 문장력을 길러 내레이션 원고를 써요.
+신문방송학과: 방송 제작 과정과 미디어 이론을 배워 프로그램을 기획해요.
+미디어학과: 다양한 미디어 콘텐츠 기획을 배워 방송 구성에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -875,6 +950,13 @@
 영어 I: 해외 역사 연구서를 참고해야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>사학과: 역사 자료를 조사·해석하는 법을 배워 정확한 역사 글을 써요.
+국어국문학과: 읽기 쉬운 문장과 글 구성을 배워 대중을 위한 책을 써요.
+문예창작학과: 이야기 창작을 배워 역사를 흥미로운 글로 풀어내요.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -914,6 +996,13 @@
 독서와 작문: 매일 연재 분량을 써내야 해서 → 글을 계획하고 고쳐 쓰는 과정을 배워요.</t>
         </is>
       </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>문예창작학과: 소설 창작과 합평을 통해 꾸준히 연재할 글쓰기 실력을 길러요.
+국어국문학과: 다양한 소설을 분석하며 이야기 구성과 문장력을 길러요.
+문화콘텐츠학과: 웹콘텐츠 시장과 독자 트렌드를 배워 인기 작품을 기획해요.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -953,6 +1042,13 @@
 영어 I: K팝 가사에 영어 표현이 자주 쓰여서 → 자연스러운 영어 표현을 배워요.</t>
         </is>
       </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>문예창작학과: 시 창작과 표현 기법을 배워 마음을 울리는 노랫말을 써요.
+실용음악과: 대중음악의 구조와 멜로디를 배워 곡에 맞는 가사를 써요.
+국어국문학과: 우리말의 운율과 표현을 깊이 배워 아름다운 노랫말을 써요.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -992,6 +1088,14 @@
 문학: 좋은 작품을 알아보는 눈이 필요해서 → 문학 작품을 해석하고 감상하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>국어국문학과: 문학 작품 분석과 글을 보는 안목을 길러 좋은 원고를 골라요.
+문예창작학과: 창작 과정을 이해해 작가와 소통하며 책을 기획할 수 있어요.
+미디어학과: 미디어 트렌드와 독자를 분석해 출판 기획에 활용해요.
+경영학과: 시장 분석과 마케팅을 배워 팔리는 책을 기획해요.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1031,6 +1135,14 @@
 문학: 작가와 작품을 깊이 이해해야 해서 → 문학 작품을 해석하는 방법을 배워요.</t>
         </is>
       </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>국어국문학과: 바른 문장과 맞춤법을 깊이 배워 원고를 정확하게 다듬어요.
+문예창작학과: 글쓰기와 합평 경험으로 원고를 보는 편집 감각을 길러요.
+문헌정보학과: 자료 조직과 출판 유통을 배워 책 만드는 과정을 이해해요.
+미디어학과: 디지털 출판과 콘텐츠 제작을 배워 전자책 편집에도 써요.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1070,6 +1182,14 @@
 확률과 통계: 통계 자료로 사회 현상을 분석해야 해서 → 자료를 해석하고 근거로 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>신문방송학과: 기사 작성과 언론 이론을 배워 매체에 맞는 칼럼을 써요.
+국어국문학과: 탄탄한 문장력과 글 구성 능력을 길러 설득력 있게 써요.
+철학과: 비판적 사고와 논리를 배워 사회 현상을 깊이 분석해요.
+정치외교학과: 정치와 사회 제도를 배워 시사 칼럼을 깊이 있게 써요.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1106,6 +1226,14 @@
 논리와 사고: 평가에 타당한 근거가 필요해서 → 논증과 비판적 사고를 배워요.
 문학: 작품을 깊이 분석하고 평가해야 해서 → 작품의 주제와 표현을 해석하는 법을 배워요.
 독서와 작문: 평가를 설득력 있는 글로 써야 해서 → 근거를 들어 논리적으로 쓰는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>국어국문학과: 문학 이론과 비평 방법을 배워 작품을 분석하고 평가해요.
+문예창작학과: 작품 창작 과정을 이해해 작품을 깊이 있게 평가해요.
+연극영화학과: 연극·영화의 연출과 이론을 배워 공연·영화 평론에 써요.
+철학과: 미학과 논리를 배워 작품의 가치를 판단하는 기준을 세워요.</t>
         </is>
       </c>
     </row>
@@ -1147,6 +1275,14 @@
 확률과 통계: 사업 효과를 자료로 보여 줘야 해서 → 자료를 정리하고 분석하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>사회복지학과: 복지 제도와 지역사회 실천을 배워 지원 사업을 운영해요.
+국제관계학과: 국제기구와 국제 협력을 배워 해외 지원 활동에 써요.
+사회학과: 빈곤·불평등 같은 사회 문제의 원인을 분석하는 법을 배워요.
+정치외교학과: 인권·정책 과정을 배워 캠페인과 정책 제안에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1183,6 +1319,13 @@
 스포츠 생활1: 범인을 쫓고 제압할 강한 체력이 필요해서 → 꾸준한 운동으로 기초 체력을 길러요.
 스포츠 생활2: 체력 시험과 현장 활동에 대비해야 해서 → 운동을 습관으로 만들어 체력을 키워요.
 화법과 언어: 시민과 대화하고 조서를 써야 해서 → 정확하고 차분한 말하기를 배워요.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>경찰행정학과: 경찰학·범죄학·수사 실무를 배워 경찰관이 되는 길이 넓어요.
+법학과: 형법·형사소송법을 배워 법에 맞게 수사하는 기초를 다져요.
+행정학과: 공공 행정과 정책을 배워 치안 행정 업무에 도움이 돼요.</t>
         </is>
       </c>
     </row>
@@ -1224,6 +1367,14 @@
 영어 I: 해외 광고 사례를 참고해야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>광고홍보학과: 광고 기획과 캠페인 제작을 배워 광고 전략을 직접 세워요.
+경영학과: 마케팅과 소비자 분석을 배워 광고주의 요구를 파악해요.
+신문방송학과: 미디어 이론과 매체 특성을 배워 알맞은 광고 매체를 골라요.
+심리학과: 소비자 심리를 배워 마음을 움직이는 광고 전략을 세워요.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1259,6 +1410,14 @@
 운동과 건강: 체력과 안전 관리가 필요해서 → 체력 관리와 건강한 운동법을 배워요.
 스포츠 생활1: 돌발 상황에 대응할 체력이 필요해서 → 꾸준한 운동으로 체력을 길러요.
 화법과 언어: 수용자를 상담하고 지도해야 해서 → 상대를 존중하며 대화하는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>교정학과: 교정 제도와 수용자 교화 방법을 전문적으로 배워 바로 실무에 써요.
+경찰행정학과: 범죄학과 교정 행정을 배워 수용자 관리에 도움이 돼요.
+법학과: 형법과 형 집행 법규를 배워 법에 맞게 수용자를 관리해요.
+사회복지학과: 상담과 사회 복귀 지원을 배워 수용자의 재출발을 도와요.</t>
         </is>
       </c>
     </row>
@@ -1300,6 +1459,14 @@
 확률과 통계: 현지 조사 자료로 사업을 평가해야 해서 → 자료를 정리하고 분석하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>국제관계학과: 국제기구와 개발 협력 이론을 배워 국제 지원 사업을 기획해요.
+정치외교학과: 국제 정치와 외교를 배워 여러 나라와 협력 사업을 이끌어요.
+경제학과: 개발 경제와 빈곤 문제를 배워 효과적인 지원 방안을 찾아요.
+사회복지학과: 복지 정책과 지역사회 실천을 배워 현지 지원 사업에 써요.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1339,6 +1506,13 @@
 영어 I: 연합 훈련에서 외국군과 소통해야 해서 → 기본 영어 의사소통을 배워요.</t>
         </is>
       </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>군사학과: 군사 전략과 지휘 능력을 배우며 장교로 임관하는 길이 열려요.
+정치외교학과: 국제 안보와 국가 관계를 배워 국방 정책을 이해해요.
+체육학과: 체력 훈련과 운동 지도법을 배워 강한 부대를 이끌어요.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1374,6 +1548,13 @@
 매체 의사소통: 방송으로 정보를 전달하므로 → 매체에 맞게 말하고 표현하는 법을 배워요.
 화법과 언어: 방송에서 날씨를 또렷이 전달해야 해서 → 정확한 발음과 말하기 방법을 배워요.
 확률과 통계: 강수 확률 같은 수치를 설명해야 해서 → 확률과 자료 해석 방법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>대기과학과: 기상 관측과 예보 원리를 배워 날씨 정보를 정확히 정리해요.
+신문방송학과: 방송 진행과 말하기를 배워 날씨를 알기 쉽게 전달해요.
+미디어학과: 방송·영상 매체를 배워 화면에 맞게 날씨 정보를 전해요.</t>
         </is>
       </c>
     </row>
@@ -1412,6 +1593,14 @@
 중국어: 중국 출신 이주민이 많아서 → 중국어 기초 의사소통을 배워요.
 화법과 언어: 이주민과 쉬운 말로 소통해야 해서 → 상대에 맞춘 말하기와 공감 대화를 배워요.
 영어 I: 여러 나라 사람과 대화하는 일이 많아서 → 기본 영어 의사소통을 배워요.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>사회복지학과: 다문화 가족 복지와 상담을 배워 이주민 가정을 지원해요.
+사회학과: 다양한 집단과 문화를 연구해 이주민의 어려움을 이해해요.
+교육학과: 평생 교육과 교육 프로그램 개발을 배워 적응 교육을 운영해요.
+국제관계학과: 여러 나라의 문화와 국제 관계를 배워 소통을 도와요.</t>
         </is>
       </c>
     </row>
@@ -1453,6 +1642,13 @@
 영어 I: 해외 범죄 심리 연구를 참고해야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>심리학과: 범죄·이상 심리와 행동 분석을 배워 범인의 특성을 추리해요.
+경찰행정학과: 범죄 수사와 과학 수사를 배워 수사 현장에 바로 써요.
+사회학과: 범죄가 생기는 사회적 원인을 분석하는 법을 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1489,6 +1685,12 @@
 논리와 사고: 법 조문을 논리적으로 해석해야 해서 → 논증과 추론하는 법을 배워요.
 독서와 작문: 법률 서류를 정확하게 작성해야 해서 → 목적에 맞게 정확한 글 쓰는 법을 배워요.
 화법과 언어: 의뢰인에게 절차를 쉽게 설명해야 해서 → 알기 쉽게 설명하는 말하기를 배워요.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>법학과: 민법·민사소송법 등을 배워 법무사 시험과 서류 작성에 써요.
+행정학과: 행정법과 행정 절차를 배워 각종 신청 서류 업무에 써요.</t>
         </is>
       </c>
     </row>
@@ -1530,6 +1732,14 @@
 독서와 작문: 조사 결과를 보고서로 정리해야 해서 → 자료를 근거로 글 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>사회학과: 사회 조사 방법론과 설문 설계를 배워 바로 실무에 써요.
+통계학과: 표본 추출과 통계 분석을 배워 조사 결과를 정확히 분석해요.
+빅데이터학과: 대용량 데이터 처리와 분석 도구를 배워 조사 자료를 다뤄요.
+심리학과: 심리 측정과 설문 문항 만들기를 배워 정확한 조사를 설계해요.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1568,6 +1778,13 @@
 스포츠 과학: 부상 없이 오래 활동해야 해서 → 운동과 신체 회복의 원리를 배워요.</t>
         </is>
       </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>소방행정학과: 재난 관리와 소방 법규·행정을 배워 소방관 시험에 도움이 돼요.
+응급구조학과: 응급 처치와 구조 기술을 배우고 응급구조사 시험을 볼 수 있어요.
+체육학과: 강한 체력과 운동 능력을 길러 구조 현장의 체력 요구에 대비해요.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1606,6 +1823,14 @@
 화법과 언어: 설문 문항을 오해 없이 만들어야 해서 → 정확하고 중립적인 언어 표현을 배워요.</t>
         </is>
       </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>통계학과: 표본 조사와 통계 분석을 배워 여론을 정확하게 측정해요.
+사회학과: 사회 조사 방법을 배워 설문을 설계하고 결과를 해석해요.
+정치외교학과: 선거와 정치 과정을 배워 정치 여론 조사를 깊이 분석해요.
+신문방송학과: 여론과 미디어의 관계를 배워 조사 결과를 알기 쉽게 발표해요.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1642,6 +1867,14 @@
 화법과 언어: 내담자의 마음을 듣고 상담해야 해서 → 공감하며 대화하는 방법을 배워요.
 독서와 작문: 상담 기록과 재활 계획서를 써야 해서 → 내용을 정확히 정리하는 글쓰기를 배워요.
 스포츠 문화: 장애인 스포츠로 재활을 도울 수 있어서 → 다양한 스포츠의 가치와 문화를 배워요.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>재활상담학과: 재활 상담 이론과 직업 재활을 배워 장애인 자립을 도와요.
+사회복지학과: 복지 제도와 서비스를 배워 장애인에게 필요한 지원을 연결해요.
+심리학과: 상담 기법과 심리 검사를 배워 장애인의 마음을 이해해요.
+특수교육과: 장애 특성과 특수 교육 방법을 배워 맞춤 지원 계획을 세워요.</t>
         </is>
       </c>
     </row>
@@ -1683,6 +1916,14 @@
 독서와 작문: 선거 전략 보고서를 써야 해서 → 논리적으로 설득하는 글쓰기를 배워요.</t>
         </is>
       </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>정치외교학과: 선거와 정당, 정치 과정을 배워 선거 전략을 세워요.
+광고홍보학과: 홍보 전략과 메시지 만들기를 배워 후보를 효과적으로 알려요.
+신문방송학과: 미디어와 여론의 관계를 배워 언론 대응 전략을 세워요.
+통계학과: 여론 조사 자료를 분석하는 법을 배워 전략 판단에 써요.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1722,6 +1963,13 @@
 영어 I: 해외 정치 소식을 직접 살펴야 해서 → 영어 기사를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>정치외교학과: 정치 이론과 정책 과정을 배워 정치 현상을 깊이 분석해요.
+신문방송학과: 언론 이론과 글쓰기·말하기를 배워 견해를 매체로 전해요.
+사학과: 역사적 사례를 배워 오늘날의 정치를 넓은 시각으로 해석해요.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1760,6 +2008,13 @@
 독서와 작문: 자기소개서 작성을 도와줘야 해서 → 목적에 맞게 글 쓰고 고치는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>심리학과: 적성·흥미 심리 검사와 상담 기법을 배워 구직자를 도와요.
+교육학과: 진로 교육과 상담을 배워 알맞은 진로를 안내해요.
+사회복지학과: 고용 복지 제도를 배워 구직자에게 취업 지원을 연결해요.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1798,6 +2053,14 @@
 스포츠 문화: 스포츠로 협동심을 기르는 활동이 많아서 → 스포츠의 가치와 문화를 배워요.</t>
         </is>
       </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>청소년학과: 청소년 활동과 프로그램 개발을 배워 청소년지도사 시험에 도움이 돼요.
+사회복지학과: 청소년 복지와 상담을 배워 도움이 필요한 청소년을 지원해요.
+교육학과: 교육 프로그램 설계를 배워 청소년 활동을 기획해요.
+아동학과: 아동·청소년 발달을 배워 나이에 맞는 활동을 이끌어요.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1834,6 +2097,14 @@
 세계시민과 지리: 여러 나라 사람을 만나므로 → 세계 여러 지역의 특성을 배워요.
 영어 I: 외국인과 매일 영어로 대화해야 해서 → 기본 영어 의사소통을 배워요.
 영어Ⅱ: 여러 나라 서류와 질문을 이해해야 해서 → 더 다양한 영어 표현과 독해를 배워요.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>법학과: 출입국관리법 등 법 지식을 배워 여권·비자를 정확히 심사해요.
+행정학과: 행정법과 공공 행정을 배워 출입국 행정 업무에 도움이 돼요.
+국제관계학과: 국제 관계와 이민 정책을 배워 외국인 체류 관리를 이해해요.
+영어영문학과: 영어 실력을 길러 공항에서 외국인과 정확하게 소통해요.</t>
         </is>
       </c>
     </row>
@@ -1875,6 +2146,14 @@
 영어 I: 광고에 영어 문구도 자주 쓰여서 → 자연스러운 영어 표현을 배워요.</t>
         </is>
       </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>광고홍보학과: 광고 기획과 소비자 심리를 배워 마음을 끄는 광고 문구를 만드는 데 도움이 돼요.
+문예창작학과: 글쓰기를 꾸준히 훈련해 짧고 인상적인 문장을 만드는 표현력을 길러요.
+국어국문학과: 우리말의 어휘와 문장을 깊이 공부해 정확하고 맛깔나는 카피를 쓸 수 있어요.
+신문방송학과: 미디어와 대중 커뮤니케이션을 배워 메시지를 효과적으로 전달하는 법을 알아요.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1914,6 +2193,13 @@
 영어 독해와 작문: 영어 논문을 읽고 써야 해서 → 영어 글을 읽고 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>경제학과: 시장·물가·고용 같은 경제 이론과 정책 분석 방법을 체계적으로 배워요.
+수학과: 경제 모형을 세우고 풀어내는 데 필요한 수학적 사고력과 계산 능력을 길러요.
+통계학과: 경제 데이터를 분석하고 예측하는 통계 기법을 배워 연구에 바로 쓸 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1953,6 +2239,14 @@
 독서와 작문: 계약서를 꼼꼼히 읽고 써야 해서 → 글을 정확히 읽고 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>부동산학과: 부동산 시장, 감정평가, 관련 법규를 배워 공인중개사 시험 준비에 유리해요.
+법학과: 민법·계약법을 배워 부동산 계약서 작성과 권리 관계 확인에 도움이 돼요.
+경제학과: 시장 원리와 가격 결정을 배워 부동산 시세와 거래 흐름을 이해할 수 있어요.
+도시공학과: 도시 계획과 토지 이용을 배워 지역 개발에 따른 부동산 가치를 판단해요.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1992,6 +2286,14 @@
 독서와 작문: 통관 서류를 정확히 작성해야 해서 → 정확하고 논리적인 글쓰기를 배워요.</t>
         </is>
       </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>무역학과: 수출입 절차와 국제 무역 규칙을 배워 통관 업무를 이해하는 데 바로 쓰여요.
+법학과: 관세법 등 법 조문을 해석하는 힘을 길러 관세사 시험과 실무에 도움이 돼요.
+경영학과: 기업 경영과 회계 기초를 배워 수출입 기업의 업무를 이해하고 상담할 수 있어요.
+세무·회계학과: 세금 계산과 회계 처리를 배워 관세를 정확히 계산하고 신고하는 데 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2031,6 +2333,14 @@
 화법과 언어: 행사 진행과 안내를 맡아야 해서 → 상황에 맞는 말하기를 배워요.</t>
         </is>
       </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>관광경영학과: 관광·컨벤션 산업과 행사 기획을 배워 국제회의 운영에 바로 활용해요.
+국제관계학과: 국제 정세와 외교 의전을 배워 여러 나라 대표가 모이는 행사를 준비해요.
+통번역학과: 외국어 통역 기술을 배워 해외 참가자와 소통하고 통역 준비를 도울 수 있어요.
+경영학과: 예산·인력·마케팅 관리를 배워 큰 행사를 계획대로 운영하는 능력을 길러요.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2067,6 +2377,14 @@
 경제: 금리와 시장 변화를 읽어야 해서 → 시장과 경제 정책의 원리를 배워요.
 확률과 통계: 고객 위험과 수익 가능성을 따져야 해서 → 확률과 통계적 추론을 배워요.
 대수: 이자와 수익률을 계산해야 해서 → 지수·로그·수열로 복리를 계산해요.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>금융보험학과: 보험·예금·투자 상품의 구조와 금융 제도를 배워 새 상품 설계에 활용해요.
+경제학과: 금리와 시장 흐름을 분석하는 법을 배워 고객이 원하는 상품을 기획해요.
+통계학과: 고객·시장 데이터를 통계로 분석해 상품의 수익성과 위험을 따져 볼 수 있어요.
+수학과: 확률과 수리 모델을 배워 상품의 가격과 수익 구조를 계산하는 데 쓰여요.</t>
         </is>
       </c>
     </row>
@@ -2108,6 +2426,14 @@
 영어 I: 해외 시장 위험 자료를 살펴야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>금융보험학과: 금융 위험의 종류와 보험·파생상품 같은 관리 수단을 체계적으로 배워요.
+경제학과: 경기 변동과 금리·환율 변화를 분석해 위험 요인을 예측하는 힘을 길러요.
+통계학과: 확률과 통계 모델로 손실 가능성을 수치로 계산하는 방법을 배워요.
+경영학과: 기업 경영과 재무 구조를 배워 회사 전체의 위험을 관리하는 데 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2147,6 +2473,14 @@
 영어 I: 해외 운송 업체와 연락해야 해서 → 기본 영어 의사소통을 배워요.</t>
         </is>
       </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>물류학과: 보관·운송·유통 등 물류 시스템 전반을 배워 현장 관리에 바로 쓸 수 있어요.
+산업공학과: 공정 최적화와 재고 관리 기법을 배워 물류를 효율적으로 설계할 수 있어요.
+경영학과: 공급망 관리와 경영 전략을 배워 물류 비용과 일정을 계획하는 데 도움이 돼요.
+무역학과: 수출입 절차와 국제 운송을 배워 해외 물류를 관리하는 데 활용할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2182,6 +2516,14 @@
 생명과학: 질병·상해 서류를 검토해야 해서 → 사람 몸의 구조와 질병을 배워요.
 확률과 통계: 사고 확률로 보험 위험을 판단해야 해서 → 확률과 통계적 추론을 배워요.
 독서와 작문: 서류를 검토하고 심사 의견을 써야 해서 → 글을 꼼꼼히 읽고 근거 있게 쓰는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>금융보험학과: 보험 상품 구조와 보험 계약 원리를 배워 가입·지급 심사에 바로 쓰여요.
+경영학과: 기업 경영과 재무를 배워 보험 계약의 손익과 위험을 판단하는 데 도움이 돼요.
+법학과: 보험 약관과 계약법을 해석하는 힘을 길러 지급 여부를 정확히 판단해요.
+간호학과: 질병과 치료 과정에 대한 의학 지식을 배워 의료 보험금 심사에 활용해요.</t>
         </is>
       </c>
     </row>
@@ -2223,6 +2565,14 @@
 영어 I: 글로벌 기업 자료를 다루는 일이 많아서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>경영학과: 경영 전략과 조직·마케팅을 배워 기업의 문제를 찾고 개선안을 제시해요.
+산업공학과: 업무 과정을 분석하고 효율을 높이는 기법을 배워 개선 방안 설계에 활용해요.
+빅데이터학과: 데이터 수집·처리·시각화를 배워 기업 데이터를 분석하는 데 바로 쓸 수 있어요.
+통계학과: 통계 분석 방법을 배워 데이터를 근거로 정확한 판단을 내리는 힘을 길러요.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2262,6 +2612,13 @@
 영어 I: 해외 상품과 트렌드를 살펴야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>경영학과: 마케팅과 소비자 행동, 유통을 배워 팔릴 상품을 기획하고 전략을 세워요.
+의류학과: 패션 소재와 유행 흐름을 배워 의류 상품을 고르고 기획하는 데 도움이 돼요.
+디자인과: 소비자가 좋아하는 형태와 색을 배워 상품의 매력을 높이는 기획에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2301,6 +2658,14 @@
 독서와 작문: 분석 보고서를 써야 해서 → 자료를 근거로 글 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>통계학과: 설문 설계와 표본 조사, 통계 분석을 배워 조사 결과를 정확히 해석해요.
+경영학과: 마케팅과 소비자 행동을 배워 조사 결과를 기업 전략으로 연결할 수 있어요.
+경제학과: 수요와 공급, 시장 구조를 배워 산업과 시장의 흐름을 분석하는 데 쓰여요.
+심리학과: 사람의 생각과 행동 원리를 배워 소비자 심리를 깊이 이해하는 데 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2340,6 +2705,13 @@
 영어 I: 해외 판매와 해외 상품을 다룰 수 있어서 → 기본 영어 의사소통을 배워요.</t>
         </is>
       </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>경영학과: 마케팅·유통·고객 관리를 배워 쇼핑몰을 운영하고 매출을 관리해요.
+광고홍보학과: 광고 기획과 SNS 홍보를 배워 쇼핑몰과 상품을 효과적으로 알릴 수 있어요.
+디자인과: 상세 페이지와 상품 사진을 보기 좋게 꾸미는 시각 디자인 능력을 길러요.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2379,6 +2751,13 @@
 영어 I: 해외 상품을 들여오는 일이 있어서 → 기본 영어 의사소통을 배워요.</t>
         </is>
       </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>경영학과: 경영 전략과 마케팅을 배워 구매·재고·판매 계획을 세우는 데 도움이 돼요.
+유통경영학과: 유통 경로와 매장·재고 관리를 전문적으로 배워 현장 업무에 바로 쓰여요.
+무역학과: 수출입과 국제 유통을 배워 해외 상품의 구매와 공급을 관리할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2418,6 +2797,14 @@
 확률과 통계: 대출 심사에 고객 자료를 분석해야 해서 → 자료를 정리하고 판단하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>경영학과: 회계·재무·마케팅을 배워 은행의 고객 응대와 금융 업무 이해에 도움이 돼요.
+경제학과: 금리·환율 같은 경제 원리를 배워 예금·대출 상품을 정확히 안내할 수 있어요.
+금융보험학과: 은행·보험·투자 상품과 금융 제도를 배워 고객에게 알맞은 상품을 추천해요.
+세무·회계학과: 회계와 세금 지식을 배워 기업 대출 심사와 재무 상담에 활용할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2457,6 +2844,14 @@
 확률과 통계: 직원 평가 자료를 분석해야 해서 → 자료를 정리하고 해석하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>경영학과: 인사·조직 관리를 배워 채용·평가·보상 제도를 운영하는 데 바로 쓰여요.
+심리학과: 사람의 성격과 동기를 배워 인재를 뽑고 조직 분위기를 관리하는 데 도움이 돼요.
+교육학과: 교육 프로그램 설계 방법을 배워 직원 교육과 역량 개발을 이끌 수 있어요.
+법학과: 노동법과 근로 계약을 배워 급여·근무 조건을 법에 맞게 관리할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2496,6 +2891,14 @@
 영어 I: 해외 기업 재무 자료를 읽어야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>경영학과: 재무 관리와 기업 가치 평가를 배워 투자·경영 판단 자료를 만들 수 있어요.
+세무·회계학과: 재무제표를 읽고 분석하는 회계 지식을 깊이 배워 분석 업무의 기초가 돼요.
+경제학과: 경기와 산업 흐름을 분석하는 힘을 길러 기업의 미래 실적을 예측해요.
+금융보험학과: 주식·채권 등 금융 시장을 배워 투자 분석과 자산 평가에 활용할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2535,6 +2938,14 @@
 확률과 통계: 투자의 위험과 수익을 비교해야 해서 → 확률과 자료 해석 방법을 배워요.</t>
         </is>
       </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>금융보험학과: 보험·연금·투자 상품을 배워 고객의 저축과 은퇴 계획을 세우는 데 쓰여요.
+경제학과: 금리·물가 등 경제 흐름을 배워 고객 자산을 장기적으로 계획할 수 있어요.
+경영학과: 재무 관리와 고객 상담을 배워 개인의 소득과 지출을 체계적으로 분석해요.
+세무·회계학과: 세금과 회계를 배워 절세 방법과 상속·증여 계획을 상담하는 데 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2574,6 +2985,14 @@
 영어 I: 해외 기업과 시장 보고서를 읽어야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>경제학과: 경제 지표와 산업 구조를 분석하는 힘을 길러 주가 전망을 세울 수 있어요.
+경영학과: 재무제표 분석과 기업 가치 평가를 배워 기업 분석 보고서 작성에 쓰여요.
+금융보험학과: 주식·채권 시장과 투자 이론을 배워 투자 의견을 내는 데 바로 활용해요.
+통계학과: 데이터를 통계로 분석해 기업 실적과 주가 흐름을 예측하는 힘을 길러요.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2613,6 +3032,14 @@
 대수: 수익률을 지수·로그로 계산해야 해서 → 지수·로그 함수와 수열을 배워요.</t>
         </is>
       </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>수학과: 확률·미적분·선형대수를 깊이 배워 금융 모델을 만드는 기초를 다져요.
+통계학과: 통계 모델과 데이터 분석을 배워 시장 데이터에서 투자 신호를 찾아요.
+금융공학과: 수학과 프로그래밍을 금융에 적용하는 법을 배워 투자 전략 개발에 쓰여요.
+컴퓨터공학과: 프로그래밍과 알고리즘을 배워 투자 모델을 코드로 만들고 검증할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2652,6 +3079,13 @@
 확률과 통계: 판매 자료로 구매량을 정해야 해서 → 자료를 정리하고 경향을 읽는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>의류학과: 의류 소재와 패션 트렌드를 배워 팔릴 옷과 잡화를 고르는 안목을 길러요.
+경영학과: 마케팅과 유통을 배워 구매 예산과 판매 전략을 세우는 데 도움이 돼요.
+무역학과: 수입 절차와 해외 거래 계약을 배워 해외 브랜드 구매 업무에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2691,6 +3125,14 @@
 영어 I: 해외 시장 정보를 직접 읽어야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>경영학과: 재무 관리와 투자론을 배워 투자할 기업을 고르고 수익을 관리할 수 있어요.
+경제학과: 경제 흐름과 금리 변화를 분석해 투자 방향을 정하는 힘을 길러요.
+금융보험학과: 주식·채권 등 금융 상품과 시장을 배워 투자와 위험 관리에 바로 쓰여요.
+통계학과: 통계 분석을 배워 수익률과 위험을 수치로 따져 보는 데 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2730,6 +3172,14 @@
 영어 I: 최신 IT 기술 문서가 영어로 되어 있어서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>컴퓨터공학과: 프로그래밍과 보안, 시스템 개발을 배워 금융 서비스를 직접 만들 수 있어요.
+소프트웨어학과: 앱·웹 개발 기술을 배워 간편결제 같은 금융 서비스를 구현하는 데 쓰여요.
+금융보험학과: 금융 제도와 상품 구조를 배워 기술을 금융 서비스에 접목하는 데 도움이 돼요.
+빅데이터학과: 빅데이터 분석과 인공지능을 배워 신용 평가나 맞춤 금융 서비스에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2769,6 +3219,14 @@
 화법과 언어: 어려운 개념을 쉽게 가르쳐야 해서 → 알기 쉽게 설명하는 말하기를 배워요.</t>
         </is>
       </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>과학교육과: 과학 지식과 교수법을 함께 배우고 중등 과학 교원 자격을 얻을 수 있어요.
+물리학과: 물리 개념과 실험을 깊이 배워 교직 이수 시 물리 교사가 될 수 있어요.
+화학과: 화학 이론과 실험을 깊이 배워 교직 이수 시 화학 교사가 될 수 있어요.
+생명과학과: 생명 현상과 실험을 깊이 배워 교직 이수 시 생명과학 교사가 될 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2808,6 +3266,12 @@
 독서와 작문: 교육 계획서와 자기소개서를 다뤄야 해서 → 목적에 맞게 글 쓰고 고치는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>교육학과: 학습 이론과 교육 제도를 배워 진로·진학 상담과 학습 계획에 활용해요.
+심리학과: 발달·학습 심리와 상담 기법을 배워 학생 특성에 맞는 조언을 할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2847,6 +3311,14 @@
 영어 I: 해외 교육 콘텐츠를 참고해야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>교육학과: 학습 이론과 교육과정을 배워 학습 목표에 맞는 콘텐츠를 기획할 수 있어요.
+교육공학과: 수업 설계와 이러닝 제작 기술을 배워 온라인 강의 개발에 바로 쓰여요.
+문화콘텐츠학과: 콘텐츠 기획과 스토리텔링을 배워 재미있고 몰입되는 학습 자료를 만들어요.
+멀티미디어학과: 영상·그래픽·인터랙티브 제작 기술을 배워 교육 영상과 앱을 만들 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2883,6 +3355,14 @@
 독서와 작문: 교재의 설명 글을 써야 해서 → 쉽고 정확한 글쓰기를 배워요.
 대수: 수학 교구의 원리를 설계해야 해서 → 식과 함수, 수열의 원리를 배워요.
 문학: 동화·이야기로 교재를 꾸미기도 해서 → 이야기의 구성과 표현을 배워요.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>유아교육과: 유아 발달과 놀이 중심 교육을 배워 아이 눈높이의 교구를 기획해요.
+아동학과: 아동의 성장과 발달 특성을 배워 나이에 맞는 교재와 놀이 도구를 만들어요.
+초등교육과: 초등 교육과정과 교수법을 배워 수업에 쓰기 좋은 교재를 기획할 수 있어요.
+디자인과: 형태·색·사용성을 고려한 디자인을 배워 보기 좋고 쓰기 쉬운 교구를 만들어요.</t>
         </is>
       </c>
     </row>
@@ -2924,6 +3404,14 @@
 독서와 작문: 교육 프로그램 기획서를 써야 해서 → 논리적으로 설득하는 글쓰기를 배워요.</t>
         </is>
       </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>교육학과: 교육 프로그램 설계와 평가 방법을 배워 직원 교육 기획에 바로 쓰여요.
+경영학과: 인사·조직 관리를 배워 회사에 필요한 인재 역량을 파악할 수 있어요.
+심리학과: 성인의 학습 동기와 행동을 배워 효과적인 교육 방법을 찾는 데 도움이 돼요.
+교육공학과: 교수 설계와 이러닝 기술을 배워 온·오프라인 직원 교육을 만들 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2959,6 +3447,14 @@
 인간과 심리: 학생의 감정과 표현을 이해해야 해서 → 사람의 마음과 발달을 배워요.
 화법과 언어: 작품을 감상하고 설명해 줘야 해서 → 알기 쉽게 설명하는 말하기를 배워요.
 문학: 그림과 이야기를 연결한 수업을 해서 → 작품을 해석하고 감상하는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>미술교육과: 미술 실기와 교수법을 함께 배우고 중등 미술 교원 자격을 얻을 수 있어요.
+회화과: 그리기 실기를 깊이 익혀 교직 이수 시 미술 교사가 되는 데 도움이 돼요.
+조소과: 입체 조형 실기를 익혀 학생들의 만들기 수업을 지도하는 데 활용해요.
+디자인과: 시각 표현과 디자인 원리를 배워 디자인·공예 수업을 지도할 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -3000,6 +3496,14 @@
 독서와 작문: 교육 프로그램 자료를 만들어야 해서 → 쉽고 정확한 글쓰기를 배워요.</t>
         </is>
       </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>미술교육과: 미술 교육 방법을 배워 관람객 연령에 맞는 체험 프로그램을 기획해요.
+미술사학과: 작품의 역사와 의미를 배워 관람객에게 작품을 깊이 있게 설명할 수 있어요.
+회화과: 작품 제작 과정을 직접 익혀 실감 나는 창작 체험 수업을 진행할 수 있어요.
+교육학과: 교육 프로그램 설계와 평가를 배워 미술관 교육을 체계적으로 운영해요.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3035,6 +3539,14 @@
 화법과 언어: 학생들에게 알기 쉽게 설명해야 해서 → 상대에 맞춘 설명과 말하기를 배워요.
 스포츠 생활1: 예체능 프로그램을 맡을 수도 있어서 → 여러 운동을 익히고 체력을 길러요.
 독서와 작문: 수업 계획서와 활동지를 만들어야 해서 → 목적에 맞는 글쓰기를 배워요.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>교육학과: 교육 이론과 수업 방법을 배워 학생 수준에 맞는 수업을 운영할 수 있어요.
+초등교육과: 초등 교육과정과 아동 지도법을 배워 초등학생 수업을 이끌 수 있어요.
+아동학과: 아동 발달과 놀이 지도를 배워 어린 학생들의 특기적성 수업에 활용해요.
+체육학과: 운동 기능과 지도법을 배워 체육·스포츠 방과후 수업을 가르칠 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -3076,6 +3588,12 @@
 영어 I: 영어 원서와 자료도 다뤄야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>문헌정보학과: 도서관 운영과 정보 조직을 배우고 교직 이수로 사서교사 자격을 얻어요.
+교육학과: 교육 이론과 교수법을 배워 독서 교육과 정보 활용 수업을 운영할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3115,6 +3633,14 @@
 확률과 통계: 사회 통계 자료를 가르쳐야 해서 → 통계 자료를 바르게 해석하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>일반사회교육과: 정치·경제·사회 지식과 교수법을 함께 배워 사회 교원 자격을 얻어요.
+역사교육과: 역사와 사회 교육을 함께 배워 사회과 수업을 폭넓게 가르칠 수 있어요.
+사회학과: 사회 구조와 문화를 깊이 배워 교직 이수 시 사회 교사가 될 수 있어요.
+정치외교학과: 정치 제도와 국제 관계를 배워 교직 이수 시 정치·사회 수업에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3154,6 +3680,12 @@
 확률과 통계: 확률과 통계를 가르쳐야 해서 → 경우의 수, 확률, 통계를 배워요.</t>
         </is>
       </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>수학교육과: 수학 지식과 교수법을 함께 배우고 중등 수학 교원 자격을 얻을 수 있어요.
+수학과: 수학 이론을 깊이 배워 교직 이수 시 수학 교사가 되는 데 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3193,6 +3725,13 @@
 스포츠 생활1: 오랜 강의를 버틸 체력이 필요해서 → 꾸준한 운동으로 체력을 길러요.</t>
         </is>
       </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>신문방송학과: 발성·전달법과 커뮤니케이션 이론을 배워 말하기 강의에 활용해요.
+국어국문학과: 정확한 우리말과 화법을 배워 바르고 설득력 있는 말하기를 가르칠 수 있어요.
+연극영화학과: 발성·호흡·표정 연기를 익혀 자신감 있는 발표 기술을 가르칠 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3232,6 +3771,13 @@
 문학: 동화로 아이 정서를 도울 수 있어서 → 이야기를 해석하고 감상하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>아동학과: 아동의 언어·정서·사회성 발달을 배워 성장 상태를 평가하는 데 쓰여요.
+심리학과: 발달 심리와 심리 검사를 배워 아이의 마음과 행동을 이해하는 데 도움이 돼요.
+유아교육과: 영유아 발달과 놀이 교육을 배워 부모에게 양육 방법을 안내할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3271,6 +3817,14 @@
 화법과 언어: 학생 눈높이에 맞게 설명해야 해서 → 알기 쉽게 설명하는 말하기를 배워요.</t>
         </is>
       </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>영어영문학과: 영어 문학과 언어학을 배워 영어 실력과 문법 이해를 탄탄히 다져요.
+영어교육과: 영어 교수법과 교육과정을 배워 학생 수준에 맞는 영어 수업을 할 수 있어요.
+통번역학과: 외국어 듣기·말하기·번역을 집중 훈련해 실용 외국어 수업에 활용해요.
+서양어학과: 서양 언어와 문화를 배워 해당 외국어를 가르치는 강사가 될 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3310,6 +3864,12 @@
 문학: 작품으로 시대 분위기를 전하기도 해서 → 작품 속 시대 배경을 해석하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>역사교육과: 역사 지식과 교수법을 함께 배우고 중등 역사 교원 자격을 얻을 수 있어요.
+사학과: 한국사·세계사를 깊이 배워 교직 이수 시 역사 교사가 될 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3349,6 +3909,11 @@
 대수: 식단의 열량과 영양소를 계산해야 해서 → 식과 비율로 수량을 계산하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>식품영양학과: 영양·식품위생을 배워 영양사 면허를 따고 교직 이수로 영양교사가 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3388,6 +3953,12 @@
 영어 독해와 작문: 학생들의 영어 글쓰기를 지도해야 해서 → 영어 글을 읽고 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>영어교육과: 영어 실력과 교수법을 함께 배우고 중등 영어 교원 자격을 얻을 수 있어요.
+영어영문학과: 영어와 영미 문학을 깊이 배워 교직 이수 시 영어 교사가 될 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3427,6 +3998,14 @@
 영어 I: 외국어 교재와 자료를 폭넓게 봐야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>영어교육과: 외국어 교수법을 배워 제2외국어 수업 설계에도 응용할 수 있어요.
+중국어교육과: 중국어와 교수법을 함께 배우고 중국어 교원 자격을 얻을 수 있어요.
+일본어교육과: 일본어와 교수법을 함께 배우고 일본어 교원 자격을 얻을 수 있어요.
+동양어학과: 동양 언어와 문화를 배워 교직 이수 시 제2외국어 교사가 될 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3466,6 +4045,14 @@
 영어 독해와 작문: 영어 에세이 첨삭을 도와야 해서 → 영어 글을 읽고 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>교육학과: 교육 제도와 진로 상담을 배워 학생에게 맞는 학교와 전공을 안내해요.
+영어영문학과: 영어 실력과 영미 문화를 익혀 해외 학교 지원 서류 준비를 도울 수 있어요.
+국제관계학과: 국제 정세와 각국 제도를 배워 나라별 유학 환경을 안내하는 데 쓰여요.
+서양어학과: 유럽 언어와 문화를 배워 비영어권 유학 상담에 활용할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3501,6 +4088,14 @@
 문학: 노랫말과 시를 함께 다뤄야 해서 → 시의 운율과 표현을 배워요.
 화법과 언어: 음악을 쉽게 설명해야 해서 → 알기 쉽게 설명하는 말하기를 배워요.
 영어 I: 외국 노래와 음악 자료를 다뤄야 해서 → 기본 영어 표현과 독해를 배워요.</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>음악교육과: 음악 실기와 교수법을 함께 배우고 중등 음악 교원 자격을 얻을 수 있어요.
+성악과: 발성과 노래 실기를 깊이 익혀 교직 이수 시 가창 수업에 활용해요.
+피아노과: 피아노 연주와 화성을 익혀 반주와 음악 이론 수업에 활용할 수 있어요.
+관현악과: 관현악기 연주와 합주를 익혀 기악 수업과 합주 지도에 활용해요.</t>
         </is>
       </c>
     </row>
@@ -3539,6 +4134,13 @@
 화법과 언어: 학생의 마음을 듣고 상담해야 해서 → 공감하며 대화하는 방법을 배워요.
 문학: 작품으로 마음을 돌보는 상담도 해서 → 작품 속 인물의 감정을 해석하는 법을 배워요.
 확률과 통계: 심리 검사 결과를 해석해야 해서 → 검사 점수와 자료를 해석하는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>교육학과: 교육·상담 이론을 배우고 교직 이수 등으로 상담교사 자격을 준비해요.
+심리학과: 마음과 행동의 원리를 배워 학생의 고민과 정서를 깊이 이해할 수 있어요.
+상담심리학과: 상담 이론과 기법을 전문적으로 익혀 학생 상담에 바로 활용할 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -3580,6 +4182,13 @@
 영어 I: 프로그래밍 자료가 영어로 되어 있어서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>컴퓨터교육과: 컴퓨터 과학과 교수법을 함께 배우고 정보·컴퓨터 교원 자격을 얻어요.
+컴퓨터공학과: 프로그래밍과 인공지능을 깊이 배워 교직 이수 시 정보 교사가 될 수 있어요.
+소프트웨어학과: 소프트웨어 개발을 깊이 배워 교직 이수 시 코딩 수업에 활용할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -3616,6 +4225,13 @@
 스포츠 생활1: 여러 종목을 직접 시범 보여야 해서 → 다양한 운동 기능을 익혀요.
 스포츠 과학: 운동을 과학적으로 지도해야 해서 → 운동과 신체 원리를 배워요.
 스포츠 문화: 스포츠의 가치를 가르쳐야 해서 → 스포츠의 역사와 문화를 배워요.</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>체육교육과: 운동 실기와 교수법을 함께 배우고 중등 체육 교원 자격을 얻을 수 있어요.
+체육학과: 여러 스포츠 기능과 지도법을 익혀 교직 이수 시 체육 교사가 될 수 있어요.
+스포츠과학과: 운동 생리와 건강 관리를 배워 과학적인 체육 수업에 활용할 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -3657,6 +4273,11 @@
 스포츠 생활1: 체육 수업도 직접 맡아야 해서 → 여러 운동을 익히고 체력을 길러요.</t>
         </is>
       </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>초등교육과: 초등 교육과정 전 과목과 교수법을 배우고 초등 교원 자격을 얻는 학과예요.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3693,6 +4314,11 @@
 화법과 언어: 학생 특성에 맞춰 소통해야 해서 → 상대에 맞춘 말하기와 대화법을 배워요.
 스포츠 생활1: 학생의 신체 활동을 도와야 해서 → 여러 운동을 익히고 체력을 길러요.
 독서와 작문: 개별 교육 계획서를 써야 해서 → 정확하고 체계적인 글쓰기를 배워요.</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>특수교육과: 장애 유형별 교육 방법을 배우고 특수학교 교원 자격을 얻는 학과예요.</t>
         </is>
       </c>
     </row>
@@ -3734,6 +4360,13 @@
 확률과 통계: 수요 조사와 만족도를 분석해야 해서 → 자료를 정리하고 해석하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>평생교육학과: 성인 학습과 프로그램 기획을 배우고 평생교육사 자격 과목을 이수해요.
+교육학과: 교육 이론과 프로그램 설계를 배우며 평생교육사 자격 과목도 이수할 수 있어요.
+사회복지학과: 지역사회와 복지 대상자를 이해해 주민 맞춤 학습 프로그램을 기획해요.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -3772,6 +4405,14 @@
 독서와 작문: 읽기·쓰기 지도법을 알아야 해서 → 읽기와 글쓰기의 과정을 배워요.</t>
         </is>
       </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>특수교육과: 학습장애 등 특수 아동의 교육 방법을 배워 맞춤형 지도에 바로 쓰여요.
+아동학과: 아동 발달 단계를 배워 아이의 학습 어려움을 발달 관점에서 이해해요.
+교육학과: 학습 이론과 교수 방법을 배워 아이에게 맞는 학습 계획을 세울 수 있어요.
+심리학과: 인지·학습 심리와 심리 검사를 배워 학습 문제의 원인을 파악할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -3807,6 +4448,14 @@
 화법과 언어: 학생을 집중시키는 강의가 필요해서 → 알기 쉽게 설명하는 말하기를 배워요.
 미적분 I: 입시 수학을 가르칠 수 있어서 → 극한, 미분, 적분의 원리를 배워요.
 영어 I: 입시 영어를 가르칠 수 있어서 → 영어 어휘와 문장 구조를 배워요.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>수학교육과: 수학 개념과 교수법을 함께 배워 학생 수준에 맞게 수학을 가르칠 수 있어요.
+국어교육과: 국어 문법·문학과 교수법을 배워 국어 과목을 체계적으로 가르칠 수 있어요.
+영어교육과: 영어 실력과 교수법을 함께 길러 내신·입시 영어 수업에 활용할 수 있어요.
+과학교육과: 과학 개념과 실험 지도를 배워 과학 과목을 쉽게 설명할 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -3848,6 +4497,13 @@
 독서와 작문: 연구 결과를 보고서로 써야 해서 → 근거를 들어 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>생명과학과: 생물의 분류와 생태를 배워 곤충의 종류와 생활을 연구하는 기초가 돼요.
+응용생물학과: 곤충학과 해충 방제를 배워 농업 해충 관리와 곤충 자원 활용에 쓰여요.
+식물자원학과: 작물과 해충의 관계를 배워 농작물 피해를 줄이는 방제 연구에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -3887,6 +4543,14 @@
 확률과 통계: 과학 자료와 그래프를 설명해야 해서 → 자료를 바르게 해석하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>물리학과: 물리 원리를 깊이 이해해 어려운 과학 개념을 정확하게 풀어 설명해요.
+생명과학과: 생명 현상을 깊이 배워 건강·생명 이야기를 정확하고 쉽게 전할 수 있어요.
+과학교육과: 과학 지식을 쉽게 가르치는 교수법을 배워 대중 강연과 설명에 활용해요.
+신문방송학과: 취재·글쓰기·영상 제작을 배워 과학 이야기를 미디어로 전달할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3926,6 +4590,13 @@
 독서와 작문: 감정 결과를 보고서로 써야 해서 → 정확하고 객관적인 글쓰기를 배워요.</t>
         </is>
       </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>화학과: 화학 분석 기법을 배워 약물·혈흔 등 증거물 성분 분석에 활용해요.
+생명과학과: 유전학과 분자생물학을 배워 DNA 감식 등 생물학적 증거 분석에 쓰여요.
+경찰행정학과: 수사 절차와 형사법을 배워 증거 수집과 범죄 수사 업무를 이해할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3965,6 +4636,13 @@
 스포츠 생활1: 산지와 시장을 다니며 검사해야 해서 → 꾸준한 운동으로 체력을 길러요.</t>
         </is>
       </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>식물자원학과: 작물의 재배와 특성을 배워 농산물의 등급과 품질을 판단할 수 있어요.
+원예학과: 채소·과일·화훼를 배워 원예 농산물의 품질을 검사하는 데 도움이 돼요.
+식품공학과: 식품 성분과 안전성 분석을 배워 농산물의 위해 물질 검사에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -4004,6 +4682,13 @@
 영어 I: 해외 농업 논문을 읽어야 해서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>식물자원학과: 작물 육종과 재배 기술을 배워 생산성 높은 품종 연구에 바로 쓰여요.
+원예학과: 채소·과수·화훼 재배를 배워 원예 작물의 품질을 높이는 연구에 활용해요.
+생명공학과: 유전공학과 생명 기술을 배워 병에 강한 새 품종을 개발하는 데 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -4043,6 +4728,13 @@
 대수: 농가 수익과 비용을 계산해야 해서 → 식과 함수로 수량을 계산하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>식물자원학과: 작물 재배와 토양 관리를 배워 농민에게 재배 기술을 조언할 수 있어요.
+원예학과: 원예 작물 재배와 시설 농업을 배워 농가의 기술 문제를 해결해 줘요.
+농업경제학과: 농산물 시장과 농업 경영을 배워 판로와 농가 소득 전략을 조언할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4081,6 +4773,13 @@
 확률과 통계: 작물 생육 자료를 정리해야 해서 → 자료를 정리하고 해석하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>원예학과: 채소·화훼 재배와 실내 정원을 배워 도시 텃밭 교육에 바로 쓰여요.
+조경학과: 공간 설계와 식재 계획을 배워 옥상 정원 같은 도시 녹지를 꾸밀 수 있어요.
+식물자원학과: 작물 재배와 토양 관리를 배워 좁은 도시 공간에서 작물 기르기를 알려요.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4119,6 +4818,13 @@
 확률과 통계: 동물의 건강 기록을 관리해야 해서 → 자료를 정리하고 해석하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>동물자원학과: 동물의 사육·영양·번식을 배워 동물원 동물을 건강하게 돌볼 수 있어요.
+동물보건학과: 동물 간호와 질병 관리를 배우고 동물보건사 자격 취득에도 도움이 돼요.
+생명과학과: 동물의 생리와 생태를 배워 동물의 습성에 맞는 환경을 만들 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4155,6 +4861,13 @@
 스포츠 생활1: 숲길을 걸으며 프로그램을 이끌어야 해서 → 꾸준한 운동으로 체력을 길러요.
 화법과 언어: 참가자의 마음을 편하게 이끌어야 해서 → 공감하며 대화하는 방법을 배워요.
 스포츠 과학: 몸 건강을 돕는 활동을 짜야 해서 → 운동과 신체 원리를 배워요.</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>산림학과: 숲 생태와 산림 환경을 배우고 산림치유지도사 자격 요건에도 해당돼요.
+원예학과: 식물 재배와 원예 치료를 배워 자연을 활용한 치유 프로그램에 활용해요.
+조경학과: 자연 공간 설계를 배워 치유 숲길과 쉼터를 효과적으로 꾸밀 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -4196,6 +4909,13 @@
 영어 I: 실험 매뉴얼이 영어인 경우가 많아서 → 영어 자료를 읽는 기본 독해를 배워요.</t>
         </is>
       </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>생명과학과: 세포·유전·미생물 실험을 배워 생물 시료 분석 업무에 바로 쓰여요.
+생명공학과: 유전자 분석과 바이오 실험 기술을 배워 연구소 시험 업무에 활용해요.
+임상병리학과: 혈액·조직 검사를 배우고 임상병리사 면허로 병원 검사실에서 일할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -4235,6 +4955,14 @@
 영어 독해와 작문: 영어 논문을 읽고 써야 해서 → 영어 글을 읽고 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>생명과학과: 유전자와 단백질의 원리를 배워 생물 데이터의 의미를 해석할 수 있어요.
+생명공학과: 유전체 분석과 바이오 실험을 배워 생물 데이터를 다루는 기초를 다져요.
+컴퓨터공학과: 프로그래밍과 알고리즘을 배워 방대한 유전체 데이터를 분석할 수 있어요.
+통계학과: 통계 분석 방법을 배워 유전자와 질병의 관계를 수치로 밝힐 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -4274,6 +5002,14 @@
 독서와 작문: 복원 계획서를 써야 해서 → 근거를 들어 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>환경공학과: 수질·토양 오염과 정화 기술을 배워 훼손된 환경을 되살리는 데 쓰여요.
+생명과학과: 생물 종과 생태계 원리를 배워 복원할 생태계를 조사하고 평가해요.
+조경학과: 자연 경관 설계와 식재 계획을 배워 하천·습지 복원 설계에 활용해요.
+산림학과: 숲 생태와 나무 관리를 배워 훼손된 산림을 다시 가꾸는 데 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4313,6 +5049,13 @@
 영어 독해와 작문: 해외 생태 논문을 읽고 써야 해서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>생명과학과: 생물과 환경의 관계, 생태계 원리를 배워 생태 연구의 기초를 다져요.
+환경공학과: 환경 오염과 환경 영향 평가를 배워 생태계 보전 방안을 찾는 데 쓰여요.
+산림학과: 숲 생태계와 산림 자원을 배워 산림 생물과 환경을 연구할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4352,6 +5095,13 @@
 대수: 어류 개체 수 증감을 예측해야 해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>해양생명과학과: 해양 생물의 생리와 양식 기술을 배워 수산 자원 연구에 바로 쓰여요.
+생명과학과: 생물의 생리와 유전을 배워 수산 생물의 번식과 성장을 연구할 수 있어요.
+수산생명의학과: 수산 생물의 질병 치료를 배우고 수산질병관리사 면허를 준비할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4390,6 +5140,14 @@
 미적분 I: 온도·습도 변화를 제어해야 해서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>원예학과: 시설 원예와 작물 생리를 배워 작물에 맞는 재배 환경을 설정할 수 있어요.
+식물자원학과: 작물 재배와 영양 관리를 배워 스마트팜 생산 계획을 세우는 데 쓰여요.
+바이오시스템공학과: 농업 기계와 센서·자동화 기술을 배워 스마트팜 시스템을 다룰 수 있어요.
+컴퓨터공학과: 프로그래밍과 데이터 분석을 배워 재배 환경 자동 제어 시스템을 만들어요.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -4428,6 +5186,14 @@
 영어 독해와 작문: 해외 병해 연구를 읽고 발표해서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>식물자원학과: 작물 재배와 식물 보호를 배워 식물 병의 원인과 방제를 연구해요.
+응용생물학과: 식물병리와 미생물을 배워 병원균을 찾아내고 방제법을 연구할 수 있어요.
+원예학과: 원예 작물의 병해를 배워 채소·과수의 병을 예방하는 연구에 활용해요.
+생명과학과: 미생물과 식물의 면역 원리를 배워 병이 생기는 과정을 밝히는 데 쓰여요.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -4464,6 +5230,13 @@
 실용 통계: 품종 비교 결과를 판단해야 해서 → 자료 분석과 통계적 추론을 배워요.
 확률과 통계: 유전 형질이 나타날 확률을 따져서 → 자료 정리와 통계적 추론을 배워요.
 영어Ⅱ: 해외 품종 연구 자료를 읽어야 해서 → 다양한 주제의 영어 글 이해를 배워요.</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>식물자원학과: 유전과 육종 원리를 배워 좋은 특성을 가진 새 품종을 만드는 데 쓰여요.
+원예학과: 채소·과수·화훼 육종을 배워 맛과 모양이 좋은 원예 품종을 개발해요.
+생명공학과: 유전자 분석과 생명공학 기술을 배워 더 빠르고 정확한 육종에 활용해요.</t>
         </is>
       </c>
     </row>
@@ -4505,6 +5278,13 @@
 독서와 작문: 안전 기준 보고서를 작성해야 해서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>식품공학과: 식품 가공과 위생 관리를 배워 식품 공정의 안전을 관리할 수 있어요.
+식품영양학과: 식품위생과 영양을 배워 식품의 안전 기준과 위해 요소를 판단할 수 있어요.
+화학과: 화학 분석 기법을 배워 식품 속 유해 물질을 정밀하게 검사할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -4543,6 +5323,12 @@
 확률과 통계: 생육 기록으로 재배법을 개선해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>원예학과: 꽃·채소·과수 재배와 번식을 배워 식물을 건강하게 기르는 데 바로 쓰여요.
+조경학과: 정원 설계와 조경 식물 관리를 배워 정원과 녹지를 가꾸는 데 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -4578,6 +5364,13 @@
 사회와 문화: 노인·장애인 등 다양한 대상자를 만나서 → 사회 집단과 복지의 기초를 배워요.
 화법과 언어: 참여자와 공감하며 대화해야 해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.
 문학: 사람의 마음과 사연을 이해해야 해서 → 작품 속 인물과 삶을 깊이 이해하는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>원예학과: 식물 재배와 원예 활동을 배워 치유 프로그램을 직접 운영할 수 있어요.
+심리학과: 사람의 마음과 상담 기법을 배워 참여자의 정서 회복을 돕는 데 쓰여요.
+사회복지학과: 복지 대상자와 지원 방법을 배워 노인·장애인 원예 프로그램에 활용해요.</t>
         </is>
       </c>
     </row>
@@ -4618,6 +5411,13 @@
 확률과 통계: 산림 자원량을 조사·분석해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>산림학과: 조림·숲 가꾸기·산림 보호를 배워 산림 관리 현장에 바로 쓰여요.
+식물자원학과: 나무와 식물의 생장 원리를 배워 나무를 심고 기르는 데 도움이 돼요.
+조경학과: 수목 식재와 관리를 배워 숲과 녹지를 계획적으로 가꿀 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -4656,6 +5456,13 @@
 문학: 향으로 이야기와 감성을 표현해서 → 작품 속 인물과 삶을 깊이 이해하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>화학과: 향료 분자의 구조와 성질을 배워 향을 조합하고 분석하는 기초가 돼요.
+화장품과학과: 화장품 원료와 향료 배합을 배워 향수·화장품 향 개발에 바로 쓰여요.
+화학공학과: 원료의 합성과 공정을 배워 향료를 대량 생산하는 과정을 이해해요.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -4694,6 +5501,12 @@
 스포츠 생활1: 산과 들로 야외 답사를 다녀서 → 꾸준한 운동 습관과 기초 체력을 길러요.</t>
         </is>
       </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>지질학과: 암석·광물·지층을 직접 조사하고 분석하는 방법을 체계적으로 배워요.
+에너지자원공학과: 지하자원 탐사와 개발 기술을 배워 석유·광물 자원 연구에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -4732,6 +5545,13 @@
 대수: 가축 성장 추세를 예측해야 해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>동물자원학과: 가축 사육·사료·번식을 배워 축산 연구 현장에 바로 활용할 수 있어요.
+수의학과: 동물 질병과 치료를 배우고 수의사 면허를 따 가축 질병을 연구할 수 있어요.
+생명공학과: 유전자와 생명공학 기술을 배워 가축 품종 개량 연구에 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -4768,6 +5588,14 @@
 기후변화와 지속가능한 세계: 지속가능한 생산을 평가하는 일이라 → 지속가능 발전과 환경 정책을 배워요.
 독서와 작문: 심사 보고서를 정확히 작성해서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.
 확률과 통계: 시료 검사 결과를 판단해야 해서 → 자료 정리와 통계적 추론을 배워요.</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>식물자원학과: 작물 재배와 토양 관리를 배워 친환경 농법을 정확히 심사할 수 있어요.
+원예학과: 원예 작물 재배를 배워 채소·과일의 친환경 생산 과정을 점검할 수 있어요.
+환경공학과: 환경 오염과 분석을 배워 농약·오염 물질 기준을 판단하는 데 쓰여요.
+식품공학과: 식품 성분과 안전 검사를 배워 친환경 가공식품 심사에 활용할 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -4809,6 +5637,13 @@
 영어 독해와 작문: 국제 공동 연구로 논문을 써서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>해양학과: 해류·해양 생물·해저 지형 등 바다를 종합적으로 연구하는 법을 배워요.
+대기과학과: 대기와 바다의 상호작용을 배워 태풍·기후 변화 같은 해양 현상을 연구해요.
+지질학과: 해저 지층과 암석을 배워 바다 밑의 지질과 자원을 연구할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -4847,6 +5682,14 @@
 영어Ⅱ: 해외 원료·규제 자료를 읽어서 → 다양한 주제의 영어 글 이해를 배워요.</t>
         </is>
       </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>화장품과학과: 피부 과학과 화장품 원료·제형을 배워 화장품 개발에 바로 쓰여요.
+화학과: 물질의 성질과 반응을 배워 새로운 화장품 원료를 개발하는 기초가 돼요.
+화학공학과: 원료 합성과 생산 공정을 배워 화장품 제조와 품질 관리에 활용해요.
+생명공학과: 피부 세포와 생리 활성 물질을 배워 효과 좋은 기능성 원료를 연구해요.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -4883,6 +5726,13 @@
 실용 통계: 측정값의 오차와 신뢰도를 판단해서 → 자료 분석과 통계의 기초를 배워요.
 대수: 농도와 희석 비율을 계산해야 해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
 독서와 작문: 시험 성적서를 정확히 써야 해서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>화학과: 분석 화학과 기기 분석을 배워 시료 성분을 시험하는 데 바로 쓰여요.
+화학공학과: 공정과 품질 관리를 배워 원료·제품의 품질 시험에 활용할 수 있어요.
+환경공학과: 대기·수질·토양 분석을 배워 환경 시료를 시험하는 데 도움이 돼요.</t>
         </is>
       </c>
     </row>
@@ -4924,6 +5774,12 @@
 영어 독해와 작문: 연구 결과를 영어 논문으로 써서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>화학과: 물질의 구조와 반응을 깊이 배워 새로운 물질을 연구하는 기초를 다져요.
+화학공학과: 화학 반응을 공정에 응용하는 법을 배워 새 소재 개발과 생산에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -4962,6 +5818,13 @@
 영어 I: 해외 장비 매뉴얼을 읽어야 해서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>기계공학과: 3D CAD 설계와 기계 구조를 배워 출력할 부품을 정확히 설계할 수 있어요.
+디자인과: 입체 조형과 제품 디자인을 배워 아이디어를 3D 모델로 만들 수 있어요.
+신소재공학과: 플라스틱·금속 등 소재의 성질을 배워 출력에 알맞은 재료를 고를 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -4997,6 +5860,13 @@
 역학과 에너지: 기계 구조의 움직임을 이해해야 해서 → 역학과 에너지를 깊이 배워요.
 미적분 I: 곡선 형태와 면적을 계산해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
 영어 I: 영문 도면과 규격을 읽어야 해서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>기계공학과: 기계 설계와 제도를 배워 CAD로 기계 부품 도면을 그리는 데 바로 쓰여요.
+건축공학과: 건축 구조와 설비를 배워 CAD로 건축 도면을 작성할 수 있어요.
+토목공학과: 도로·교량 등 구조물을 배워 CAD로 토목 설계 도면을 그릴 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -5037,6 +5907,13 @@
 스포츠 생활1: 건설 현장을 다니며 점검해서 → 꾸준한 운동 습관과 기초 체력을 길러요.</t>
         </is>
       </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>건축공학과: 건축 구조·시공·안전을 배워 공사가 설계대로 되는지 점검할 수 있어요.
+토목공학과: 도로·교량 시공과 구조를 배워 토목 공사 현장을 감독하는 데 쓰여요.
+건축학과: 건축 설계와 법규를 배워 설계 의도대로 지어지는지 확인할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -5075,6 +5952,13 @@
 화법과 언어: 작업자와 소통하며 지휘해야 해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>건축공학과: 건축 시공·공정·안전 관리를 배워 공사 현장을 이끄는 데 바로 쓰여요.
+토목공학과: 토목 시공과 구조를 배워 도로·교량 같은 시설 공사를 관리할 수 있어요.
+건축학과: 건축 설계와 도면을 배워 설계를 현장 시공으로 옮기는 데 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -5113,6 +5997,13 @@
 독서와 작문: 사업 계획서와 보고서를 써서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>건축공학과: 건축 시공과 공사 관리를 배워 비용·일정·품질을 총괄하는 데 쓰여요.
+건축학과: 건축 설계와 기획을 배워 사업 초기부터 설계 과정을 관리할 수 있어요.
+토목공학과: 토목 구조와 시공을 배워 대형 기반 시설 사업을 관리할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -5149,6 +6040,13 @@
 물리학: 구조와 자재의 쓰임을 이해해야 해서 → 힘과 운동의 기초를 배워요.
 대수: 자재 물량과 비용을 계산해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.
 미적분 I: 곡면 구조의 면적·부피를 구해서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>건축공학과: 건축 시공과 재료를 배워 공사에 필요한 자재와 비용을 계산할 수 있어요.
+건축학과: 건축 도면을 읽고 이해하는 법을 배워 정확한 물량 산출에 도움이 돼요.
+토목공학과: 토목 시공과 재료를 배워 토목 공사의 물량과 공사비를 계산할 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -5190,6 +6088,13 @@
 확률과 통계: 측정 오차를 통계로 줄여야 해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>제어계측공학과: 센서 원리와 측정·제어 시스템을 함께 배워 계측 장비 설계에 바로 연결돼요.
+전자공학과: 전자 회로와 신호 처리를 배워 센서 신호를 정확히 읽는 장치를 만들 수 있어요.
+전기공학과: 전기 회로와 계측 이론을 배워 전압·전류를 정밀하게 재는 시스템을 다룰 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -5228,6 +6133,13 @@
 미적분 I: 차량 흐름의 변화를 분석해서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>교통공학과: 교통량 조사, 신호 운영, 대중교통 계획을 직접 배우는 학과예요.
+도시공학과: 도시 공간과 교통망을 함께 계획하는 방법을 배워 교통 문제 해결에 활용해요.
+토목공학과: 도로·교량 설계와 시공을 배워 교통 시설을 실제로 만드는 데 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -5266,6 +6178,13 @@
 대수: 구조 안전 계수를 계산해야 해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>건축공학과: 건물 구조 역학과 내진 설계를 배워 안전한 건축 구조를 계산할 수 있어요.
+토목공학과: 다리·터널 같은 구조물의 역학과 설계를 배워 구조 계산 능력을 키워요.
+건축학과: 건물 설계 전반을 배워 디자인과 구조를 함께 고려하는 시각을 길러요.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -5302,6 +6221,14 @@
 경제: 시장과 고객의 요구를 파악해야 해서 → 시장과 경제 원리를 배워요.
 화법과 언어: 고객에게 기술을 쉽게 설명해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.
 영어Ⅱ: 해외 고객과 소통해야 해서 → 다양한 주제의 영어 글 이해를 배워요.</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>산업공학과: 생산·경영·품질을 함께 배워 기술과 비즈니스를 잇는 영업에 잘 맞아요.
+기계공학과: 기계 원리와 설계를 배워 장비의 기술 내용을 고객에게 정확히 설명할 수 있어요.
+전자공학과: 전자 부품과 회로를 배워 전자 제품의 성능을 전문적으로 소개할 수 있어요.
+화학공학과: 화학 공정과 소재를 배워 화학 제품의 특성을 고객에게 설명할 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -5343,6 +6270,14 @@
 영어 독해와 작문: 최신 해외 논문을 읽고 써서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>신소재공학과: 원자 수준의 재료 구조와 물성을 배워 새로운 나노 소재 개발에 연결돼요.
+물리학과: 양자역학과 고체물리를 배워 나노 세계에서 일어나는 현상을 이해할 수 있어요.
+화학과: 분자 구조와 합성을 배워 나노 물질을 직접 만들고 분석할 수 있어요.
+전자공학과: 반도체 소자와 미세 공정을 배워 나노 크기의 전자 소자 개발에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -5381,6 +6316,13 @@
 확률과 통계: 건물 에너지 자료를 평가해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>건축학과: 건축 설계를 배우며 자연 채광·환기 같은 친환경 설계 방법을 익혀요.
+건축공학과: 단열·냉난방 설비와 에너지 효율을 배워 에너지 절약형 건물을 만들 수 있어요.
+환경공학과: 오염과 자원 순환을 배워 건축물이 환경에 주는 영향을 평가할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -5419,6 +6361,14 @@
 독서와 작문: 재생 계획서를 설득력 있게 써서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>도시공학과: 도시 계획과 개발 방법을 배워 낡은 지역을 되살리는 계획을 세울 수 있어요.
+건축학과: 건축 설계와 리모델링을 배워 오래된 건물을 새 공간으로 바꿀 수 있어요.
+조경학과: 공원·녹지 설계를 배워 주민이 머무는 쾌적한 동네 공간을 만들 수 있어요.
+행정학과: 공공 정책과 행정 절차를 배워 주민·정부와 함께 사업을 이끌 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -5457,6 +6407,14 @@
 영어 I: 해외 기체 매뉴얼을 읽어야 해서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>항공우주공학과: 비행 원리와 항공기 설계를 배워 드론 기체를 직접 설계할 수 있어요.
+로봇공학과: 로봇 제어와 자율 이동 기술을 배워 스스로 나는 드론 개발에 연결돼요.
+기계공학과: 기계 설계와 동역학을 배워 드론의 구조와 모터 부품을 다룰 수 있어요.
+전자공학과: 전자 회로와 통신을 배워 드론의 비행 제어 장치와 센서를 만들 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -5495,6 +6453,14 @@
 영어Ⅱ: 해외 기술 자료를 읽어야 해서 → 다양한 주제의 영어 글 이해를 배워요.</t>
         </is>
       </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>전자공학과: 반도체 소자와 회로를 배워 화면을 구동하는 장치를 설계할 수 있어요.
+신소재공학과: 발광 소재와 박막 재료를 배워 OLED 같은 디스플레이 소재 개발에 연결돼요.
+물리학과: 빛과 전자의 성질을 배워 화면이 빛을 내는 원리를 깊이 이해할 수 있어요.
+화학공학과: 소재 합성과 생산 공정을 배워 디스플레이 대량 생산 공정을 다룰 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -5531,6 +6497,14 @@
 정보: 장비를 프로그램으로 제어하므로 → 프로그래밍과 자료 처리를 배워요.
 미적분 I: 로봇 움직임을 수식으로 제어해서 → 미분·적분으로 변화율을 다루는 법을 배워요.
 영어 I: 해외 부품 사양서를 읽어서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>기계공학과: 기계 설계와 역학을 배워 자동화 장비의 몸체를 만들 수 있어요.
+로봇공학과: 기계·전자·소프트웨어를 함께 배워 로봇 개발에 바로 연결되는 학과예요.
+제어계측공학과: 센서와 제어 이론을 배워 기계가 정확히 움직이도록 만들 수 있어요.
+전자공학과: 회로와 마이크로컨트롤러를 배워 장비를 움직이는 전자 장치를 만들 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -5572,6 +6546,14 @@
 확률과 통계: 공정 수율과 불량률을 분석해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>전자공학과: 반도체 소자와 회로 설계를 배워 칩 설계에 바로 연결되는 학과예요.
+신소재공학과: 반도체 재료와 박막 공정을 배워 칩을 만드는 소재 개발에 활용해요.
+물리학과: 고체물리와 전자 성질을 배워 반도체가 작동하는 원리를 이해할 수 있어요.
+화학공학과: 식각·증착 같은 화학 공정을 배워 반도체 생산 공정 관리에 연결돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -5610,6 +6592,14 @@
 확률과 통계: 성능 시험 자료를 분석해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>화학공학과: 전기화학과 생산 공정을 배워 배터리 셀 제조 공정 개발에 연결돼요.
+신소재공학과: 양극·음극 소재와 재료 분석을 배워 배터리 소재 개발에 활용해요.
+화학과: 전기화학 반응과 물질 합성을 배워 배터리 속 화학 원리를 이해할 수 있어요.
+전기공학과: 전력 변환과 전기 회로를 배워 배터리 관리 시스템(BMS)을 다룰 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -5645,6 +6635,13 @@
 물리학 실험: 검사 장비로 직접 측정해서 → 측정 실험과 자료 분석을 경험해요.
 확률과 통계: 검사 신호로 결함을 판정해서 → 자료 정리와 통계적 추론을 배워요.
 영어 I: 국제 검사 규격을 읽어야 해서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>기계공학과: 기계 구조와 재료 강도를 배워 결함이 어디에 생기는지 판단할 수 있어요.
+재료공학과: 금속 조직과 재료 손상을 배워 검사 결과로 결함 원인을 분석할 수 있어요.
+물리학과: 초음파·방사선의 물리 원리를 배워 검사 장비를 정확히 이해할 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -5685,6 +6682,14 @@
 화법과 언어: 작업자에게 안전 교육을 해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>안전공학과: 사고 예방과 위험성 평가를 직접 배워 산업안전 자격 준비에 유리해요.
+산업공학과: 작업 공정과 인간공학을 배워 위험을 줄이는 작업 환경을 설계할 수 있어요.
+기계공학과: 기계 구조와 작동 원리를 배워 기계 설비의 위험 요소를 찾아낼 수 있어요.
+화학공학과: 화학 공정과 물질 특성을 배워 화재·폭발·누출 사고를 예방할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -5723,6 +6728,13 @@
 대수: 생산 계획과 원가를 계산해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>산업공학과: 생산 계획, 공정 관리, 품질 관리를 직접 배워 공장 효율화에 연결돼요.
+기계공학과: 기계와 제조 공정을 배워 생산 현장의 설비와 공정을 잘 이해할 수 있어요.
+경영학과: 원가 관리와 운영 관리를 배워 생산 비용을 줄이는 전략을 세울 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -5761,6 +6773,13 @@
 영어 I: 해외 설비 매뉴얼을 읽어서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>기계공학과: 열역학과 유체역학을 배워 냉난방·기계 설비를 설계할 수 있어요.
+전기공학과: 전력 설비와 전기 회로를 배워 건물·공장의 전기 설비를 다룰 수 있어요.
+건축공학과: 건축 설비와 시공을 배워 건물 안 냉난방·배관 설비를 계획할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -5799,6 +6818,14 @@
 대수: 원료 배합 비율을 계산해야 해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>섬유공학과: 섬유 소재와 원단 제조 공정을 직접 배우는 학과예요.
+신소재공학과: 고분자와 첨단 소재를 배워 새로운 기능성 섬유 개발에 활용해요.
+화학공학과: 고분자 합성과 염색 공정을 배워 섬유를 대량으로 만드는 공정에 연결돼요.
+의류학과: 옷감의 특성과 의복 구성을 배워 입기 좋은 원단을 개발하는 데 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -5837,6 +6864,14 @@
 미적분 I: 공정 변화를 실시간 제어해서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>산업공학과: 생산 시스템과 공정 최적화를 배워 공장 운영을 똑똑하게 바꿀 수 있어요.
+기계공학과: 기계 설비와 자동화 장비를 배워 공장 생산 라인을 설계할 수 있어요.
+제어계측공학과: 센서와 자동 제어를 배워 설비가 스스로 움직이는 공장을 만들 수 있어요.
+컴퓨터공학과: 프로그래밍과 데이터 처리를 배워 공장 데이터를 분석하는 시스템을 만들어요.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -5875,6 +6910,13 @@
 미적분 I: 살균 온도·시간 변화를 다뤄서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>식품공학과: 식품 가공·저장·포장 기술과 생산 공정을 직접 배우는 학과예요.
+식품영양학과: 식품 성분과 영양을 배워 건강하고 안전한 식품 개발에 활용할 수 있어요.
+생명공학과: 미생물과 발효 기술을 배워 새로운 식품 소재 개발에 연결돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -5913,6 +6955,12 @@
 미적분 I: 에너지 변화를 정밀히 계산해서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>원자력공학과: 원자로 설계, 방사선 안전, 핵연료를 직접 배우는 학과예요.
+물리학과: 핵물리와 방사선의 성질을 배워 원자력의 기본 원리를 깊이 이해해요.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -5951,6 +6999,14 @@
 확률과 통계: 임상 시험으로 안전성을 검증해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>의공학과: 의학과 공학을 함께 배워 의료기기 개발에 바로 연결되는 학과예요.
+전자공학과: 전자 회로와 신호 처리를 배워 심전도·영상 장비 같은 기기를 만들 수 있어요.
+기계공학과: 기계 설계와 생체역학을 배워 인공관절·수술 기구 개발에 활용해요.
+로봇공학과: 로봇 제어를 배워 수술 로봇이나 재활 로봇 개발에 연결돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -5989,6 +7045,13 @@
 스포츠 과학: 몸의 움직임과 피로를 이해해서 → 몸의 움직임과 체력 향상 원리를 배워요.</t>
         </is>
       </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>산업공학과: 인간공학과 작업 설계를 배워 편하고 안전한 작업 환경을 만들 수 있어요.
+심리학과: 사람의 인지·지각·행동 특성을 배워 쓰기 편한 제품 설계에 활용해요.
+디자인과: 제품 디자인과 사용자 경험을 배워 사람에게 맞는 형태를 만들 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -6027,6 +7090,14 @@
 대수: 반복 신호를 수열로 분석해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>제어계측공학과: 제어 이론과 센서·계측을 직접 배워 자동 제어 시스템 설계에 연결돼요.
+전기공학과: 전력 전자와 모터 제어를 배워 기계를 원하는 대로 움직이게 할 수 있어요.
+전자공학과: 회로와 마이크로프로세서를 배워 제어 장치의 전자 부분을 만들 수 있어요.
+기계공학과: 동역학과 기계 시스템을 배워 제어할 대상의 움직임을 이해할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -6065,6 +7136,13 @@
 확률과 통계: 주행 시험 자료를 분석해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>자동차공학과: 엔진·차체·전기차 구동 장치를 직접 배우는 자동차 전문 학과예요.
+기계공학과: 열역학·동역학·기계 설계를 배워 자동차 부품 설계의 기초를 다져요.
+전기공학과: 모터와 전력 변환을 배워 전기차 구동 시스템 개발에 연결돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -6100,6 +7178,12 @@
 물리학 실험: 측정 장비로 차량을 점검해서 → 측정과 실험 방법을 경험해요.
 영어 I: 영문 정비 매뉴얼을 읽어야 해서 → 영어 글의 핵심을 파악하는 법을 배워요.
 스포츠 생활1: 무거운 부품을 다루며 일해서 → 꾸준한 운동 습관과 기초 체력을 길러요.</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>자동차공학과: 자동차 구조와 고장 진단을 배워 정비 자격증 준비에 바로 연결돼요.
+기계공학과: 엔진과 동력 전달 장치의 원리를 배워 고장 원인을 찾는 데 도움이 돼요.</t>
         </is>
       </c>
     </row>
@@ -6141,6 +7225,14 @@
 미적분 I: 차량 움직임을 실시간 계산해서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>자동차공학과: 차량 구조와 주행 제어를 배워 자율주행차 시스템을 이해할 수 있어요.
+인공지능학과: 머신러닝과 컴퓨터 비전을 배워 차가 주변을 인식하는 기술을 만들어요.
+컴퓨터공학과: 프로그래밍과 알고리즘을 배워 자율주행 소프트웨어를 개발할 수 있어요.
+전자공학과: 센서와 신호 처리를 배워 라이다·카메라 같은 인식 장치를 다룰 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -6179,6 +7271,12 @@
 대수: 교류 전기의 주기를 다뤄서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>전기공학과: 전력 설비와 전기 회로를 배워 전기기사 자격 준비에 바로 연결돼요.
+전자공학과: 전자 회로와 제어를 배워 전기 설비의 제어·보호 장치를 다룰 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -6217,6 +7315,13 @@
 미적분 I: 지형 곡면과 면적을 계산해서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>조경학과: 공원·정원·녹지 설계를 직접 배워 조경 설계에 바로 연결되는 학과예요.
+원예학과: 식물의 특성과 재배를 배워 공간에 어울리는 식물을 고를 수 있어요.
+도시공학과: 도시 계획을 배워 도시 전체의 녹지와 공원 배치를 계획할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -6255,6 +7360,13 @@
 영어Ⅱ: 해외 선주와 소통해야 해서 → 다양한 주제의 영어 글 이해를 배워요.</t>
         </is>
       </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>조선해양공학과: 선박 설계와 건조, 해양 구조물을 직접 배우는 학과예요.
+해양공학과: 해양 환경과 해양 구조물을 배워 바다에서 견디는 설비를 설계해요.
+기계공학과: 유체역학과 기계 설계를 배워 선박 엔진과 추진 장치를 다룰 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -6293,6 +7405,13 @@
 스포츠 생활1: 장비를 들고 현장을 다녀서 → 꾸준한 운동 습관과 기초 체력을 길러요.</t>
         </is>
       </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>토목공학과: 측량학과 토목 설계를 배워 공사 현장의 측량 업무에 바로 쓸 수 있어요.
+지적학과: 토지 측량과 지적 제도를 배워 땅의 경계와 면적을 다룰 수 있어요.
+지리학과: 지도와 공간 정보 분석을 배워 측량 자료를 지도로 만들 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -6331,6 +7450,12 @@
 스포츠 생활1: 야외 현장에서 오래 일해서 → 꾸준한 운동 습관과 기초 체력을 길러요.</t>
         </is>
       </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>토목공학과: 구조·토질·수리학을 배워 도로·다리·댐 설계에 바로 연결되는 학과예요.
+도시공학과: 도시 기반 시설 계획을 배워 도로·상하수도 같은 시설 배치를 계획해요.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -6367,6 +7492,14 @@
 물리학: 기계·전자 제품의 성능을 시험해서 → 힘·전기·파동의 원리를 배워요.
 확률과 통계: 불량률을 통계로 관리해야 해서 → 자료 정리와 통계적 추론을 배워요.
 독서와 작문: 품질 보고서를 정확히 써야 해서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>산업공학과: 품질 관리와 통계적 공정 관리를 직접 배워 불량 줄이기에 연결돼요.
+화학공학과: 화학 분석과 공정을 배워 화학 제품의 품질을 검사할 수 있어요.
+기계공학과: 기계 부품과 정밀 측정을 배워 기계 제품의 품질을 검사할 수 있어요.
+통계학과: 데이터 분석과 통계 기법을 배워 불량 원인을 숫자로 찾아낼 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -6408,6 +7541,14 @@
 확률과 통계: 설비 운전 자료를 분석해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>화학공학과: 화학 공정 설계를 배워 정유·화학 공장 설계에 바로 연결돼요.
+기계공학과: 열·유체와 기계 설비를 배워 플랜트의 펌프·배관·보일러를 다룰 수 있어요.
+토목공학과: 구조물과 기초 공사를 배워 대형 설비가 들어설 시설을 건설할 수 있어요.
+전기공학과: 전력 계통과 전기 설비를 배워 발전소와 공장의 전기 시스템을 다뤄요.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -6446,6 +7587,13 @@
 미적분 I: 기체 힘과 운동을 이해해야 해서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>항공정비학과: 항공기 구조와 정비 실무를 배워 항공정비사 자격 준비에 바로 연결돼요.
+항공우주공학과: 항공기 설계와 비행 원리를 배워 기체와 엔진을 깊이 이해할 수 있어요.
+기계공학과: 기계 구조와 동력 장치를 배워 항공기 엔진·부품 정비에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -6484,6 +7632,14 @@
 화법과 언어: 작업자에게 안전 수칙을 알려서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>화학공학과: 화학 공정과 설비를 배워 공장 속 화학물질 사고 예방에 활용해요.
+화학과: 화학물질의 성질과 반응을 배워 위험 물질을 안전하게 다룰 수 있어요.
+안전공학과: 위험성 평가와 사고 예방을 배워 안전 관리 체계를 세울 수 있어요.
+환경공학과: 오염 물질 처리와 환경 법규를 배워 화학물질 유출 피해를 막을 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -6522,6 +7678,13 @@
 독서와 작문: 환경 진단 보고서를 써야 해서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>환경공학과: 대기·수질·폐기물 처리 기술을 배워 환경 문제 해결책을 제시할 수 있어요.
+화학공학과: 공정 설계를 배워 공장에서 오염을 덜 내는 공정 개선안을 낼 수 있어요.
+생명과학과: 생태계와 생물을 배워 오염이 생물에 주는 영향을 분석할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -6560,6 +7723,13 @@
 독서와 작문: 평가서를 논리적으로 써야 해서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>환경공학과: 대기·수질·소음 측정과 분석을 배워 환경 영향을 예측할 수 있어요.
+생명과학과: 생태계 조사와 생물 다양성을 배워 개발이 자연에 주는 영향을 평가해요.
+대기과학과: 기상과 대기 확산을 배워 개발로 인한 대기 오염 변화를 예측할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -6598,6 +7768,13 @@
 대수: 좌표 변환과 축척을 계산해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>지리학과: 지도와 공간 분석을 직접 배워 GIS 데이터 분석에 바로 연결돼요.
+도시공학과: 도시 공간 계획을 배워 공간 데이터를 도시 정책에 활용할 수 있어요.
+토목공학과: 측량과 공간 정보 기술을 배워 지리 정보를 정확히 수집할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -6636,6 +7813,14 @@
 확률과 통계: 사용자 데이터로 개선점을 찾아서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>경영정보학과: 경영과 정보 시스템을 함께 배워 IT 서비스 기획에 잘 맞는 학과예요.
+소프트웨어학과: 소프트웨어 개발 과정을 배워 개발팀과 원활하게 소통할 수 있어요.
+산업공학과: 데이터 분석과 시스템 설계를 배워 서비스를 효율적으로 구상할 수 있어요.
+경영학과: 마케팅과 사업 전략을 배워 사용자가 원하는 서비스를 기획할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -6674,6 +7859,14 @@
 확률과 통계: 센서 데이터를 분석해야 해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>전자공학과: 센서와 전자 회로를 배워 인터넷에 연결되는 기기를 만들 수 있어요.
+컴퓨터공학과: 프로그래밍과 네트워크를 배워 기기끼리 정보를 주고받게 만들 수 있어요.
+정보통신학과: 무선 통신과 네트워크 기술을 배워 사물 간 연결 방식을 설계해요.
+소프트웨어학과: 앱·서버 개발을 배워 IoT 기기를 조작하는 서비스를 만들 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -6712,6 +7905,14 @@
 화법과 언어: 사용자 인터뷰를 진행해야 해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>디자인과: 시각 디자인과 인터랙션 디자인을 배워 보기 좋고 쓰기 쉬운 화면을 만들어요.
+멀티미디어학과: 영상·그래픽·웹 제작을 배워 움직이는 화면 디자인에 활용할 수 있어요.
+심리학과: 사람의 인지와 행동을 배워 사용자가 편하게 느끼는 흐름을 설계해요.
+산업공학과: 인간공학과 사용성 평가를 배워 화면의 불편한 점을 찾고 개선해요.</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -6749,6 +7950,14 @@
 문학: 몰입감 있는 이야기를 만들어서 → 작품 속 인물과 삶을 깊이 이해하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>멀티미디어학과: 3D 그래픽과 인터랙티브 콘텐츠를 배워 가상 공간을 만들 수 있어요.
+컴퓨터공학과: 컴퓨터 그래픽스와 프로그래밍을 배워 VR 프로그램을 개발할 수 있어요.
+소프트웨어학과: 게임 엔진과 소프트웨어 개발을 배워 실감형 콘텐츠를 만들 수 있어요.
+영상학과: 영상 촬영과 연출을 배워 360도 영상 같은 실감 콘텐츠를 제작해요.</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -6786,6 +7995,13 @@
 영어Ⅱ: 영문 장비 문서를 읽어야 해서 → 다양한 주제의 영어 글 이해를 배워요.</t>
         </is>
       </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>정보통신학과: 통신망 구조와 네트워크 프로토콜을 직접 배워 망 설계에 연결돼요.
+컴퓨터공학과: 운영체제와 네트워크 프로그래밍을 배워 서버·망 관리에 활용해요.
+전자공학과: 통신 회로와 신호 처리를 배워 네트워크 장비를 깊이 이해할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -6823,6 +8039,13 @@
 영어 I: 영문 기술 문서를 읽어야 해서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>컴퓨터공학과: 데이터베이스와 자료 구조를 배워 데이터 저장 구조를 설계할 수 있어요.
+소프트웨어학과: SQL과 서버 프로그래밍을 배워 데이터베이스를 직접 운영할 수 있어요.
+빅데이터학과: 대용량 데이터 처리와 분석을 배워 많은 데이터를 효율적으로 관리해요.</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -6860,6 +8083,14 @@
 영어Ⅱ: 해외 개발 커뮤니티와 소통해서 → 다양한 주제의 영어 글 이해를 배워요.</t>
         </is>
       </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>컴퓨터공학과: 분산 시스템과 프로그래밍을 배워 블록체인 구조를 개발할 수 있어요.
+소프트웨어학과: 소프트웨어 개발을 배워 스마트 계약과 블록체인 서비스를 만들 수 있어요.
+정보보안학과: 암호 기술과 보안을 배워 위조할 수 없는 거래 시스템을 설계해요.
+수학과: 정수론과 암호 수학을 배워 블록체인 암호 원리를 깊이 이해할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -6895,6 +8126,12 @@
 매체 의사소통: 정보를 효과적으로 전달해야 해서 → 매체 언어와 소통 방식을 배워요.
 영어 I: 해외 디자인 자료를 참고해서 → 영어 글의 핵심을 파악하는 법을 배워요.
 화법과 언어: 고객 요구를 듣고 시안을 설명해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>디자인과: 색채·타이포그래피·레이아웃을 배워 보기 좋은 웹 화면을 디자인해요.
+멀티미디어학과: 웹 제작과 그래픽 도구를 배워 디자인을 실제 웹페이지로 구현해요.</t>
         </is>
       </c>
     </row>
@@ -6936,6 +8173,14 @@
 미적분 I: AI 학습이 미분으로 이뤄져서 → 미분·적분으로 변화율을 다루는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>인공지능학과: 머신러닝과 딥러닝을 직접 배워 인공지능 모델 개발에 바로 연결돼요.
+컴퓨터공학과: 알고리즘과 프로그래밍을 배워 AI 시스템을 구현할 수 있어요.
+소프트웨어학과: 소프트웨어 개발을 배워 AI 모델을 실제 서비스로 만들 수 있어요.
+통계학과: 확률과 통계 모델을 배워 AI가 데이터를 학습하는 원리를 이해해요.</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -6974,6 +8219,14 @@
 영어 I: 영문 칩 데이터시트를 읽어서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>전자공학과: 마이크로프로세서와 회로를 배워 기기 속 제어 장치를 다룰 수 있어요.
+컴퓨터공학과: C언어와 운영체제를 배워 기기를 움직이는 소프트웨어를 만들 수 있어요.
+제어계측공학과: 센서와 제어 이론을 배워 기계를 정확히 움직이는 프로그램을 짜요.
+전기공학과: 전기 회로와 모터를 배워 전기로 움직이는 기기 제어에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -7012,6 +8265,14 @@
 확률과 통계: 공격 패턴 데이터를 분석해서 → 자료 정리와 통계적 추론을 배워요.</t>
         </is>
       </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>정보보안학과: 해킹 방어와 암호 기술을 직접 배워 보안 전문가로 바로 연결돼요.
+컴퓨터공학과: 운영체제와 네트워크를 배워 시스템의 약점을 찾아낼 수 있어요.
+소프트웨어학과: 프로그래밍과 소프트웨어 구조를 배워 안전한 코드를 만들 수 있어요.
+수학과: 암호 이론과 수학적 사고를 배워 안전한 암호 기술을 이해할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -7050,6 +8311,13 @@
 영어Ⅱ: 영문 부품 사양서를 읽어서 → 다양한 주제의 영어 글 이해를 배워요.</t>
         </is>
       </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>전자공학과: 반도체와 디지털 회로를 배워 CPU·메모리 설계에 연결돼요.
+컴퓨터공학과: 컴퓨터 구조를 배워 하드웨어와 소프트웨어의 연결을 이해할 수 있어요.
+전기공학과: 전기 회로와 전원 장치를 배워 컴퓨터 회로 기판 설계에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -7085,6 +8353,13 @@
 직무 영어: 기술 문서가 대부분 영어라서 → 업무용 영어 읽기를 배워요.
 영어Ⅱ: 영문 기술 문서를 매일 읽어서 → 다양한 주제의 영어 글 이해를 배워요.
 확률과 통계: 서버 사용량을 분석·예측해서 → 자료 정리와 통계적 추론을 배워요.</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>컴퓨터공학과: 운영체제와 분산 시스템을 배워 클라우드 서버를 설계할 수 있어요.
+소프트웨어학과: 서버 개발과 자동화를 배워 클라우드 서비스를 안정적으로 운영해요.
+정보통신학과: 네트워크와 통신 기술을 배워 클라우드 데이터 연결을 관리할 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -7125,6 +8400,13 @@
 대수: 신호 세기를 로그로 다뤄서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>정보통신학과: 유무선 통신과 네트워크를 직접 배워 통신망 설계에 바로 연결돼요.
+전자공학과: 통신 회로와 전파·신호 처리를 배워 통신 장비를 개발할 수 있어요.
+컴퓨터공학과: 네트워크 프로토콜과 프로그래밍을 배워 통신 시스템을 관리해요.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -7160,6 +8442,12 @@
 생명과학 실험: 검사 보조를 맡아서 → 실험 기구 사용과 관찰을 익혀요.
 화법과 언어: 보호자에게 돌봄법을 설명해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.
 스포츠 생활1: 동물을 안고 다루는 일이 많아서 → 꾸준한 운동 습관과 기초 체력을 길러요.</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>동물보건학과: 동물 간호와 진료 보조를 배워 동물보건사 국가시험을 볼 수 있는 학과예요.
+동물자원학과: 동물의 생리와 사육·관리를 배워 동물을 돌보는 기초를 쌓을 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -7200,6 +8488,11 @@
 화법과 언어: 환자에게 검사 과정을 안내해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>방사선학과: 방사선사 면허 시험을 볼 수 있는 학과로, 영상 촬영과 방사선 치료를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -7238,6 +8531,13 @@
 독서와 작문: 행정 문서와 보고서를 써서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>보건행정학과: 병원 경영과 의료 제도를 직접 배워 병원 행정에 바로 연결돼요.
+경영학과: 인사·재무·마케팅을 배워 병원을 효율적으로 운영하는 데 활용해요.
+행정학과: 공공 정책과 조직 관리를 배워 병원 조직과 의료 정책을 이해할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -7276,6 +8576,13 @@
 스포츠 과학: 운동과 건강의 원리를 알려서 → 몸의 움직임과 체력 향상 원리를 배워요.</t>
         </is>
       </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>보건학과: 질병 예방과 건강 증진을 배워 보건교육사 자격 준비에 연결돼요.
+보건행정학과: 보건 정책과 프로그램 운영을 배워 건강 교육 사업을 기획할 수 있어요.
+간호학과: 의학 지식과 환자 교육을 배워 건강 생활 지도에 활용할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -7314,6 +8621,14 @@
 영어 독해와 작문: 연구 결과를 논문으로 써서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>보건학과: 역학과 보건 통계를 배워 국민 건강 문제를 조사·분석할 수 있어요.
+생명과학과: 생물과 질병의 원리를 배워 감염병 등 실험 연구에 활용할 수 있어요.
+임상병리학과: 혈액·미생물 검사 기술을 배워 보건 실험실 연구에 바로 쓸 수 있어요.
+식품영양학과: 식품과 영양을 배워 식품 안전과 국민 영양 연구에 활용할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -7350,6 +8665,12 @@
 직무 영어: 진단명·의학 용어가 영어라서 → 업무용 영어를 배워요.
 확률과 통계: 의료 데이터를 통계로 정리해서 → 자료 정리와 통계적 추론을 배워요.
 영어 I: 영문 의학 용어를 다뤄야 해서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>보건의료정보학과: 진료 기록과 질병 분류를 배워 보건의료정보관리사 시험을 볼 수 있어요.
+보건행정학과: 의료 제도와 병원 행정을 배워 의료 정보 관리 업무에 활용할 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -7391,6 +8712,14 @@
 영어 독해와 작문: 해외 논문을 읽고 써야 해서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>약학과: 약의 작용과 합성을 배워 신약 후보 물질 연구에 바로 연결돼요.
+생명과학과: 세포와 질병의 원리를 배워 약이 몸에 작용하는 과정을 연구해요.
+화학과: 유기 합성과 분석을 배워 신약 후보 물질을 직접 만들 수 있어요.
+생명공학과: 바이오 기술을 배워 항체·백신 같은 바이오 의약품 개발에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -7428,6 +8757,14 @@
 화법과 언어: 아이 눈높이에 맞춰 말해야 해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>아동학과: 아동 발달과 놀이를 배워 아픈 아이의 마음에 맞춰 도울 수 있어요.
+심리학과: 상담과 정서 이해를 배워 치료를 두려워하는 아이를 안심시킬 수 있어요.
+사회복지학과: 가족 지원과 복지 제도를 배워 환자 가족까지 함께 도울 수 있어요.
+유아교육과: 유아 교육과 놀이 지도를 배워 병원에서 쓰는 놀이 프로그램을 만들어요.</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -7465,6 +8802,11 @@
 화법과 언어: 고객에게 시력 상태를 설명해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>안경광학과: 안경사 면허 시험을 볼 수 있는 학과로, 시력 검사와 렌즈 조제를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -7500,6 +8842,13 @@
 교육의 이해: 단계적으로 훈련시켜야 해서 → 학습과 교육의 원리를 배워요.
 화법과 언어: 말소리와 언어 구조를 분석해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.
 문학: 이야기로 표현력을 키워 줘서 → 작품 속 인물과 삶을 깊이 이해하는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>언어치료학과: 언어재활사 자격 시험을 볼 수 있는 학과로, 말·언어 평가와 치료를 배워요.
+재활치료학과: 여러 재활 분야를 배우며 언어 재활 과정을 함께 이수할 수 있어요.
+특수교육과: 장애 학생의 의사소통 지도를 배워 언어 지원 이해에 도움이 돼요.</t>
         </is>
       </c>
     </row>
@@ -7540,6 +8889,11 @@
 화법과 언어: 식습관 상담을 해야 해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>식품영양학과: 영양사 면허 시험을 볼 수 있는 학과로, 식단 작성과 급식 관리를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -7578,6 +8932,13 @@
 화법과 언어: 시민에게 위생 수칙을 알려서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>보건학과: 감염병 예방과 공중위생을 배워 위생사 시험 준비에 연결돼요.
+환경보건학과: 먹는 물·공기·생활 환경 관리를 배워 환경 위생 점검에 활용해요.
+식품영양학과: 식품 위생과 안전을 배워 식품의 위생 상태를 점검할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -7614,6 +8975,11 @@
 스포츠 생활1: 환자를 옮기는 강한 체력이 필요해서 → 꾸준한 운동 습관과 기초 체력을 길러요.
 스포츠 과학: 몸의 손상과 회복을 이해해서 → 몸의 움직임과 체력 향상 원리를 배워요.
 화법과 언어: 위급할 때 정확히 소통해야 해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>응급구조학과: 1급 응급구조사 시험을 볼 수 있는 학과로, 응급 처치와 환자 이송을 배워요.</t>
         </is>
       </c>
     </row>
@@ -7655,6 +9021,13 @@
 영어 독해와 작문: 연구를 영어 논문으로 발표해서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>의예과: 의대 과정으로 인체와 질병을 배워 임상과 연구를 잇는 의과학자로 성장해요.
+생명과학과: 세포·유전자·질병의 원리를 배워 질병 원인을 밝히는 연구에 연결돼요.
+생명공학과: 유전자·세포 공학 기술을 배워 새로운 치료법 개발 연구에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -7693,6 +9066,13 @@
 영어 독해와 작문: 해외 의학물리 논문을 읽어서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>물리학과: 방사선과 원자핵 물리를 배워 대학원에서 의학물리로 이어갈 수 있어요.
+방사선학과: 방사선 영상과 치료 장비를 배워 의료 현장의 방사선 관리에 활용해요.
+의공학과: 의료 장비의 원리와 공학을 배워 영상·치료 장비 관리에 연결돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -7729,6 +9109,13 @@
 인간과 심리: 불안한 환자를 응대해서 → 사람의 마음과 감정을 배워요.
 화법과 언어: 환자에게 진료 과정을 안내해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.
 영어Ⅱ: 외국인 환자와 소통해야 해서 → 다양한 주제의 영어 글 이해를 배워요.</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>보건행정학과: 병원 행정과 의료 서비스를 배워 환자 일정 관리와 안내에 활용해요.
+간호학과: 의학 지식과 환자 간호를 배워 환자 상태를 이해하며 안내할 수 있어요.
+통번역학과: 외국어 통역을 배워 외국인 환자 상담과 진료 안내를 맡을 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -7770,6 +9157,11 @@
 영어 독해와 작문: 최신 의학 논문을 읽어야 해서 → 영어 글을 읽고 직접 쓰는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>의예과: 의학과로 이어지는 과정으로, 졸업 후 의사 국가시험을 볼 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -7806,6 +9198,13 @@
 심화 영어 독해와 작문: 해외 허가 문서를 다뤄서 → 전문적인 영어 읽기·쓰기를 배워요.
 독서와 작문: 허가 서류를 정확히 작성해서 → 글을 분석하고 논리적으로 쓰는 법을 배워요.
 확률과 통계: 임상 자료의 타당성을 검토해서 → 자료 정리와 통계적 추론을 배워요.</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>약학과: 약의 효능·안전성과 약사 법규를 배워 허가 자료 작성에 바로 연결돼요.
+생명과학과: 생명 현상과 독성 원리를 배워 의약품 안전성 자료를 이해할 수 있어요.
+화학과: 성분 분석과 품질 시험을 배워 의약품 품질 자료를 준비할 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -7847,6 +9246,11 @@
 대수: 시약 농도와 희석을 계산해서 → 지수·로그·수열로 변화를 계산하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>임상병리학과: 임상병리사 면허 시험을 볼 수 있는 학과로, 혈액·조직 검사를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -7885,6 +9289,11 @@
 화법과 언어: 내담자와 공감하며 대화해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>심리학과: 심리 평가와 상담 이론을 배워 임상심리사 자격 준비에 바로 연결돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -7923,6 +9332,14 @@
 화법과 언어: 참여자에게 연구를 설명해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>간호학과: 임상 지식과 환자 관리를 배워 임상시험 참여자를 안전하게 돌봐요.
+약학과: 약의 작용과 임상시험 과정을 배워 시험 진행 관리에 활용해요.
+임상병리학과: 검체 검사와 자료 관리를 배워 임상시험 데이터를 정확히 다룰 수 있어요.
+생명과학과: 질병과 생명 현상을 배워 임상시험 내용을 깊이 이해할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -7958,6 +9375,12 @@
 물리학: 몸의 움직임을 분석해야 해서 → 힘과 운동의 원리를 배워요.
 스포츠 과학: 몸의 움직임과 재활 원리를 알아서 → 몸의 움직임과 체력 향상 원리를 배워요.
 화법과 언어: 환자를 격려하며 치료해서 → 상황에 맞게 말하고 정확히 표현하는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>작업치료학과: 작업치료사 면허 시험을 볼 수 있는 학과로, 일상생활 재활을 배워요.
+재활치료학과: 재활 이론과 치료 방법을 배우며 작업치료 과정을 이수할 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -7998,6 +9421,14 @@
 영어 I: 해외 약품 자료를 읽어야 해서 → 영어 글의 핵심을 파악하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>약학과: 약의 성분과 효능을 배워 의사·약사에게 의약품을 정확히 설명해요.
+생명과학과: 질병과 인체의 원리를 배워 의약품 정보를 쉽게 이해할 수 있어요.
+화학과: 약의 화학 성분을 배워 제품의 특징을 전문적으로 소개할 수 있어요.
+경영학과: 마케팅과 영업 전략을 배워 의약품 판매 계획을 세울 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -8036,6 +9467,13 @@
 화법과 언어: 환자에게 결과를 쉽게 설명해야 해서 → 상황에 맞는 말하기와 언어 원리를 배워요.</t>
         </is>
       </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>청각학과: 청력 검사와 보청기 적합을 직접 배워 청능 재활에 바로 연결돼요.
+언어치료학과: 말·언어 발달을 배워 청각 장애인의 말하기 재활을 함께 도울 수 있어요.
+재활치료학과: 재활 이론과 치료 방법을 배워 청각 재활 프로그램을 운영할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -8074,6 +9512,11 @@
 영어 I: 최신 재료·장비 설명서를 읽어야 해서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>치기공학과: 치과기공사 면허 시험을 볼 수 있는 학과로, 보철물 제작 기술을 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -8110,6 +9553,11 @@
 직무 의사소통: 환자에게 관리법을 설명해야 해서 → 업무 상황에 맞는 말하기를 배워요.
 화법과 언어: 환자에게 구강 관리법을 안내해야 해서 → 정확하고 친절한 말하기를 배워요.
 확률과 통계: 구강 검진 자료를 기록·관리해야 해서 → 자료 정리와 통계 해석을 배워요.</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>치위생학과: 치과위생사 면허 시험을 볼 수 있는 학과로, 예방 처치와 구강 교육을 배워요.</t>
         </is>
       </c>
     </row>
@@ -8151,6 +9599,11 @@
 영어 독해와 작문: 최신 치의학 논문을 읽어야 해서 → 영어 글을 읽고 요약하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>치의예과: 치의학과로 이어지는 과정으로, 졸업 후 치과의사 국가시험을 볼 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -8189,6 +9642,11 @@
 확률과 통계: 치료 효과를 객관적으로 검증해야 해서 → 자료 분석과 통계적 추론을 배워요.</t>
         </is>
       </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>한의예과: 한의학과로 이어지는 과정으로, 졸업 후 한의사 국가시험을 볼 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -8227,6 +9685,13 @@
 영어 I: 3D 툴과 해외 튜토리얼이 영어라서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>디자인과: 조형과 제품 디자인을 배워 입체 형태를 아름답게 만드는 감각을 길러요.
+멀티미디어학과: 3D 그래픽 프로그램을 배워 캐릭터와 공간을 모델링할 수 있어요.
+만화애니메이션학과: 캐릭터 디자인과 3D 애니메이션을 배워 게임·영상 모델 제작에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -8265,6 +9730,13 @@
 영어Ⅱ: 해외 리그·구단과 소통할 일이 많아서 → 다양한 영어 글과 표현을 익혀요.</t>
         </is>
       </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>e스포츠학과: 게임 산업과 e스포츠 운영을 직접 배워 프로팀 관리에 바로 연결돼요.
+스포츠경영학과: 스포츠 마케팅과 선수 관리를 배워 팀 운영과 계약 업무에 활용해요.
+경영학과: 경영·마케팅·회계를 배워 팀 예산 관리와 홍보 전략을 세울 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -8303,6 +9775,14 @@
 화법과 언어: 아티스트·관계자와 협의가 많아서 → 상황에 맞는 말하기와 협상을 배워요.</t>
         </is>
       </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>문화콘텐츠학과: 문화 산업과 콘텐츠 기획을 배워 공연 아이디어를 만들 수 있어요.
+예술경영학과: 예술 경영과 공연 마케팅을 배워 공연 기획·운영에 바로 연결돼요.
+연극영화학과: 연출과 무대 제작을 배워 공연 현장을 깊이 이해할 수 있어요.
+경영학과: 예산 관리와 마케팅을 배워 공연 비용과 홍보 계획을 세울 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -8338,6 +9818,12 @@
 동아시아 역사 기행: 전통 공예의 뿌리를 알아야 해서 → 동아시아의 역사와 문화를 배워요.
 문학: 작품에 담을 이야기와 감성이 중요해서 → 문학 작품의 표현과 정서를 배워요.
 화법과 언어: 전시·판매 때 작품을 소개해야 해서 → 효과적으로 말하고 설명하는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>공예과(조형학과): 도자·금속·목공 같은 재료와 제작 기법을 직접 배워 작품을 만들어요.
+디자인과: 형태와 색채 디자인을 배워 쓰임과 아름다움을 갖춘 작품을 기획해요.</t>
         </is>
       </c>
     </row>
@@ -8378,6 +9864,14 @@
 화법과 언어: 광고주에게 아이디어를 발표해야 해서 → 설득력 있는 말하기를 배워요.</t>
         </is>
       </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>영상학과: 촬영·편집·영상 연출을 배워 광고 영상 제작에 바로 쓸 수 있어요.
+연극영화학과: 연출과 배우 지도를 배워 짧은 광고 속 이야기를 생생하게 그릴 수 있어요.
+광고홍보학과: 광고 기획과 소비자 심리를 배워 효과적인 광고 아이디어를 만들어요.
+미디어학과: 영상 콘텐츠와 미디어 환경을 배워 다양한 매체에 맞는 광고를 만들어요.</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -8415,6 +9909,12 @@
 문학: 판소리·민요 가사를 이해해야 해서 → 고전 시가와 문학 표현을 배워요.</t>
         </is>
       </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>국악(한국음악)과: 판소리·가야금 등 전통 음악 실기와 이론을 깊이 배우는 학과예요.
+음악교육과: 음악 교수법을 배워 학생에게 국악을 쉽고 재미있게 가르칠 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -8450,6 +9950,11 @@
 동아시아 역사 기행: 국악의 역사적 배경을 알아야 해서 → 동아시아의 역사와 문화를 배워요.
 문학: 판소리 사설과 가사를 해석해야 해서 → 고전 문학의 정서와 표현을 배워요.
 영어 I: 해외 공연에서 국악을 알릴 기회가 많아서 → 기초 영어 표현을 익혀요.</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>국악(한국음악)과: 국악기 연주와 판소리 등 전통 음악을 전공 실기로 깊이 익혀 무대에 설 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -8490,6 +9995,13 @@
 영어 I: 툴 사용법과 해외 레퍼런스가 영어라서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>영상학과: 영상 촬영·편집과 효과 작업을 배워 움직이는 그래픽을 영상에 녹여낼 수 있어요.
+디자인과: 색·글자·구도 등 시각 디자인 원리를 배워 보기 좋은 그래픽을 만들 수 있어요.
+멀티미디어학과: 애니메이션·영상 프로그램을 다루는 법을 배워 화면 속 그래픽에 움직임을 줄 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -8528,6 +10040,13 @@
 대수: 도면의 치수와 비율을 계산해야 해서 → 수와 식을 다루는 계산력을 키워요.</t>
         </is>
       </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>무대미술학과: 무대 세트·소품 설계와 제작을 전공으로 배워 공연 공간을 직접 꾸밀 수 있어요.
+연극영화학과: 연극·영화 제작 과정을 배워 작품 내용에 맞는 무대를 기획하는 눈을 길러요.
+디자인과: 공간 구성과 조형 감각을 배워 무대 세트를 아름답게 설계하는 데 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -8566,6 +10085,13 @@
 화법과 언어: 연출가와 콘셉트를 맞춰야 해서 → 생각을 정확히 전달하는 말하기를 배워요.</t>
         </is>
       </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>의류학과: 옷감·패턴·봉제를 배워 공연 의상을 직접 디자인하고 제작할 수 있어요.
+무대미술학과: 무대 의상과 분장 등 공연 미술을 배워 인물에 맞는 의상을 구상해요.
+연극영화학과: 작품 분석과 인물 해석을 배워 시대와 배역에 맞는 의상을 이해할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -8604,6 +10130,12 @@
 화법과 언어: 동작을 말로 정확히 설명해야 해서 → 알기 쉽게 말하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>무용학과: 발레·현대무용·한국무용 실기와 지도법을 배워 춤을 체계적으로 가르쳐요.
+체육학과: 운동 원리와 신체 지도법을 배워 학생 수준에 맞게 안전하게 수업할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -8640,6 +10172,11 @@
 스포츠 과학: 몸을 정밀하게 쓰고 부상을 막아야 해서 → 운동 원리와 체력 관리법을 배워요.
 스포츠 생활1: 기초 체력과 유연성이 필수라서 → 꾸준한 신체 활동과 체력 관리를 익혀요.
 문학: 작품의 이야기를 몸으로 표현해서 → 작품 속 정서와 주제 해석을 배워요.</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>무용학과: 다양한 춤 기술과 표현력을 전공 실기로 익혀 무대 공연을 준비해요.</t>
         </is>
       </c>
     </row>
@@ -8681,6 +10218,14 @@
 화법과 언어: 정확한 발음과 대사 전달이 중요해서 → 말소리와 말하기 원리를 배워요.</t>
         </is>
       </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>뮤지컬학과: 노래·연기·춤을 함께 훈련해 뮤지컬 무대에 필요한 실력을 고루 길러요.
+연극영화학과: 배역 분석과 연기 훈련을 배워 무대에서 인물을 생생하게 표현할 수 있어요.
+성악과: 발성과 노래 실력을 전문적으로 다듬어 뮤지컬 넘버를 소화하는 힘을 길러요.
+실용음악과: 대중음악 보컬과 무대 표현을 배워 다양한 장르의 뮤지컬 노래에 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -8719,6 +10264,13 @@
 확률과 통계: 치료 효과를 기록·평가해야 해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>미술치료학과: 미술 활동을 이용한 심리 평가와 치료 기법을 직접 배우는 학과예요.
+심리학과: 마음의 작동 원리와 상담 이론을 배워 내담자를 깊이 이해하는 바탕이 돼요.
+회화과: 다양한 그림 재료와 표현 방법을 익혀 미술 활동을 이끄는 힘을 길러요.</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -8757,6 +10309,14 @@
 독서와 작문: 복원 과정을 보고서로 남겨야 해서 → 정확하고 논리적인 글쓰기를 배워요.</t>
         </is>
       </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>문화재보존학과: 문화재의 재료 분석과 보존·복원 기술을 전문적으로 배우는 학과예요.
+회화과: 물감·화법을 깊이 익혀 손상된 그림을 원래 느낌대로 되살리는 데 도움이 돼요.
+화학과: 물질의 성질과 화학 반응을 배워 작품 재료 분석과 보존 처리에 활용해요.
+공예과(조형학과): 도자·금속·목공 등 재료 다루는 법을 익혀 공예품 복원에 바로 쓸 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -8794,6 +10354,12 @@
 확률과 통계: 진열 변화에 따른 매출을 분석해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>디자인과: 공간·색채·디스플레이 디자인을 배워 매장을 매력적으로 연출할 수 있어요.
+의류학과: 패션 상품과 유행, 머천다이징을 배워 옷이 돋보이는 진열을 기획해요.</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -8829,6 +10395,13 @@
 문학과 영상: 사진 한 장에 이야기를 담아야 해서 → 이미지와 서사 표현을 배워요.
 문학: 한 장의 사진에 이야기를 담아야 해서 → 작품의 주제와 정서 표현을 배워요.
 영어 I: 해외 공모전·작가 활동 기회가 있어서 → 기초 영어 독해와 표현을 익혀요.</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>사진학과: 촬영 기술과 조명, 사진 보정을 전공으로 배워 작품 사진을 만들 수 있어요.
+영상학과: 카메라 촬영과 화면 구성을 배워 사진에 필요한 구도 감각을 길러요.
+미디어학과: 미디어와 이미지 표현을 배워 광고·보도 사진의 목적을 이해할 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -8869,6 +10442,13 @@
 대수: 감마 곡선 등 색값을 수식으로 다뤄서 → 지수·로그 함수를 배워요.</t>
         </is>
       </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>영상학과: 영상 촬영과 편집, 색 보정 프로그램을 배워 장면의 색감을 다룰 수 있어요.
+연극영화학과: 영화 제작 과정과 촬영·조명을 배워 장면에 맞는 분위기를 이해해요.
+멀티미디어학과: 영상 처리 소프트웨어를 익혀 색과 밝기를 정교하게 조정할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -8906,6 +10486,12 @@
 문학: 대본 속 인물의 감정을 살려야 해서 → 작품의 정서와 인물 해석을 배워요.</t>
         </is>
       </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>연극영화학과: 발성·화술과 연기를 훈련해 목소리로 인물을 표현하는 힘을 길러요.
+방송연예학과: 방송 진행과 연기, 발음 훈련을 배워 내레이션과 더빙에 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -8941,6 +10527,13 @@
 인간과 심리: 고객의 개성과 원하는 이미지를 파악해서 → 인간의 감정과 심리를 배워요.
 화법과 언어: 고객의 취향을 듣고 제안해야 해서 → 경청하고 설득하는 말하기를 배워요.
 영어 I: 해외 패션 트렌드를 빠르게 읽어야 해서 → 기초 영어 독해 능력을 키워요.</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>의류학과: 패션 소재와 유행, 코디네이션을 배워 사람에게 맞는 옷을 고를 수 있어요.
+디자인과: 색채와 시각 디자인 감각을 길러 전체 이미지를 조화롭게 연출해요.
+뷰티디자인학과: 헤어·메이크업과 이미지 연출을 배워 전체 스타일을 완성하는 데 도움이 돼요.</t>
         </is>
       </c>
     </row>
@@ -8982,6 +10575,13 @@
 영어Ⅱ: 외국인 선수와 소통해야 해서 → 다양한 영어 표현을 익혀요.</t>
         </is>
       </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>스포츠경영학과: 스포츠 마케팅·재무·구단 운영을 직접 배워 구단 살림에 바로 쓸 수 있어요.
+체육학과: 스포츠 종목과 선수 훈련을 이해해 선수 관리와 경기 운영에 도움이 돼요.
+경영학과: 조직 관리·마케팅·회계를 배워 구단을 기업처럼 운영하는 능력을 길러요.</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -9021,6 +10621,14 @@
 영어 I: 분석 도구와 해외 자료가 영어라서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>스포츠과학과: 운동 동작과 경기력을 과학적으로 측정·분석하는 방법을 배워요.
+통계학과: 데이터를 모으고 통계로 해석하는 법을 배워 경기 기록 분석에 바로 써요.
+빅데이터학과: 대용량 데이터 처리와 프로그래밍을 배워 선수 움직임 데이터를 분석해요.
+체육학과: 종목별 경기 규칙과 전술을 이해해 데이터에 담긴 의미를 잘 읽을 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -9056,6 +10664,13 @@
 직무 의사소통: 이용객·직원과 소통이 많아서 → 업무 상황에 맞는 말하기를 배워요.
 스포츠 생활1: 이용자 프로그램을 직접 운영해서 → 다양한 스포츠 활동을 익혀요.
 확률과 통계: 이용률·운영비 자료를 관리해서 → 자료 정리와 통계 해석을 배워요.</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>스포츠경영학과: 스포츠 시설 경영과 프로그램 운영을 배워 체육 시설 관리에 바로 써요.
+체육학과: 다양한 종목과 안전 지도를 배워 시설 이용자를 안전하게 이끌 수 있어요.
+스포츠과학과: 운동 과학과 체력 관리를 배워 이용자에게 맞는 프로그램을 짤 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -9094,6 +10709,13 @@
 스포츠 생활1: 경기 내내 선수와 함께 뛰어야 해서 → 기초 체력과 경기 규칙을 익혀요.
 스포츠 문화: 공정성과 스포츠맨십을 지켜야 해서 → 스포츠의 가치와 윤리를 배워요.
 화법과 언어: 판정을 분명하게 설명해야 해서 → 정확하고 단호한 말하기를 배워요.</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>체육학과: 여러 종목의 규칙과 경기 운영을 배워 공정한 판정의 바탕을 다져요.
+체육교육과: 체육 이론과 종목 지도를 배워 경기 규칙을 깊이 이해할 수 있어요.
+스포츠과학과: 선수 움직임과 체력을 과학적으로 배워 경기 흐름을 정확히 읽을 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -9135,6 +10757,14 @@
 스포츠 문화: 스포츠 산업의 흐름을 알아야 해서 → 스포츠의 사회·문화적 의미를 배워요.</t>
         </is>
       </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>스포츠경영학과: 스포츠 마케팅과 계약·선수 관리를 배워 에이전트 업무에 바로 써요.
+법학과: 계약법과 권리 보호를 배워 선수에게 유리한 계약 협상에 도움이 돼요.
+체육학과: 종목과 선수 생활을 이해해 선수의 활동을 잘 관리할 수 있어요.
+경영학과: 협상·마케팅·재무를 배워 후원 계약과 선수 브랜드 관리에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -9173,6 +10803,13 @@
 확률과 통계: 기록을 근거로 경기를 분석해서 → 통계 자료 해석법을 배워요.</t>
         </is>
       </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>체육학과: 종목별 규칙과 전술을 깊이 배워 경기 상황을 정확히 설명할 수 있어요.
+신문방송학과: 방송 제작과 말하기·전달 기술을 배워 시청자에게 쉽게 풀어 줄 수 있어요.
+체육교육과: 스포츠를 가르치는 법을 배워 어려운 전술도 이해하기 쉽게 설명해요.</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -9209,6 +10846,13 @@
 스포츠 과학: 선수의 몸과 마음을 함께 봐야 해서 → 운동 수행의 과학 원리를 배워요.
 화법과 언어: 선수와 신뢰 있는 대화를 해야 해서 → 경청하고 공감하는 말하기를 배워요.
 확률과 통계: 심리 검사 결과를 해석해야 해서 → 자료 분석과 통계 해석을 배워요.</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>심리학과: 불안·동기 등 마음의 원리와 상담 기법을 배워 선수 상담에 활용해요.
+스포츠과학과: 스포츠 심리와 경기력 향상 이론을 배워 선수 마음 관리에 바로 써요.
+체육학과: 운동 종목과 훈련 과정을 이해해 선수가 겪는 압박을 잘 공감할 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -9250,6 +10894,14 @@
 확률과 통계: 제품 테스트 결과를 비교해야 해서 → 실험 자료의 통계 분석을 배워요.</t>
         </is>
       </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>스포츠과학과: 운동 동작과 신체 원리를 배워 몸에 맞는 용품을 설계할 수 있어요.
+기계공학과: 힘과 구조, 기계 설계를 배워 라켓·운동화 같은 제품 구조를 만들어요.
+신소재공학과: 가볍고 튼튼한 새 소재를 연구하는 법을 배워 용품 성능을 높일 수 있어요.
+섬유공학과: 섬유의 성질과 기능성 원단을 배워 운동복·신발 소재 개발에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -9285,6 +10937,12 @@
 인간과 심리: 수강생의 동기를 키워야 해서 → 인간의 감정과 동기를 배워요.
 화법과 언어: 학생에게 발성과 연주법을 설명해서 → 알기 쉽게 말하는 법을 배워요.
 영어 I: 팝 가사와 해외 교재를 다뤄서 → 기초 영어 독해와 발음을 익혀요.</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>실용음악과: 보컬·악기·작곡 등 대중음악 실기를 전공으로 익혀 바로 가르칠 수 있어요.
+음악교육과: 음악 교수법과 교육 이론을 배워 학생 수준에 맞게 체계적으로 가르쳐요.</t>
         </is>
       </c>
     </row>
@@ -9325,6 +10983,11 @@
 스포츠 생활1: 직접 시범을 보일 체력이 필요해서 → 기초 체력과 신체 활동을 익혀요.</t>
         </is>
       </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>무용학과: 춤 기술과 안무 구성법을 배워 음악에 맞는 동작과 대형을 만들 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -9360,6 +11023,13 @@
 정보: 애니메이션 프로그램을 다루므로 → 컴퓨팅 사고와 프로그래밍 기초를 배워요.
 문학: 캐릭터와 이야기에 생명을 불어넣어서 → 서사와 인물 표현을 배워요.
 미적분 I: 움직임의 속도 변화를 자연스럽게 그려서 → 함수와 변화율의 개념을 배워요.</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>만화애니메이션학과: 캐릭터 그리기와 움직임 표현, 애니메이션 제작을 직접 배우는 학과예요.
+영상학과: 영상 편집과 연출을 배워 애니메이션을 영상 작품으로 완성할 수 있어요.
+디자인과: 드로잉과 시각 디자인을 배워 캐릭터와 배경을 보기 좋게 그릴 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -9400,6 +11070,14 @@
 영어Ⅱ: 해외 활동 일정을 조율해야 해서 → 다양한 영어 표현을 익혀요.</t>
         </is>
       </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>광고홍보학과: 홍보·마케팅 전략을 배워 연예인의 이미지와 활동을 알리는 데 활용해요.
+문화콘텐츠학과: 엔터테인먼트 산업과 콘텐츠 기획을 배워 연예인 활동을 계획할 수 있어요.
+경영학과: 계약·일정·재무 관리를 배워 연예인 활동을 체계적으로 관리할 수 있어요.
+신문방송학과: 방송과 언론 환경을 배워 방송 섭외와 언론 홍보에 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -9438,6 +11116,14 @@
 확률과 통계: 조회수·시청 지표를 분석해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>영상학과: 기획·촬영·편집 등 영상 제작 전 과정을 실습으로 배워요.
+미디어학과: 미디어 환경과 콘텐츠 기획을 배워 시청자가 좋아할 영상을 만들 수 있어요.
+신문방송학과: 방송 제작과 취재·구성을 배워 방송용 콘텐츠를 만드는 데 도움이 돼요.
+연극영화학과: 연출과 촬영, 이야기 구성을 배워 완성도 높은 영상을 만들 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -9474,6 +11160,13 @@
 미술 감상과 비평: 화면의 구도·색감을 판단해서 → 작품을 분석하고 평가하는 법을 배워요.
 문학: 장면을 이어 이야기의 흐름을 만들어서 → 서사 구조와 전개 방식을 배워요.
 영어 I: 편집 프로그램과 해외 자료가 영어라서 → 기초 영어 독해 능력을 키워요.</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>영상학과: 편집 프로그램과 영상 효과를 직접 다뤄 보며 편집 실력을 길러요.
+연극영화학과: 영화 연출과 편집 이론을 배워 이야기 흐름에 맞게 장면을 이을 수 있어요.
+멀티미디어학과: 영상·음향 소프트웨어를 익혀 자막·음악·효과를 더하는 데 바로 써요.</t>
         </is>
       </c>
     </row>
@@ -9515,6 +11208,12 @@
 화법과 언어: 배우·스태프를 이끌어야 해서 → 생각을 정확히 전달하는 말하기를 배워요.</t>
         </is>
       </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>연극영화학과: 연출·시나리오·촬영을 배우고 단편 영화를 직접 만들며 감독 역량을 길러요.
+영상학과: 촬영과 편집 등 영상 제작 기술을 배워 영화를 완성하는 힘을 길러요.</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -9553,6 +11252,11 @@
 스포츠 생활1: 액션과 장시간 촬영을 버텨야 해서 → 기초 체력과 신체 활동을 익혀요.</t>
         </is>
       </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>연극영화학과: 인물 분석과 연기 훈련을 전공으로 배워 스크린 연기를 준비할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -9589,6 +11293,14 @@
 사회와 문화: 내담자의 생활 환경을 이해해서 → 사회 구조와 문화 현상을 배워요.
 화법과 언어: 내담자의 마음을 듣고 공감해야 해서 → 경청과 공감의 말하기를 배워요.
 확률과 통계: 치료 효과를 기록·평가해야 해서 → 자료 정리와 통계 해석을 배워요.</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>미술치료학과: 미술 활동을 이용한 심리 평가와 치료 기법을 직접 배워요.
+음악치료학과: 음악을 활용한 치료 이론과 실습을 배워 예술치료에 바로 쓸 수 있어요.
+심리학과: 마음의 원리와 상담 이론을 배워 내담자를 이해하고 돕는 바탕을 다져요.
+연극영화학과: 연기와 역할극을 배워 연극을 활용한 치료 활동을 이끌 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -9630,6 +11342,14 @@
 영어 독해와 작문: 해외 논문을 읽고 써야 해서 → 영어 글 읽기와 쓰기를 배워요.</t>
         </is>
       </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>스포츠과학과: 운동할 때 몸의 변화를 측정·분석하는 운동생리학을 직접 배워요.
+체육학과: 체육 이론과 트레이닝을 배워 운동이 몸에 주는 효과를 이해할 수 있어요.
+스포츠의학과: 부상 예방과 재활, 인체 구조를 배워 건강과 운동의 관계를 연구해요.
+생명과학과: 세포와 인체 기능을 배워 운동 중 몸에서 일어나는 변화를 깊이 이해해요.</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -9668,6 +11388,13 @@
 영어 I: 해외 대회와 전지훈련에 나가서 → 기초 영어 의사소통을 익혀요.</t>
         </is>
       </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>체육학과: 종목 훈련과 체력 관리, 경기 이론을 배워 선수 생활에 도움이 돼요.
+스포츠과학과: 운동 동작과 체력을 과학적으로 분석해 기량을 키우는 방법을 배워요.
+체육교육과: 운동 지도법을 함께 배워 선수 생활 이후 지도자의 길도 준비할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -9706,6 +11433,13 @@
 화법과 언어: 고객에게 운동법을 설명해야 해서 → 알기 쉽게 설명하는 말하기를 배워요.</t>
         </is>
       </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>스포츠과학과: 체력 측정과 운동 처방 방법을 배워 맞춤 운동 프로그램을 짤 수 있어요.
+스포츠의학과: 인체 구조와 재활 운동을 배워 몸 상태에 맞는 안전한 운동을 지도해요.
+체육학과: 운동 지도법과 트레이닝 이론을 배워 사람들의 운동을 이끄는 데 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -9741,6 +11475,14 @@
 미술 감상과 비평: 그림 실력과 안목이 바탕이라 → 작품을 분석하고 평가하는 법을 배워요.
 문학: 독자를 끌어당기는 이야기를 만들어서 → 서사 구조와 인물 표현을 배워요.
 화법과 언어: 대사 한 줄로 캐릭터를 살려야 해서 → 상황에 맞는 언어 표현을 배워요.</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>만화애니메이션학과: 스토리 구성과 만화 연출, 디지털 작화를 직접 배우는 학과예요.
+회화과: 드로잉과 표현 기법을 깊이 익혀 개성 있는 그림체를 만들 수 있어요.
+문예창작학과: 이야기를 짓고 글을 쓰는 법을 배워 탄탄한 웹툰 줄거리를 만들 수 있어요.
+디자인과: 색채·구성 등 시각 디자인을 배워 보기 좋은 웹툰 화면을 만들어요.</t>
         </is>
       </c>
     </row>
@@ -9782,6 +11524,14 @@
 확률과 통계: 조회수·구독자 지표를 분석해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>미디어학과: 미디어 환경과 콘텐츠 기획을 배워 구독자가 좋아할 영상을 구상해요.
+영상학과: 촬영과 편집 기술을 배워 영상을 직접 만들고 올릴 수 있어요.
+신문방송학과: 취재·구성과 말하기 전달력을 배워 정보를 쉽고 정확하게 전할 수 있어요.
+문화콘텐츠학과: 문화 트렌드와 콘텐츠 기획을 배워 나만의 채널 주제를 정할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -9821,6 +11571,13 @@
 확률과 통계: 음원 차트와 판매 자료를 분석해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>실용음악과: 작곡·편곡과 녹음 과정을 배워 음반 제작 흐름을 잘 이해할 수 있어요.
+문화콘텐츠학과: 엔터테인먼트 산업과 콘텐츠 기획을 배워 음반 콘셉트를 정할 수 있어요.
+경영학과: 마케팅·유통·예산 관리를 배워 음반 홍보와 판매 전략을 세울 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -9856,6 +11613,12 @@
 대수: 음의 주파수가 지수적으로 변해서 → 지수·로그 함수를 배워요.
 영어 I: 장비와 프로그램이 영어로 되어 있어서 → 기초 영어 독해 능력을 키워요.
 문학: 가사의 메시지를 다듬어야 해서 → 시적 표현과 정서를 배워요.</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>실용음악과: 작곡·편곡과 녹음·믹싱 실습을 배워 곡 작업 전체를 이끌 수 있어요.
+작곡과: 화성학과 작곡 이론을 깊이 배워 탄탄한 곡을 만드는 바탕이 돼요.</t>
         </is>
       </c>
     </row>
@@ -9896,6 +11659,13 @@
 확률과 통계: 치료 효과를 기록·평가해야 해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>음악치료학과: 음악을 활용한 치료 이론과 임상 실습을 직접 배우는 학과예요.
+음악교육과: 악기 연주와 음악 지도법을 배워 치료 활동에서 음악을 잘 활용해요.
+심리학과: 마음의 원리와 상담 이론을 배워 내담자의 정서를 이해하고 도울 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -9933,6 +11703,13 @@
 화법과 언어: 고객에게 디자인을 제안해야 해서 → 설득력 있는 말하기를 배워요.</t>
         </is>
       </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>실내디자인학과: 실내 공간 설계와 재료·가구·조명 계획을 직접 배우는 학과예요.
+건축학과: 건축 구조와 공간 설계, 도면 그리기를 배워 실내 설계에 활용해요.
+디자인과: 색채와 조형 감각을 배워 공간 분위기를 아름답게 꾸밀 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -9970,6 +11747,13 @@
 영어 I: 해외 클라이언트와 작업할 수 있어서 → 기초 영어 독해와 표현을 익혀요.</t>
         </is>
       </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>회화과: 드로잉과 다양한 그림 재료를 깊이 익혀 개성 있는 그림을 그릴 수 있어요.
+디자인과: 시각 디자인과 디지털 그림 도구를 배워 목적에 맞는 그림을 만들어요.
+만화애니메이션학과: 캐릭터 그리기와 이야기 표현을 배워 책·게임 그림에 바로 쓸 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -10007,6 +11791,12 @@
 영어Ⅱ: 해외 디자인 센터와 협업이 많아서 → 다양한 영어 표현을 익혀요.</t>
         </is>
       </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>디자인과: 제품 디자인과 3D 모델링을 배워 자동차 겉모양과 실내를 설계해요.
+자동차공학과: 자동차 구조와 성능을 배워 멋있고 실제로 만들 수 있는 디자인을 해요.</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -10044,6 +11834,13 @@
 확률과 통계: 판매 자료로 인기 상품을 분석해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>디자인과: 제품·패션 디자인을 배워 가방·신발 등 잡화의 모양을 구상할 수 있어요.
+공예과(조형학과): 가죽·금속·섬유 등 재료를 다루는 법을 배워 잡화를 직접 만들 수 있어요.
+의류학과: 패션 유행과 소재를 배워 옷과 어울리는 잡화를 기획할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -10081,6 +11878,11 @@
 독서와 작문: 작가 노트와 전시 소개를 써야 해서 → 생각을 글로 정리하는 법을 배워요.</t>
         </is>
       </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>조소과: 돌·나무·금속 등으로 입체 작품을 만드는 조각 기법을 전공으로 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -10118,6 +11920,13 @@
 문학: 장면의 분위기를 빛으로 표현해서 → 작품의 정서와 분위기 해석을 배워요.</t>
         </is>
       </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>무대미술학과: 무대 조명과 공연 미술을 배워 장면에 맞는 빛을 설계할 수 있어요.
+연극영화학과: 공연 제작 과정과 연출을 배워 작품 분위기에 맞는 조명을 구상해요.
+디자인과: 색채와 공간 감각을 배워 전시·건축 공간의 빛을 아름답게 연출해요.</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -10155,6 +11964,12 @@
 영어 I: 해외 보석 시장 정보를 참고해서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>공예과(조형학과): 금속 공예와 보석 세팅을 배워 장신구를 직접 디자인하고 만들어요.
+디자인과: 제품 디자인과 3D 모델링을 배워 장신구 디자인을 구체화할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -10192,6 +12007,13 @@
 영어 I: 촬영 장비 매뉴얼이 영어라서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>연극영화학과: 촬영·조명과 연출을 배우고 영화 제작 실습으로 현장 경험을 쌓아요.
+영상학과: 카메라 촬영과 영상 기술을 배워 장면을 원하는 대로 찍을 수 있어요.
+사진학과: 빛과 구도, 카메라 원리를 깊이 배워 화면 구성 감각을 길러요.</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -10229,6 +12051,13 @@
 화법과 언어: 색채 기획을 고객에게 설명해서 → 설득력 있는 말하기를 배워요.</t>
         </is>
       </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>디자인과: 색채 이론과 배색 기법을 배워 제품·공간에 어울리는 색을 제안해요.
+의류학과: 패션 색채와 유행을 배워 옷에 어울리는 색을 기획하는 데 활용해요.
+회화과: 물감으로 색을 섞고 표현하며 색을 보는 섬세한 감각을 길러요.</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -10266,6 +12095,14 @@
 영어 I: 해외 섬유 박람회 정보를 읽어서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>디자인과: 무늬와 색을 구성하는 디자인 감각을 배워 섬유 디자인에 활용해요.
+섬유공학과: 섬유 소재의 성질과 가공 기술을 배워 쓰임에 맞는 원단을 개발해요.
+의류학과: 옷감과 패션 소재를 배워 옷에 어울리는 원단을 디자인할 수 있어요.
+공예과(조형학과): 염색·직조 등 섬유 공예를 직접 배워 원단 무늬와 질감을 만들 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -10303,6 +12140,12 @@
 화법과 언어: 컬렉션 콘셉트를 발표해야 해서 → 설득력 있는 말하기를 배워요.</t>
         </is>
       </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>의류학과: 의상 디자인·패턴·봉제와 패션 마케팅을 배워 옷을 상품으로 만들어요.
+디자인과: 색채와 시각 디자인 감각을 배워 개성 있는 옷을 구상하는 데 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -10337,6 +12180,11 @@
 미술과 매체: 디자인 의도를 이해해야 해서 → 조형 요소와 시각 표현을 배워요.
 대수: 치수를 비율대로 늘리고 줄여서 → 수와 식, 수열의 계산을 배워요.
 미적분 I: 몸의 곡선에 맞는 패턴을 그려서 → 곡선과 함수의 성질을 배워요.</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>의류학과: 인체 치수 측정과 패턴 제작·봉제를 배워 옷의 본을 직접 그릴 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -10377,6 +12225,11 @@
 영어 I: 해외 선수와 대회에서 소통해서 → 기초 영어 의사소통을 익혀요.</t>
         </is>
       </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>e스포츠학과: 게임 전략 분석과 e스포츠 훈련·산업을 배워 선수 활동에 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -10415,6 +12268,13 @@
 스포츠 생활2: 직접 시범을 보일 체력이 필요해서 → 다양한 운동과 체력 관리를 익혀요.</t>
         </is>
       </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>체육학과: 인체 움직임과 운동 지도법을 배워 수강생을 안전하게 가르칠 수 있어요.
+스포츠과학과: 근육·자세와 운동 원리를 과학적으로 배워 바른 동작을 지도할 수 있어요.
+무용학과: 유연성과 몸의 균형, 호흡을 훈련해 정확한 동작 시범에 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -10452,6 +12312,13 @@
 영어 I: 한복을 해외에 알릴 기회가 많아서 → 기초 영어 표현을 익혀요.</t>
         </is>
       </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>의류학과: 옷감·패턴·봉제를 배워 한복을 직접 디자인하고 지을 수 있어요.
+디자인과: 색채와 디자인 감각을 배워 전통에 새 감각을 더한 한복을 구상해요.
+공예과(조형학과): 자수·염색 등 전통 공예를 배워 한복에 아름다운 장식을 더할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -10487,6 +12354,12 @@
 세계사: 미술사의 흐름을 이해해야 해서 → 시대별 세계의 역사와 문화를 배워요.
 문학: 그림에 담을 주제와 감정을 고민해서 → 문학 속 주제와 상징 해석을 배워요.
 독서와 작문: 작가 노트와 전시 서문을 써야 해서 → 생각을 글로 정리하는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>회화과: 다양한 회화 기법과 재료를 전공 실기로 익혀 자신만의 작품을 만들어요.
+미술교육과: 미술 실기와 미술사·이론을 함께 배워 작품 활동의 폭을 넓힐 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -10527,6 +12400,13 @@
 영어 I: 외국 귀빈을 경호하기도 해서 → 기초 영어 의사소통을 익혀요.</t>
         </is>
       </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>경호학과: 무도 실기와 경호 이론·실무를 직접 배워 경호 업무에 바로 쓸 수 있어요.
+체육학과: 체력과 운동 능력을 길러 위험 상황에 빠르게 대응하는 데 도움이 돼요.
+경찰행정학과: 법과 치안, 범죄 예방을 배워 안전 활동의 기준을 이해할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -10564,6 +12444,12 @@
 독서와 작문: 상담 내용과 안내문을 글로 써서 → 정확하고 간결한 글쓰기를 배워요.</t>
         </is>
       </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>경영학과: 고객 서비스와 마케팅을 배워 고객의 요구를 잘 파악할 수 있어요.
+심리학과: 사람의 마음과 의사소통을 배워 고객의 불만을 공감하며 해결할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -10601,6 +12487,11 @@
 영어 I: 해외 트렌드와 제품 정보를 찾아서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>뷰티디자인학과: 네일 관리와 아트 기법, 위생 관리를 배워 네일미용사 자격 준비에 도움돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -10638,6 +12529,11 @@
 영어 I: 해외 화장품 성분·트렌드를 읽어서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>뷰티디자인학과: 메이크업 기법과 색채, 피부 이해를 배워 목적에 맞는 화장을 할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -10674,6 +12570,13 @@
 영어 I: 원두 산지 정보와 대회 자료가 영어라서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>외식조리학과: 음료 제조와 식음료 서비스를 배워 커피를 맛있게 만드는 데 도움이 돼요.
+식품영양학과: 식품의 성분과 맛의 원리를 배워 원두와 음료의 특성을 이해할 수 있어요.
+외식경영학과: 카페 운영과 서비스 경영을 배워 매장을 꾸리는 능력을 길러요.</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -10708,6 +12611,13 @@
 직무 의사소통: 보호자를 교육·상담해야 해서 → 업무 상황의 설명·상담 화법을 배워요.
 화법과 언어: 보호자에게 교정법을 설명해야 해서 → 알기 쉽게 설명하는 말하기를 배워요.
 영어 I: 해외 동물행동학 자료를 참고해서 → 기초 영어 독해 능력을 키워요.</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>반려동물학과: 반려동물 행동학과 훈련법을 직접 배워 문제 행동 교정에 바로 써요.
+동물자원학과: 동물의 생리와 사육·관리를 배워 동물의 습성을 깊이 이해할 수 있어요.
+동물보건학과: 동물 건강과 간호를 배워 건강 문제로 생긴 행동도 살필 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -10745,6 +12655,14 @@
 사회와 문화: 유행과 소비자 반응을 읽어야 해서 → 대중문화와 사회 변화를 배워요.
 독서와 작문: 콘텐츠 기획안과 대본을 써서 → 구성력 있는 글쓰기를 배워요.
 확률과 통계: 조회수와 소비자 반응을 분석해서 → 자료 정리와 통계 해석을 배워요.</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>뷰티디자인학과: 메이크업과 피부 관리를 배워 정확한 뷰티 정보를 전할 수 있어요.
+미디어학과: 영상 제작과 콘텐츠 기획을 배워 뷰티 영상과 SNS 콘텐츠를 만들어요.
+화장품과학과: 화장품 성분과 효능을 배워 제품을 믿을 수 있게 소개할 수 있어요.
+광고홍보학과: 마케팅과 홍보 전략을 배워 뷰티 콘텐츠를 널리 알리는 데 활용해요.</t>
         </is>
       </c>
     </row>
@@ -10785,6 +12703,11 @@
 스포츠 생활1: 긴 항해를 견딜 체력이 필요해서 → 기초 체력 관리를 익혀요.</t>
         </is>
       </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>항해학과: 항해술·선박 운용과 승선 실습을 배워 해기사(항해사) 면허를 준비해요.</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -10820,6 +12743,13 @@
 실생활 영어 회화: 외국 손님과 와인 용어를 접해서 → 생활 속 영어 회화를 연습해요.
 화법과 언어: 와인의 맛과 향을 말로 표현해서 → 풍부한 언어 표현을 배워요.
 영어Ⅱ: 와인 산지·라벨 정보가 외국어라서 → 다양한 영어 글 독해를 익혀요.</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>외식조리학과: 식음료와 음식 궁합을 배워 요리에 어울리는 와인을 추천할 수 있어요.
+호텔경영학과: 호텔 식음료 서비스와 레스토랑 운영을 배워 와인 서비스에 활용해요.
+식품영양학과: 식품의 성분과 맛의 원리를 배워 와인의 맛과 향을 깊이 이해해요.</t>
         </is>
       </c>
     </row>
@@ -10861,6 +12791,13 @@
 확률과 통계: 여행 수요를 분석해 상품을 짜서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>관광경영학과: 여행업과 관광 상품 개발을 배워 여행상품 기획에 바로 쓸 수 있어요.
+경영학과: 마케팅과 판매 전략을 배워 여행상품을 잘 알리고 팔 수 있어요.
+지리학과: 세계 각 지역의 자연과 문화를 배워 매력 있는 여행지를 고를 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -10899,6 +12836,13 @@
 스포츠 생활1: 오래 서서 이동하며 일해서 → 기초 체력 관리를 익혀요.</t>
         </is>
       </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>철도경영학과: 철도 운영과 서비스 경영을 배워 열차 안 승객 응대와 운영을 이해해요.
+관광경영학과: 고객 서비스와 관광 산업을 배워 승객을 친절하게 안내할 수 있어요.
+항공서비스학과: 승무원 서비스 예절과 안전 교육을 배워 열차 승무 업무에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -10936,6 +12880,14 @@
 화법과 언어: 직원과 손님을 모두 상대해서 → 상황에 맞는 말하기를 배워요.</t>
         </is>
       </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>외식경영학과: 외식 마케팅·메뉴 개발과 매장 운영을 배워 식당 경영에 바로 써요.
+호텔경영학과: 식음료 서비스와 고객 관리를 배워 매장 서비스 품질을 높일 수 있어요.
+외식조리학과: 조리와 위생을 배워 주방을 이해하고 메뉴와 위생을 관리할 수 있어요.
+경영학과: 인사·회계·마케팅을 배워 직원과 매출을 체계적으로 관리할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -10971,6 +12923,12 @@
 매체 의사소통: 방송·SNS로 요리를 알리므로 → 매체 특성과 콘텐츠 표현을 배워요.
 독서와 작문: 레시피와 요리책을 써야 해서 → 정확하고 읽기 쉬운 글쓰기를 배워요.
 영어 I: 세계 요리 자료를 찾아봐서 → 기초 영어 독해 능력을 키워요.</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>조리과학과: 조리 원리와 실습을 배워 새로운 요리법을 개발하는 바탕을 다져요.
+식품영양학과: 영양과 식품의 성질을 배워 건강하고 맛있는 요리를 연구할 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -11011,6 +12969,12 @@
 확률과 통계: 기상 확률로 운항 여부를 판단해서 → 확률과 자료 해석을 배워요.</t>
         </is>
       </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>항공운항학과: 항공기 운항과 항공 기상을 배워 비행 계획을 세우는 데 바로 써요.
+항공교통물류학과: 항공 교통과 공항 운영을 배워 안전하고 효율적인 운항을 도울 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -11048,6 +13012,13 @@
 독서와 작문: 견적서와 진행 계획서를 써서 → 정확한 실용 글쓰기를 배워요.</t>
         </is>
       </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>관광경영학과: 행사 기획과 서비스 경영을 배워 결혼식을 기획하고 진행할 수 있어요.
+호텔경영학과: 연회와 행사 운영, 고객 서비스를 배워 결혼식 진행에 바로 활용해요.
+경영학과: 마케팅과 예산 관리를 배워 고객 상담과 웨딩 사업 운영에 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -11085,6 +13056,13 @@
 영어 I: 해외 레시피와 제과 용어를 읽어서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>제과제빵학과: 빵·과자 만들기 실습과 이론을 배워 제과·제빵기능사 준비에 도움이 돼요.
+조리과학과: 조리 원리와 위생을 배워 맛있고 안전한 제품을 만들 수 있어요.
+식품영양학과: 재료의 성분과 영양을 배워 건강한 새 제품을 개발하는 데 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -11122,6 +13100,13 @@
 스포츠 생활1: 뜨거운 주방에서 오래 서서 일해서 → 기초 체력 관리를 익혀요.</t>
         </is>
       </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>조리과학과: 조리 원리와 실습을 배워 조리기능사 준비와 주방 일에 바로 써요.
+외식조리학과: 다양한 요리 실습과 메뉴·주방 관리를 배워 셰프의 기본기를 다져요.
+식품영양학과: 영양과 식품 위생을 배워 건강하고 안전한 음식을 만들 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -11157,6 +13142,13 @@
 운동과 건강: 오랜 시간 집중력과 체력이 필요해서 → 체력과 건강 관리 방법을 배워요.
 미적분 I: 열차의 가속·제동 거리를 판단해서 → 미분으로 속도 변화를 배워요.
 화법과 언어: 관제실과 정확히 교신해야 해서 → 정확하게 말하고 듣는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>철도운전시스템학과: 철도 차량 운전과 신호 체계를 배워 철도차량 운전면허 준비에 바로 써요.
+기계공학과: 엔진과 기계 구조를 배워 기관차의 작동 원리를 이해할 수 있어요.
+전기공학과: 전기와 전동기 원리를 배워 전기 기관차·전동차를 이해하는 데 도움돼요.</t>
         </is>
       </c>
     </row>
@@ -11197,6 +13189,13 @@
 화법과 언어: 고객과 매너 있게 대화해야 해서 → 품위 있는 말하기를 배워요.</t>
         </is>
       </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>카지노경영학과: 카지노 게임 진행과 딜링 실습을 배워 딜러 업무에 바로 쓸 수 있어요.
+관광경영학과: 관광 산업과 고객 서비스를 배워 외국인 손님을 잘 응대할 수 있어요.
+호텔경영학과: 호텔·리조트 서비스를 배워 카지노가 있는 시설의 손님 응대에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -11235,6 +13234,13 @@
 화법과 언어: 승객을 친절하게 안내해야 해서 → 상황에 맞는 말하기를 배워요.</t>
         </is>
       </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>관광경영학과: 관광 산업과 여가 서비스를 배워 승객의 여행을 즐겁게 도울 수 있어요.
+호텔경영학과: 객실·식음료 서비스를 배워 배 위의 숙박과 식사 서비스에 활용해요.
+항공서비스학과: 승무원 서비스와 안전 교육을 배워 승객 안전을 살피는 데 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -11272,6 +13278,13 @@
 영어 I: 해외 푸드 트렌드를 참고해서 → 기초 영어 독해 능력을 키워요.</t>
         </is>
       </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>외식조리학과: 요리 실습과 메뉴 구성을 배워 음식을 맛있게 만들고 담을 수 있어요.
+식품영양학과: 식재료의 특성을 배워 음식이 가장 맛있어 보이는 상태를 연출해요.
+디자인과: 색채와 구도 감각을 배워 사진·영상 속 음식을 아름답게 꾸밀 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -11309,6 +13322,12 @@
 화법과 언어: 고객의 사연을 듣고 꽃을 제안해서 → 경청하고 제안하는 말하기를 배워요.</t>
         </is>
       </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>원예학과: 꽃과 식물의 특성, 재배·관리법을 배워 싱싱한 꽃 장식을 만들 수 있어요.
+디자인과: 색채와 공간 구성을 배워 꽃다발과 행사 장식을 아름답게 디자인해요.</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -11344,6 +13363,12 @@
 직무 의사소통: 고객과 상담하며 관리해서 → 업무 상황의 상담 화법을 배워요.
 화법과 언어: 고객 피부 상태를 상담해야 해서 → 친절하고 정확한 말하기를 배워요.
 영어 I: 화장품 성분 표기를 읽어야 해서 → 기초 영어 독해 능력을 키워요.</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>뷰티디자인학과: 피부 관리와 마사지 기법을 배워 미용사(피부) 자격 준비에 도움이 돼요.
+화장품과학과: 피부 구조와 화장품 성분을 배워 피부에 맞는 제품을 고를 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -11385,6 +13410,13 @@
 영어Ⅱ: 국제선 기내 안내가 영어라서 → 다양한 영어 표현을 익혀요.</t>
         </is>
       </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>항공서비스학과: 기내 서비스와 비상 안전 훈련을 배워 승무원 업무에 바로 쓸 수 있어요.
+관광경영학과: 관광 산업과 고객 서비스를 배워 여행객을 친절하게 응대할 수 있어요.
+영어영문학과: 영어 소통 능력을 키워 외국인 승객 안내와 기내 방송에 활용해요.</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -11421,6 +13453,12 @@
 영어Ⅱ: 조종사와 영어로 교신해서 → 다양한 영어 표현과 듣기를 익혀요.
 대수: 항공기 간격과 고도를 계산해서 → 수와 식, 삼각함수를 배워요.
 화법과 언어: 짧고 정확한 지시가 생명이라서 → 정확하게 말하고 듣는 법을 배워요.</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>항공교통물류학과: 항공 교통과 관제 절차를 배워 항공교통관제사 자격 준비에 도움이 돼요.
+항공운항학과: 항공기 운항 원리와 항공 기상을 배워 비행 흐름을 잘 이해할 수 있어요.</t>
         </is>
       </c>
     </row>
@@ -11462,6 +13500,11 @@
 스포츠 생활1: 엄격한 신체검사를 통과해야 해서 → 기초 체력 관리를 익혀요.</t>
         </is>
       </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>항공운항학과: 비행 이론과 비행 훈련으로 조종사 면허를 준비할 수 있는 학과예요.</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -11497,6 +13540,13 @@
 일본어 회화: 일본인 승객도 자주 만나서 → 일본어로 말하고 듣는 연습을 해요.
 화법과 언어: 탑승 수속과 안내를 맡아서 → 친절하고 정확한 말하기를 배워요.
 영어Ⅱ: 외국인 승객 응대가 많아서 → 다양한 영어 표현을 익혀요.</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>항공서비스학과: 항공 서비스와 승객 응대를 배워 탑승 수속과 안내에 바로 쓸 수 있어요.
+관광경영학과: 관광 산업과 고객 서비스를 배워 여행객을 친절하게 도울 수 있어요.
+항공교통물류학과: 공항 운영과 항공 물류를 배워 수하물과 출도착 업무를 이해해요.</t>
         </is>
       </c>
     </row>
@@ -11537,6 +13587,13 @@
 확률과 통계: 사고 위험을 자료로 평가해서 → 확률과 통계 해석을 배워요.</t>
         </is>
       </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>항공운항학과: 항공기 운항과 항공 법규를 배워 운항 안전 점검에 활용할 수 있어요.
+항공우주공학과: 항공기 구조와 설계 원리를 배워 기체의 안전성을 판단할 수 있어요.
+항공정비학과: 항공기 정비와 점검 기술을 배워 정비 상태를 꼼꼼히 감독할 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -11575,6 +13632,14 @@
 확률과 통계: 참가자 설문 결과를 분석해서 → 자료 정리와 통계 해석을 배워요.</t>
         </is>
       </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>관광경영학과: 축제·컨벤션 기획과 운영을 배워 행사 준비부터 진행까지 이끌어요.
+문화콘텐츠학과: 문화 콘텐츠와 공연·전시 기획을 배워 매력 있는 행사를 구상해요.
+광고홍보학과: 홍보와 광고 전략을 배워 행사를 널리 알리고 관객을 모을 수 있어요.
+경영학과: 예산과 조직 관리를 배워 행사 비용과 인력을 체계적으로 운영해요.</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -11610,6 +13675,11 @@
 직무 의사소통: 고객 취향을 듣고 스타일을 제안해서 → 업무 상황의 말하기·듣기를 배워요.
 화법과 언어: 고객이 원하는 스타일을 파악해서 → 경청하고 제안하는 말하기를 배워요.
 영어 I: 해외 헤어 트렌드를 참고해서 → 기초 영어 독해 능력을 키워요.</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>뷰티디자인학과: 커트·염색·펌 실습을 배워 미용사(일반) 자격 준비에 도움이 돼요.</t>
         </is>
       </c>
     </row>
@@ -11648,6 +13718,13 @@
 경제: 객실 가격과 수익을 관리해서 → 시장과 기업 활동의 원리를 배워요.
 화법과 언어: 투숙객을 품위 있게 응대해서 → 상황에 맞는 존중의 말하기를 배워요.
 영어Ⅱ: 외국인 투숙객과 소통이 많아서 → 다양한 영어 표현을 익혀요.</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>호텔경영학과: 객실·식음료·연회 운영을 배워 호텔 업무에 바로 쓸 수 있어요.
+관광경영학과: 관광 산업과 고객 서비스를 배워 손님을 친절하게 맞이할 수 있어요.
+영어영문학과: 영어 소통 능력을 키워 외국인 손님 응대에 바로 활용할 수 있어요.</t>
         </is>
       </c>
     </row>
